--- a/Roster_Builder/output/Final_Roster.xlsx
+++ b/Roster_Builder/output/Final_Roster.xlsx
@@ -2306,15 +2306,15 @@
       <c r="O9" s="33" t="n"/>
       <c r="P9" s="33" t="n"/>
       <c r="Q9" s="34" t="n"/>
-      <c r="R9" s="45" t="n"/>
+      <c r="R9" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="S9" s="33" t="n"/>
       <c r="T9" s="33" t="n"/>
       <c r="U9" s="34" t="n"/>
-      <c r="V9" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="V9" s="45" t="n"/>
       <c r="W9" s="33" t="n"/>
       <c r="X9" s="33" t="n"/>
       <c r="Y9" s="34" t="n"/>
@@ -2413,15 +2413,15 @@
       <c r="K10" s="39" t="n"/>
       <c r="L10" s="39" t="n"/>
       <c r="M10" s="40" t="n"/>
-      <c r="N10" s="45" t="n"/>
+      <c r="N10" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="O10" s="33" t="n"/>
       <c r="P10" s="33" t="n"/>
       <c r="Q10" s="34" t="n"/>
-      <c r="R10" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="R10" s="45" t="n"/>
       <c r="S10" s="33" t="n"/>
       <c r="T10" s="33" t="n"/>
       <c r="U10" s="34" t="n"/>
@@ -2554,7 +2554,11 @@
         </is>
       </c>
       <c r="AC11" s="34" t="n"/>
-      <c r="AD11" s="35" t="n"/>
+      <c r="AD11" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AE11" s="33" t="n"/>
       <c r="AF11" s="33" t="n"/>
       <c r="AG11" s="34" t="n"/>
@@ -2809,11 +2813,7 @@
       <c r="AM13" s="33" t="n"/>
       <c r="AN13" s="33" t="n"/>
       <c r="AO13" s="34" t="n"/>
-      <c r="AP13" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AP13" s="45" t="n"/>
       <c r="AQ13" s="33" t="n"/>
       <c r="AR13" s="33" t="n"/>
       <c r="AS13" s="34" t="n"/>
@@ -2932,11 +2932,7 @@
         </is>
       </c>
       <c r="AK14" s="34" t="n"/>
-      <c r="AL14" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AL14" s="45" t="n"/>
       <c r="AM14" s="33" t="n"/>
       <c r="AN14" s="33" t="n"/>
       <c r="AO14" s="34" t="n"/>
@@ -3039,7 +3035,11 @@
       <c r="W15" s="33" t="n"/>
       <c r="X15" s="33" t="n"/>
       <c r="Y15" s="34" t="n"/>
-      <c r="Z15" s="45" t="n"/>
+      <c r="Z15" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AA15" s="33" t="n"/>
       <c r="AB15" s="33" t="n"/>
       <c r="AC15" s="34" t="n"/>
@@ -3194,11 +3194,7 @@
       <c r="BC16" s="33" t="n"/>
       <c r="BD16" s="33" t="n"/>
       <c r="BE16" s="34" t="n"/>
-      <c r="BF16" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BF16" s="35" t="n"/>
       <c r="BG16" s="33" t="n"/>
       <c r="BH16" s="33" t="n"/>
       <c r="BI16" s="34" t="n"/>
@@ -3638,15 +3634,15 @@
       <c r="AU20" s="39" t="n"/>
       <c r="AV20" s="39" t="n"/>
       <c r="AW20" s="40" t="n"/>
-      <c r="AX20" s="45" t="n"/>
+      <c r="AX20" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AY20" s="33" t="n"/>
       <c r="AZ20" s="33" t="n"/>
       <c r="BA20" s="34" t="n"/>
-      <c r="BB20" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BB20" s="45" t="n"/>
       <c r="BC20" s="33" t="n"/>
       <c r="BD20" s="33" t="n"/>
       <c r="BE20" s="34" t="n"/>
@@ -3781,7 +3777,11 @@
       <c r="BS21" s="33" t="n"/>
       <c r="BT21" s="33" t="n"/>
       <c r="BU21" s="34" t="n"/>
-      <c r="BV21" s="45" t="n"/>
+      <c r="BV21" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BW21" s="33" t="n"/>
       <c r="BX21" s="33" t="n"/>
       <c r="BY21" s="34" t="n"/>
@@ -3892,7 +3892,11 @@
         </is>
       </c>
       <c r="BQ22" s="34" t="n"/>
-      <c r="BR22" s="45" t="n"/>
+      <c r="BR22" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BS22" s="33" t="n"/>
       <c r="BT22" s="33" t="n"/>
       <c r="BU22" s="34" t="n"/>
@@ -4755,11 +4759,7 @@
       <c r="G32" s="81" t="n"/>
       <c r="H32" s="33" t="n"/>
       <c r="I32" s="34" t="n"/>
-      <c r="J32" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="J32" s="82" t="n"/>
       <c r="K32" s="33" t="n"/>
       <c r="L32" s="33" t="n"/>
       <c r="M32" s="34" t="n"/>
@@ -5001,11 +5001,7 @@
       <c r="K34" s="39" t="n"/>
       <c r="L34" s="39" t="n"/>
       <c r="M34" s="40" t="n"/>
-      <c r="N34" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="N34" s="82" t="n"/>
       <c r="O34" s="33" t="n"/>
       <c r="P34" s="33" t="n"/>
       <c r="Q34" s="34" t="n"/>
@@ -5013,7 +5009,11 @@
       <c r="S34" s="33" t="n"/>
       <c r="T34" s="33" t="n"/>
       <c r="U34" s="34" t="n"/>
-      <c r="V34" s="82" t="n"/>
+      <c r="V34" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="W34" s="33" t="n"/>
       <c r="X34" s="33" t="n"/>
       <c r="Y34" s="34" t="n"/>
@@ -5259,7 +5259,11 @@
       <c r="AI36" s="33" t="n"/>
       <c r="AJ36" s="33" t="n"/>
       <c r="AK36" s="34" t="n"/>
-      <c r="AL36" s="88" t="n"/>
+      <c r="AL36" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AM36" s="33" t="n"/>
       <c r="AN36" s="33" t="n"/>
       <c r="AO36" s="34" t="n"/>
@@ -5854,15 +5858,15 @@
       <c r="BK41" s="33" t="n"/>
       <c r="BL41" s="33" t="n"/>
       <c r="BM41" s="34" t="n"/>
-      <c r="BN41" s="88" t="n"/>
+      <c r="BN41" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BO41" s="33" t="n"/>
       <c r="BP41" s="33" t="n"/>
       <c r="BQ41" s="34" t="n"/>
-      <c r="BR41" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BR41" s="88" t="n"/>
       <c r="BS41" s="33" t="n"/>
       <c r="BT41" s="33" t="n"/>
       <c r="BU41" s="34" t="n"/>
@@ -6060,15 +6064,15 @@
       <c r="AU43" s="39" t="n"/>
       <c r="AV43" s="39" t="n"/>
       <c r="AW43" s="40" t="n"/>
-      <c r="AX43" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AX43" s="88" t="n"/>
       <c r="AY43" s="33" t="n"/>
       <c r="AZ43" s="33" t="n"/>
       <c r="BA43" s="34" t="n"/>
-      <c r="BB43" s="88" t="n"/>
+      <c r="BB43" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BC43" s="33" t="n"/>
       <c r="BD43" s="33" t="n"/>
       <c r="BE43" s="34" t="n"/>
@@ -6298,15 +6302,15 @@
       <c r="BG45" s="33" t="n"/>
       <c r="BH45" s="33" t="n"/>
       <c r="BI45" s="34" t="n"/>
-      <c r="BJ45" s="82" t="n"/>
+      <c r="BJ45" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BK45" s="33" t="n"/>
       <c r="BL45" s="33" t="n"/>
       <c r="BM45" s="34" t="n"/>
-      <c r="BN45" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BN45" s="82" t="n"/>
       <c r="BO45" s="33" t="n"/>
       <c r="BP45" s="33" t="n"/>
       <c r="BQ45" s="34" t="n"/>
@@ -7074,7 +7078,11 @@
       <c r="G54" s="93" t="n"/>
       <c r="H54" s="33" t="n"/>
       <c r="I54" s="34" t="n"/>
-      <c r="J54" s="94" t="n"/>
+      <c r="J54" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="K54" s="33" t="n"/>
       <c r="L54" s="33" t="n"/>
       <c r="M54" s="34" t="n"/>
@@ -7098,11 +7106,7 @@
         </is>
       </c>
       <c r="Y54" s="34" t="n"/>
-      <c r="Z54" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="Z54" s="94" t="n"/>
       <c r="AA54" s="33" t="n"/>
       <c r="AB54" s="33" t="n"/>
       <c r="AC54" s="34" t="n"/>
@@ -7340,11 +7344,7 @@
         </is>
       </c>
       <c r="AC56" s="34" t="n"/>
-      <c r="AD56" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AD56" s="94" t="n"/>
       <c r="AE56" s="33" t="n"/>
       <c r="AF56" s="33" t="n"/>
       <c r="AG56" s="34" t="n"/>
@@ -7463,7 +7463,11 @@
       <c r="AM57" s="33" t="n"/>
       <c r="AN57" s="33" t="n"/>
       <c r="AO57" s="34" t="n"/>
-      <c r="AP57" s="94" t="n"/>
+      <c r="AP57" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AQ57" s="33" t="n"/>
       <c r="AR57" s="33" t="n"/>
       <c r="AS57" s="34" t="n"/>
@@ -7491,11 +7495,7 @@
       <c r="BG57" s="33" t="n"/>
       <c r="BH57" s="33" t="n"/>
       <c r="BI57" s="34" t="n"/>
-      <c r="BJ57" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BJ57" s="94" t="n"/>
       <c r="BK57" s="33" t="n"/>
       <c r="BL57" s="33" t="n"/>
       <c r="BM57" s="34" t="n"/>
@@ -7713,7 +7713,11 @@
       <c r="BC59" s="33" t="n"/>
       <c r="BD59" s="33" t="n"/>
       <c r="BE59" s="34" t="n"/>
-      <c r="BF59" s="94" t="n"/>
+      <c r="BF59" s="49" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BG59" s="33" t="n"/>
       <c r="BH59" s="33" t="n"/>
       <c r="BI59" s="34" t="n"/>
@@ -7737,11 +7741,7 @@
       <c r="BS59" s="33" t="n"/>
       <c r="BT59" s="33" t="n"/>
       <c r="BU59" s="34" t="n"/>
-      <c r="BV59" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BV59" s="94" t="n"/>
       <c r="BW59" s="33" t="n"/>
       <c r="BX59" s="33" t="n"/>
       <c r="BY59" s="34" t="n"/>

--- a/Roster_Builder/output/Final_Roster.xlsx
+++ b/Roster_Builder/output/Final_Roster.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,14 +39,21 @@
       <sz val="7"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <color rgb="00FFFFFF"/>
       <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,11 +66,10 @@
       <sz val="14"/>
     </font>
     <font>
-      <b val="1"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +105,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C00101"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0060497A"/>
       </patternFill>
     </fill>
@@ -109,7 +120,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00101"/>
+        <fgColor rgb="00A895BE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006BE181"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFF2F"/>
       </patternFill>
     </fill>
     <fill>
@@ -704,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -758,33 +779,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -795,42 +822,48 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -846,16 +879,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -870,49 +903,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2068,94 +2101,102 @@
       <c r="G7" s="32" t="n"/>
       <c r="H7" s="33" t="n"/>
       <c r="I7" s="34" t="n"/>
-      <c r="J7" s="35" t="n"/>
+      <c r="J7" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="K7" s="33" t="n"/>
       <c r="L7" s="33" t="n"/>
       <c r="M7" s="34" t="n"/>
-      <c r="N7" s="35" t="n"/>
+      <c r="N7" s="36" t="n"/>
       <c r="O7" s="33" t="n"/>
       <c r="P7" s="33" t="n"/>
       <c r="Q7" s="34" t="n"/>
-      <c r="R7" s="35" t="n"/>
+      <c r="R7" s="36" t="n"/>
       <c r="S7" s="33" t="n"/>
       <c r="T7" s="33" t="n"/>
       <c r="U7" s="34" t="n"/>
-      <c r="V7" s="36" t="inlineStr">
+      <c r="V7" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="W7" s="33" t="n"/>
-      <c r="X7" s="37" t="inlineStr">
+      <c r="X7" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="Y7" s="34" t="n"/>
-      <c r="Z7" s="35" t="n"/>
+      <c r="Z7" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="AA7" s="33" t="n"/>
       <c r="AB7" s="33" t="n"/>
       <c r="AC7" s="34" t="n"/>
-      <c r="AD7" s="35" t="n"/>
+      <c r="AD7" s="36" t="n"/>
       <c r="AE7" s="33" t="n"/>
       <c r="AF7" s="33" t="n"/>
       <c r="AG7" s="34" t="n"/>
-      <c r="AH7" s="38" t="n"/>
+      <c r="AH7" s="40" t="n"/>
       <c r="AI7" s="33" t="n"/>
-      <c r="AJ7" s="39" t="n"/>
-      <c r="AK7" s="40" t="n"/>
+      <c r="AJ7" s="41" t="n"/>
+      <c r="AK7" s="42" t="n"/>
       <c r="AL7" s="31" t="n"/>
-      <c r="AM7" s="39" t="n"/>
-      <c r="AN7" s="39" t="n"/>
-      <c r="AO7" s="40" t="n"/>
+      <c r="AM7" s="41" t="n"/>
+      <c r="AN7" s="41" t="n"/>
+      <c r="AO7" s="42" t="n"/>
       <c r="AP7" s="31" t="n"/>
-      <c r="AQ7" s="39" t="n"/>
-      <c r="AR7" s="39" t="n"/>
-      <c r="AS7" s="40" t="n"/>
+      <c r="AQ7" s="41" t="n"/>
+      <c r="AR7" s="41" t="n"/>
+      <c r="AS7" s="42" t="n"/>
       <c r="AT7" s="31" t="n"/>
-      <c r="AU7" s="39" t="n"/>
-      <c r="AV7" s="39" t="n"/>
-      <c r="AW7" s="40" t="n"/>
+      <c r="AU7" s="41" t="n"/>
+      <c r="AV7" s="41" t="n"/>
+      <c r="AW7" s="42" t="n"/>
       <c r="AX7" s="31" t="n"/>
-      <c r="AY7" s="39" t="n"/>
-      <c r="AZ7" s="39" t="n"/>
-      <c r="BA7" s="40" t="n"/>
+      <c r="AY7" s="41" t="n"/>
+      <c r="AZ7" s="41" t="n"/>
+      <c r="BA7" s="42" t="n"/>
       <c r="BB7" s="31" t="n"/>
-      <c r="BC7" s="39" t="n"/>
-      <c r="BD7" s="39" t="n"/>
-      <c r="BE7" s="40" t="n"/>
+      <c r="BC7" s="41" t="n"/>
+      <c r="BD7" s="41" t="n"/>
+      <c r="BE7" s="42" t="n"/>
       <c r="BF7" s="31" t="n"/>
-      <c r="BG7" s="39" t="n"/>
-      <c r="BH7" s="39" t="n"/>
-      <c r="BI7" s="40" t="n"/>
-      <c r="BJ7" s="41" t="inlineStr">
+      <c r="BG7" s="41" t="n"/>
+      <c r="BH7" s="41" t="n"/>
+      <c r="BI7" s="42" t="n"/>
+      <c r="BJ7" s="43" t="inlineStr">
         <is>
           <t>VICTORIA</t>
         </is>
       </c>
-      <c r="BK7" s="42" t="n"/>
-      <c r="BL7" s="42" t="n"/>
-      <c r="BM7" s="42" t="n"/>
-      <c r="BN7" s="42" t="n"/>
-      <c r="BO7" s="42" t="n"/>
-      <c r="BP7" s="42" t="n"/>
-      <c r="BQ7" s="42" t="n"/>
-      <c r="BR7" s="42" t="n"/>
-      <c r="BS7" s="42" t="n"/>
-      <c r="BT7" s="42" t="n"/>
-      <c r="BU7" s="42" t="n"/>
-      <c r="BV7" s="42" t="n"/>
-      <c r="BW7" s="42" t="n"/>
-      <c r="BX7" s="42" t="n"/>
-      <c r="BY7" s="42" t="n"/>
-      <c r="BZ7" s="42" t="n"/>
-      <c r="CA7" s="42" t="n"/>
-      <c r="CB7" s="42" t="n"/>
-      <c r="CC7" s="42" t="n"/>
-      <c r="CD7" s="42" t="n"/>
-      <c r="CE7" s="42" t="n"/>
-      <c r="CF7" s="42" t="n"/>
-      <c r="CG7" s="43" t="n"/>
+      <c r="BK7" s="44" t="n"/>
+      <c r="BL7" s="44" t="n"/>
+      <c r="BM7" s="44" t="n"/>
+      <c r="BN7" s="44" t="n"/>
+      <c r="BO7" s="44" t="n"/>
+      <c r="BP7" s="44" t="n"/>
+      <c r="BQ7" s="44" t="n"/>
+      <c r="BR7" s="44" t="n"/>
+      <c r="BS7" s="44" t="n"/>
+      <c r="BT7" s="44" t="n"/>
+      <c r="BU7" s="44" t="n"/>
+      <c r="BV7" s="44" t="n"/>
+      <c r="BW7" s="44" t="n"/>
+      <c r="BX7" s="44" t="n"/>
+      <c r="BY7" s="44" t="n"/>
+      <c r="BZ7" s="44" t="n"/>
+      <c r="CA7" s="44" t="n"/>
+      <c r="CB7" s="44" t="n"/>
+      <c r="CC7" s="44" t="n"/>
+      <c r="CD7" s="44" t="n"/>
+      <c r="CE7" s="44" t="n"/>
+      <c r="CF7" s="44" t="n"/>
+      <c r="CG7" s="45" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
@@ -2184,93 +2225,101 @@
         </is>
       </c>
       <c r="F8" s="31" t="n"/>
-      <c r="G8" s="44" t="n"/>
+      <c r="G8" s="46" t="n"/>
       <c r="H8" s="33" t="n"/>
       <c r="I8" s="34" t="n"/>
-      <c r="J8" s="45" t="n"/>
+      <c r="J8" s="47" t="n"/>
       <c r="K8" s="33" t="n"/>
       <c r="L8" s="33" t="n"/>
       <c r="M8" s="34" t="n"/>
-      <c r="N8" s="45" t="n"/>
+      <c r="N8" s="47" t="n"/>
       <c r="O8" s="33" t="n"/>
       <c r="P8" s="33" t="n"/>
       <c r="Q8" s="34" t="n"/>
-      <c r="R8" s="45" t="n"/>
+      <c r="R8" s="48" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="S8" s="33" t="n"/>
       <c r="T8" s="33" t="n"/>
       <c r="U8" s="34" t="n"/>
-      <c r="V8" s="36" t="inlineStr">
+      <c r="V8" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="W8" s="33" t="n"/>
-      <c r="X8" s="37" t="inlineStr">
+      <c r="X8" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="Y8" s="34" t="n"/>
-      <c r="Z8" s="45" t="n"/>
+      <c r="Z8" s="47" t="n"/>
       <c r="AA8" s="33" t="n"/>
       <c r="AB8" s="33" t="n"/>
       <c r="AC8" s="34" t="n"/>
-      <c r="AD8" s="45" t="n"/>
+      <c r="AD8" s="47" t="n"/>
       <c r="AE8" s="33" t="n"/>
       <c r="AF8" s="33" t="n"/>
       <c r="AG8" s="34" t="n"/>
-      <c r="AH8" s="45" t="n"/>
+      <c r="AH8" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AI8" s="33" t="n"/>
       <c r="AJ8" s="33" t="n"/>
       <c r="AK8" s="34" t="n"/>
       <c r="AL8" s="31" t="n"/>
-      <c r="AM8" s="39" t="n"/>
-      <c r="AN8" s="39" t="n"/>
-      <c r="AO8" s="40" t="n"/>
+      <c r="AM8" s="41" t="n"/>
+      <c r="AN8" s="41" t="n"/>
+      <c r="AO8" s="42" t="n"/>
       <c r="AP8" s="31" t="n"/>
-      <c r="AQ8" s="39" t="n"/>
-      <c r="AR8" s="39" t="n"/>
-      <c r="AS8" s="40" t="n"/>
+      <c r="AQ8" s="41" t="n"/>
+      <c r="AR8" s="41" t="n"/>
+      <c r="AS8" s="42" t="n"/>
       <c r="AT8" s="31" t="n"/>
-      <c r="AU8" s="39" t="n"/>
-      <c r="AV8" s="39" t="n"/>
-      <c r="AW8" s="40" t="n"/>
+      <c r="AU8" s="41" t="n"/>
+      <c r="AV8" s="41" t="n"/>
+      <c r="AW8" s="42" t="n"/>
       <c r="AX8" s="31" t="n"/>
-      <c r="AY8" s="39" t="n"/>
-      <c r="AZ8" s="39" t="n"/>
-      <c r="BA8" s="40" t="n"/>
+      <c r="AY8" s="41" t="n"/>
+      <c r="AZ8" s="41" t="n"/>
+      <c r="BA8" s="42" t="n"/>
       <c r="BB8" s="31" t="n"/>
-      <c r="BC8" s="39" t="n"/>
-      <c r="BD8" s="39" t="n"/>
-      <c r="BE8" s="40" t="n"/>
+      <c r="BC8" s="41" t="n"/>
+      <c r="BD8" s="41" t="n"/>
+      <c r="BE8" s="42" t="n"/>
       <c r="BF8" s="31" t="n"/>
-      <c r="BG8" s="39" t="n"/>
-      <c r="BH8" s="39" t="n"/>
-      <c r="BI8" s="40" t="n"/>
-      <c r="BJ8" s="46" t="n"/>
-      <c r="BK8" s="47" t="n"/>
-      <c r="BL8" s="47" t="n"/>
-      <c r="BM8" s="47" t="n"/>
-      <c r="BN8" s="47" t="n"/>
-      <c r="BO8" s="47" t="n"/>
-      <c r="BP8" s="47" t="n"/>
-      <c r="BQ8" s="47" t="n"/>
-      <c r="BR8" s="47" t="n"/>
-      <c r="BS8" s="47" t="n"/>
-      <c r="BT8" s="47" t="n"/>
-      <c r="BU8" s="47" t="n"/>
-      <c r="BV8" s="47" t="n"/>
-      <c r="BW8" s="47" t="n"/>
-      <c r="BX8" s="47" t="n"/>
-      <c r="BY8" s="47" t="n"/>
-      <c r="BZ8" s="47" t="n"/>
-      <c r="CA8" s="47" t="n"/>
-      <c r="CB8" s="47" t="n"/>
-      <c r="CC8" s="47" t="n"/>
-      <c r="CD8" s="47" t="n"/>
-      <c r="CE8" s="47" t="n"/>
-      <c r="CF8" s="47" t="n"/>
-      <c r="CG8" s="48" t="n"/>
+      <c r="BG8" s="41" t="n"/>
+      <c r="BH8" s="41" t="n"/>
+      <c r="BI8" s="42" t="n"/>
+      <c r="BJ8" s="49" t="n"/>
+      <c r="BK8" s="50" t="n"/>
+      <c r="BL8" s="50" t="n"/>
+      <c r="BM8" s="50" t="n"/>
+      <c r="BN8" s="50" t="n"/>
+      <c r="BO8" s="50" t="n"/>
+      <c r="BP8" s="50" t="n"/>
+      <c r="BQ8" s="50" t="n"/>
+      <c r="BR8" s="50" t="n"/>
+      <c r="BS8" s="50" t="n"/>
+      <c r="BT8" s="50" t="n"/>
+      <c r="BU8" s="50" t="n"/>
+      <c r="BV8" s="50" t="n"/>
+      <c r="BW8" s="50" t="n"/>
+      <c r="BX8" s="50" t="n"/>
+      <c r="BY8" s="50" t="n"/>
+      <c r="BZ8" s="50" t="n"/>
+      <c r="CA8" s="50" t="n"/>
+      <c r="CB8" s="50" t="n"/>
+      <c r="CC8" s="50" t="n"/>
+      <c r="CD8" s="50" t="n"/>
+      <c r="CE8" s="50" t="n"/>
+      <c r="CF8" s="50" t="n"/>
+      <c r="CG8" s="51" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="29" t="inlineStr">
@@ -2295,89 +2344,97 @@
       </c>
       <c r="E9" s="30" t="inlineStr"/>
       <c r="F9" s="31" t="n"/>
-      <c r="G9" s="39" t="n"/>
-      <c r="H9" s="39" t="n"/>
-      <c r="I9" s="40" t="n"/>
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="41" t="n"/>
+      <c r="I9" s="42" t="n"/>
       <c r="J9" s="31" t="n"/>
-      <c r="K9" s="39" t="n"/>
-      <c r="L9" s="39" t="n"/>
-      <c r="M9" s="40" t="n"/>
-      <c r="N9" s="45" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="41" t="n"/>
+      <c r="M9" s="42" t="n"/>
+      <c r="N9" s="52" t="n"/>
       <c r="O9" s="33" t="n"/>
-      <c r="P9" s="33" t="n"/>
+      <c r="P9" s="53" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="Q9" s="34" t="n"/>
-      <c r="R9" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="R9" s="47" t="n"/>
       <c r="S9" s="33" t="n"/>
       <c r="T9" s="33" t="n"/>
       <c r="U9" s="34" t="n"/>
-      <c r="V9" s="45" t="n"/>
+      <c r="V9" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="W9" s="33" t="n"/>
       <c r="X9" s="33" t="n"/>
       <c r="Y9" s="34" t="n"/>
-      <c r="Z9" s="45" t="n"/>
+      <c r="Z9" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AA9" s="33" t="n"/>
       <c r="AB9" s="33" t="n"/>
       <c r="AC9" s="34" t="n"/>
       <c r="AD9" s="31" t="n"/>
-      <c r="AE9" s="39" t="n"/>
-      <c r="AF9" s="39" t="n"/>
-      <c r="AG9" s="40" t="n"/>
+      <c r="AE9" s="41" t="n"/>
+      <c r="AF9" s="41" t="n"/>
+      <c r="AG9" s="42" t="n"/>
       <c r="AH9" s="31" t="n"/>
-      <c r="AI9" s="39" t="n"/>
-      <c r="AJ9" s="39" t="n"/>
-      <c r="AK9" s="40" t="n"/>
+      <c r="AI9" s="41" t="n"/>
+      <c r="AJ9" s="41" t="n"/>
+      <c r="AK9" s="42" t="n"/>
       <c r="AL9" s="31" t="n"/>
-      <c r="AM9" s="39" t="n"/>
-      <c r="AN9" s="39" t="n"/>
-      <c r="AO9" s="40" t="n"/>
+      <c r="AM9" s="41" t="n"/>
+      <c r="AN9" s="41" t="n"/>
+      <c r="AO9" s="42" t="n"/>
       <c r="AP9" s="31" t="n"/>
-      <c r="AQ9" s="39" t="n"/>
-      <c r="AR9" s="39" t="n"/>
-      <c r="AS9" s="40" t="n"/>
+      <c r="AQ9" s="41" t="n"/>
+      <c r="AR9" s="41" t="n"/>
+      <c r="AS9" s="42" t="n"/>
       <c r="AT9" s="31" t="n"/>
-      <c r="AU9" s="39" t="n"/>
-      <c r="AV9" s="39" t="n"/>
-      <c r="AW9" s="40" t="n"/>
+      <c r="AU9" s="41" t="n"/>
+      <c r="AV9" s="41" t="n"/>
+      <c r="AW9" s="42" t="n"/>
       <c r="AX9" s="31" t="n"/>
-      <c r="AY9" s="39" t="n"/>
-      <c r="AZ9" s="39" t="n"/>
-      <c r="BA9" s="40" t="n"/>
+      <c r="AY9" s="41" t="n"/>
+      <c r="AZ9" s="41" t="n"/>
+      <c r="BA9" s="42" t="n"/>
       <c r="BB9" s="31" t="n"/>
-      <c r="BC9" s="39" t="n"/>
-      <c r="BD9" s="39" t="n"/>
-      <c r="BE9" s="40" t="n"/>
+      <c r="BC9" s="41" t="n"/>
+      <c r="BD9" s="41" t="n"/>
+      <c r="BE9" s="42" t="n"/>
       <c r="BF9" s="31" t="n"/>
-      <c r="BG9" s="39" t="n"/>
-      <c r="BH9" s="39" t="n"/>
-      <c r="BI9" s="40" t="n"/>
+      <c r="BG9" s="41" t="n"/>
+      <c r="BH9" s="41" t="n"/>
+      <c r="BI9" s="42" t="n"/>
       <c r="BJ9" s="31" t="n"/>
-      <c r="BK9" s="39" t="n"/>
-      <c r="BL9" s="39" t="n"/>
-      <c r="BM9" s="40" t="n"/>
+      <c r="BK9" s="41" t="n"/>
+      <c r="BL9" s="41" t="n"/>
+      <c r="BM9" s="42" t="n"/>
       <c r="BN9" s="31" t="n"/>
-      <c r="BO9" s="39" t="n"/>
-      <c r="BP9" s="39" t="n"/>
-      <c r="BQ9" s="40" t="n"/>
+      <c r="BO9" s="41" t="n"/>
+      <c r="BP9" s="41" t="n"/>
+      <c r="BQ9" s="42" t="n"/>
       <c r="BR9" s="31" t="n"/>
-      <c r="BS9" s="39" t="n"/>
-      <c r="BT9" s="39" t="n"/>
-      <c r="BU9" s="40" t="n"/>
+      <c r="BS9" s="41" t="n"/>
+      <c r="BT9" s="41" t="n"/>
+      <c r="BU9" s="42" t="n"/>
       <c r="BV9" s="31" t="n"/>
-      <c r="BW9" s="39" t="n"/>
-      <c r="BX9" s="39" t="n"/>
-      <c r="BY9" s="40" t="n"/>
+      <c r="BW9" s="41" t="n"/>
+      <c r="BX9" s="41" t="n"/>
+      <c r="BY9" s="42" t="n"/>
       <c r="BZ9" s="31" t="n"/>
-      <c r="CA9" s="39" t="n"/>
-      <c r="CB9" s="39" t="n"/>
-      <c r="CC9" s="40" t="n"/>
+      <c r="CA9" s="41" t="n"/>
+      <c r="CB9" s="41" t="n"/>
+      <c r="CC9" s="42" t="n"/>
       <c r="CD9" s="31" t="n"/>
-      <c r="CE9" s="39" t="n"/>
-      <c r="CF9" s="39" t="n"/>
-      <c r="CG9" s="50" t="n"/>
+      <c r="CE9" s="41" t="n"/>
+      <c r="CF9" s="41" t="n"/>
+      <c r="CG9" s="54" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="29" t="inlineStr">
@@ -2406,98 +2463,106 @@
         </is>
       </c>
       <c r="F10" s="31" t="n"/>
-      <c r="G10" s="39" t="n"/>
-      <c r="H10" s="39" t="n"/>
-      <c r="I10" s="40" t="n"/>
+      <c r="G10" s="41" t="n"/>
+      <c r="H10" s="41" t="n"/>
+      <c r="I10" s="42" t="n"/>
       <c r="J10" s="31" t="n"/>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="39" t="n"/>
-      <c r="M10" s="40" t="n"/>
-      <c r="N10" s="49" t="inlineStr">
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="41" t="n"/>
+      <c r="M10" s="42" t="n"/>
+      <c r="N10" s="52" t="n"/>
+      <c r="O10" s="33" t="n"/>
+      <c r="P10" s="53" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q10" s="34" t="n"/>
+      <c r="R10" s="35" t="inlineStr">
         <is>
           <t>Security Check</t>
         </is>
       </c>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="33" t="n"/>
-      <c r="Q10" s="34" t="n"/>
-      <c r="R10" s="45" t="n"/>
       <c r="S10" s="33" t="n"/>
       <c r="T10" s="33" t="n"/>
       <c r="U10" s="34" t="n"/>
-      <c r="V10" s="45" t="n"/>
+      <c r="V10" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="W10" s="33" t="n"/>
       <c r="X10" s="33" t="n"/>
       <c r="Y10" s="34" t="n"/>
-      <c r="Z10" s="45" t="n"/>
+      <c r="Z10" s="47" t="n"/>
       <c r="AA10" s="33" t="n"/>
       <c r="AB10" s="33" t="n"/>
       <c r="AC10" s="34" t="n"/>
       <c r="AD10" s="31" t="n"/>
-      <c r="AE10" s="39" t="n"/>
-      <c r="AF10" s="39" t="n"/>
-      <c r="AG10" s="40" t="n"/>
+      <c r="AE10" s="41" t="n"/>
+      <c r="AF10" s="41" t="n"/>
+      <c r="AG10" s="42" t="n"/>
       <c r="AH10" s="31" t="n"/>
-      <c r="AI10" s="39" t="n"/>
-      <c r="AJ10" s="39" t="n"/>
-      <c r="AK10" s="40" t="n"/>
+      <c r="AI10" s="41" t="n"/>
+      <c r="AJ10" s="41" t="n"/>
+      <c r="AK10" s="42" t="n"/>
       <c r="AL10" s="31" t="n"/>
-      <c r="AM10" s="39" t="n"/>
-      <c r="AN10" s="39" t="n"/>
-      <c r="AO10" s="40" t="n"/>
+      <c r="AM10" s="41" t="n"/>
+      <c r="AN10" s="41" t="n"/>
+      <c r="AO10" s="42" t="n"/>
       <c r="AP10" s="31" t="n"/>
-      <c r="AQ10" s="39" t="n"/>
-      <c r="AR10" s="39" t="n"/>
-      <c r="AS10" s="40" t="n"/>
+      <c r="AQ10" s="41" t="n"/>
+      <c r="AR10" s="41" t="n"/>
+      <c r="AS10" s="42" t="n"/>
       <c r="AT10" s="31" t="n"/>
-      <c r="AU10" s="39" t="n"/>
-      <c r="AV10" s="39" t="n"/>
-      <c r="AW10" s="40" t="n"/>
+      <c r="AU10" s="41" t="n"/>
+      <c r="AV10" s="41" t="n"/>
+      <c r="AW10" s="42" t="n"/>
       <c r="AX10" s="31" t="n"/>
-      <c r="AY10" s="39" t="n"/>
-      <c r="AZ10" s="39" t="n"/>
-      <c r="BA10" s="40" t="n"/>
+      <c r="AY10" s="41" t="n"/>
+      <c r="AZ10" s="41" t="n"/>
+      <c r="BA10" s="42" t="n"/>
       <c r="BB10" s="31" t="n"/>
-      <c r="BC10" s="39" t="n"/>
-      <c r="BD10" s="39" t="n"/>
-      <c r="BE10" s="40" t="n"/>
+      <c r="BC10" s="41" t="n"/>
+      <c r="BD10" s="41" t="n"/>
+      <c r="BE10" s="42" t="n"/>
       <c r="BF10" s="31" t="n"/>
-      <c r="BG10" s="39" t="n"/>
-      <c r="BH10" s="39" t="n"/>
-      <c r="BI10" s="40" t="n"/>
+      <c r="BG10" s="41" t="n"/>
+      <c r="BH10" s="41" t="n"/>
+      <c r="BI10" s="42" t="n"/>
       <c r="BJ10" s="31" t="n"/>
-      <c r="BK10" s="39" t="n"/>
-      <c r="BL10" s="39" t="n"/>
-      <c r="BM10" s="40" t="n"/>
+      <c r="BK10" s="41" t="n"/>
+      <c r="BL10" s="41" t="n"/>
+      <c r="BM10" s="42" t="n"/>
       <c r="BN10" s="31" t="n"/>
-      <c r="BO10" s="39" t="n"/>
-      <c r="BP10" s="39" t="n"/>
-      <c r="BQ10" s="40" t="n"/>
+      <c r="BO10" s="41" t="n"/>
+      <c r="BP10" s="41" t="n"/>
+      <c r="BQ10" s="42" t="n"/>
       <c r="BR10" s="31" t="n"/>
-      <c r="BS10" s="39" t="n"/>
-      <c r="BT10" s="39" t="n"/>
-      <c r="BU10" s="40" t="n"/>
-      <c r="BV10" s="51" t="inlineStr">
+      <c r="BS10" s="41" t="n"/>
+      <c r="BT10" s="41" t="n"/>
+      <c r="BU10" s="42" t="n"/>
+      <c r="BV10" s="56" t="inlineStr">
         <is>
           <t>TOP OF ESC
 4–6</t>
         </is>
       </c>
-      <c r="BW10" s="52" t="n"/>
-      <c r="BX10" s="52" t="n"/>
-      <c r="BY10" s="53" t="n"/>
-      <c r="BZ10" s="51" t="inlineStr">
+      <c r="BW10" s="57" t="n"/>
+      <c r="BX10" s="57" t="n"/>
+      <c r="BY10" s="58" t="n"/>
+      <c r="BZ10" s="56" t="inlineStr">
         <is>
           <t>AREA AT THE TOP OF ESC
 6</t>
         </is>
       </c>
-      <c r="CA10" s="52" t="n"/>
-      <c r="CB10" s="52" t="n"/>
-      <c r="CC10" s="52" t="n"/>
-      <c r="CD10" s="52" t="n"/>
-      <c r="CE10" s="52" t="n"/>
-      <c r="CF10" s="52" t="n"/>
+      <c r="CA10" s="57" t="n"/>
+      <c r="CB10" s="57" t="n"/>
+      <c r="CC10" s="57" t="n"/>
+      <c r="CD10" s="57" t="n"/>
+      <c r="CE10" s="57" t="n"/>
+      <c r="CF10" s="57" t="n"/>
       <c r="CG10" s="28" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2523,38 +2588,38 @@
       </c>
       <c r="E11" s="30" t="inlineStr"/>
       <c r="F11" s="31" t="n"/>
-      <c r="G11" s="39" t="n"/>
-      <c r="H11" s="39" t="n"/>
-      <c r="I11" s="40" t="n"/>
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="41" t="n"/>
+      <c r="I11" s="42" t="n"/>
       <c r="J11" s="31" t="n"/>
-      <c r="K11" s="39" t="n"/>
-      <c r="L11" s="39" t="n"/>
-      <c r="M11" s="40" t="n"/>
-      <c r="N11" s="35" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="41" t="n"/>
+      <c r="M11" s="42" t="n"/>
+      <c r="N11" s="36" t="n"/>
       <c r="O11" s="33" t="n"/>
       <c r="P11" s="33" t="n"/>
       <c r="Q11" s="34" t="n"/>
-      <c r="R11" s="35" t="n"/>
+      <c r="R11" s="36" t="n"/>
       <c r="S11" s="33" t="n"/>
       <c r="T11" s="33" t="n"/>
       <c r="U11" s="34" t="n"/>
-      <c r="V11" s="35" t="n"/>
+      <c r="V11" s="36" t="n"/>
       <c r="W11" s="33" t="n"/>
       <c r="X11" s="33" t="n"/>
       <c r="Y11" s="34" t="n"/>
-      <c r="Z11" s="36" t="inlineStr">
+      <c r="Z11" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AA11" s="33" t="n"/>
-      <c r="AB11" s="37" t="inlineStr">
+      <c r="AB11" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AC11" s="34" t="n"/>
-      <c r="AD11" s="49" t="inlineStr">
+      <c r="AD11" s="35" t="inlineStr">
         <is>
           <t>Security Check</t>
         </is>
@@ -2562,66 +2627,66 @@
       <c r="AE11" s="33" t="n"/>
       <c r="AF11" s="33" t="n"/>
       <c r="AG11" s="34" t="n"/>
-      <c r="AH11" s="35" t="n"/>
+      <c r="AH11" s="36" t="n"/>
       <c r="AI11" s="33" t="n"/>
       <c r="AJ11" s="33" t="n"/>
       <c r="AK11" s="34" t="n"/>
-      <c r="AL11" s="35" t="n"/>
+      <c r="AL11" s="36" t="n"/>
       <c r="AM11" s="33" t="n"/>
       <c r="AN11" s="33" t="n"/>
       <c r="AO11" s="34" t="n"/>
-      <c r="AP11" s="38" t="n"/>
+      <c r="AP11" s="40" t="n"/>
       <c r="AQ11" s="33" t="n"/>
-      <c r="AR11" s="39" t="n"/>
-      <c r="AS11" s="40" t="n"/>
+      <c r="AR11" s="41" t="n"/>
+      <c r="AS11" s="42" t="n"/>
       <c r="AT11" s="31" t="n"/>
-      <c r="AU11" s="39" t="n"/>
-      <c r="AV11" s="39" t="n"/>
-      <c r="AW11" s="40" t="n"/>
+      <c r="AU11" s="41" t="n"/>
+      <c r="AV11" s="41" t="n"/>
+      <c r="AW11" s="42" t="n"/>
       <c r="AX11" s="31" t="n"/>
-      <c r="AY11" s="39" t="n"/>
-      <c r="AZ11" s="39" t="n"/>
-      <c r="BA11" s="40" t="n"/>
+      <c r="AY11" s="41" t="n"/>
+      <c r="AZ11" s="41" t="n"/>
+      <c r="BA11" s="42" t="n"/>
       <c r="BB11" s="31" t="n"/>
-      <c r="BC11" s="39" t="n"/>
-      <c r="BD11" s="39" t="n"/>
-      <c r="BE11" s="40" t="n"/>
+      <c r="BC11" s="41" t="n"/>
+      <c r="BD11" s="41" t="n"/>
+      <c r="BE11" s="42" t="n"/>
       <c r="BF11" s="31" t="n"/>
-      <c r="BG11" s="39" t="n"/>
-      <c r="BH11" s="39" t="n"/>
-      <c r="BI11" s="40" t="n"/>
+      <c r="BG11" s="41" t="n"/>
+      <c r="BH11" s="41" t="n"/>
+      <c r="BI11" s="42" t="n"/>
       <c r="BJ11" s="31" t="n"/>
-      <c r="BK11" s="39" t="n"/>
-      <c r="BL11" s="39" t="n"/>
-      <c r="BM11" s="40" t="n"/>
+      <c r="BK11" s="41" t="n"/>
+      <c r="BL11" s="41" t="n"/>
+      <c r="BM11" s="42" t="n"/>
       <c r="BN11" s="31" t="n"/>
-      <c r="BO11" s="39" t="n"/>
-      <c r="BP11" s="39" t="n"/>
-      <c r="BQ11" s="40" t="n"/>
+      <c r="BO11" s="41" t="n"/>
+      <c r="BP11" s="41" t="n"/>
+      <c r="BQ11" s="42" t="n"/>
       <c r="BR11" s="31" t="n"/>
-      <c r="BS11" s="39" t="n"/>
-      <c r="BT11" s="39" t="n"/>
-      <c r="BU11" s="40" t="n"/>
-      <c r="BV11" s="54" t="inlineStr">
+      <c r="BS11" s="41" t="n"/>
+      <c r="BT11" s="41" t="n"/>
+      <c r="BU11" s="42" t="n"/>
+      <c r="BV11" s="59" t="inlineStr">
         <is>
           <t>VIP/MIP</t>
         </is>
       </c>
-      <c r="BW11" s="52" t="n"/>
-      <c r="BX11" s="52" t="n"/>
-      <c r="BY11" s="53" t="n"/>
-      <c r="BZ11" s="54" t="inlineStr">
+      <c r="BW11" s="57" t="n"/>
+      <c r="BX11" s="57" t="n"/>
+      <c r="BY11" s="58" t="n"/>
+      <c r="BZ11" s="59" t="inlineStr">
         <is>
           <t>PERSON ALLOCATED TO ASSIST
 WITH VIP/MIPs</t>
         </is>
       </c>
-      <c r="CA11" s="52" t="n"/>
-      <c r="CB11" s="52" t="n"/>
-      <c r="CC11" s="52" t="n"/>
-      <c r="CD11" s="52" t="n"/>
-      <c r="CE11" s="52" t="n"/>
-      <c r="CF11" s="52" t="n"/>
+      <c r="CA11" s="57" t="n"/>
+      <c r="CB11" s="57" t="n"/>
+      <c r="CC11" s="57" t="n"/>
+      <c r="CD11" s="57" t="n"/>
+      <c r="CE11" s="57" t="n"/>
+      <c r="CF11" s="57" t="n"/>
       <c r="CG11" s="28" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2647,100 +2712,108 @@
       </c>
       <c r="E12" s="30" t="inlineStr"/>
       <c r="F12" s="31" t="n"/>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="n"/>
-      <c r="I12" s="40" t="n"/>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="42" t="n"/>
       <c r="J12" s="31" t="n"/>
-      <c r="K12" s="39" t="n"/>
-      <c r="L12" s="39" t="n"/>
-      <c r="M12" s="40" t="n"/>
-      <c r="N12" s="45" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="41" t="n"/>
+      <c r="M12" s="42" t="n"/>
+      <c r="N12" s="47" t="n"/>
       <c r="O12" s="33" t="n"/>
       <c r="P12" s="33" t="n"/>
       <c r="Q12" s="34" t="n"/>
-      <c r="R12" s="45" t="n"/>
+      <c r="R12" s="47" t="n"/>
       <c r="S12" s="33" t="n"/>
       <c r="T12" s="33" t="n"/>
       <c r="U12" s="34" t="n"/>
-      <c r="V12" s="45" t="n"/>
+      <c r="V12" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="W12" s="33" t="n"/>
       <c r="X12" s="33" t="n"/>
       <c r="Y12" s="34" t="n"/>
-      <c r="Z12" s="36" t="inlineStr">
+      <c r="Z12" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AA12" s="33" t="n"/>
-      <c r="AB12" s="37" t="inlineStr">
+      <c r="AB12" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AC12" s="34" t="n"/>
-      <c r="AD12" s="45" t="n"/>
+      <c r="AD12" s="47" t="n"/>
       <c r="AE12" s="33" t="n"/>
       <c r="AF12" s="33" t="n"/>
       <c r="AG12" s="34" t="n"/>
-      <c r="AH12" s="45" t="n"/>
+      <c r="AH12" s="47" t="n"/>
       <c r="AI12" s="33" t="n"/>
       <c r="AJ12" s="33" t="n"/>
       <c r="AK12" s="34" t="n"/>
-      <c r="AL12" s="45" t="n"/>
+      <c r="AL12" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="AM12" s="33" t="n"/>
       <c r="AN12" s="33" t="n"/>
       <c r="AO12" s="34" t="n"/>
-      <c r="AP12" s="45" t="n"/>
+      <c r="AP12" s="47" t="n"/>
       <c r="AQ12" s="33" t="n"/>
       <c r="AR12" s="33" t="n"/>
       <c r="AS12" s="34" t="n"/>
       <c r="AT12" s="31" t="n"/>
-      <c r="AU12" s="39" t="n"/>
-      <c r="AV12" s="39" t="n"/>
-      <c r="AW12" s="40" t="n"/>
+      <c r="AU12" s="41" t="n"/>
+      <c r="AV12" s="41" t="n"/>
+      <c r="AW12" s="42" t="n"/>
       <c r="AX12" s="31" t="n"/>
-      <c r="AY12" s="39" t="n"/>
-      <c r="AZ12" s="39" t="n"/>
-      <c r="BA12" s="40" t="n"/>
+      <c r="AY12" s="41" t="n"/>
+      <c r="AZ12" s="41" t="n"/>
+      <c r="BA12" s="42" t="n"/>
       <c r="BB12" s="31" t="n"/>
-      <c r="BC12" s="39" t="n"/>
-      <c r="BD12" s="39" t="n"/>
-      <c r="BE12" s="40" t="n"/>
+      <c r="BC12" s="41" t="n"/>
+      <c r="BD12" s="41" t="n"/>
+      <c r="BE12" s="42" t="n"/>
       <c r="BF12" s="31" t="n"/>
-      <c r="BG12" s="39" t="n"/>
-      <c r="BH12" s="39" t="n"/>
-      <c r="BI12" s="40" t="n"/>
+      <c r="BG12" s="41" t="n"/>
+      <c r="BH12" s="41" t="n"/>
+      <c r="BI12" s="42" t="n"/>
       <c r="BJ12" s="31" t="n"/>
-      <c r="BK12" s="39" t="n"/>
-      <c r="BL12" s="39" t="n"/>
-      <c r="BM12" s="40" t="n"/>
+      <c r="BK12" s="41" t="n"/>
+      <c r="BL12" s="41" t="n"/>
+      <c r="BM12" s="42" t="n"/>
       <c r="BN12" s="31" t="n"/>
-      <c r="BO12" s="39" t="n"/>
-      <c r="BP12" s="39" t="n"/>
-      <c r="BQ12" s="40" t="n"/>
+      <c r="BO12" s="41" t="n"/>
+      <c r="BP12" s="41" t="n"/>
+      <c r="BQ12" s="42" t="n"/>
       <c r="BR12" s="31" t="n"/>
-      <c r="BS12" s="39" t="n"/>
-      <c r="BT12" s="39" t="n"/>
-      <c r="BU12" s="40" t="n"/>
-      <c r="BV12" s="55" t="inlineStr">
+      <c r="BS12" s="41" t="n"/>
+      <c r="BT12" s="41" t="n"/>
+      <c r="BU12" s="42" t="n"/>
+      <c r="BV12" s="60" t="inlineStr">
         <is>
           <t>POM SERVICING</t>
         </is>
       </c>
-      <c r="BW12" s="52" t="n"/>
-      <c r="BX12" s="52" t="n"/>
-      <c r="BY12" s="53" t="n"/>
-      <c r="BZ12" s="55" t="inlineStr">
+      <c r="BW12" s="57" t="n"/>
+      <c r="BX12" s="57" t="n"/>
+      <c r="BY12" s="58" t="n"/>
+      <c r="BZ12" s="60" t="inlineStr">
         <is>
           <t>SERVICE ALL POMS</t>
         </is>
       </c>
-      <c r="CA12" s="52" t="n"/>
-      <c r="CB12" s="52" t="n"/>
-      <c r="CC12" s="52" t="n"/>
-      <c r="CD12" s="52" t="n"/>
-      <c r="CE12" s="52" t="n"/>
-      <c r="CF12" s="52" t="n"/>
+      <c r="CA12" s="57" t="n"/>
+      <c r="CB12" s="57" t="n"/>
+      <c r="CC12" s="57" t="n"/>
+      <c r="CD12" s="57" t="n"/>
+      <c r="CE12" s="57" t="n"/>
+      <c r="CF12" s="57" t="n"/>
       <c r="CG12" s="28" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2770,100 +2843,108 @@
         </is>
       </c>
       <c r="F13" s="31" t="n"/>
-      <c r="G13" s="39" t="n"/>
-      <c r="H13" s="39" t="n"/>
-      <c r="I13" s="40" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="41" t="n"/>
+      <c r="I13" s="42" t="n"/>
       <c r="J13" s="31" t="n"/>
-      <c r="K13" s="39" t="n"/>
-      <c r="L13" s="39" t="n"/>
-      <c r="M13" s="40" t="n"/>
-      <c r="N13" s="45" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="41" t="n"/>
+      <c r="M13" s="42" t="n"/>
+      <c r="N13" s="47" t="n"/>
       <c r="O13" s="33" t="n"/>
       <c r="P13" s="33" t="n"/>
       <c r="Q13" s="34" t="n"/>
-      <c r="R13" s="45" t="n"/>
+      <c r="R13" s="47" t="n"/>
       <c r="S13" s="33" t="n"/>
       <c r="T13" s="33" t="n"/>
       <c r="U13" s="34" t="n"/>
-      <c r="V13" s="45" t="n"/>
+      <c r="V13" s="47" t="n"/>
       <c r="W13" s="33" t="n"/>
       <c r="X13" s="33" t="n"/>
       <c r="Y13" s="34" t="n"/>
-      <c r="Z13" s="56" t="inlineStr">
+      <c r="Z13" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AA13" s="33" t="n"/>
-      <c r="AB13" s="57" t="inlineStr">
+      <c r="AB13" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AC13" s="34" t="n"/>
-      <c r="AD13" s="45" t="n"/>
+      <c r="AD13" s="47" t="n"/>
       <c r="AE13" s="33" t="n"/>
       <c r="AF13" s="33" t="n"/>
       <c r="AG13" s="34" t="n"/>
-      <c r="AH13" s="45" t="n"/>
+      <c r="AH13" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="AI13" s="33" t="n"/>
       <c r="AJ13" s="33" t="n"/>
       <c r="AK13" s="34" t="n"/>
-      <c r="AL13" s="45" t="n"/>
+      <c r="AL13" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="AM13" s="33" t="n"/>
       <c r="AN13" s="33" t="n"/>
       <c r="AO13" s="34" t="n"/>
-      <c r="AP13" s="45" t="n"/>
+      <c r="AP13" s="47" t="n"/>
       <c r="AQ13" s="33" t="n"/>
       <c r="AR13" s="33" t="n"/>
       <c r="AS13" s="34" t="n"/>
       <c r="AT13" s="31" t="n"/>
-      <c r="AU13" s="39" t="n"/>
-      <c r="AV13" s="39" t="n"/>
-      <c r="AW13" s="40" t="n"/>
+      <c r="AU13" s="41" t="n"/>
+      <c r="AV13" s="41" t="n"/>
+      <c r="AW13" s="42" t="n"/>
       <c r="AX13" s="31" t="n"/>
-      <c r="AY13" s="39" t="n"/>
-      <c r="AZ13" s="39" t="n"/>
-      <c r="BA13" s="40" t="n"/>
+      <c r="AY13" s="41" t="n"/>
+      <c r="AZ13" s="41" t="n"/>
+      <c r="BA13" s="42" t="n"/>
       <c r="BB13" s="31" t="n"/>
-      <c r="BC13" s="39" t="n"/>
-      <c r="BD13" s="39" t="n"/>
-      <c r="BE13" s="40" t="n"/>
+      <c r="BC13" s="41" t="n"/>
+      <c r="BD13" s="41" t="n"/>
+      <c r="BE13" s="42" t="n"/>
       <c r="BF13" s="31" t="n"/>
-      <c r="BG13" s="39" t="n"/>
-      <c r="BH13" s="39" t="n"/>
-      <c r="BI13" s="40" t="n"/>
+      <c r="BG13" s="41" t="n"/>
+      <c r="BH13" s="41" t="n"/>
+      <c r="BI13" s="42" t="n"/>
       <c r="BJ13" s="31" t="n"/>
-      <c r="BK13" s="39" t="n"/>
-      <c r="BL13" s="39" t="n"/>
-      <c r="BM13" s="40" t="n"/>
+      <c r="BK13" s="41" t="n"/>
+      <c r="BL13" s="41" t="n"/>
+      <c r="BM13" s="42" t="n"/>
       <c r="BN13" s="31" t="n"/>
-      <c r="BO13" s="39" t="n"/>
-      <c r="BP13" s="39" t="n"/>
-      <c r="BQ13" s="40" t="n"/>
+      <c r="BO13" s="41" t="n"/>
+      <c r="BP13" s="41" t="n"/>
+      <c r="BQ13" s="42" t="n"/>
       <c r="BR13" s="31" t="n"/>
-      <c r="BS13" s="39" t="n"/>
-      <c r="BT13" s="39" t="n"/>
-      <c r="BU13" s="40" t="n"/>
-      <c r="BV13" s="58" t="inlineStr">
-        <is>
-          <t>PLATFORM?</t>
-        </is>
-      </c>
-      <c r="BW13" s="52" t="n"/>
-      <c r="BX13" s="52" t="n"/>
-      <c r="BY13" s="53" t="n"/>
-      <c r="BZ13" s="58" t="inlineStr">
+      <c r="BS13" s="41" t="n"/>
+      <c r="BT13" s="41" t="n"/>
+      <c r="BU13" s="42" t="n"/>
+      <c r="BV13" s="63" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="BW13" s="57" t="n"/>
+      <c r="BX13" s="57" t="n"/>
+      <c r="BY13" s="58" t="n"/>
+      <c r="BZ13" s="63" t="inlineStr">
         <is>
           <t>PLATFORM SATS</t>
         </is>
       </c>
-      <c r="CA13" s="52" t="n"/>
-      <c r="CB13" s="52" t="n"/>
-      <c r="CC13" s="52" t="n"/>
-      <c r="CD13" s="52" t="n"/>
-      <c r="CE13" s="52" t="n"/>
-      <c r="CF13" s="52" t="n"/>
+      <c r="CA13" s="57" t="n"/>
+      <c r="CB13" s="57" t="n"/>
+      <c r="CC13" s="57" t="n"/>
+      <c r="CD13" s="57" t="n"/>
+      <c r="CE13" s="57" t="n"/>
+      <c r="CF13" s="57" t="n"/>
       <c r="CG13" s="28" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2893,100 +2974,108 @@
         </is>
       </c>
       <c r="F14" s="31" t="n"/>
-      <c r="G14" s="39" t="n"/>
-      <c r="H14" s="39" t="n"/>
-      <c r="I14" s="40" t="n"/>
+      <c r="G14" s="41" t="n"/>
+      <c r="H14" s="41" t="n"/>
+      <c r="I14" s="42" t="n"/>
       <c r="J14" s="31" t="n"/>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
-      <c r="M14" s="40" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="41" t="n"/>
+      <c r="M14" s="42" t="n"/>
       <c r="N14" s="31" t="n"/>
-      <c r="O14" s="39" t="n"/>
-      <c r="P14" s="39" t="n"/>
-      <c r="Q14" s="40" t="n"/>
+      <c r="O14" s="41" t="n"/>
+      <c r="P14" s="41" t="n"/>
+      <c r="Q14" s="42" t="n"/>
       <c r="R14" s="31" t="n"/>
-      <c r="S14" s="39" t="n"/>
-      <c r="T14" s="39" t="n"/>
-      <c r="U14" s="40" t="n"/>
-      <c r="V14" s="45" t="n"/>
+      <c r="S14" s="41" t="n"/>
+      <c r="T14" s="41" t="n"/>
+      <c r="U14" s="42" t="n"/>
+      <c r="V14" s="47" t="n"/>
       <c r="W14" s="33" t="n"/>
       <c r="X14" s="33" t="n"/>
       <c r="Y14" s="34" t="n"/>
-      <c r="Z14" s="45" t="n"/>
+      <c r="Z14" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="AA14" s="33" t="n"/>
       <c r="AB14" s="33" t="n"/>
       <c r="AC14" s="34" t="n"/>
-      <c r="AD14" s="45" t="n"/>
+      <c r="AD14" s="47" t="n"/>
       <c r="AE14" s="33" t="n"/>
       <c r="AF14" s="33" t="n"/>
       <c r="AG14" s="34" t="n"/>
-      <c r="AH14" s="36" t="inlineStr">
+      <c r="AH14" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AI14" s="33" t="n"/>
-      <c r="AJ14" s="37" t="inlineStr">
+      <c r="AJ14" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AK14" s="34" t="n"/>
-      <c r="AL14" s="45" t="n"/>
+      <c r="AL14" s="47" t="n"/>
       <c r="AM14" s="33" t="n"/>
       <c r="AN14" s="33" t="n"/>
       <c r="AO14" s="34" t="n"/>
-      <c r="AP14" s="45" t="n"/>
+      <c r="AP14" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="AQ14" s="33" t="n"/>
       <c r="AR14" s="33" t="n"/>
       <c r="AS14" s="34" t="n"/>
-      <c r="AT14" s="45" t="n"/>
+      <c r="AT14" s="47" t="n"/>
       <c r="AU14" s="33" t="n"/>
       <c r="AV14" s="33" t="n"/>
       <c r="AW14" s="34" t="n"/>
-      <c r="AX14" s="45" t="n"/>
+      <c r="AX14" s="47" t="n"/>
       <c r="AY14" s="33" t="n"/>
       <c r="AZ14" s="33" t="n"/>
       <c r="BA14" s="34" t="n"/>
       <c r="BB14" s="31" t="n"/>
-      <c r="BC14" s="39" t="n"/>
-      <c r="BD14" s="39" t="n"/>
-      <c r="BE14" s="40" t="n"/>
+      <c r="BC14" s="41" t="n"/>
+      <c r="BD14" s="41" t="n"/>
+      <c r="BE14" s="42" t="n"/>
       <c r="BF14" s="31" t="n"/>
-      <c r="BG14" s="39" t="n"/>
-      <c r="BH14" s="39" t="n"/>
-      <c r="BI14" s="40" t="n"/>
+      <c r="BG14" s="41" t="n"/>
+      <c r="BH14" s="41" t="n"/>
+      <c r="BI14" s="42" t="n"/>
       <c r="BJ14" s="31" t="n"/>
-      <c r="BK14" s="39" t="n"/>
-      <c r="BL14" s="39" t="n"/>
-      <c r="BM14" s="40" t="n"/>
+      <c r="BK14" s="41" t="n"/>
+      <c r="BL14" s="41" t="n"/>
+      <c r="BM14" s="42" t="n"/>
       <c r="BN14" s="31" t="n"/>
-      <c r="BO14" s="39" t="n"/>
-      <c r="BP14" s="39" t="n"/>
-      <c r="BQ14" s="40" t="n"/>
+      <c r="BO14" s="41" t="n"/>
+      <c r="BP14" s="41" t="n"/>
+      <c r="BQ14" s="42" t="n"/>
       <c r="BR14" s="31" t="n"/>
-      <c r="BS14" s="39" t="n"/>
-      <c r="BT14" s="39" t="n"/>
-      <c r="BU14" s="40" t="n"/>
-      <c r="BV14" s="59" t="inlineStr">
+      <c r="BS14" s="41" t="n"/>
+      <c r="BT14" s="41" t="n"/>
+      <c r="BU14" s="42" t="n"/>
+      <c r="BV14" s="64" t="inlineStr">
         <is>
           <t>PTI</t>
         </is>
       </c>
-      <c r="BW14" s="52" t="n"/>
-      <c r="BX14" s="52" t="n"/>
-      <c r="BY14" s="53" t="n"/>
-      <c r="BZ14" s="59" t="inlineStr">
+      <c r="BW14" s="57" t="n"/>
+      <c r="BX14" s="57" t="n"/>
+      <c r="BY14" s="58" t="n"/>
+      <c r="BZ14" s="64" t="inlineStr">
         <is>
           <t>PTI DUTY</t>
         </is>
       </c>
-      <c r="CA14" s="52" t="n"/>
-      <c r="CB14" s="52" t="n"/>
-      <c r="CC14" s="52" t="n"/>
-      <c r="CD14" s="52" t="n"/>
-      <c r="CE14" s="52" t="n"/>
-      <c r="CF14" s="52" t="n"/>
+      <c r="CA14" s="57" t="n"/>
+      <c r="CB14" s="57" t="n"/>
+      <c r="CC14" s="57" t="n"/>
+      <c r="CD14" s="57" t="n"/>
+      <c r="CE14" s="57" t="n"/>
+      <c r="CF14" s="57" t="n"/>
       <c r="CG14" s="28" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3016,97 +3105,101 @@
         </is>
       </c>
       <c r="F15" s="31" t="n"/>
-      <c r="G15" s="39" t="n"/>
-      <c r="H15" s="39" t="n"/>
-      <c r="I15" s="40" t="n"/>
+      <c r="G15" s="41" t="n"/>
+      <c r="H15" s="41" t="n"/>
+      <c r="I15" s="42" t="n"/>
       <c r="J15" s="31" t="n"/>
-      <c r="K15" s="39" t="n"/>
-      <c r="L15" s="39" t="n"/>
-      <c r="M15" s="40" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="41" t="n"/>
+      <c r="M15" s="42" t="n"/>
       <c r="N15" s="31" t="n"/>
-      <c r="O15" s="39" t="n"/>
-      <c r="P15" s="39" t="n"/>
-      <c r="Q15" s="40" t="n"/>
+      <c r="O15" s="41" t="n"/>
+      <c r="P15" s="41" t="n"/>
+      <c r="Q15" s="42" t="n"/>
       <c r="R15" s="31" t="n"/>
-      <c r="S15" s="39" t="n"/>
-      <c r="T15" s="39" t="n"/>
-      <c r="U15" s="40" t="n"/>
-      <c r="V15" s="45" t="n"/>
+      <c r="S15" s="41" t="n"/>
+      <c r="T15" s="41" t="n"/>
+      <c r="U15" s="42" t="n"/>
+      <c r="V15" s="47" t="n"/>
       <c r="W15" s="33" t="n"/>
       <c r="X15" s="33" t="n"/>
       <c r="Y15" s="34" t="n"/>
-      <c r="Z15" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="Z15" s="47" t="n"/>
       <c r="AA15" s="33" t="n"/>
       <c r="AB15" s="33" t="n"/>
       <c r="AC15" s="34" t="n"/>
-      <c r="AD15" s="45" t="n"/>
+      <c r="AD15" s="47" t="n"/>
       <c r="AE15" s="33" t="n"/>
       <c r="AF15" s="33" t="n"/>
       <c r="AG15" s="34" t="n"/>
-      <c r="AH15" s="56" t="inlineStr">
+      <c r="AH15" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AI15" s="33" t="n"/>
-      <c r="AJ15" s="57" t="inlineStr">
+      <c r="AJ15" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AK15" s="34" t="n"/>
-      <c r="AL15" s="45" t="n"/>
+      <c r="AL15" s="47" t="n"/>
       <c r="AM15" s="33" t="n"/>
       <c r="AN15" s="33" t="n"/>
       <c r="AO15" s="34" t="n"/>
-      <c r="AP15" s="45" t="n"/>
+      <c r="AP15" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AQ15" s="33" t="n"/>
       <c r="AR15" s="33" t="n"/>
       <c r="AS15" s="34" t="n"/>
-      <c r="AT15" s="45" t="n"/>
+      <c r="AT15" s="47" t="n"/>
       <c r="AU15" s="33" t="n"/>
       <c r="AV15" s="33" t="n"/>
       <c r="AW15" s="34" t="n"/>
-      <c r="AX15" s="45" t="n"/>
+      <c r="AX15" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="AY15" s="33" t="n"/>
       <c r="AZ15" s="33" t="n"/>
       <c r="BA15" s="34" t="n"/>
       <c r="BB15" s="31" t="n"/>
-      <c r="BC15" s="39" t="n"/>
-      <c r="BD15" s="39" t="n"/>
-      <c r="BE15" s="40" t="n"/>
+      <c r="BC15" s="41" t="n"/>
+      <c r="BD15" s="41" t="n"/>
+      <c r="BE15" s="42" t="n"/>
       <c r="BF15" s="31" t="n"/>
-      <c r="BG15" s="39" t="n"/>
-      <c r="BH15" s="39" t="n"/>
-      <c r="BI15" s="40" t="n"/>
+      <c r="BG15" s="41" t="n"/>
+      <c r="BH15" s="41" t="n"/>
+      <c r="BI15" s="42" t="n"/>
       <c r="BJ15" s="31" t="n"/>
-      <c r="BK15" s="39" t="n"/>
-      <c r="BL15" s="39" t="n"/>
-      <c r="BM15" s="40" t="n"/>
+      <c r="BK15" s="41" t="n"/>
+      <c r="BL15" s="41" t="n"/>
+      <c r="BM15" s="42" t="n"/>
       <c r="BN15" s="31" t="n"/>
-      <c r="BO15" s="39" t="n"/>
-      <c r="BP15" s="39" t="n"/>
-      <c r="BQ15" s="40" t="n"/>
+      <c r="BO15" s="41" t="n"/>
+      <c r="BP15" s="41" t="n"/>
+      <c r="BQ15" s="42" t="n"/>
       <c r="BR15" s="31" t="n"/>
-      <c r="BS15" s="39" t="n"/>
-      <c r="BT15" s="39" t="n"/>
-      <c r="BU15" s="40" t="n"/>
+      <c r="BS15" s="41" t="n"/>
+      <c r="BT15" s="41" t="n"/>
+      <c r="BU15" s="42" t="n"/>
       <c r="BV15" s="31" t="n"/>
-      <c r="BW15" s="39" t="n"/>
-      <c r="BX15" s="39" t="n"/>
-      <c r="BY15" s="40" t="n"/>
+      <c r="BW15" s="41" t="n"/>
+      <c r="BX15" s="41" t="n"/>
+      <c r="BY15" s="42" t="n"/>
       <c r="BZ15" s="31" t="n"/>
-      <c r="CA15" s="39" t="n"/>
-      <c r="CB15" s="39" t="n"/>
-      <c r="CC15" s="40" t="n"/>
+      <c r="CA15" s="41" t="n"/>
+      <c r="CB15" s="41" t="n"/>
+      <c r="CC15" s="42" t="n"/>
       <c r="CD15" s="31" t="n"/>
-      <c r="CE15" s="39" t="n"/>
-      <c r="CF15" s="39" t="n"/>
-      <c r="CG15" s="50" t="n"/>
+      <c r="CE15" s="41" t="n"/>
+      <c r="CF15" s="41" t="n"/>
+      <c r="CG15" s="54" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
@@ -3135,93 +3228,97 @@
         </is>
       </c>
       <c r="F16" s="31" t="n"/>
-      <c r="G16" s="39" t="n"/>
-      <c r="H16" s="39" t="n"/>
-      <c r="I16" s="40" t="n"/>
+      <c r="G16" s="41" t="n"/>
+      <c r="H16" s="41" t="n"/>
+      <c r="I16" s="42" t="n"/>
       <c r="J16" s="31" t="n"/>
-      <c r="K16" s="39" t="n"/>
-      <c r="L16" s="39" t="n"/>
-      <c r="M16" s="40" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="41" t="n"/>
+      <c r="M16" s="42" t="n"/>
       <c r="N16" s="31" t="n"/>
-      <c r="O16" s="39" t="n"/>
-      <c r="P16" s="39" t="n"/>
-      <c r="Q16" s="40" t="n"/>
+      <c r="O16" s="41" t="n"/>
+      <c r="P16" s="41" t="n"/>
+      <c r="Q16" s="42" t="n"/>
       <c r="R16" s="31" t="n"/>
-      <c r="S16" s="39" t="n"/>
-      <c r="T16" s="39" t="n"/>
-      <c r="U16" s="40" t="n"/>
+      <c r="S16" s="41" t="n"/>
+      <c r="T16" s="41" t="n"/>
+      <c r="U16" s="42" t="n"/>
       <c r="V16" s="31" t="n"/>
-      <c r="W16" s="39" t="n"/>
-      <c r="X16" s="39" t="n"/>
-      <c r="Y16" s="40" t="n"/>
+      <c r="W16" s="41" t="n"/>
+      <c r="X16" s="41" t="n"/>
+      <c r="Y16" s="42" t="n"/>
       <c r="Z16" s="31" t="n"/>
-      <c r="AA16" s="39" t="n"/>
-      <c r="AB16" s="39" t="n"/>
-      <c r="AC16" s="40" t="n"/>
+      <c r="AA16" s="41" t="n"/>
+      <c r="AB16" s="41" t="n"/>
+      <c r="AC16" s="42" t="n"/>
       <c r="AD16" s="31" t="n"/>
-      <c r="AE16" s="39" t="n"/>
-      <c r="AF16" s="39" t="n"/>
-      <c r="AG16" s="40" t="n"/>
+      <c r="AE16" s="41" t="n"/>
+      <c r="AF16" s="41" t="n"/>
+      <c r="AG16" s="42" t="n"/>
       <c r="AH16" s="31" t="n"/>
-      <c r="AI16" s="39" t="n"/>
+      <c r="AI16" s="41" t="n"/>
       <c r="AJ16" s="32" t="n"/>
       <c r="AK16" s="34" t="n"/>
-      <c r="AL16" s="56" t="inlineStr">
+      <c r="AL16" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AM16" s="33" t="n"/>
-      <c r="AN16" s="57" t="inlineStr">
+      <c r="AN16" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AO16" s="34" t="n"/>
-      <c r="AP16" s="35" t="n"/>
+      <c r="AP16" s="36" t="n"/>
       <c r="AQ16" s="33" t="n"/>
       <c r="AR16" s="33" t="n"/>
       <c r="AS16" s="34" t="n"/>
-      <c r="AT16" s="35" t="n"/>
+      <c r="AT16" s="36" t="n"/>
       <c r="AU16" s="33" t="n"/>
       <c r="AV16" s="33" t="n"/>
       <c r="AW16" s="34" t="n"/>
-      <c r="AX16" s="35" t="n"/>
+      <c r="AX16" s="36" t="n"/>
       <c r="AY16" s="33" t="n"/>
       <c r="AZ16" s="33" t="n"/>
       <c r="BA16" s="34" t="n"/>
-      <c r="BB16" s="35" t="n"/>
+      <c r="BB16" s="36" t="n"/>
       <c r="BC16" s="33" t="n"/>
       <c r="BD16" s="33" t="n"/>
       <c r="BE16" s="34" t="n"/>
-      <c r="BF16" s="35" t="n"/>
+      <c r="BF16" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="BG16" s="33" t="n"/>
       <c r="BH16" s="33" t="n"/>
       <c r="BI16" s="34" t="n"/>
-      <c r="BJ16" s="35" t="n"/>
+      <c r="BJ16" s="36" t="n"/>
       <c r="BK16" s="33" t="n"/>
       <c r="BL16" s="33" t="n"/>
       <c r="BM16" s="34" t="n"/>
       <c r="BN16" s="31" t="n"/>
-      <c r="BO16" s="39" t="n"/>
-      <c r="BP16" s="39" t="n"/>
-      <c r="BQ16" s="40" t="n"/>
+      <c r="BO16" s="41" t="n"/>
+      <c r="BP16" s="41" t="n"/>
+      <c r="BQ16" s="42" t="n"/>
       <c r="BR16" s="31" t="n"/>
-      <c r="BS16" s="39" t="n"/>
-      <c r="BT16" s="39" t="n"/>
-      <c r="BU16" s="40" t="n"/>
+      <c r="BS16" s="41" t="n"/>
+      <c r="BT16" s="41" t="n"/>
+      <c r="BU16" s="42" t="n"/>
       <c r="BV16" s="31" t="n"/>
-      <c r="BW16" s="39" t="n"/>
-      <c r="BX16" s="39" t="n"/>
-      <c r="BY16" s="40" t="n"/>
+      <c r="BW16" s="41" t="n"/>
+      <c r="BX16" s="41" t="n"/>
+      <c r="BY16" s="42" t="n"/>
       <c r="BZ16" s="31" t="n"/>
-      <c r="CA16" s="39" t="n"/>
-      <c r="CB16" s="39" t="n"/>
-      <c r="CC16" s="40" t="n"/>
+      <c r="CA16" s="41" t="n"/>
+      <c r="CB16" s="41" t="n"/>
+      <c r="CC16" s="42" t="n"/>
       <c r="CD16" s="31" t="n"/>
-      <c r="CE16" s="39" t="n"/>
-      <c r="CF16" s="39" t="n"/>
-      <c r="CG16" s="50" t="n"/>
+      <c r="CE16" s="41" t="n"/>
+      <c r="CF16" s="41" t="n"/>
+      <c r="CG16" s="54" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
@@ -3250,93 +3347,101 @@
         </is>
       </c>
       <c r="F17" s="31" t="n"/>
-      <c r="G17" s="39" t="n"/>
-      <c r="H17" s="39" t="n"/>
-      <c r="I17" s="40" t="n"/>
+      <c r="G17" s="41" t="n"/>
+      <c r="H17" s="41" t="n"/>
+      <c r="I17" s="42" t="n"/>
       <c r="J17" s="31" t="n"/>
-      <c r="K17" s="39" t="n"/>
-      <c r="L17" s="39" t="n"/>
-      <c r="M17" s="40" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="41" t="n"/>
+      <c r="M17" s="42" t="n"/>
       <c r="N17" s="31" t="n"/>
-      <c r="O17" s="39" t="n"/>
-      <c r="P17" s="39" t="n"/>
-      <c r="Q17" s="40" t="n"/>
+      <c r="O17" s="41" t="n"/>
+      <c r="P17" s="41" t="n"/>
+      <c r="Q17" s="42" t="n"/>
       <c r="R17" s="31" t="n"/>
-      <c r="S17" s="39" t="n"/>
-      <c r="T17" s="39" t="n"/>
-      <c r="U17" s="40" t="n"/>
+      <c r="S17" s="41" t="n"/>
+      <c r="T17" s="41" t="n"/>
+      <c r="U17" s="42" t="n"/>
       <c r="V17" s="31" t="n"/>
-      <c r="W17" s="39" t="n"/>
-      <c r="X17" s="39" t="n"/>
-      <c r="Y17" s="40" t="n"/>
+      <c r="W17" s="41" t="n"/>
+      <c r="X17" s="41" t="n"/>
+      <c r="Y17" s="42" t="n"/>
       <c r="Z17" s="31" t="n"/>
-      <c r="AA17" s="39" t="n"/>
-      <c r="AB17" s="39" t="n"/>
-      <c r="AC17" s="40" t="n"/>
+      <c r="AA17" s="41" t="n"/>
+      <c r="AB17" s="41" t="n"/>
+      <c r="AC17" s="42" t="n"/>
       <c r="AD17" s="31" t="n"/>
-      <c r="AE17" s="39" t="n"/>
-      <c r="AF17" s="39" t="n"/>
-      <c r="AG17" s="40" t="n"/>
+      <c r="AE17" s="41" t="n"/>
+      <c r="AF17" s="41" t="n"/>
+      <c r="AG17" s="42" t="n"/>
       <c r="AH17" s="31" t="n"/>
-      <c r="AI17" s="39" t="n"/>
-      <c r="AJ17" s="39" t="n"/>
-      <c r="AK17" s="40" t="n"/>
+      <c r="AI17" s="41" t="n"/>
+      <c r="AJ17" s="41" t="n"/>
+      <c r="AK17" s="42" t="n"/>
       <c r="AL17" s="31" t="n"/>
-      <c r="AM17" s="39" t="n"/>
-      <c r="AN17" s="39" t="n"/>
-      <c r="AO17" s="40" t="n"/>
-      <c r="AP17" s="35" t="n"/>
+      <c r="AM17" s="41" t="n"/>
+      <c r="AN17" s="41" t="n"/>
+      <c r="AO17" s="42" t="n"/>
+      <c r="AP17" s="36" t="n"/>
       <c r="AQ17" s="33" t="n"/>
       <c r="AR17" s="33" t="n"/>
       <c r="AS17" s="34" t="n"/>
-      <c r="AT17" s="35" t="n"/>
+      <c r="AT17" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="AU17" s="33" t="n"/>
       <c r="AV17" s="33" t="n"/>
       <c r="AW17" s="34" t="n"/>
-      <c r="AX17" s="56" t="inlineStr">
+      <c r="AX17" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AY17" s="33" t="n"/>
-      <c r="AZ17" s="57" t="inlineStr">
+      <c r="AZ17" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BA17" s="34" t="n"/>
-      <c r="BB17" s="35" t="n"/>
+      <c r="BB17" s="36" t="n"/>
       <c r="BC17" s="33" t="n"/>
       <c r="BD17" s="33" t="n"/>
       <c r="BE17" s="34" t="n"/>
-      <c r="BF17" s="35" t="n"/>
+      <c r="BF17" s="36" t="n"/>
       <c r="BG17" s="33" t="n"/>
       <c r="BH17" s="33" t="n"/>
       <c r="BI17" s="34" t="n"/>
-      <c r="BJ17" s="35" t="n"/>
+      <c r="BJ17" s="36" t="n"/>
       <c r="BK17" s="33" t="n"/>
       <c r="BL17" s="33" t="n"/>
       <c r="BM17" s="34" t="n"/>
-      <c r="BN17" s="35" t="n"/>
+      <c r="BN17" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="BO17" s="33" t="n"/>
       <c r="BP17" s="33" t="n"/>
       <c r="BQ17" s="34" t="n"/>
-      <c r="BR17" s="38" t="n"/>
+      <c r="BR17" s="40" t="n"/>
       <c r="BS17" s="33" t="n"/>
-      <c r="BT17" s="39" t="n"/>
-      <c r="BU17" s="40" t="n"/>
+      <c r="BT17" s="41" t="n"/>
+      <c r="BU17" s="42" t="n"/>
       <c r="BV17" s="31" t="n"/>
-      <c r="BW17" s="39" t="n"/>
-      <c r="BX17" s="39" t="n"/>
-      <c r="BY17" s="40" t="n"/>
+      <c r="BW17" s="41" t="n"/>
+      <c r="BX17" s="41" t="n"/>
+      <c r="BY17" s="42" t="n"/>
       <c r="BZ17" s="31" t="n"/>
-      <c r="CA17" s="39" t="n"/>
-      <c r="CB17" s="39" t="n"/>
-      <c r="CC17" s="40" t="n"/>
+      <c r="CA17" s="41" t="n"/>
+      <c r="CB17" s="41" t="n"/>
+      <c r="CC17" s="42" t="n"/>
       <c r="CD17" s="31" t="n"/>
-      <c r="CE17" s="39" t="n"/>
-      <c r="CF17" s="39" t="n"/>
-      <c r="CG17" s="50" t="n"/>
+      <c r="CE17" s="41" t="n"/>
+      <c r="CF17" s="41" t="n"/>
+      <c r="CG17" s="54" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
@@ -3361,93 +3466,101 @@
       </c>
       <c r="E18" s="30" t="inlineStr"/>
       <c r="F18" s="31" t="n"/>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="39" t="n"/>
-      <c r="I18" s="40" t="n"/>
+      <c r="G18" s="41" t="n"/>
+      <c r="H18" s="41" t="n"/>
+      <c r="I18" s="42" t="n"/>
       <c r="J18" s="31" t="n"/>
-      <c r="K18" s="39" t="n"/>
-      <c r="L18" s="39" t="n"/>
-      <c r="M18" s="40" t="n"/>
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="41" t="n"/>
+      <c r="M18" s="42" t="n"/>
       <c r="N18" s="31" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="39" t="n"/>
-      <c r="Q18" s="40" t="n"/>
+      <c r="O18" s="41" t="n"/>
+      <c r="P18" s="41" t="n"/>
+      <c r="Q18" s="42" t="n"/>
       <c r="R18" s="31" t="n"/>
-      <c r="S18" s="39" t="n"/>
-      <c r="T18" s="39" t="n"/>
-      <c r="U18" s="40" t="n"/>
+      <c r="S18" s="41" t="n"/>
+      <c r="T18" s="41" t="n"/>
+      <c r="U18" s="42" t="n"/>
       <c r="V18" s="31" t="n"/>
-      <c r="W18" s="39" t="n"/>
-      <c r="X18" s="39" t="n"/>
-      <c r="Y18" s="40" t="n"/>
+      <c r="W18" s="41" t="n"/>
+      <c r="X18" s="41" t="n"/>
+      <c r="Y18" s="42" t="n"/>
       <c r="Z18" s="31" t="n"/>
-      <c r="AA18" s="39" t="n"/>
-      <c r="AB18" s="39" t="n"/>
-      <c r="AC18" s="40" t="n"/>
+      <c r="AA18" s="41" t="n"/>
+      <c r="AB18" s="41" t="n"/>
+      <c r="AC18" s="42" t="n"/>
       <c r="AD18" s="31" t="n"/>
-      <c r="AE18" s="39" t="n"/>
-      <c r="AF18" s="39" t="n"/>
-      <c r="AG18" s="40" t="n"/>
+      <c r="AE18" s="41" t="n"/>
+      <c r="AF18" s="41" t="n"/>
+      <c r="AG18" s="42" t="n"/>
       <c r="AH18" s="31" t="n"/>
-      <c r="AI18" s="39" t="n"/>
-      <c r="AJ18" s="39" t="n"/>
-      <c r="AK18" s="40" t="n"/>
+      <c r="AI18" s="41" t="n"/>
+      <c r="AJ18" s="41" t="n"/>
+      <c r="AK18" s="42" t="n"/>
       <c r="AL18" s="31" t="n"/>
-      <c r="AM18" s="39" t="n"/>
-      <c r="AN18" s="39" t="n"/>
-      <c r="AO18" s="40" t="n"/>
+      <c r="AM18" s="41" t="n"/>
+      <c r="AN18" s="41" t="n"/>
+      <c r="AO18" s="42" t="n"/>
       <c r="AP18" s="31" t="n"/>
-      <c r="AQ18" s="39" t="n"/>
-      <c r="AR18" s="39" t="n"/>
-      <c r="AS18" s="40" t="n"/>
-      <c r="AT18" s="45" t="n"/>
+      <c r="AQ18" s="41" t="n"/>
+      <c r="AR18" s="41" t="n"/>
+      <c r="AS18" s="42" t="n"/>
+      <c r="AT18" s="47" t="n"/>
       <c r="AU18" s="33" t="n"/>
       <c r="AV18" s="33" t="n"/>
       <c r="AW18" s="34" t="n"/>
-      <c r="AX18" s="45" t="n"/>
+      <c r="AX18" s="47" t="n"/>
       <c r="AY18" s="33" t="n"/>
       <c r="AZ18" s="33" t="n"/>
       <c r="BA18" s="34" t="n"/>
-      <c r="BB18" s="56" t="inlineStr">
+      <c r="BB18" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BC18" s="33" t="n"/>
-      <c r="BD18" s="57" t="inlineStr">
+      <c r="BD18" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BE18" s="34" t="n"/>
-      <c r="BF18" s="45" t="n"/>
+      <c r="BF18" s="47" t="n"/>
       <c r="BG18" s="33" t="n"/>
       <c r="BH18" s="33" t="n"/>
       <c r="BI18" s="34" t="n"/>
-      <c r="BJ18" s="45" t="n"/>
+      <c r="BJ18" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="BK18" s="33" t="n"/>
       <c r="BL18" s="33" t="n"/>
       <c r="BM18" s="34" t="n"/>
-      <c r="BN18" s="45" t="n"/>
+      <c r="BN18" s="47" t="n"/>
       <c r="BO18" s="33" t="n"/>
       <c r="BP18" s="33" t="n"/>
       <c r="BQ18" s="34" t="n"/>
-      <c r="BR18" s="45" t="n"/>
+      <c r="BR18" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BS18" s="33" t="n"/>
       <c r="BT18" s="33" t="n"/>
       <c r="BU18" s="34" t="n"/>
-      <c r="BV18" s="45" t="n"/>
+      <c r="BV18" s="47" t="n"/>
       <c r="BW18" s="33" t="n"/>
       <c r="BX18" s="33" t="n"/>
       <c r="BY18" s="34" t="n"/>
       <c r="BZ18" s="31" t="n"/>
-      <c r="CA18" s="39" t="n"/>
-      <c r="CB18" s="39" t="n"/>
-      <c r="CC18" s="40" t="n"/>
+      <c r="CA18" s="41" t="n"/>
+      <c r="CB18" s="41" t="n"/>
+      <c r="CC18" s="42" t="n"/>
       <c r="CD18" s="31" t="n"/>
-      <c r="CE18" s="39" t="n"/>
-      <c r="CF18" s="39" t="n"/>
-      <c r="CG18" s="50" t="n"/>
+      <c r="CE18" s="41" t="n"/>
+      <c r="CF18" s="41" t="n"/>
+      <c r="CG18" s="54" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
@@ -3476,93 +3589,101 @@
         </is>
       </c>
       <c r="F19" s="31" t="n"/>
-      <c r="G19" s="39" t="n"/>
-      <c r="H19" s="39" t="n"/>
-      <c r="I19" s="40" t="n"/>
+      <c r="G19" s="41" t="n"/>
+      <c r="H19" s="41" t="n"/>
+      <c r="I19" s="42" t="n"/>
       <c r="J19" s="31" t="n"/>
-      <c r="K19" s="39" t="n"/>
-      <c r="L19" s="39" t="n"/>
-      <c r="M19" s="40" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="41" t="n"/>
+      <c r="M19" s="42" t="n"/>
       <c r="N19" s="31" t="n"/>
-      <c r="O19" s="39" t="n"/>
-      <c r="P19" s="39" t="n"/>
-      <c r="Q19" s="40" t="n"/>
+      <c r="O19" s="41" t="n"/>
+      <c r="P19" s="41" t="n"/>
+      <c r="Q19" s="42" t="n"/>
       <c r="R19" s="31" t="n"/>
-      <c r="S19" s="39" t="n"/>
-      <c r="T19" s="39" t="n"/>
-      <c r="U19" s="40" t="n"/>
+      <c r="S19" s="41" t="n"/>
+      <c r="T19" s="41" t="n"/>
+      <c r="U19" s="42" t="n"/>
       <c r="V19" s="31" t="n"/>
-      <c r="W19" s="39" t="n"/>
-      <c r="X19" s="39" t="n"/>
-      <c r="Y19" s="40" t="n"/>
+      <c r="W19" s="41" t="n"/>
+      <c r="X19" s="41" t="n"/>
+      <c r="Y19" s="42" t="n"/>
       <c r="Z19" s="31" t="n"/>
-      <c r="AA19" s="39" t="n"/>
-      <c r="AB19" s="39" t="n"/>
-      <c r="AC19" s="40" t="n"/>
+      <c r="AA19" s="41" t="n"/>
+      <c r="AB19" s="41" t="n"/>
+      <c r="AC19" s="42" t="n"/>
       <c r="AD19" s="31" t="n"/>
-      <c r="AE19" s="39" t="n"/>
-      <c r="AF19" s="39" t="n"/>
-      <c r="AG19" s="40" t="n"/>
+      <c r="AE19" s="41" t="n"/>
+      <c r="AF19" s="41" t="n"/>
+      <c r="AG19" s="42" t="n"/>
       <c r="AH19" s="31" t="n"/>
-      <c r="AI19" s="39" t="n"/>
-      <c r="AJ19" s="39" t="n"/>
-      <c r="AK19" s="40" t="n"/>
+      <c r="AI19" s="41" t="n"/>
+      <c r="AJ19" s="41" t="n"/>
+      <c r="AK19" s="42" t="n"/>
       <c r="AL19" s="31" t="n"/>
-      <c r="AM19" s="39" t="n"/>
-      <c r="AN19" s="39" t="n"/>
-      <c r="AO19" s="40" t="n"/>
+      <c r="AM19" s="41" t="n"/>
+      <c r="AN19" s="41" t="n"/>
+      <c r="AO19" s="42" t="n"/>
       <c r="AP19" s="31" t="n"/>
-      <c r="AQ19" s="39" t="n"/>
-      <c r="AR19" s="39" t="n"/>
-      <c r="AS19" s="40" t="n"/>
-      <c r="AT19" s="45" t="n"/>
+      <c r="AQ19" s="41" t="n"/>
+      <c r="AR19" s="41" t="n"/>
+      <c r="AS19" s="42" t="n"/>
+      <c r="AT19" s="47" t="n"/>
       <c r="AU19" s="33" t="n"/>
       <c r="AV19" s="33" t="n"/>
       <c r="AW19" s="34" t="n"/>
-      <c r="AX19" s="45" t="n"/>
+      <c r="AX19" s="47" t="n"/>
       <c r="AY19" s="33" t="n"/>
       <c r="AZ19" s="33" t="n"/>
       <c r="BA19" s="34" t="n"/>
-      <c r="BB19" s="45" t="n"/>
+      <c r="BB19" s="48" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="BC19" s="33" t="n"/>
       <c r="BD19" s="33" t="n"/>
       <c r="BE19" s="34" t="n"/>
-      <c r="BF19" s="36" t="inlineStr">
+      <c r="BF19" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BG19" s="33" t="n"/>
-      <c r="BH19" s="37" t="inlineStr">
+      <c r="BH19" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BI19" s="34" t="n"/>
-      <c r="BJ19" s="45" t="n"/>
+      <c r="BJ19" s="47" t="n"/>
       <c r="BK19" s="33" t="n"/>
       <c r="BL19" s="33" t="n"/>
       <c r="BM19" s="34" t="n"/>
-      <c r="BN19" s="45" t="n"/>
+      <c r="BN19" s="47" t="n"/>
       <c r="BO19" s="33" t="n"/>
       <c r="BP19" s="33" t="n"/>
       <c r="BQ19" s="34" t="n"/>
-      <c r="BR19" s="45" t="n"/>
+      <c r="BR19" s="47" t="n"/>
       <c r="BS19" s="33" t="n"/>
       <c r="BT19" s="33" t="n"/>
       <c r="BU19" s="34" t="n"/>
-      <c r="BV19" s="45" t="n"/>
+      <c r="BV19" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BW19" s="33" t="n"/>
       <c r="BX19" s="33" t="n"/>
       <c r="BY19" s="34" t="n"/>
       <c r="BZ19" s="31" t="n"/>
-      <c r="CA19" s="39" t="n"/>
-      <c r="CB19" s="39" t="n"/>
-      <c r="CC19" s="40" t="n"/>
+      <c r="CA19" s="41" t="n"/>
+      <c r="CB19" s="41" t="n"/>
+      <c r="CC19" s="42" t="n"/>
       <c r="CD19" s="31" t="n"/>
-      <c r="CE19" s="39" t="n"/>
-      <c r="CF19" s="39" t="n"/>
-      <c r="CG19" s="50" t="n"/>
+      <c r="CE19" s="41" t="n"/>
+      <c r="CF19" s="41" t="n"/>
+      <c r="CG19" s="54" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="29" t="inlineStr">
@@ -3591,89 +3712,97 @@
         </is>
       </c>
       <c r="F20" s="31" t="n"/>
-      <c r="G20" s="39" t="n"/>
-      <c r="H20" s="39" t="n"/>
-      <c r="I20" s="40" t="n"/>
+      <c r="G20" s="41" t="n"/>
+      <c r="H20" s="41" t="n"/>
+      <c r="I20" s="42" t="n"/>
       <c r="J20" s="31" t="n"/>
-      <c r="K20" s="39" t="n"/>
-      <c r="L20" s="39" t="n"/>
-      <c r="M20" s="40" t="n"/>
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="41" t="n"/>
+      <c r="M20" s="42" t="n"/>
       <c r="N20" s="31" t="n"/>
-      <c r="O20" s="39" t="n"/>
-      <c r="P20" s="39" t="n"/>
-      <c r="Q20" s="40" t="n"/>
+      <c r="O20" s="41" t="n"/>
+      <c r="P20" s="41" t="n"/>
+      <c r="Q20" s="42" t="n"/>
       <c r="R20" s="31" t="n"/>
-      <c r="S20" s="39" t="n"/>
-      <c r="T20" s="39" t="n"/>
-      <c r="U20" s="40" t="n"/>
+      <c r="S20" s="41" t="n"/>
+      <c r="T20" s="41" t="n"/>
+      <c r="U20" s="42" t="n"/>
       <c r="V20" s="31" t="n"/>
-      <c r="W20" s="39" t="n"/>
-      <c r="X20" s="39" t="n"/>
-      <c r="Y20" s="40" t="n"/>
+      <c r="W20" s="41" t="n"/>
+      <c r="X20" s="41" t="n"/>
+      <c r="Y20" s="42" t="n"/>
       <c r="Z20" s="31" t="n"/>
-      <c r="AA20" s="39" t="n"/>
-      <c r="AB20" s="39" t="n"/>
-      <c r="AC20" s="40" t="n"/>
+      <c r="AA20" s="41" t="n"/>
+      <c r="AB20" s="41" t="n"/>
+      <c r="AC20" s="42" t="n"/>
       <c r="AD20" s="31" t="n"/>
-      <c r="AE20" s="39" t="n"/>
-      <c r="AF20" s="39" t="n"/>
-      <c r="AG20" s="40" t="n"/>
+      <c r="AE20" s="41" t="n"/>
+      <c r="AF20" s="41" t="n"/>
+      <c r="AG20" s="42" t="n"/>
       <c r="AH20" s="31" t="n"/>
-      <c r="AI20" s="39" t="n"/>
-      <c r="AJ20" s="39" t="n"/>
-      <c r="AK20" s="40" t="n"/>
+      <c r="AI20" s="41" t="n"/>
+      <c r="AJ20" s="41" t="n"/>
+      <c r="AK20" s="42" t="n"/>
       <c r="AL20" s="31" t="n"/>
-      <c r="AM20" s="39" t="n"/>
-      <c r="AN20" s="39" t="n"/>
-      <c r="AO20" s="40" t="n"/>
+      <c r="AM20" s="41" t="n"/>
+      <c r="AN20" s="41" t="n"/>
+      <c r="AO20" s="42" t="n"/>
       <c r="AP20" s="31" t="n"/>
-      <c r="AQ20" s="39" t="n"/>
-      <c r="AR20" s="39" t="n"/>
-      <c r="AS20" s="40" t="n"/>
+      <c r="AQ20" s="41" t="n"/>
+      <c r="AR20" s="41" t="n"/>
+      <c r="AS20" s="42" t="n"/>
       <c r="AT20" s="31" t="n"/>
-      <c r="AU20" s="39" t="n"/>
-      <c r="AV20" s="39" t="n"/>
-      <c r="AW20" s="40" t="n"/>
-      <c r="AX20" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
+      <c r="AU20" s="41" t="n"/>
+      <c r="AV20" s="41" t="n"/>
+      <c r="AW20" s="42" t="n"/>
+      <c r="AX20" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
         </is>
       </c>
       <c r="AY20" s="33" t="n"/>
       <c r="AZ20" s="33" t="n"/>
       <c r="BA20" s="34" t="n"/>
-      <c r="BB20" s="45" t="n"/>
+      <c r="BB20" s="48" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="BC20" s="33" t="n"/>
       <c r="BD20" s="33" t="n"/>
       <c r="BE20" s="34" t="n"/>
-      <c r="BF20" s="45" t="n"/>
+      <c r="BF20" s="47" t="n"/>
       <c r="BG20" s="33" t="n"/>
       <c r="BH20" s="33" t="n"/>
       <c r="BI20" s="34" t="n"/>
-      <c r="BJ20" s="45" t="n"/>
+      <c r="BJ20" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BK20" s="33" t="n"/>
       <c r="BL20" s="33" t="n"/>
       <c r="BM20" s="34" t="n"/>
       <c r="BN20" s="31" t="n"/>
-      <c r="BO20" s="39" t="n"/>
-      <c r="BP20" s="39" t="n"/>
-      <c r="BQ20" s="40" t="n"/>
+      <c r="BO20" s="41" t="n"/>
+      <c r="BP20" s="41" t="n"/>
+      <c r="BQ20" s="42" t="n"/>
       <c r="BR20" s="31" t="n"/>
-      <c r="BS20" s="39" t="n"/>
-      <c r="BT20" s="39" t="n"/>
-      <c r="BU20" s="40" t="n"/>
+      <c r="BS20" s="41" t="n"/>
+      <c r="BT20" s="41" t="n"/>
+      <c r="BU20" s="42" t="n"/>
       <c r="BV20" s="31" t="n"/>
-      <c r="BW20" s="39" t="n"/>
-      <c r="BX20" s="39" t="n"/>
-      <c r="BY20" s="40" t="n"/>
+      <c r="BW20" s="41" t="n"/>
+      <c r="BX20" s="41" t="n"/>
+      <c r="BY20" s="42" t="n"/>
       <c r="BZ20" s="31" t="n"/>
-      <c r="CA20" s="39" t="n"/>
-      <c r="CB20" s="39" t="n"/>
-      <c r="CC20" s="40" t="n"/>
+      <c r="CA20" s="41" t="n"/>
+      <c r="CB20" s="41" t="n"/>
+      <c r="CC20" s="42" t="n"/>
       <c r="CD20" s="31" t="n"/>
-      <c r="CE20" s="39" t="n"/>
-      <c r="CF20" s="39" t="n"/>
-      <c r="CG20" s="50" t="n"/>
+      <c r="CE20" s="41" t="n"/>
+      <c r="CF20" s="41" t="n"/>
+      <c r="CG20" s="54" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="29" t="inlineStr">
@@ -3702,97 +3831,101 @@
         </is>
       </c>
       <c r="F21" s="31" t="n"/>
-      <c r="G21" s="39" t="n"/>
-      <c r="H21" s="39" t="n"/>
-      <c r="I21" s="40" t="n"/>
+      <c r="G21" s="41" t="n"/>
+      <c r="H21" s="41" t="n"/>
+      <c r="I21" s="42" t="n"/>
       <c r="J21" s="31" t="n"/>
-      <c r="K21" s="39" t="n"/>
-      <c r="L21" s="39" t="n"/>
-      <c r="M21" s="40" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="41" t="n"/>
+      <c r="M21" s="42" t="n"/>
       <c r="N21" s="31" t="n"/>
-      <c r="O21" s="39" t="n"/>
-      <c r="P21" s="39" t="n"/>
-      <c r="Q21" s="40" t="n"/>
+      <c r="O21" s="41" t="n"/>
+      <c r="P21" s="41" t="n"/>
+      <c r="Q21" s="42" t="n"/>
       <c r="R21" s="31" t="n"/>
-      <c r="S21" s="39" t="n"/>
-      <c r="T21" s="39" t="n"/>
-      <c r="U21" s="40" t="n"/>
+      <c r="S21" s="41" t="n"/>
+      <c r="T21" s="41" t="n"/>
+      <c r="U21" s="42" t="n"/>
       <c r="V21" s="31" t="n"/>
-      <c r="W21" s="39" t="n"/>
-      <c r="X21" s="39" t="n"/>
-      <c r="Y21" s="40" t="n"/>
+      <c r="W21" s="41" t="n"/>
+      <c r="X21" s="41" t="n"/>
+      <c r="Y21" s="42" t="n"/>
       <c r="Z21" s="31" t="n"/>
-      <c r="AA21" s="39" t="n"/>
-      <c r="AB21" s="39" t="n"/>
-      <c r="AC21" s="40" t="n"/>
+      <c r="AA21" s="41" t="n"/>
+      <c r="AB21" s="41" t="n"/>
+      <c r="AC21" s="42" t="n"/>
       <c r="AD21" s="31" t="n"/>
-      <c r="AE21" s="39" t="n"/>
-      <c r="AF21" s="39" t="n"/>
-      <c r="AG21" s="40" t="n"/>
+      <c r="AE21" s="41" t="n"/>
+      <c r="AF21" s="41" t="n"/>
+      <c r="AG21" s="42" t="n"/>
       <c r="AH21" s="31" t="n"/>
-      <c r="AI21" s="39" t="n"/>
-      <c r="AJ21" s="39" t="n"/>
-      <c r="AK21" s="40" t="n"/>
+      <c r="AI21" s="41" t="n"/>
+      <c r="AJ21" s="41" t="n"/>
+      <c r="AK21" s="42" t="n"/>
       <c r="AL21" s="31" t="n"/>
-      <c r="AM21" s="39" t="n"/>
-      <c r="AN21" s="39" t="n"/>
-      <c r="AO21" s="40" t="n"/>
+      <c r="AM21" s="41" t="n"/>
+      <c r="AN21" s="41" t="n"/>
+      <c r="AO21" s="42" t="n"/>
       <c r="AP21" s="31" t="n"/>
-      <c r="AQ21" s="39" t="n"/>
-      <c r="AR21" s="39" t="n"/>
-      <c r="AS21" s="40" t="n"/>
+      <c r="AQ21" s="41" t="n"/>
+      <c r="AR21" s="41" t="n"/>
+      <c r="AS21" s="42" t="n"/>
       <c r="AT21" s="31" t="n"/>
-      <c r="AU21" s="39" t="n"/>
-      <c r="AV21" s="39" t="n"/>
-      <c r="AW21" s="40" t="n"/>
+      <c r="AU21" s="41" t="n"/>
+      <c r="AV21" s="41" t="n"/>
+      <c r="AW21" s="42" t="n"/>
       <c r="AX21" s="31" t="n"/>
-      <c r="AY21" s="39" t="n"/>
-      <c r="AZ21" s="39" t="n"/>
-      <c r="BA21" s="40" t="n"/>
-      <c r="BB21" s="45" t="n"/>
+      <c r="AY21" s="41" t="n"/>
+      <c r="AZ21" s="41" t="n"/>
+      <c r="BA21" s="42" t="n"/>
+      <c r="BB21" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="BC21" s="33" t="n"/>
       <c r="BD21" s="33" t="n"/>
       <c r="BE21" s="34" t="n"/>
-      <c r="BF21" s="45" t="n"/>
+      <c r="BF21" s="47" t="n"/>
       <c r="BG21" s="33" t="n"/>
       <c r="BH21" s="33" t="n"/>
       <c r="BI21" s="34" t="n"/>
-      <c r="BJ21" s="56" t="inlineStr">
+      <c r="BJ21" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BK21" s="33" t="n"/>
-      <c r="BL21" s="57" t="inlineStr">
+      <c r="BL21" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BM21" s="34" t="n"/>
-      <c r="BN21" s="45" t="n"/>
+      <c r="BN21" s="47" t="n"/>
       <c r="BO21" s="33" t="n"/>
       <c r="BP21" s="33" t="n"/>
       <c r="BQ21" s="34" t="n"/>
-      <c r="BR21" s="45" t="n"/>
+      <c r="BR21" s="47" t="n"/>
       <c r="BS21" s="33" t="n"/>
       <c r="BT21" s="33" t="n"/>
       <c r="BU21" s="34" t="n"/>
-      <c r="BV21" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BV21" s="47" t="n"/>
       <c r="BW21" s="33" t="n"/>
       <c r="BX21" s="33" t="n"/>
       <c r="BY21" s="34" t="n"/>
-      <c r="BZ21" s="45" t="n"/>
+      <c r="BZ21" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="CA21" s="33" t="n"/>
       <c r="CB21" s="33" t="n"/>
       <c r="CC21" s="34" t="n"/>
-      <c r="CD21" s="60" t="n"/>
+      <c r="CD21" s="52" t="n"/>
       <c r="CE21" s="33" t="n"/>
       <c r="CF21" s="33" t="n"/>
-      <c r="CG21" s="50" t="n"/>
+      <c r="CG21" s="54" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="29" t="inlineStr">
@@ -3821,97 +3954,101 @@
         </is>
       </c>
       <c r="F22" s="31" t="n"/>
-      <c r="G22" s="39" t="n"/>
-      <c r="H22" s="39" t="n"/>
-      <c r="I22" s="40" t="n"/>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="n"/>
+      <c r="I22" s="42" t="n"/>
       <c r="J22" s="31" t="n"/>
-      <c r="K22" s="39" t="n"/>
-      <c r="L22" s="39" t="n"/>
-      <c r="M22" s="40" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="41" t="n"/>
+      <c r="M22" s="42" t="n"/>
       <c r="N22" s="31" t="n"/>
-      <c r="O22" s="39" t="n"/>
-      <c r="P22" s="39" t="n"/>
-      <c r="Q22" s="40" t="n"/>
+      <c r="O22" s="41" t="n"/>
+      <c r="P22" s="41" t="n"/>
+      <c r="Q22" s="42" t="n"/>
       <c r="R22" s="31" t="n"/>
-      <c r="S22" s="39" t="n"/>
-      <c r="T22" s="39" t="n"/>
-      <c r="U22" s="40" t="n"/>
+      <c r="S22" s="41" t="n"/>
+      <c r="T22" s="41" t="n"/>
+      <c r="U22" s="42" t="n"/>
       <c r="V22" s="31" t="n"/>
-      <c r="W22" s="39" t="n"/>
-      <c r="X22" s="39" t="n"/>
-      <c r="Y22" s="40" t="n"/>
+      <c r="W22" s="41" t="n"/>
+      <c r="X22" s="41" t="n"/>
+      <c r="Y22" s="42" t="n"/>
       <c r="Z22" s="31" t="n"/>
-      <c r="AA22" s="39" t="n"/>
-      <c r="AB22" s="39" t="n"/>
-      <c r="AC22" s="40" t="n"/>
+      <c r="AA22" s="41" t="n"/>
+      <c r="AB22" s="41" t="n"/>
+      <c r="AC22" s="42" t="n"/>
       <c r="AD22" s="31" t="n"/>
-      <c r="AE22" s="39" t="n"/>
-      <c r="AF22" s="39" t="n"/>
-      <c r="AG22" s="40" t="n"/>
+      <c r="AE22" s="41" t="n"/>
+      <c r="AF22" s="41" t="n"/>
+      <c r="AG22" s="42" t="n"/>
       <c r="AH22" s="31" t="n"/>
-      <c r="AI22" s="39" t="n"/>
-      <c r="AJ22" s="39" t="n"/>
-      <c r="AK22" s="40" t="n"/>
+      <c r="AI22" s="41" t="n"/>
+      <c r="AJ22" s="41" t="n"/>
+      <c r="AK22" s="42" t="n"/>
       <c r="AL22" s="31" t="n"/>
-      <c r="AM22" s="39" t="n"/>
-      <c r="AN22" s="39" t="n"/>
-      <c r="AO22" s="40" t="n"/>
+      <c r="AM22" s="41" t="n"/>
+      <c r="AN22" s="41" t="n"/>
+      <c r="AO22" s="42" t="n"/>
       <c r="AP22" s="31" t="n"/>
-      <c r="AQ22" s="39" t="n"/>
-      <c r="AR22" s="39" t="n"/>
-      <c r="AS22" s="40" t="n"/>
+      <c r="AQ22" s="41" t="n"/>
+      <c r="AR22" s="41" t="n"/>
+      <c r="AS22" s="42" t="n"/>
       <c r="AT22" s="31" t="n"/>
-      <c r="AU22" s="39" t="n"/>
-      <c r="AV22" s="39" t="n"/>
-      <c r="AW22" s="40" t="n"/>
+      <c r="AU22" s="41" t="n"/>
+      <c r="AV22" s="41" t="n"/>
+      <c r="AW22" s="42" t="n"/>
       <c r="AX22" s="31" t="n"/>
-      <c r="AY22" s="39" t="n"/>
-      <c r="AZ22" s="39" t="n"/>
-      <c r="BA22" s="40" t="n"/>
-      <c r="BB22" s="45" t="n"/>
+      <c r="AY22" s="41" t="n"/>
+      <c r="AZ22" s="41" t="n"/>
+      <c r="BA22" s="42" t="n"/>
+      <c r="BB22" s="47" t="n"/>
       <c r="BC22" s="33" t="n"/>
       <c r="BD22" s="33" t="n"/>
       <c r="BE22" s="34" t="n"/>
-      <c r="BF22" s="45" t="n"/>
+      <c r="BF22" s="48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="BG22" s="33" t="n"/>
       <c r="BH22" s="33" t="n"/>
       <c r="BI22" s="34" t="n"/>
-      <c r="BJ22" s="45" t="n"/>
+      <c r="BJ22" s="47" t="n"/>
       <c r="BK22" s="33" t="n"/>
       <c r="BL22" s="33" t="n"/>
       <c r="BM22" s="34" t="n"/>
-      <c r="BN22" s="36" t="inlineStr">
+      <c r="BN22" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BO22" s="33" t="n"/>
-      <c r="BP22" s="37" t="inlineStr">
+      <c r="BP22" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BQ22" s="34" t="n"/>
-      <c r="BR22" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
+      <c r="BR22" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
         </is>
       </c>
       <c r="BS22" s="33" t="n"/>
       <c r="BT22" s="33" t="n"/>
       <c r="BU22" s="34" t="n"/>
-      <c r="BV22" s="45" t="n"/>
+      <c r="BV22" s="47" t="n"/>
       <c r="BW22" s="33" t="n"/>
       <c r="BX22" s="33" t="n"/>
       <c r="BY22" s="34" t="n"/>
-      <c r="BZ22" s="45" t="n"/>
+      <c r="BZ22" s="47" t="n"/>
       <c r="CA22" s="33" t="n"/>
       <c r="CB22" s="33" t="n"/>
       <c r="CC22" s="34" t="n"/>
-      <c r="CD22" s="60" t="n"/>
+      <c r="CD22" s="52" t="n"/>
       <c r="CE22" s="33" t="n"/>
       <c r="CF22" s="33" t="n"/>
-      <c r="CG22" s="50" t="n"/>
+      <c r="CG22" s="54" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="29" t="inlineStr">
@@ -3940,97 +4077,97 @@
         </is>
       </c>
       <c r="F23" s="31" t="n"/>
-      <c r="G23" s="39" t="n"/>
-      <c r="H23" s="39" t="n"/>
-      <c r="I23" s="40" t="n"/>
+      <c r="G23" s="41" t="n"/>
+      <c r="H23" s="41" t="n"/>
+      <c r="I23" s="42" t="n"/>
       <c r="J23" s="31" t="n"/>
-      <c r="K23" s="39" t="n"/>
-      <c r="L23" s="39" t="n"/>
-      <c r="M23" s="40" t="n"/>
+      <c r="K23" s="41" t="n"/>
+      <c r="L23" s="41" t="n"/>
+      <c r="M23" s="42" t="n"/>
       <c r="N23" s="31" t="n"/>
-      <c r="O23" s="39" t="n"/>
-      <c r="P23" s="39" t="n"/>
-      <c r="Q23" s="40" t="n"/>
+      <c r="O23" s="41" t="n"/>
+      <c r="P23" s="41" t="n"/>
+      <c r="Q23" s="42" t="n"/>
       <c r="R23" s="31" t="n"/>
-      <c r="S23" s="39" t="n"/>
-      <c r="T23" s="39" t="n"/>
-      <c r="U23" s="40" t="n"/>
+      <c r="S23" s="41" t="n"/>
+      <c r="T23" s="41" t="n"/>
+      <c r="U23" s="42" t="n"/>
       <c r="V23" s="31" t="n"/>
-      <c r="W23" s="39" t="n"/>
-      <c r="X23" s="39" t="n"/>
-      <c r="Y23" s="40" t="n"/>
+      <c r="W23" s="41" t="n"/>
+      <c r="X23" s="41" t="n"/>
+      <c r="Y23" s="42" t="n"/>
       <c r="Z23" s="31" t="n"/>
-      <c r="AA23" s="39" t="n"/>
-      <c r="AB23" s="39" t="n"/>
-      <c r="AC23" s="40" t="n"/>
+      <c r="AA23" s="41" t="n"/>
+      <c r="AB23" s="41" t="n"/>
+      <c r="AC23" s="42" t="n"/>
       <c r="AD23" s="31" t="n"/>
-      <c r="AE23" s="39" t="n"/>
-      <c r="AF23" s="39" t="n"/>
-      <c r="AG23" s="40" t="n"/>
+      <c r="AE23" s="41" t="n"/>
+      <c r="AF23" s="41" t="n"/>
+      <c r="AG23" s="42" t="n"/>
       <c r="AH23" s="31" t="n"/>
-      <c r="AI23" s="39" t="n"/>
-      <c r="AJ23" s="39" t="n"/>
-      <c r="AK23" s="40" t="n"/>
+      <c r="AI23" s="41" t="n"/>
+      <c r="AJ23" s="41" t="n"/>
+      <c r="AK23" s="42" t="n"/>
       <c r="AL23" s="31" t="n"/>
-      <c r="AM23" s="39" t="n"/>
-      <c r="AN23" s="39" t="n"/>
-      <c r="AO23" s="40" t="n"/>
+      <c r="AM23" s="41" t="n"/>
+      <c r="AN23" s="41" t="n"/>
+      <c r="AO23" s="42" t="n"/>
       <c r="AP23" s="31" t="n"/>
-      <c r="AQ23" s="39" t="n"/>
-      <c r="AR23" s="39" t="n"/>
-      <c r="AS23" s="40" t="n"/>
+      <c r="AQ23" s="41" t="n"/>
+      <c r="AR23" s="41" t="n"/>
+      <c r="AS23" s="42" t="n"/>
       <c r="AT23" s="31" t="n"/>
-      <c r="AU23" s="39" t="n"/>
-      <c r="AV23" s="39" t="n"/>
-      <c r="AW23" s="40" t="n"/>
+      <c r="AU23" s="41" t="n"/>
+      <c r="AV23" s="41" t="n"/>
+      <c r="AW23" s="42" t="n"/>
       <c r="AX23" s="31" t="n"/>
-      <c r="AY23" s="39" t="n"/>
-      <c r="AZ23" s="39" t="n"/>
-      <c r="BA23" s="40" t="n"/>
+      <c r="AY23" s="41" t="n"/>
+      <c r="AZ23" s="41" t="n"/>
+      <c r="BA23" s="42" t="n"/>
       <c r="BB23" s="31" t="n"/>
-      <c r="BC23" s="39" t="n"/>
+      <c r="BC23" s="41" t="n"/>
       <c r="BD23" s="32" t="n"/>
       <c r="BE23" s="34" t="n"/>
-      <c r="BF23" s="35" t="n"/>
+      <c r="BF23" s="36" t="n"/>
       <c r="BG23" s="33" t="n"/>
       <c r="BH23" s="33" t="n"/>
       <c r="BI23" s="34" t="n"/>
-      <c r="BJ23" s="35" t="n"/>
+      <c r="BJ23" s="36" t="n"/>
       <c r="BK23" s="33" t="n"/>
       <c r="BL23" s="33" t="n"/>
       <c r="BM23" s="34" t="n"/>
-      <c r="BN23" s="56" t="inlineStr">
+      <c r="BN23" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BO23" s="33" t="n"/>
-      <c r="BP23" s="57" t="inlineStr">
+      <c r="BP23" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BQ23" s="34" t="n"/>
-      <c r="BR23" s="35" t="n"/>
+      <c r="BR23" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="BS23" s="33" t="n"/>
       <c r="BT23" s="33" t="n"/>
       <c r="BU23" s="34" t="n"/>
-      <c r="BV23" s="35" t="n"/>
+      <c r="BV23" s="36" t="n"/>
       <c r="BW23" s="33" t="n"/>
       <c r="BX23" s="33" t="n"/>
       <c r="BY23" s="34" t="n"/>
-      <c r="BZ23" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BZ23" s="36" t="n"/>
       <c r="CA23" s="33" t="n"/>
       <c r="CB23" s="33" t="n"/>
       <c r="CC23" s="34" t="n"/>
-      <c r="CD23" s="38" t="n"/>
+      <c r="CD23" s="40" t="n"/>
       <c r="CE23" s="33" t="n"/>
       <c r="CF23" s="33" t="n"/>
-      <c r="CG23" s="50" t="n"/>
+      <c r="CG23" s="54" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="29" t="inlineStr"/>
@@ -4039,91 +4176,91 @@
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="30" t="n"/>
       <c r="F24" s="31" t="n"/>
-      <c r="G24" s="39" t="n"/>
-      <c r="H24" s="39" t="n"/>
-      <c r="I24" s="40" t="n"/>
+      <c r="G24" s="41" t="n"/>
+      <c r="H24" s="41" t="n"/>
+      <c r="I24" s="42" t="n"/>
       <c r="J24" s="31" t="n"/>
-      <c r="K24" s="39" t="n"/>
-      <c r="L24" s="39" t="n"/>
-      <c r="M24" s="40" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="41" t="n"/>
+      <c r="M24" s="42" t="n"/>
       <c r="N24" s="31" t="n"/>
-      <c r="O24" s="39" t="n"/>
-      <c r="P24" s="39" t="n"/>
-      <c r="Q24" s="40" t="n"/>
+      <c r="O24" s="41" t="n"/>
+      <c r="P24" s="41" t="n"/>
+      <c r="Q24" s="42" t="n"/>
       <c r="R24" s="31" t="n"/>
-      <c r="S24" s="39" t="n"/>
-      <c r="T24" s="39" t="n"/>
-      <c r="U24" s="40" t="n"/>
+      <c r="S24" s="41" t="n"/>
+      <c r="T24" s="41" t="n"/>
+      <c r="U24" s="42" t="n"/>
       <c r="V24" s="31" t="n"/>
-      <c r="W24" s="39" t="n"/>
-      <c r="X24" s="39" t="n"/>
-      <c r="Y24" s="40" t="n"/>
+      <c r="W24" s="41" t="n"/>
+      <c r="X24" s="41" t="n"/>
+      <c r="Y24" s="42" t="n"/>
       <c r="Z24" s="31" t="n"/>
-      <c r="AA24" s="39" t="n"/>
-      <c r="AB24" s="39" t="n"/>
-      <c r="AC24" s="40" t="n"/>
+      <c r="AA24" s="41" t="n"/>
+      <c r="AB24" s="41" t="n"/>
+      <c r="AC24" s="42" t="n"/>
       <c r="AD24" s="31" t="n"/>
-      <c r="AE24" s="39" t="n"/>
-      <c r="AF24" s="39" t="n"/>
-      <c r="AG24" s="40" t="n"/>
+      <c r="AE24" s="41" t="n"/>
+      <c r="AF24" s="41" t="n"/>
+      <c r="AG24" s="42" t="n"/>
       <c r="AH24" s="31" t="n"/>
-      <c r="AI24" s="39" t="n"/>
-      <c r="AJ24" s="39" t="n"/>
-      <c r="AK24" s="40" t="n"/>
-      <c r="AL24" s="61" t="inlineStr">
+      <c r="AI24" s="41" t="n"/>
+      <c r="AJ24" s="41" t="n"/>
+      <c r="AK24" s="42" t="n"/>
+      <c r="AL24" s="65" t="inlineStr">
         <is>
           <t>PLEASE NOTE: CSSI INDICATES
 THAT YOU MUST BE ON THE
 STATION DURING THIS TIME.</t>
         </is>
       </c>
-      <c r="AM24" s="62" t="n"/>
-      <c r="AN24" s="62" t="n"/>
-      <c r="AO24" s="62" t="n"/>
-      <c r="AP24" s="62" t="n"/>
-      <c r="AQ24" s="62" t="n"/>
-      <c r="AR24" s="62" t="n"/>
-      <c r="AS24" s="62" t="n"/>
-      <c r="AT24" s="62" t="n"/>
-      <c r="AU24" s="62" t="n"/>
-      <c r="AV24" s="62" t="n"/>
-      <c r="AW24" s="62" t="n"/>
-      <c r="AX24" s="62" t="n"/>
-      <c r="AY24" s="62" t="n"/>
-      <c r="AZ24" s="62" t="n"/>
-      <c r="BA24" s="62" t="n"/>
-      <c r="BB24" s="62" t="n"/>
-      <c r="BC24" s="62" t="n"/>
-      <c r="BD24" s="62" t="n"/>
-      <c r="BE24" s="63" t="n"/>
+      <c r="AM24" s="66" t="n"/>
+      <c r="AN24" s="66" t="n"/>
+      <c r="AO24" s="66" t="n"/>
+      <c r="AP24" s="66" t="n"/>
+      <c r="AQ24" s="66" t="n"/>
+      <c r="AR24" s="66" t="n"/>
+      <c r="AS24" s="66" t="n"/>
+      <c r="AT24" s="66" t="n"/>
+      <c r="AU24" s="66" t="n"/>
+      <c r="AV24" s="66" t="n"/>
+      <c r="AW24" s="66" t="n"/>
+      <c r="AX24" s="66" t="n"/>
+      <c r="AY24" s="66" t="n"/>
+      <c r="AZ24" s="66" t="n"/>
+      <c r="BA24" s="66" t="n"/>
+      <c r="BB24" s="66" t="n"/>
+      <c r="BC24" s="66" t="n"/>
+      <c r="BD24" s="66" t="n"/>
+      <c r="BE24" s="67" t="n"/>
       <c r="BF24" s="31" t="n"/>
-      <c r="BG24" s="39" t="n"/>
-      <c r="BH24" s="39" t="n"/>
-      <c r="BI24" s="40" t="n"/>
+      <c r="BG24" s="41" t="n"/>
+      <c r="BH24" s="41" t="n"/>
+      <c r="BI24" s="42" t="n"/>
       <c r="BJ24" s="31" t="n"/>
-      <c r="BK24" s="39" t="n"/>
-      <c r="BL24" s="39" t="n"/>
-      <c r="BM24" s="40" t="n"/>
+      <c r="BK24" s="41" t="n"/>
+      <c r="BL24" s="41" t="n"/>
+      <c r="BM24" s="42" t="n"/>
       <c r="BN24" s="31" t="n"/>
-      <c r="BO24" s="39" t="n"/>
-      <c r="BP24" s="39" t="n"/>
-      <c r="BQ24" s="40" t="n"/>
+      <c r="BO24" s="41" t="n"/>
+      <c r="BP24" s="41" t="n"/>
+      <c r="BQ24" s="42" t="n"/>
       <c r="BR24" s="31" t="n"/>
-      <c r="BS24" s="39" t="n"/>
-      <c r="BT24" s="39" t="n"/>
-      <c r="BU24" s="40" t="n"/>
+      <c r="BS24" s="41" t="n"/>
+      <c r="BT24" s="41" t="n"/>
+      <c r="BU24" s="42" t="n"/>
       <c r="BV24" s="31" t="n"/>
-      <c r="BW24" s="39" t="n"/>
-      <c r="BX24" s="39" t="n"/>
-      <c r="BY24" s="40" t="n"/>
+      <c r="BW24" s="41" t="n"/>
+      <c r="BX24" s="41" t="n"/>
+      <c r="BY24" s="42" t="n"/>
       <c r="BZ24" s="31" t="n"/>
-      <c r="CA24" s="39" t="n"/>
-      <c r="CB24" s="39" t="n"/>
-      <c r="CC24" s="40" t="n"/>
+      <c r="CA24" s="41" t="n"/>
+      <c r="CB24" s="41" t="n"/>
+      <c r="CC24" s="42" t="n"/>
       <c r="CD24" s="31" t="n"/>
-      <c r="CE24" s="39" t="n"/>
-      <c r="CF24" s="39" t="n"/>
-      <c r="CG24" s="50" t="n"/>
+      <c r="CE24" s="41" t="n"/>
+      <c r="CF24" s="41" t="n"/>
+      <c r="CG24" s="54" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="29" t="inlineStr"/>
@@ -4132,67 +4269,67 @@
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="30" t="n"/>
       <c r="F25" s="31" t="n"/>
-      <c r="G25" s="39" t="n"/>
-      <c r="H25" s="39" t="n"/>
-      <c r="I25" s="40" t="n"/>
+      <c r="G25" s="41" t="n"/>
+      <c r="H25" s="41" t="n"/>
+      <c r="I25" s="42" t="n"/>
       <c r="J25" s="31" t="n"/>
-      <c r="K25" s="39" t="n"/>
-      <c r="L25" s="39" t="n"/>
-      <c r="M25" s="40" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="41" t="n"/>
+      <c r="M25" s="42" t="n"/>
       <c r="N25" s="31" t="n"/>
-      <c r="O25" s="39" t="n"/>
-      <c r="P25" s="39" t="n"/>
-      <c r="Q25" s="40" t="n"/>
+      <c r="O25" s="41" t="n"/>
+      <c r="P25" s="41" t="n"/>
+      <c r="Q25" s="42" t="n"/>
       <c r="R25" s="31" t="n"/>
-      <c r="S25" s="39" t="n"/>
-      <c r="T25" s="39" t="n"/>
-      <c r="U25" s="40" t="n"/>
+      <c r="S25" s="41" t="n"/>
+      <c r="T25" s="41" t="n"/>
+      <c r="U25" s="42" t="n"/>
       <c r="V25" s="31" t="n"/>
-      <c r="W25" s="39" t="n"/>
-      <c r="X25" s="39" t="n"/>
-      <c r="Y25" s="40" t="n"/>
+      <c r="W25" s="41" t="n"/>
+      <c r="X25" s="41" t="n"/>
+      <c r="Y25" s="42" t="n"/>
       <c r="Z25" s="31" t="n"/>
-      <c r="AA25" s="39" t="n"/>
-      <c r="AB25" s="39" t="n"/>
-      <c r="AC25" s="40" t="n"/>
+      <c r="AA25" s="41" t="n"/>
+      <c r="AB25" s="41" t="n"/>
+      <c r="AC25" s="42" t="n"/>
       <c r="AD25" s="31" t="n"/>
-      <c r="AE25" s="39" t="n"/>
-      <c r="AF25" s="39" t="n"/>
-      <c r="AG25" s="40" t="n"/>
+      <c r="AE25" s="41" t="n"/>
+      <c r="AF25" s="41" t="n"/>
+      <c r="AG25" s="42" t="n"/>
       <c r="AH25" s="31" t="n"/>
-      <c r="AI25" s="39" t="n"/>
-      <c r="AJ25" s="39" t="n"/>
-      <c r="AK25" s="40" t="n"/>
-      <c r="AL25" s="64" t="n"/>
-      <c r="BE25" s="65" t="n"/>
+      <c r="AI25" s="41" t="n"/>
+      <c r="AJ25" s="41" t="n"/>
+      <c r="AK25" s="42" t="n"/>
+      <c r="AL25" s="68" t="n"/>
+      <c r="BE25" s="69" t="n"/>
       <c r="BF25" s="31" t="n"/>
-      <c r="BG25" s="39" t="n"/>
-      <c r="BH25" s="39" t="n"/>
-      <c r="BI25" s="40" t="n"/>
+      <c r="BG25" s="41" t="n"/>
+      <c r="BH25" s="41" t="n"/>
+      <c r="BI25" s="42" t="n"/>
       <c r="BJ25" s="31" t="n"/>
-      <c r="BK25" s="39" t="n"/>
-      <c r="BL25" s="39" t="n"/>
-      <c r="BM25" s="40" t="n"/>
+      <c r="BK25" s="41" t="n"/>
+      <c r="BL25" s="41" t="n"/>
+      <c r="BM25" s="42" t="n"/>
       <c r="BN25" s="31" t="n"/>
-      <c r="BO25" s="39" t="n"/>
-      <c r="BP25" s="39" t="n"/>
-      <c r="BQ25" s="40" t="n"/>
+      <c r="BO25" s="41" t="n"/>
+      <c r="BP25" s="41" t="n"/>
+      <c r="BQ25" s="42" t="n"/>
       <c r="BR25" s="31" t="n"/>
-      <c r="BS25" s="39" t="n"/>
-      <c r="BT25" s="39" t="n"/>
-      <c r="BU25" s="40" t="n"/>
+      <c r="BS25" s="41" t="n"/>
+      <c r="BT25" s="41" t="n"/>
+      <c r="BU25" s="42" t="n"/>
       <c r="BV25" s="31" t="n"/>
-      <c r="BW25" s="39" t="n"/>
-      <c r="BX25" s="39" t="n"/>
-      <c r="BY25" s="40" t="n"/>
+      <c r="BW25" s="41" t="n"/>
+      <c r="BX25" s="41" t="n"/>
+      <c r="BY25" s="42" t="n"/>
       <c r="BZ25" s="31" t="n"/>
-      <c r="CA25" s="39" t="n"/>
-      <c r="CB25" s="39" t="n"/>
-      <c r="CC25" s="40" t="n"/>
+      <c r="CA25" s="41" t="n"/>
+      <c r="CB25" s="41" t="n"/>
+      <c r="CC25" s="42" t="n"/>
       <c r="CD25" s="31" t="n"/>
-      <c r="CE25" s="39" t="n"/>
-      <c r="CF25" s="39" t="n"/>
-      <c r="CG25" s="50" t="n"/>
+      <c r="CE25" s="41" t="n"/>
+      <c r="CF25" s="41" t="n"/>
+      <c r="CG25" s="54" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="29" t="inlineStr"/>
@@ -4201,85 +4338,85 @@
       <c r="D26" s="30" t="n"/>
       <c r="E26" s="30" t="n"/>
       <c r="F26" s="31" t="n"/>
-      <c r="G26" s="39" t="n"/>
-      <c r="H26" s="39" t="n"/>
-      <c r="I26" s="40" t="n"/>
+      <c r="G26" s="41" t="n"/>
+      <c r="H26" s="41" t="n"/>
+      <c r="I26" s="42" t="n"/>
       <c r="J26" s="31" t="n"/>
-      <c r="K26" s="39" t="n"/>
-      <c r="L26" s="39" t="n"/>
-      <c r="M26" s="40" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="41" t="n"/>
+      <c r="M26" s="42" t="n"/>
       <c r="N26" s="31" t="n"/>
-      <c r="O26" s="39" t="n"/>
-      <c r="P26" s="39" t="n"/>
-      <c r="Q26" s="40" t="n"/>
+      <c r="O26" s="41" t="n"/>
+      <c r="P26" s="41" t="n"/>
+      <c r="Q26" s="42" t="n"/>
       <c r="R26" s="31" t="n"/>
-      <c r="S26" s="39" t="n"/>
-      <c r="T26" s="39" t="n"/>
-      <c r="U26" s="40" t="n"/>
+      <c r="S26" s="41" t="n"/>
+      <c r="T26" s="41" t="n"/>
+      <c r="U26" s="42" t="n"/>
       <c r="V26" s="31" t="n"/>
-      <c r="W26" s="39" t="n"/>
-      <c r="X26" s="39" t="n"/>
-      <c r="Y26" s="40" t="n"/>
+      <c r="W26" s="41" t="n"/>
+      <c r="X26" s="41" t="n"/>
+      <c r="Y26" s="42" t="n"/>
       <c r="Z26" s="31" t="n"/>
-      <c r="AA26" s="39" t="n"/>
-      <c r="AB26" s="39" t="n"/>
-      <c r="AC26" s="40" t="n"/>
+      <c r="AA26" s="41" t="n"/>
+      <c r="AB26" s="41" t="n"/>
+      <c r="AC26" s="42" t="n"/>
       <c r="AD26" s="31" t="n"/>
-      <c r="AE26" s="39" t="n"/>
-      <c r="AF26" s="39" t="n"/>
-      <c r="AG26" s="40" t="n"/>
+      <c r="AE26" s="41" t="n"/>
+      <c r="AF26" s="41" t="n"/>
+      <c r="AG26" s="42" t="n"/>
       <c r="AH26" s="31" t="n"/>
-      <c r="AI26" s="39" t="n"/>
-      <c r="AJ26" s="39" t="n"/>
-      <c r="AK26" s="40" t="n"/>
-      <c r="AL26" s="66" t="n"/>
-      <c r="AM26" s="67" t="n"/>
-      <c r="AN26" s="67" t="n"/>
-      <c r="AO26" s="67" t="n"/>
-      <c r="AP26" s="67" t="n"/>
-      <c r="AQ26" s="67" t="n"/>
-      <c r="AR26" s="67" t="n"/>
-      <c r="AS26" s="67" t="n"/>
-      <c r="AT26" s="67" t="n"/>
-      <c r="AU26" s="67" t="n"/>
-      <c r="AV26" s="67" t="n"/>
-      <c r="AW26" s="67" t="n"/>
-      <c r="AX26" s="67" t="n"/>
-      <c r="AY26" s="67" t="n"/>
-      <c r="AZ26" s="67" t="n"/>
-      <c r="BA26" s="67" t="n"/>
-      <c r="BB26" s="67" t="n"/>
-      <c r="BC26" s="67" t="n"/>
-      <c r="BD26" s="67" t="n"/>
-      <c r="BE26" s="68" t="n"/>
+      <c r="AI26" s="41" t="n"/>
+      <c r="AJ26" s="41" t="n"/>
+      <c r="AK26" s="42" t="n"/>
+      <c r="AL26" s="70" t="n"/>
+      <c r="AM26" s="71" t="n"/>
+      <c r="AN26" s="71" t="n"/>
+      <c r="AO26" s="71" t="n"/>
+      <c r="AP26" s="71" t="n"/>
+      <c r="AQ26" s="71" t="n"/>
+      <c r="AR26" s="71" t="n"/>
+      <c r="AS26" s="71" t="n"/>
+      <c r="AT26" s="71" t="n"/>
+      <c r="AU26" s="71" t="n"/>
+      <c r="AV26" s="71" t="n"/>
+      <c r="AW26" s="71" t="n"/>
+      <c r="AX26" s="71" t="n"/>
+      <c r="AY26" s="71" t="n"/>
+      <c r="AZ26" s="71" t="n"/>
+      <c r="BA26" s="71" t="n"/>
+      <c r="BB26" s="71" t="n"/>
+      <c r="BC26" s="71" t="n"/>
+      <c r="BD26" s="71" t="n"/>
+      <c r="BE26" s="72" t="n"/>
       <c r="BF26" s="31" t="n"/>
-      <c r="BG26" s="39" t="n"/>
-      <c r="BH26" s="39" t="n"/>
-      <c r="BI26" s="40" t="n"/>
+      <c r="BG26" s="41" t="n"/>
+      <c r="BH26" s="41" t="n"/>
+      <c r="BI26" s="42" t="n"/>
       <c r="BJ26" s="31" t="n"/>
-      <c r="BK26" s="39" t="n"/>
-      <c r="BL26" s="39" t="n"/>
-      <c r="BM26" s="40" t="n"/>
+      <c r="BK26" s="41" t="n"/>
+      <c r="BL26" s="41" t="n"/>
+      <c r="BM26" s="42" t="n"/>
       <c r="BN26" s="31" t="n"/>
-      <c r="BO26" s="39" t="n"/>
-      <c r="BP26" s="39" t="n"/>
-      <c r="BQ26" s="40" t="n"/>
+      <c r="BO26" s="41" t="n"/>
+      <c r="BP26" s="41" t="n"/>
+      <c r="BQ26" s="42" t="n"/>
       <c r="BR26" s="31" t="n"/>
-      <c r="BS26" s="39" t="n"/>
-      <c r="BT26" s="39" t="n"/>
-      <c r="BU26" s="40" t="n"/>
+      <c r="BS26" s="41" t="n"/>
+      <c r="BT26" s="41" t="n"/>
+      <c r="BU26" s="42" t="n"/>
       <c r="BV26" s="31" t="n"/>
-      <c r="BW26" s="39" t="n"/>
-      <c r="BX26" s="39" t="n"/>
-      <c r="BY26" s="40" t="n"/>
+      <c r="BW26" s="41" t="n"/>
+      <c r="BX26" s="41" t="n"/>
+      <c r="BY26" s="42" t="n"/>
       <c r="BZ26" s="31" t="n"/>
-      <c r="CA26" s="39" t="n"/>
-      <c r="CB26" s="39" t="n"/>
-      <c r="CC26" s="40" t="n"/>
+      <c r="CA26" s="41" t="n"/>
+      <c r="CB26" s="41" t="n"/>
+      <c r="CC26" s="42" t="n"/>
       <c r="CD26" s="31" t="n"/>
-      <c r="CE26" s="39" t="n"/>
-      <c r="CF26" s="39" t="n"/>
-      <c r="CG26" s="50" t="n"/>
+      <c r="CE26" s="41" t="n"/>
+      <c r="CF26" s="41" t="n"/>
+      <c r="CG26" s="54" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="29" t="inlineStr"/>
@@ -4288,172 +4425,172 @@
       <c r="D27" s="30" t="n"/>
       <c r="E27" s="30" t="n"/>
       <c r="F27" s="31" t="n"/>
-      <c r="G27" s="39" t="n"/>
-      <c r="H27" s="39" t="n"/>
-      <c r="I27" s="40" t="n"/>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="41" t="n"/>
+      <c r="I27" s="42" t="n"/>
       <c r="J27" s="31" t="n"/>
-      <c r="K27" s="39" t="n"/>
-      <c r="L27" s="39" t="n"/>
-      <c r="M27" s="40" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="41" t="n"/>
+      <c r="M27" s="42" t="n"/>
       <c r="N27" s="31" t="n"/>
-      <c r="O27" s="39" t="n"/>
-      <c r="P27" s="39" t="n"/>
-      <c r="Q27" s="40" t="n"/>
+      <c r="O27" s="41" t="n"/>
+      <c r="P27" s="41" t="n"/>
+      <c r="Q27" s="42" t="n"/>
       <c r="R27" s="31" t="n"/>
-      <c r="S27" s="39" t="n"/>
-      <c r="T27" s="39" t="n"/>
-      <c r="U27" s="40" t="n"/>
+      <c r="S27" s="41" t="n"/>
+      <c r="T27" s="41" t="n"/>
+      <c r="U27" s="42" t="n"/>
       <c r="V27" s="31" t="n"/>
-      <c r="W27" s="39" t="n"/>
-      <c r="X27" s="39" t="n"/>
-      <c r="Y27" s="40" t="n"/>
+      <c r="W27" s="41" t="n"/>
+      <c r="X27" s="41" t="n"/>
+      <c r="Y27" s="42" t="n"/>
       <c r="Z27" s="31" t="n"/>
-      <c r="AA27" s="39" t="n"/>
-      <c r="AB27" s="39" t="n"/>
-      <c r="AC27" s="40" t="n"/>
+      <c r="AA27" s="41" t="n"/>
+      <c r="AB27" s="41" t="n"/>
+      <c r="AC27" s="42" t="n"/>
       <c r="AD27" s="31" t="n"/>
-      <c r="AE27" s="39" t="n"/>
-      <c r="AF27" s="39" t="n"/>
-      <c r="AG27" s="40" t="n"/>
+      <c r="AE27" s="41" t="n"/>
+      <c r="AF27" s="41" t="n"/>
+      <c r="AG27" s="42" t="n"/>
       <c r="AH27" s="31" t="n"/>
-      <c r="AI27" s="39" t="n"/>
-      <c r="AJ27" s="39" t="n"/>
-      <c r="AK27" s="40" t="n"/>
+      <c r="AI27" s="41" t="n"/>
+      <c r="AJ27" s="41" t="n"/>
+      <c r="AK27" s="42" t="n"/>
       <c r="AL27" s="31" t="n"/>
-      <c r="AM27" s="39" t="n"/>
-      <c r="AN27" s="39" t="n"/>
-      <c r="AO27" s="40" t="n"/>
+      <c r="AM27" s="41" t="n"/>
+      <c r="AN27" s="41" t="n"/>
+      <c r="AO27" s="42" t="n"/>
       <c r="AP27" s="31" t="n"/>
-      <c r="AQ27" s="39" t="n"/>
-      <c r="AR27" s="39" t="n"/>
-      <c r="AS27" s="40" t="n"/>
+      <c r="AQ27" s="41" t="n"/>
+      <c r="AR27" s="41" t="n"/>
+      <c r="AS27" s="42" t="n"/>
       <c r="AT27" s="31" t="n"/>
-      <c r="AU27" s="39" t="n"/>
-      <c r="AV27" s="39" t="n"/>
-      <c r="AW27" s="40" t="n"/>
+      <c r="AU27" s="41" t="n"/>
+      <c r="AV27" s="41" t="n"/>
+      <c r="AW27" s="42" t="n"/>
       <c r="AX27" s="31" t="n"/>
-      <c r="AY27" s="39" t="n"/>
-      <c r="AZ27" s="39" t="n"/>
-      <c r="BA27" s="40" t="n"/>
+      <c r="AY27" s="41" t="n"/>
+      <c r="AZ27" s="41" t="n"/>
+      <c r="BA27" s="42" t="n"/>
       <c r="BB27" s="31" t="n"/>
-      <c r="BC27" s="39" t="n"/>
-      <c r="BD27" s="39" t="n"/>
-      <c r="BE27" s="40" t="n"/>
+      <c r="BC27" s="41" t="n"/>
+      <c r="BD27" s="41" t="n"/>
+      <c r="BE27" s="42" t="n"/>
       <c r="BF27" s="31" t="n"/>
-      <c r="BG27" s="39" t="n"/>
-      <c r="BH27" s="39" t="n"/>
-      <c r="BI27" s="40" t="n"/>
+      <c r="BG27" s="41" t="n"/>
+      <c r="BH27" s="41" t="n"/>
+      <c r="BI27" s="42" t="n"/>
       <c r="BJ27" s="31" t="n"/>
-      <c r="BK27" s="39" t="n"/>
-      <c r="BL27" s="39" t="n"/>
-      <c r="BM27" s="40" t="n"/>
+      <c r="BK27" s="41" t="n"/>
+      <c r="BL27" s="41" t="n"/>
+      <c r="BM27" s="42" t="n"/>
       <c r="BN27" s="31" t="n"/>
-      <c r="BO27" s="39" t="n"/>
-      <c r="BP27" s="39" t="n"/>
-      <c r="BQ27" s="40" t="n"/>
+      <c r="BO27" s="41" t="n"/>
+      <c r="BP27" s="41" t="n"/>
+      <c r="BQ27" s="42" t="n"/>
       <c r="BR27" s="31" t="n"/>
-      <c r="BS27" s="39" t="n"/>
-      <c r="BT27" s="39" t="n"/>
-      <c r="BU27" s="40" t="n"/>
+      <c r="BS27" s="41" t="n"/>
+      <c r="BT27" s="41" t="n"/>
+      <c r="BU27" s="42" t="n"/>
       <c r="BV27" s="31" t="n"/>
-      <c r="BW27" s="39" t="n"/>
-      <c r="BX27" s="39" t="n"/>
-      <c r="BY27" s="40" t="n"/>
+      <c r="BW27" s="41" t="n"/>
+      <c r="BX27" s="41" t="n"/>
+      <c r="BY27" s="42" t="n"/>
       <c r="BZ27" s="31" t="n"/>
-      <c r="CA27" s="39" t="n"/>
-      <c r="CB27" s="39" t="n"/>
-      <c r="CC27" s="40" t="n"/>
+      <c r="CA27" s="41" t="n"/>
+      <c r="CB27" s="41" t="n"/>
+      <c r="CC27" s="42" t="n"/>
       <c r="CD27" s="31" t="n"/>
-      <c r="CE27" s="39" t="n"/>
-      <c r="CF27" s="39" t="n"/>
-      <c r="CG27" s="50" t="n"/>
+      <c r="CE27" s="41" t="n"/>
+      <c r="CF27" s="41" t="n"/>
+      <c r="CG27" s="54" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="69" t="inlineStr"/>
-      <c r="B28" s="70" t="n"/>
-      <c r="C28" s="70" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="71" t="n"/>
-      <c r="G28" s="72" t="n"/>
-      <c r="H28" s="72" t="n"/>
-      <c r="I28" s="73" t="n"/>
-      <c r="J28" s="71" t="n"/>
-      <c r="K28" s="72" t="n"/>
-      <c r="L28" s="72" t="n"/>
-      <c r="M28" s="73" t="n"/>
-      <c r="N28" s="71" t="n"/>
-      <c r="O28" s="72" t="n"/>
-      <c r="P28" s="72" t="n"/>
-      <c r="Q28" s="73" t="n"/>
-      <c r="R28" s="71" t="n"/>
-      <c r="S28" s="72" t="n"/>
-      <c r="T28" s="72" t="n"/>
-      <c r="U28" s="73" t="n"/>
-      <c r="V28" s="71" t="n"/>
-      <c r="W28" s="72" t="n"/>
-      <c r="X28" s="72" t="n"/>
-      <c r="Y28" s="73" t="n"/>
-      <c r="Z28" s="71" t="n"/>
-      <c r="AA28" s="72" t="n"/>
-      <c r="AB28" s="72" t="n"/>
-      <c r="AC28" s="73" t="n"/>
-      <c r="AD28" s="71" t="n"/>
-      <c r="AE28" s="72" t="n"/>
-      <c r="AF28" s="72" t="n"/>
-      <c r="AG28" s="73" t="n"/>
-      <c r="AH28" s="71" t="n"/>
-      <c r="AI28" s="72" t="n"/>
-      <c r="AJ28" s="72" t="n"/>
-      <c r="AK28" s="73" t="n"/>
-      <c r="AL28" s="71" t="n"/>
-      <c r="AM28" s="72" t="n"/>
-      <c r="AN28" s="72" t="n"/>
-      <c r="AO28" s="73" t="n"/>
-      <c r="AP28" s="71" t="n"/>
-      <c r="AQ28" s="72" t="n"/>
-      <c r="AR28" s="72" t="n"/>
-      <c r="AS28" s="73" t="n"/>
-      <c r="AT28" s="71" t="n"/>
-      <c r="AU28" s="72" t="n"/>
-      <c r="AV28" s="72" t="n"/>
-      <c r="AW28" s="73" t="n"/>
-      <c r="AX28" s="71" t="n"/>
-      <c r="AY28" s="72" t="n"/>
-      <c r="AZ28" s="72" t="n"/>
-      <c r="BA28" s="73" t="n"/>
-      <c r="BB28" s="71" t="n"/>
-      <c r="BC28" s="72" t="n"/>
-      <c r="BD28" s="72" t="n"/>
-      <c r="BE28" s="73" t="n"/>
-      <c r="BF28" s="71" t="n"/>
-      <c r="BG28" s="72" t="n"/>
-      <c r="BH28" s="72" t="n"/>
-      <c r="BI28" s="73" t="n"/>
-      <c r="BJ28" s="71" t="n"/>
-      <c r="BK28" s="72" t="n"/>
-      <c r="BL28" s="72" t="n"/>
-      <c r="BM28" s="73" t="n"/>
-      <c r="BN28" s="71" t="n"/>
-      <c r="BO28" s="72" t="n"/>
-      <c r="BP28" s="72" t="n"/>
-      <c r="BQ28" s="73" t="n"/>
-      <c r="BR28" s="71" t="n"/>
-      <c r="BS28" s="72" t="n"/>
-      <c r="BT28" s="72" t="n"/>
-      <c r="BU28" s="73" t="n"/>
-      <c r="BV28" s="71" t="n"/>
-      <c r="BW28" s="72" t="n"/>
-      <c r="BX28" s="72" t="n"/>
-      <c r="BY28" s="73" t="n"/>
-      <c r="BZ28" s="71" t="n"/>
-      <c r="CA28" s="72" t="n"/>
-      <c r="CB28" s="72" t="n"/>
-      <c r="CC28" s="73" t="n"/>
-      <c r="CD28" s="71" t="n"/>
-      <c r="CE28" s="72" t="n"/>
-      <c r="CF28" s="72" t="n"/>
-      <c r="CG28" s="74" t="n"/>
+      <c r="A28" s="73" t="inlineStr"/>
+      <c r="B28" s="74" t="n"/>
+      <c r="C28" s="74" t="n"/>
+      <c r="D28" s="74" t="n"/>
+      <c r="E28" s="74" t="n"/>
+      <c r="F28" s="75" t="n"/>
+      <c r="G28" s="76" t="n"/>
+      <c r="H28" s="76" t="n"/>
+      <c r="I28" s="77" t="n"/>
+      <c r="J28" s="75" t="n"/>
+      <c r="K28" s="76" t="n"/>
+      <c r="L28" s="76" t="n"/>
+      <c r="M28" s="77" t="n"/>
+      <c r="N28" s="75" t="n"/>
+      <c r="O28" s="76" t="n"/>
+      <c r="P28" s="76" t="n"/>
+      <c r="Q28" s="77" t="n"/>
+      <c r="R28" s="75" t="n"/>
+      <c r="S28" s="76" t="n"/>
+      <c r="T28" s="76" t="n"/>
+      <c r="U28" s="77" t="n"/>
+      <c r="V28" s="75" t="n"/>
+      <c r="W28" s="76" t="n"/>
+      <c r="X28" s="76" t="n"/>
+      <c r="Y28" s="77" t="n"/>
+      <c r="Z28" s="75" t="n"/>
+      <c r="AA28" s="76" t="n"/>
+      <c r="AB28" s="76" t="n"/>
+      <c r="AC28" s="77" t="n"/>
+      <c r="AD28" s="75" t="n"/>
+      <c r="AE28" s="76" t="n"/>
+      <c r="AF28" s="76" t="n"/>
+      <c r="AG28" s="77" t="n"/>
+      <c r="AH28" s="75" t="n"/>
+      <c r="AI28" s="76" t="n"/>
+      <c r="AJ28" s="76" t="n"/>
+      <c r="AK28" s="77" t="n"/>
+      <c r="AL28" s="75" t="n"/>
+      <c r="AM28" s="76" t="n"/>
+      <c r="AN28" s="76" t="n"/>
+      <c r="AO28" s="77" t="n"/>
+      <c r="AP28" s="75" t="n"/>
+      <c r="AQ28" s="76" t="n"/>
+      <c r="AR28" s="76" t="n"/>
+      <c r="AS28" s="77" t="n"/>
+      <c r="AT28" s="75" t="n"/>
+      <c r="AU28" s="76" t="n"/>
+      <c r="AV28" s="76" t="n"/>
+      <c r="AW28" s="77" t="n"/>
+      <c r="AX28" s="75" t="n"/>
+      <c r="AY28" s="76" t="n"/>
+      <c r="AZ28" s="76" t="n"/>
+      <c r="BA28" s="77" t="n"/>
+      <c r="BB28" s="75" t="n"/>
+      <c r="BC28" s="76" t="n"/>
+      <c r="BD28" s="76" t="n"/>
+      <c r="BE28" s="77" t="n"/>
+      <c r="BF28" s="75" t="n"/>
+      <c r="BG28" s="76" t="n"/>
+      <c r="BH28" s="76" t="n"/>
+      <c r="BI28" s="77" t="n"/>
+      <c r="BJ28" s="75" t="n"/>
+      <c r="BK28" s="76" t="n"/>
+      <c r="BL28" s="76" t="n"/>
+      <c r="BM28" s="77" t="n"/>
+      <c r="BN28" s="75" t="n"/>
+      <c r="BO28" s="76" t="n"/>
+      <c r="BP28" s="76" t="n"/>
+      <c r="BQ28" s="77" t="n"/>
+      <c r="BR28" s="75" t="n"/>
+      <c r="BS28" s="76" t="n"/>
+      <c r="BT28" s="76" t="n"/>
+      <c r="BU28" s="77" t="n"/>
+      <c r="BV28" s="75" t="n"/>
+      <c r="BW28" s="76" t="n"/>
+      <c r="BX28" s="76" t="n"/>
+      <c r="BY28" s="77" t="n"/>
+      <c r="BZ28" s="75" t="n"/>
+      <c r="CA28" s="76" t="n"/>
+      <c r="CB28" s="76" t="n"/>
+      <c r="CC28" s="77" t="n"/>
+      <c r="CD28" s="75" t="n"/>
+      <c r="CE28" s="76" t="n"/>
+      <c r="CF28" s="76" t="n"/>
+      <c r="CG28" s="78" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -4623,111 +4760,111 @@
       <c r="CG30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="75" t="inlineStr">
+      <c r="A31" s="79" t="inlineStr">
         <is>
           <t>Duty No.</t>
         </is>
       </c>
-      <c r="B31" s="76" t="inlineStr">
+      <c r="B31" s="80" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="C31" s="76" t="inlineStr">
+      <c r="C31" s="80" t="inlineStr">
         <is>
           <t>Finish Time</t>
         </is>
       </c>
-      <c r="D31" s="76" t="inlineStr">
+      <c r="D31" s="80" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E31" s="76" t="inlineStr">
+      <c r="E31" s="80" t="inlineStr">
         <is>
           <t>Radio</t>
         </is>
       </c>
-      <c r="F31" s="77" t="n"/>
-      <c r="G31" s="78" t="n"/>
-      <c r="H31" s="78" t="n"/>
-      <c r="I31" s="79" t="n"/>
-      <c r="J31" s="77" t="n"/>
-      <c r="K31" s="78" t="n"/>
-      <c r="L31" s="78" t="n"/>
-      <c r="M31" s="79" t="n"/>
-      <c r="N31" s="77" t="n"/>
-      <c r="O31" s="78" t="n"/>
-      <c r="P31" s="78" t="n"/>
-      <c r="Q31" s="79" t="n"/>
-      <c r="R31" s="77" t="n"/>
-      <c r="S31" s="78" t="n"/>
-      <c r="T31" s="78" t="n"/>
-      <c r="U31" s="79" t="n"/>
-      <c r="V31" s="77" t="n"/>
-      <c r="W31" s="78" t="n"/>
-      <c r="X31" s="78" t="n"/>
-      <c r="Y31" s="79" t="n"/>
-      <c r="Z31" s="77" t="n"/>
-      <c r="AA31" s="78" t="n"/>
-      <c r="AB31" s="78" t="n"/>
-      <c r="AC31" s="79" t="n"/>
-      <c r="AD31" s="77" t="n"/>
-      <c r="AE31" s="78" t="n"/>
-      <c r="AF31" s="78" t="n"/>
-      <c r="AG31" s="79" t="n"/>
-      <c r="AH31" s="77" t="n"/>
-      <c r="AI31" s="78" t="n"/>
-      <c r="AJ31" s="78" t="n"/>
-      <c r="AK31" s="79" t="n"/>
-      <c r="AL31" s="77" t="n"/>
-      <c r="AM31" s="78" t="n"/>
-      <c r="AN31" s="78" t="n"/>
-      <c r="AO31" s="79" t="n"/>
-      <c r="AP31" s="77" t="n"/>
-      <c r="AQ31" s="78" t="n"/>
-      <c r="AR31" s="78" t="n"/>
-      <c r="AS31" s="79" t="n"/>
-      <c r="AT31" s="77" t="n"/>
-      <c r="AU31" s="78" t="n"/>
-      <c r="AV31" s="78" t="n"/>
-      <c r="AW31" s="79" t="n"/>
-      <c r="AX31" s="77" t="n"/>
-      <c r="AY31" s="78" t="n"/>
-      <c r="AZ31" s="78" t="n"/>
-      <c r="BA31" s="79" t="n"/>
-      <c r="BB31" s="77" t="n"/>
-      <c r="BC31" s="78" t="n"/>
-      <c r="BD31" s="78" t="n"/>
-      <c r="BE31" s="79" t="n"/>
-      <c r="BF31" s="77" t="n"/>
-      <c r="BG31" s="78" t="n"/>
-      <c r="BH31" s="78" t="n"/>
-      <c r="BI31" s="79" t="n"/>
-      <c r="BJ31" s="77" t="n"/>
-      <c r="BK31" s="78" t="n"/>
-      <c r="BL31" s="78" t="n"/>
-      <c r="BM31" s="79" t="n"/>
-      <c r="BN31" s="77" t="n"/>
-      <c r="BO31" s="78" t="n"/>
-      <c r="BP31" s="78" t="n"/>
-      <c r="BQ31" s="79" t="n"/>
-      <c r="BR31" s="77" t="n"/>
-      <c r="BS31" s="78" t="n"/>
-      <c r="BT31" s="78" t="n"/>
-      <c r="BU31" s="79" t="n"/>
-      <c r="BV31" s="77" t="n"/>
-      <c r="BW31" s="78" t="n"/>
-      <c r="BX31" s="78" t="n"/>
-      <c r="BY31" s="79" t="n"/>
-      <c r="BZ31" s="77" t="n"/>
-      <c r="CA31" s="78" t="n"/>
-      <c r="CB31" s="78" t="n"/>
-      <c r="CC31" s="79" t="n"/>
-      <c r="CD31" s="77" t="n"/>
-      <c r="CE31" s="78" t="n"/>
-      <c r="CF31" s="78" t="n"/>
-      <c r="CG31" s="80" t="n"/>
+      <c r="F31" s="81" t="n"/>
+      <c r="G31" s="82" t="n"/>
+      <c r="H31" s="82" t="n"/>
+      <c r="I31" s="83" t="n"/>
+      <c r="J31" s="81" t="n"/>
+      <c r="K31" s="82" t="n"/>
+      <c r="L31" s="82" t="n"/>
+      <c r="M31" s="83" t="n"/>
+      <c r="N31" s="81" t="n"/>
+      <c r="O31" s="82" t="n"/>
+      <c r="P31" s="82" t="n"/>
+      <c r="Q31" s="83" t="n"/>
+      <c r="R31" s="81" t="n"/>
+      <c r="S31" s="82" t="n"/>
+      <c r="T31" s="82" t="n"/>
+      <c r="U31" s="83" t="n"/>
+      <c r="V31" s="81" t="n"/>
+      <c r="W31" s="82" t="n"/>
+      <c r="X31" s="82" t="n"/>
+      <c r="Y31" s="83" t="n"/>
+      <c r="Z31" s="81" t="n"/>
+      <c r="AA31" s="82" t="n"/>
+      <c r="AB31" s="82" t="n"/>
+      <c r="AC31" s="83" t="n"/>
+      <c r="AD31" s="81" t="n"/>
+      <c r="AE31" s="82" t="n"/>
+      <c r="AF31" s="82" t="n"/>
+      <c r="AG31" s="83" t="n"/>
+      <c r="AH31" s="81" t="n"/>
+      <c r="AI31" s="82" t="n"/>
+      <c r="AJ31" s="82" t="n"/>
+      <c r="AK31" s="83" t="n"/>
+      <c r="AL31" s="81" t="n"/>
+      <c r="AM31" s="82" t="n"/>
+      <c r="AN31" s="82" t="n"/>
+      <c r="AO31" s="83" t="n"/>
+      <c r="AP31" s="81" t="n"/>
+      <c r="AQ31" s="82" t="n"/>
+      <c r="AR31" s="82" t="n"/>
+      <c r="AS31" s="83" t="n"/>
+      <c r="AT31" s="81" t="n"/>
+      <c r="AU31" s="82" t="n"/>
+      <c r="AV31" s="82" t="n"/>
+      <c r="AW31" s="83" t="n"/>
+      <c r="AX31" s="81" t="n"/>
+      <c r="AY31" s="82" t="n"/>
+      <c r="AZ31" s="82" t="n"/>
+      <c r="BA31" s="83" t="n"/>
+      <c r="BB31" s="81" t="n"/>
+      <c r="BC31" s="82" t="n"/>
+      <c r="BD31" s="82" t="n"/>
+      <c r="BE31" s="83" t="n"/>
+      <c r="BF31" s="81" t="n"/>
+      <c r="BG31" s="82" t="n"/>
+      <c r="BH31" s="82" t="n"/>
+      <c r="BI31" s="83" t="n"/>
+      <c r="BJ31" s="81" t="n"/>
+      <c r="BK31" s="82" t="n"/>
+      <c r="BL31" s="82" t="n"/>
+      <c r="BM31" s="83" t="n"/>
+      <c r="BN31" s="81" t="n"/>
+      <c r="BO31" s="82" t="n"/>
+      <c r="BP31" s="82" t="n"/>
+      <c r="BQ31" s="83" t="n"/>
+      <c r="BR31" s="81" t="n"/>
+      <c r="BS31" s="82" t="n"/>
+      <c r="BT31" s="82" t="n"/>
+      <c r="BU31" s="83" t="n"/>
+      <c r="BV31" s="81" t="n"/>
+      <c r="BW31" s="82" t="n"/>
+      <c r="BX31" s="82" t="n"/>
+      <c r="BY31" s="83" t="n"/>
+      <c r="BZ31" s="81" t="n"/>
+      <c r="CA31" s="82" t="n"/>
+      <c r="CB31" s="82" t="n"/>
+      <c r="CC31" s="83" t="n"/>
+      <c r="CD31" s="81" t="n"/>
+      <c r="CE31" s="82" t="n"/>
+      <c r="CF31" s="82" t="n"/>
+      <c r="CG31" s="84" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
@@ -4756,97 +4893,101 @@
         </is>
       </c>
       <c r="F32" s="31" t="n"/>
-      <c r="G32" s="81" t="n"/>
+      <c r="G32" s="85" t="n"/>
       <c r="H32" s="33" t="n"/>
       <c r="I32" s="34" t="n"/>
-      <c r="J32" s="82" t="n"/>
+      <c r="J32" s="86" t="n"/>
       <c r="K32" s="33" t="n"/>
       <c r="L32" s="33" t="n"/>
       <c r="M32" s="34" t="n"/>
-      <c r="N32" s="82" t="n"/>
+      <c r="N32" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="O32" s="33" t="n"/>
       <c r="P32" s="33" t="n"/>
       <c r="Q32" s="34" t="n"/>
-      <c r="R32" s="82" t="n"/>
+      <c r="R32" s="86" t="n"/>
       <c r="S32" s="33" t="n"/>
       <c r="T32" s="33" t="n"/>
       <c r="U32" s="34" t="n"/>
-      <c r="V32" s="56" t="inlineStr">
+      <c r="V32" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="W32" s="33" t="n"/>
-      <c r="X32" s="57" t="inlineStr">
+      <c r="X32" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="Y32" s="34" t="n"/>
-      <c r="Z32" s="82" t="n"/>
+      <c r="Z32" s="86" t="n"/>
       <c r="AA32" s="33" t="n"/>
       <c r="AB32" s="33" t="n"/>
       <c r="AC32" s="34" t="n"/>
-      <c r="AD32" s="82" t="n"/>
+      <c r="AD32" s="86" t="n"/>
       <c r="AE32" s="33" t="n"/>
       <c r="AF32" s="33" t="n"/>
       <c r="AG32" s="34" t="n"/>
-      <c r="AH32" s="83" t="n"/>
+      <c r="AH32" s="87" t="n"/>
       <c r="AI32" s="33" t="n"/>
-      <c r="AJ32" s="39" t="n"/>
-      <c r="AK32" s="40" t="n"/>
+      <c r="AJ32" s="41" t="n"/>
+      <c r="AK32" s="42" t="n"/>
       <c r="AL32" s="31" t="n"/>
-      <c r="AM32" s="39" t="n"/>
-      <c r="AN32" s="39" t="n"/>
-      <c r="AO32" s="40" t="n"/>
+      <c r="AM32" s="41" t="n"/>
+      <c r="AN32" s="41" t="n"/>
+      <c r="AO32" s="42" t="n"/>
       <c r="AP32" s="31" t="n"/>
-      <c r="AQ32" s="39" t="n"/>
-      <c r="AR32" s="39" t="n"/>
-      <c r="AS32" s="40" t="n"/>
+      <c r="AQ32" s="41" t="n"/>
+      <c r="AR32" s="41" t="n"/>
+      <c r="AS32" s="42" t="n"/>
       <c r="AT32" s="31" t="n"/>
-      <c r="AU32" s="39" t="n"/>
-      <c r="AV32" s="39" t="n"/>
-      <c r="AW32" s="40" t="n"/>
+      <c r="AU32" s="41" t="n"/>
+      <c r="AV32" s="41" t="n"/>
+      <c r="AW32" s="42" t="n"/>
       <c r="AX32" s="31" t="n"/>
-      <c r="AY32" s="39" t="n"/>
-      <c r="AZ32" s="39" t="n"/>
-      <c r="BA32" s="40" t="n"/>
+      <c r="AY32" s="41" t="n"/>
+      <c r="AZ32" s="41" t="n"/>
+      <c r="BA32" s="42" t="n"/>
       <c r="BB32" s="31" t="n"/>
-      <c r="BC32" s="39" t="n"/>
-      <c r="BD32" s="39" t="n"/>
-      <c r="BE32" s="40" t="n"/>
+      <c r="BC32" s="41" t="n"/>
+      <c r="BD32" s="41" t="n"/>
+      <c r="BE32" s="42" t="n"/>
       <c r="BF32" s="31" t="n"/>
-      <c r="BG32" s="39" t="n"/>
-      <c r="BH32" s="39" t="n"/>
-      <c r="BI32" s="40" t="n"/>
-      <c r="BJ32" s="84" t="inlineStr">
+      <c r="BG32" s="41" t="n"/>
+      <c r="BH32" s="41" t="n"/>
+      <c r="BI32" s="42" t="n"/>
+      <c r="BJ32" s="88" t="inlineStr">
         <is>
           <t>DISTRICT</t>
         </is>
       </c>
-      <c r="BK32" s="85" t="n"/>
-      <c r="BL32" s="85" t="n"/>
-      <c r="BM32" s="85" t="n"/>
-      <c r="BN32" s="85" t="n"/>
-      <c r="BO32" s="85" t="n"/>
-      <c r="BP32" s="85" t="n"/>
-      <c r="BQ32" s="85" t="n"/>
-      <c r="BR32" s="85" t="n"/>
-      <c r="BS32" s="85" t="n"/>
-      <c r="BT32" s="85" t="n"/>
-      <c r="BU32" s="85" t="n"/>
-      <c r="BV32" s="85" t="n"/>
-      <c r="BW32" s="85" t="n"/>
-      <c r="BX32" s="85" t="n"/>
-      <c r="BY32" s="85" t="n"/>
-      <c r="BZ32" s="85" t="n"/>
-      <c r="CA32" s="85" t="n"/>
-      <c r="CB32" s="85" t="n"/>
-      <c r="CC32" s="85" t="n"/>
-      <c r="CD32" s="85" t="n"/>
-      <c r="CE32" s="85" t="n"/>
-      <c r="CF32" s="85" t="n"/>
-      <c r="CG32" s="86" t="n"/>
+      <c r="BK32" s="89" t="n"/>
+      <c r="BL32" s="89" t="n"/>
+      <c r="BM32" s="89" t="n"/>
+      <c r="BN32" s="89" t="n"/>
+      <c r="BO32" s="89" t="n"/>
+      <c r="BP32" s="89" t="n"/>
+      <c r="BQ32" s="89" t="n"/>
+      <c r="BR32" s="89" t="n"/>
+      <c r="BS32" s="89" t="n"/>
+      <c r="BT32" s="89" t="n"/>
+      <c r="BU32" s="89" t="n"/>
+      <c r="BV32" s="89" t="n"/>
+      <c r="BW32" s="89" t="n"/>
+      <c r="BX32" s="89" t="n"/>
+      <c r="BY32" s="89" t="n"/>
+      <c r="BZ32" s="89" t="n"/>
+      <c r="CA32" s="89" t="n"/>
+      <c r="CB32" s="89" t="n"/>
+      <c r="CC32" s="89" t="n"/>
+      <c r="CD32" s="89" t="n"/>
+      <c r="CE32" s="89" t="n"/>
+      <c r="CF32" s="89" t="n"/>
+      <c r="CG32" s="90" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="29" t="inlineStr">
@@ -4875,97 +5016,101 @@
         </is>
       </c>
       <c r="F33" s="31" t="n"/>
-      <c r="G33" s="87" t="n"/>
+      <c r="G33" s="91" t="n"/>
       <c r="H33" s="33" t="n"/>
       <c r="I33" s="34" t="n"/>
-      <c r="J33" s="88" t="n"/>
+      <c r="J33" s="92" t="n"/>
       <c r="K33" s="33" t="n"/>
       <c r="L33" s="33" t="n"/>
       <c r="M33" s="34" t="n"/>
-      <c r="N33" s="88" t="n"/>
+      <c r="N33" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="O33" s="33" t="n"/>
       <c r="P33" s="33" t="n"/>
       <c r="Q33" s="34" t="n"/>
-      <c r="R33" s="88" t="n"/>
+      <c r="R33" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="S33" s="33" t="n"/>
       <c r="T33" s="33" t="n"/>
       <c r="U33" s="34" t="n"/>
-      <c r="V33" s="56" t="inlineStr">
+      <c r="V33" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="W33" s="33" t="n"/>
-      <c r="X33" s="57" t="inlineStr">
+      <c r="X33" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="Y33" s="34" t="n"/>
-      <c r="Z33" s="88" t="n"/>
+      <c r="Z33" s="92" t="n"/>
       <c r="AA33" s="33" t="n"/>
       <c r="AB33" s="33" t="n"/>
       <c r="AC33" s="34" t="n"/>
-      <c r="AD33" s="88" t="n"/>
+      <c r="AD33" s="92" t="n"/>
       <c r="AE33" s="33" t="n"/>
       <c r="AF33" s="33" t="n"/>
       <c r="AG33" s="34" t="n"/>
-      <c r="AH33" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AH33" s="92" t="n"/>
       <c r="AI33" s="33" t="n"/>
       <c r="AJ33" s="33" t="n"/>
       <c r="AK33" s="34" t="n"/>
       <c r="AL33" s="31" t="n"/>
-      <c r="AM33" s="39" t="n"/>
-      <c r="AN33" s="39" t="n"/>
-      <c r="AO33" s="40" t="n"/>
+      <c r="AM33" s="41" t="n"/>
+      <c r="AN33" s="41" t="n"/>
+      <c r="AO33" s="42" t="n"/>
       <c r="AP33" s="31" t="n"/>
-      <c r="AQ33" s="39" t="n"/>
-      <c r="AR33" s="39" t="n"/>
-      <c r="AS33" s="40" t="n"/>
+      <c r="AQ33" s="41" t="n"/>
+      <c r="AR33" s="41" t="n"/>
+      <c r="AS33" s="42" t="n"/>
       <c r="AT33" s="31" t="n"/>
-      <c r="AU33" s="39" t="n"/>
-      <c r="AV33" s="39" t="n"/>
-      <c r="AW33" s="40" t="n"/>
+      <c r="AU33" s="41" t="n"/>
+      <c r="AV33" s="41" t="n"/>
+      <c r="AW33" s="42" t="n"/>
       <c r="AX33" s="31" t="n"/>
-      <c r="AY33" s="39" t="n"/>
-      <c r="AZ33" s="39" t="n"/>
-      <c r="BA33" s="40" t="n"/>
+      <c r="AY33" s="41" t="n"/>
+      <c r="AZ33" s="41" t="n"/>
+      <c r="BA33" s="42" t="n"/>
       <c r="BB33" s="31" t="n"/>
-      <c r="BC33" s="39" t="n"/>
-      <c r="BD33" s="39" t="n"/>
-      <c r="BE33" s="40" t="n"/>
+      <c r="BC33" s="41" t="n"/>
+      <c r="BD33" s="41" t="n"/>
+      <c r="BE33" s="42" t="n"/>
       <c r="BF33" s="31" t="n"/>
-      <c r="BG33" s="39" t="n"/>
-      <c r="BH33" s="39" t="n"/>
-      <c r="BI33" s="40" t="n"/>
-      <c r="BJ33" s="89" t="n"/>
-      <c r="BK33" s="90" t="n"/>
-      <c r="BL33" s="90" t="n"/>
-      <c r="BM33" s="90" t="n"/>
-      <c r="BN33" s="90" t="n"/>
-      <c r="BO33" s="90" t="n"/>
-      <c r="BP33" s="90" t="n"/>
-      <c r="BQ33" s="90" t="n"/>
-      <c r="BR33" s="90" t="n"/>
-      <c r="BS33" s="90" t="n"/>
-      <c r="BT33" s="90" t="n"/>
-      <c r="BU33" s="90" t="n"/>
-      <c r="BV33" s="90" t="n"/>
-      <c r="BW33" s="90" t="n"/>
-      <c r="BX33" s="90" t="n"/>
-      <c r="BY33" s="90" t="n"/>
-      <c r="BZ33" s="90" t="n"/>
-      <c r="CA33" s="90" t="n"/>
-      <c r="CB33" s="90" t="n"/>
-      <c r="CC33" s="90" t="n"/>
-      <c r="CD33" s="90" t="n"/>
-      <c r="CE33" s="90" t="n"/>
-      <c r="CF33" s="90" t="n"/>
-      <c r="CG33" s="91" t="n"/>
+      <c r="BG33" s="41" t="n"/>
+      <c r="BH33" s="41" t="n"/>
+      <c r="BI33" s="42" t="n"/>
+      <c r="BJ33" s="93" t="n"/>
+      <c r="BK33" s="94" t="n"/>
+      <c r="BL33" s="94" t="n"/>
+      <c r="BM33" s="94" t="n"/>
+      <c r="BN33" s="94" t="n"/>
+      <c r="BO33" s="94" t="n"/>
+      <c r="BP33" s="94" t="n"/>
+      <c r="BQ33" s="94" t="n"/>
+      <c r="BR33" s="94" t="n"/>
+      <c r="BS33" s="94" t="n"/>
+      <c r="BT33" s="94" t="n"/>
+      <c r="BU33" s="94" t="n"/>
+      <c r="BV33" s="94" t="n"/>
+      <c r="BW33" s="94" t="n"/>
+      <c r="BX33" s="94" t="n"/>
+      <c r="BY33" s="94" t="n"/>
+      <c r="BZ33" s="94" t="n"/>
+      <c r="CA33" s="94" t="n"/>
+      <c r="CB33" s="94" t="n"/>
+      <c r="CC33" s="94" t="n"/>
+      <c r="CD33" s="94" t="n"/>
+      <c r="CE33" s="94" t="n"/>
+      <c r="CF33" s="94" t="n"/>
+      <c r="CG33" s="95" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="29" t="inlineStr">
@@ -4994,89 +5139,89 @@
         </is>
       </c>
       <c r="F34" s="31" t="n"/>
-      <c r="G34" s="39" t="n"/>
-      <c r="H34" s="39" t="n"/>
-      <c r="I34" s="40" t="n"/>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="41" t="n"/>
+      <c r="I34" s="42" t="n"/>
       <c r="J34" s="31" t="n"/>
-      <c r="K34" s="39" t="n"/>
-      <c r="L34" s="39" t="n"/>
-      <c r="M34" s="40" t="n"/>
-      <c r="N34" s="82" t="n"/>
+      <c r="K34" s="41" t="n"/>
+      <c r="L34" s="41" t="n"/>
+      <c r="M34" s="42" t="n"/>
+      <c r="N34" s="86" t="n"/>
       <c r="O34" s="33" t="n"/>
       <c r="P34" s="33" t="n"/>
       <c r="Q34" s="34" t="n"/>
-      <c r="R34" s="82" t="n"/>
+      <c r="R34" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="S34" s="33" t="n"/>
       <c r="T34" s="33" t="n"/>
       <c r="U34" s="34" t="n"/>
-      <c r="V34" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="V34" s="86" t="n"/>
       <c r="W34" s="33" t="n"/>
       <c r="X34" s="33" t="n"/>
       <c r="Y34" s="34" t="n"/>
-      <c r="Z34" s="82" t="n"/>
+      <c r="Z34" s="86" t="n"/>
       <c r="AA34" s="33" t="n"/>
       <c r="AB34" s="33" t="n"/>
       <c r="AC34" s="34" t="n"/>
       <c r="AD34" s="31" t="n"/>
-      <c r="AE34" s="39" t="n"/>
-      <c r="AF34" s="39" t="n"/>
-      <c r="AG34" s="40" t="n"/>
+      <c r="AE34" s="41" t="n"/>
+      <c r="AF34" s="41" t="n"/>
+      <c r="AG34" s="42" t="n"/>
       <c r="AH34" s="31" t="n"/>
-      <c r="AI34" s="39" t="n"/>
-      <c r="AJ34" s="39" t="n"/>
-      <c r="AK34" s="40" t="n"/>
+      <c r="AI34" s="41" t="n"/>
+      <c r="AJ34" s="41" t="n"/>
+      <c r="AK34" s="42" t="n"/>
       <c r="AL34" s="31" t="n"/>
-      <c r="AM34" s="39" t="n"/>
-      <c r="AN34" s="39" t="n"/>
-      <c r="AO34" s="40" t="n"/>
+      <c r="AM34" s="41" t="n"/>
+      <c r="AN34" s="41" t="n"/>
+      <c r="AO34" s="42" t="n"/>
       <c r="AP34" s="31" t="n"/>
-      <c r="AQ34" s="39" t="n"/>
-      <c r="AR34" s="39" t="n"/>
-      <c r="AS34" s="40" t="n"/>
+      <c r="AQ34" s="41" t="n"/>
+      <c r="AR34" s="41" t="n"/>
+      <c r="AS34" s="42" t="n"/>
       <c r="AT34" s="31" t="n"/>
-      <c r="AU34" s="39" t="n"/>
-      <c r="AV34" s="39" t="n"/>
-      <c r="AW34" s="40" t="n"/>
+      <c r="AU34" s="41" t="n"/>
+      <c r="AV34" s="41" t="n"/>
+      <c r="AW34" s="42" t="n"/>
       <c r="AX34" s="31" t="n"/>
-      <c r="AY34" s="39" t="n"/>
-      <c r="AZ34" s="39" t="n"/>
-      <c r="BA34" s="40" t="n"/>
+      <c r="AY34" s="41" t="n"/>
+      <c r="AZ34" s="41" t="n"/>
+      <c r="BA34" s="42" t="n"/>
       <c r="BB34" s="31" t="n"/>
-      <c r="BC34" s="39" t="n"/>
-      <c r="BD34" s="39" t="n"/>
-      <c r="BE34" s="40" t="n"/>
+      <c r="BC34" s="41" t="n"/>
+      <c r="BD34" s="41" t="n"/>
+      <c r="BE34" s="42" t="n"/>
       <c r="BF34" s="31" t="n"/>
-      <c r="BG34" s="39" t="n"/>
-      <c r="BH34" s="39" t="n"/>
-      <c r="BI34" s="40" t="n"/>
+      <c r="BG34" s="41" t="n"/>
+      <c r="BH34" s="41" t="n"/>
+      <c r="BI34" s="42" t="n"/>
       <c r="BJ34" s="31" t="n"/>
-      <c r="BK34" s="39" t="n"/>
-      <c r="BL34" s="39" t="n"/>
-      <c r="BM34" s="40" t="n"/>
+      <c r="BK34" s="41" t="n"/>
+      <c r="BL34" s="41" t="n"/>
+      <c r="BM34" s="42" t="n"/>
       <c r="BN34" s="31" t="n"/>
-      <c r="BO34" s="39" t="n"/>
-      <c r="BP34" s="39" t="n"/>
-      <c r="BQ34" s="40" t="n"/>
+      <c r="BO34" s="41" t="n"/>
+      <c r="BP34" s="41" t="n"/>
+      <c r="BQ34" s="42" t="n"/>
       <c r="BR34" s="31" t="n"/>
-      <c r="BS34" s="39" t="n"/>
-      <c r="BT34" s="39" t="n"/>
-      <c r="BU34" s="40" t="n"/>
+      <c r="BS34" s="41" t="n"/>
+      <c r="BT34" s="41" t="n"/>
+      <c r="BU34" s="42" t="n"/>
       <c r="BV34" s="31" t="n"/>
-      <c r="BW34" s="39" t="n"/>
-      <c r="BX34" s="39" t="n"/>
-      <c r="BY34" s="40" t="n"/>
+      <c r="BW34" s="41" t="n"/>
+      <c r="BX34" s="41" t="n"/>
+      <c r="BY34" s="42" t="n"/>
       <c r="BZ34" s="31" t="n"/>
-      <c r="CA34" s="39" t="n"/>
-      <c r="CB34" s="39" t="n"/>
-      <c r="CC34" s="40" t="n"/>
+      <c r="CA34" s="41" t="n"/>
+      <c r="CB34" s="41" t="n"/>
+      <c r="CC34" s="42" t="n"/>
       <c r="CD34" s="31" t="n"/>
-      <c r="CE34" s="39" t="n"/>
-      <c r="CF34" s="39" t="n"/>
-      <c r="CG34" s="50" t="n"/>
+      <c r="CE34" s="41" t="n"/>
+      <c r="CF34" s="41" t="n"/>
+      <c r="CG34" s="54" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="29" t="inlineStr">
@@ -5105,93 +5250,101 @@
         </is>
       </c>
       <c r="F35" s="31" t="n"/>
-      <c r="G35" s="39" t="n"/>
-      <c r="H35" s="39" t="n"/>
-      <c r="I35" s="40" t="n"/>
+      <c r="G35" s="41" t="n"/>
+      <c r="H35" s="41" t="n"/>
+      <c r="I35" s="42" t="n"/>
       <c r="J35" s="31" t="n"/>
-      <c r="K35" s="39" t="n"/>
-      <c r="L35" s="39" t="n"/>
-      <c r="M35" s="40" t="n"/>
-      <c r="N35" s="82" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="41" t="n"/>
+      <c r="M35" s="42" t="n"/>
+      <c r="N35" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="O35" s="33" t="n"/>
       <c r="P35" s="33" t="n"/>
       <c r="Q35" s="34" t="n"/>
-      <c r="R35" s="82" t="n"/>
+      <c r="R35" s="86" t="n"/>
       <c r="S35" s="33" t="n"/>
       <c r="T35" s="33" t="n"/>
       <c r="U35" s="34" t="n"/>
-      <c r="V35" s="82" t="n"/>
+      <c r="V35" s="86" t="n"/>
       <c r="W35" s="33" t="n"/>
       <c r="X35" s="33" t="n"/>
       <c r="Y35" s="34" t="n"/>
-      <c r="Z35" s="56" t="inlineStr">
+      <c r="Z35" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AA35" s="33" t="n"/>
-      <c r="AB35" s="57" t="inlineStr">
+      <c r="AB35" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AC35" s="34" t="n"/>
-      <c r="AD35" s="82" t="n"/>
+      <c r="AD35" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="AE35" s="33" t="n"/>
       <c r="AF35" s="33" t="n"/>
       <c r="AG35" s="34" t="n"/>
-      <c r="AH35" s="82" t="n"/>
+      <c r="AH35" s="86" t="n"/>
       <c r="AI35" s="33" t="n"/>
       <c r="AJ35" s="33" t="n"/>
       <c r="AK35" s="34" t="n"/>
-      <c r="AL35" s="82" t="n"/>
+      <c r="AL35" s="86" t="n"/>
       <c r="AM35" s="33" t="n"/>
       <c r="AN35" s="33" t="n"/>
       <c r="AO35" s="34" t="n"/>
-      <c r="AP35" s="83" t="n"/>
+      <c r="AP35" s="87" t="n"/>
       <c r="AQ35" s="33" t="n"/>
-      <c r="AR35" s="39" t="n"/>
-      <c r="AS35" s="40" t="n"/>
+      <c r="AR35" s="41" t="n"/>
+      <c r="AS35" s="42" t="n"/>
       <c r="AT35" s="31" t="n"/>
-      <c r="AU35" s="39" t="n"/>
-      <c r="AV35" s="39" t="n"/>
-      <c r="AW35" s="40" t="n"/>
+      <c r="AU35" s="41" t="n"/>
+      <c r="AV35" s="41" t="n"/>
+      <c r="AW35" s="42" t="n"/>
       <c r="AX35" s="31" t="n"/>
-      <c r="AY35" s="39" t="n"/>
-      <c r="AZ35" s="39" t="n"/>
-      <c r="BA35" s="40" t="n"/>
+      <c r="AY35" s="41" t="n"/>
+      <c r="AZ35" s="41" t="n"/>
+      <c r="BA35" s="42" t="n"/>
       <c r="BB35" s="31" t="n"/>
-      <c r="BC35" s="39" t="n"/>
-      <c r="BD35" s="39" t="n"/>
-      <c r="BE35" s="40" t="n"/>
+      <c r="BC35" s="41" t="n"/>
+      <c r="BD35" s="41" t="n"/>
+      <c r="BE35" s="42" t="n"/>
       <c r="BF35" s="31" t="n"/>
-      <c r="BG35" s="39" t="n"/>
-      <c r="BH35" s="39" t="n"/>
-      <c r="BI35" s="40" t="n"/>
+      <c r="BG35" s="41" t="n"/>
+      <c r="BH35" s="41" t="n"/>
+      <c r="BI35" s="42" t="n"/>
       <c r="BJ35" s="31" t="n"/>
-      <c r="BK35" s="39" t="n"/>
-      <c r="BL35" s="39" t="n"/>
-      <c r="BM35" s="40" t="n"/>
+      <c r="BK35" s="41" t="n"/>
+      <c r="BL35" s="41" t="n"/>
+      <c r="BM35" s="42" t="n"/>
       <c r="BN35" s="31" t="n"/>
-      <c r="BO35" s="39" t="n"/>
-      <c r="BP35" s="39" t="n"/>
-      <c r="BQ35" s="40" t="n"/>
+      <c r="BO35" s="41" t="n"/>
+      <c r="BP35" s="41" t="n"/>
+      <c r="BQ35" s="42" t="n"/>
       <c r="BR35" s="31" t="n"/>
-      <c r="BS35" s="39" t="n"/>
-      <c r="BT35" s="39" t="n"/>
-      <c r="BU35" s="40" t="n"/>
+      <c r="BS35" s="41" t="n"/>
+      <c r="BT35" s="41" t="n"/>
+      <c r="BU35" s="42" t="n"/>
       <c r="BV35" s="31" t="n"/>
-      <c r="BW35" s="39" t="n"/>
-      <c r="BX35" s="39" t="n"/>
-      <c r="BY35" s="40" t="n"/>
+      <c r="BW35" s="41" t="n"/>
+      <c r="BX35" s="41" t="n"/>
+      <c r="BY35" s="42" t="n"/>
       <c r="BZ35" s="31" t="n"/>
-      <c r="CA35" s="39" t="n"/>
-      <c r="CB35" s="39" t="n"/>
-      <c r="CC35" s="40" t="n"/>
+      <c r="CA35" s="41" t="n"/>
+      <c r="CB35" s="41" t="n"/>
+      <c r="CC35" s="42" t="n"/>
       <c r="CD35" s="31" t="n"/>
-      <c r="CE35" s="39" t="n"/>
-      <c r="CF35" s="39" t="n"/>
-      <c r="CG35" s="50" t="n"/>
+      <c r="CE35" s="41" t="n"/>
+      <c r="CF35" s="41" t="n"/>
+      <c r="CG35" s="54" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
@@ -5220,97 +5373,97 @@
         </is>
       </c>
       <c r="F36" s="31" t="n"/>
-      <c r="G36" s="39" t="n"/>
-      <c r="H36" s="39" t="n"/>
-      <c r="I36" s="40" t="n"/>
+      <c r="G36" s="41" t="n"/>
+      <c r="H36" s="41" t="n"/>
+      <c r="I36" s="42" t="n"/>
       <c r="J36" s="31" t="n"/>
-      <c r="K36" s="39" t="n"/>
-      <c r="L36" s="39" t="n"/>
-      <c r="M36" s="40" t="n"/>
-      <c r="N36" s="88" t="n"/>
+      <c r="K36" s="41" t="n"/>
+      <c r="L36" s="41" t="n"/>
+      <c r="M36" s="42" t="n"/>
+      <c r="N36" s="92" t="n"/>
       <c r="O36" s="33" t="n"/>
       <c r="P36" s="33" t="n"/>
       <c r="Q36" s="34" t="n"/>
-      <c r="R36" s="88" t="n"/>
+      <c r="R36" s="48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="S36" s="33" t="n"/>
       <c r="T36" s="33" t="n"/>
       <c r="U36" s="34" t="n"/>
-      <c r="V36" s="88" t="n"/>
+      <c r="V36" s="92" t="n"/>
       <c r="W36" s="33" t="n"/>
       <c r="X36" s="33" t="n"/>
       <c r="Y36" s="34" t="n"/>
-      <c r="Z36" s="36" t="inlineStr">
+      <c r="Z36" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AA36" s="33" t="n"/>
-      <c r="AB36" s="37" t="inlineStr">
+      <c r="AB36" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AC36" s="34" t="n"/>
-      <c r="AD36" s="88" t="n"/>
+      <c r="AD36" s="92" t="n"/>
       <c r="AE36" s="33" t="n"/>
       <c r="AF36" s="33" t="n"/>
       <c r="AG36" s="34" t="n"/>
-      <c r="AH36" s="88" t="n"/>
+      <c r="AH36" s="92" t="n"/>
       <c r="AI36" s="33" t="n"/>
       <c r="AJ36" s="33" t="n"/>
       <c r="AK36" s="34" t="n"/>
-      <c r="AL36" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AL36" s="92" t="n"/>
       <c r="AM36" s="33" t="n"/>
       <c r="AN36" s="33" t="n"/>
       <c r="AO36" s="34" t="n"/>
-      <c r="AP36" s="88" t="n"/>
+      <c r="AP36" s="92" t="n"/>
       <c r="AQ36" s="33" t="n"/>
       <c r="AR36" s="33" t="n"/>
       <c r="AS36" s="34" t="n"/>
       <c r="AT36" s="31" t="n"/>
-      <c r="AU36" s="39" t="n"/>
-      <c r="AV36" s="39" t="n"/>
-      <c r="AW36" s="40" t="n"/>
+      <c r="AU36" s="41" t="n"/>
+      <c r="AV36" s="41" t="n"/>
+      <c r="AW36" s="42" t="n"/>
       <c r="AX36" s="31" t="n"/>
-      <c r="AY36" s="39" t="n"/>
-      <c r="AZ36" s="39" t="n"/>
-      <c r="BA36" s="40" t="n"/>
+      <c r="AY36" s="41" t="n"/>
+      <c r="AZ36" s="41" t="n"/>
+      <c r="BA36" s="42" t="n"/>
       <c r="BB36" s="31" t="n"/>
-      <c r="BC36" s="39" t="n"/>
-      <c r="BD36" s="39" t="n"/>
-      <c r="BE36" s="40" t="n"/>
+      <c r="BC36" s="41" t="n"/>
+      <c r="BD36" s="41" t="n"/>
+      <c r="BE36" s="42" t="n"/>
       <c r="BF36" s="31" t="n"/>
-      <c r="BG36" s="39" t="n"/>
-      <c r="BH36" s="39" t="n"/>
-      <c r="BI36" s="40" t="n"/>
+      <c r="BG36" s="41" t="n"/>
+      <c r="BH36" s="41" t="n"/>
+      <c r="BI36" s="42" t="n"/>
       <c r="BJ36" s="31" t="n"/>
-      <c r="BK36" s="39" t="n"/>
-      <c r="BL36" s="39" t="n"/>
-      <c r="BM36" s="40" t="n"/>
+      <c r="BK36" s="41" t="n"/>
+      <c r="BL36" s="41" t="n"/>
+      <c r="BM36" s="42" t="n"/>
       <c r="BN36" s="31" t="n"/>
-      <c r="BO36" s="39" t="n"/>
-      <c r="BP36" s="39" t="n"/>
-      <c r="BQ36" s="40" t="n"/>
+      <c r="BO36" s="41" t="n"/>
+      <c r="BP36" s="41" t="n"/>
+      <c r="BQ36" s="42" t="n"/>
       <c r="BR36" s="31" t="n"/>
-      <c r="BS36" s="39" t="n"/>
-      <c r="BT36" s="39" t="n"/>
-      <c r="BU36" s="40" t="n"/>
+      <c r="BS36" s="41" t="n"/>
+      <c r="BT36" s="41" t="n"/>
+      <c r="BU36" s="42" t="n"/>
       <c r="BV36" s="31" t="n"/>
-      <c r="BW36" s="39" t="n"/>
-      <c r="BX36" s="39" t="n"/>
-      <c r="BY36" s="40" t="n"/>
+      <c r="BW36" s="41" t="n"/>
+      <c r="BX36" s="41" t="n"/>
+      <c r="BY36" s="42" t="n"/>
       <c r="BZ36" s="31" t="n"/>
-      <c r="CA36" s="39" t="n"/>
-      <c r="CB36" s="39" t="n"/>
-      <c r="CC36" s="40" t="n"/>
+      <c r="CA36" s="41" t="n"/>
+      <c r="CB36" s="41" t="n"/>
+      <c r="CC36" s="42" t="n"/>
       <c r="CD36" s="31" t="n"/>
-      <c r="CE36" s="39" t="n"/>
-      <c r="CF36" s="39" t="n"/>
-      <c r="CG36" s="50" t="n"/>
+      <c r="CE36" s="41" t="n"/>
+      <c r="CF36" s="41" t="n"/>
+      <c r="CG36" s="54" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="29" t="inlineStr">
@@ -5339,93 +5492,97 @@
         </is>
       </c>
       <c r="F37" s="31" t="n"/>
-      <c r="G37" s="39" t="n"/>
-      <c r="H37" s="39" t="n"/>
-      <c r="I37" s="40" t="n"/>
+      <c r="G37" s="41" t="n"/>
+      <c r="H37" s="41" t="n"/>
+      <c r="I37" s="42" t="n"/>
       <c r="J37" s="31" t="n"/>
-      <c r="K37" s="39" t="n"/>
-      <c r="L37" s="39" t="n"/>
-      <c r="M37" s="40" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="41" t="n"/>
+      <c r="M37" s="42" t="n"/>
       <c r="N37" s="31" t="n"/>
-      <c r="O37" s="39" t="n"/>
-      <c r="P37" s="39" t="n"/>
-      <c r="Q37" s="40" t="n"/>
+      <c r="O37" s="41" t="n"/>
+      <c r="P37" s="41" t="n"/>
+      <c r="Q37" s="42" t="n"/>
       <c r="R37" s="31" t="n"/>
-      <c r="S37" s="39" t="n"/>
-      <c r="T37" s="39" t="n"/>
-      <c r="U37" s="40" t="n"/>
+      <c r="S37" s="41" t="n"/>
+      <c r="T37" s="41" t="n"/>
+      <c r="U37" s="42" t="n"/>
       <c r="V37" s="31" t="n"/>
-      <c r="W37" s="39" t="n"/>
-      <c r="X37" s="87" t="n"/>
+      <c r="W37" s="41" t="n"/>
+      <c r="X37" s="91" t="n"/>
       <c r="Y37" s="34" t="n"/>
-      <c r="Z37" s="88" t="n"/>
+      <c r="Z37" s="92" t="n"/>
       <c r="AA37" s="33" t="n"/>
       <c r="AB37" s="33" t="n"/>
       <c r="AC37" s="34" t="n"/>
-      <c r="AD37" s="88" t="n"/>
+      <c r="AD37" s="92" t="n"/>
       <c r="AE37" s="33" t="n"/>
       <c r="AF37" s="33" t="n"/>
       <c r="AG37" s="34" t="n"/>
-      <c r="AH37" s="88" t="n"/>
+      <c r="AH37" s="92" t="n"/>
       <c r="AI37" s="33" t="n"/>
       <c r="AJ37" s="33" t="n"/>
       <c r="AK37" s="34" t="n"/>
-      <c r="AL37" s="36" t="inlineStr">
+      <c r="AL37" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AM37" s="33" t="n"/>
-      <c r="AN37" s="37" t="inlineStr">
+      <c r="AN37" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AO37" s="34" t="n"/>
-      <c r="AP37" s="88" t="n"/>
+      <c r="AP37" s="92" t="n"/>
       <c r="AQ37" s="33" t="n"/>
       <c r="AR37" s="33" t="n"/>
       <c r="AS37" s="34" t="n"/>
-      <c r="AT37" s="88" t="n"/>
+      <c r="AT37" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AU37" s="33" t="n"/>
       <c r="AV37" s="33" t="n"/>
       <c r="AW37" s="34" t="n"/>
-      <c r="AX37" s="88" t="n"/>
+      <c r="AX37" s="92" t="n"/>
       <c r="AY37" s="33" t="n"/>
       <c r="AZ37" s="33" t="n"/>
       <c r="BA37" s="34" t="n"/>
-      <c r="BB37" s="92" t="n"/>
+      <c r="BB37" s="96" t="n"/>
       <c r="BC37" s="33" t="n"/>
-      <c r="BD37" s="39" t="n"/>
-      <c r="BE37" s="40" t="n"/>
+      <c r="BD37" s="41" t="n"/>
+      <c r="BE37" s="42" t="n"/>
       <c r="BF37" s="31" t="n"/>
-      <c r="BG37" s="39" t="n"/>
-      <c r="BH37" s="39" t="n"/>
-      <c r="BI37" s="40" t="n"/>
+      <c r="BG37" s="41" t="n"/>
+      <c r="BH37" s="41" t="n"/>
+      <c r="BI37" s="42" t="n"/>
       <c r="BJ37" s="31" t="n"/>
-      <c r="BK37" s="39" t="n"/>
-      <c r="BL37" s="39" t="n"/>
-      <c r="BM37" s="40" t="n"/>
+      <c r="BK37" s="41" t="n"/>
+      <c r="BL37" s="41" t="n"/>
+      <c r="BM37" s="42" t="n"/>
       <c r="BN37" s="31" t="n"/>
-      <c r="BO37" s="39" t="n"/>
-      <c r="BP37" s="39" t="n"/>
-      <c r="BQ37" s="40" t="n"/>
+      <c r="BO37" s="41" t="n"/>
+      <c r="BP37" s="41" t="n"/>
+      <c r="BQ37" s="42" t="n"/>
       <c r="BR37" s="31" t="n"/>
-      <c r="BS37" s="39" t="n"/>
-      <c r="BT37" s="39" t="n"/>
-      <c r="BU37" s="40" t="n"/>
+      <c r="BS37" s="41" t="n"/>
+      <c r="BT37" s="41" t="n"/>
+      <c r="BU37" s="42" t="n"/>
       <c r="BV37" s="31" t="n"/>
-      <c r="BW37" s="39" t="n"/>
-      <c r="BX37" s="39" t="n"/>
-      <c r="BY37" s="40" t="n"/>
+      <c r="BW37" s="41" t="n"/>
+      <c r="BX37" s="41" t="n"/>
+      <c r="BY37" s="42" t="n"/>
       <c r="BZ37" s="31" t="n"/>
-      <c r="CA37" s="39" t="n"/>
-      <c r="CB37" s="39" t="n"/>
-      <c r="CC37" s="40" t="n"/>
+      <c r="CA37" s="41" t="n"/>
+      <c r="CB37" s="41" t="n"/>
+      <c r="CC37" s="42" t="n"/>
       <c r="CD37" s="31" t="n"/>
-      <c r="CE37" s="39" t="n"/>
-      <c r="CF37" s="39" t="n"/>
-      <c r="CG37" s="50" t="n"/>
+      <c r="CE37" s="41" t="n"/>
+      <c r="CF37" s="41" t="n"/>
+      <c r="CG37" s="54" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="29" t="inlineStr">
@@ -5454,93 +5611,97 @@
         </is>
       </c>
       <c r="F38" s="31" t="n"/>
-      <c r="G38" s="39" t="n"/>
-      <c r="H38" s="39" t="n"/>
-      <c r="I38" s="40" t="n"/>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="41" t="n"/>
+      <c r="I38" s="42" t="n"/>
       <c r="J38" s="31" t="n"/>
-      <c r="K38" s="39" t="n"/>
-      <c r="L38" s="39" t="n"/>
-      <c r="M38" s="40" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="41" t="n"/>
+      <c r="M38" s="42" t="n"/>
       <c r="N38" s="31" t="n"/>
-      <c r="O38" s="39" t="n"/>
-      <c r="P38" s="39" t="n"/>
-      <c r="Q38" s="40" t="n"/>
+      <c r="O38" s="41" t="n"/>
+      <c r="P38" s="41" t="n"/>
+      <c r="Q38" s="42" t="n"/>
       <c r="R38" s="31" t="n"/>
-      <c r="S38" s="39" t="n"/>
-      <c r="T38" s="39" t="n"/>
-      <c r="U38" s="40" t="n"/>
+      <c r="S38" s="41" t="n"/>
+      <c r="T38" s="41" t="n"/>
+      <c r="U38" s="42" t="n"/>
       <c r="V38" s="31" t="n"/>
-      <c r="W38" s="39" t="n"/>
-      <c r="X38" s="39" t="n"/>
-      <c r="Y38" s="40" t="n"/>
+      <c r="W38" s="41" t="n"/>
+      <c r="X38" s="41" t="n"/>
+      <c r="Y38" s="42" t="n"/>
       <c r="Z38" s="31" t="n"/>
-      <c r="AA38" s="39" t="n"/>
-      <c r="AB38" s="39" t="n"/>
-      <c r="AC38" s="40" t="n"/>
+      <c r="AA38" s="41" t="n"/>
+      <c r="AB38" s="41" t="n"/>
+      <c r="AC38" s="42" t="n"/>
       <c r="AD38" s="31" t="n"/>
-      <c r="AE38" s="39" t="n"/>
-      <c r="AF38" s="39" t="n"/>
-      <c r="AG38" s="40" t="n"/>
+      <c r="AE38" s="41" t="n"/>
+      <c r="AF38" s="41" t="n"/>
+      <c r="AG38" s="42" t="n"/>
       <c r="AH38" s="31" t="n"/>
-      <c r="AI38" s="39" t="n"/>
-      <c r="AJ38" s="81" t="n"/>
+      <c r="AI38" s="41" t="n"/>
+      <c r="AJ38" s="85" t="n"/>
       <c r="AK38" s="34" t="n"/>
-      <c r="AL38" s="82" t="n"/>
+      <c r="AL38" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AM38" s="33" t="n"/>
       <c r="AN38" s="33" t="n"/>
       <c r="AO38" s="34" t="n"/>
-      <c r="AP38" s="82" t="n"/>
+      <c r="AP38" s="86" t="n"/>
       <c r="AQ38" s="33" t="n"/>
       <c r="AR38" s="33" t="n"/>
       <c r="AS38" s="34" t="n"/>
-      <c r="AT38" s="82" t="n"/>
+      <c r="AT38" s="86" t="n"/>
       <c r="AU38" s="33" t="n"/>
       <c r="AV38" s="33" t="n"/>
       <c r="AW38" s="34" t="n"/>
-      <c r="AX38" s="36" t="inlineStr">
+      <c r="AX38" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AY38" s="33" t="n"/>
-      <c r="AZ38" s="37" t="inlineStr">
+      <c r="AZ38" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BA38" s="34" t="n"/>
-      <c r="BB38" s="82" t="n"/>
+      <c r="BB38" s="86" t="n"/>
       <c r="BC38" s="33" t="n"/>
       <c r="BD38" s="33" t="n"/>
       <c r="BE38" s="34" t="n"/>
-      <c r="BF38" s="82" t="n"/>
+      <c r="BF38" s="86" t="n"/>
       <c r="BG38" s="33" t="n"/>
       <c r="BH38" s="33" t="n"/>
       <c r="BI38" s="34" t="n"/>
-      <c r="BJ38" s="82" t="n"/>
+      <c r="BJ38" s="86" t="n"/>
       <c r="BK38" s="33" t="n"/>
       <c r="BL38" s="33" t="n"/>
       <c r="BM38" s="34" t="n"/>
       <c r="BN38" s="31" t="n"/>
-      <c r="BO38" s="39" t="n"/>
-      <c r="BP38" s="39" t="n"/>
-      <c r="BQ38" s="40" t="n"/>
+      <c r="BO38" s="41" t="n"/>
+      <c r="BP38" s="41" t="n"/>
+      <c r="BQ38" s="42" t="n"/>
       <c r="BR38" s="31" t="n"/>
-      <c r="BS38" s="39" t="n"/>
-      <c r="BT38" s="39" t="n"/>
-      <c r="BU38" s="40" t="n"/>
+      <c r="BS38" s="41" t="n"/>
+      <c r="BT38" s="41" t="n"/>
+      <c r="BU38" s="42" t="n"/>
       <c r="BV38" s="31" t="n"/>
-      <c r="BW38" s="39" t="n"/>
-      <c r="BX38" s="39" t="n"/>
-      <c r="BY38" s="40" t="n"/>
+      <c r="BW38" s="41" t="n"/>
+      <c r="BX38" s="41" t="n"/>
+      <c r="BY38" s="42" t="n"/>
       <c r="BZ38" s="31" t="n"/>
-      <c r="CA38" s="39" t="n"/>
-      <c r="CB38" s="39" t="n"/>
-      <c r="CC38" s="40" t="n"/>
+      <c r="CA38" s="41" t="n"/>
+      <c r="CB38" s="41" t="n"/>
+      <c r="CC38" s="42" t="n"/>
       <c r="CD38" s="31" t="n"/>
-      <c r="CE38" s="39" t="n"/>
-      <c r="CF38" s="39" t="n"/>
-      <c r="CG38" s="50" t="n"/>
+      <c r="CE38" s="41" t="n"/>
+      <c r="CF38" s="41" t="n"/>
+      <c r="CG38" s="54" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="29" t="inlineStr">
@@ -5569,93 +5730,97 @@
         </is>
       </c>
       <c r="F39" s="31" t="n"/>
-      <c r="G39" s="39" t="n"/>
-      <c r="H39" s="39" t="n"/>
-      <c r="I39" s="40" t="n"/>
+      <c r="G39" s="41" t="n"/>
+      <c r="H39" s="41" t="n"/>
+      <c r="I39" s="42" t="n"/>
       <c r="J39" s="31" t="n"/>
-      <c r="K39" s="39" t="n"/>
-      <c r="L39" s="39" t="n"/>
-      <c r="M39" s="40" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="41" t="n"/>
+      <c r="M39" s="42" t="n"/>
       <c r="N39" s="31" t="n"/>
-      <c r="O39" s="39" t="n"/>
-      <c r="P39" s="39" t="n"/>
-      <c r="Q39" s="40" t="n"/>
+      <c r="O39" s="41" t="n"/>
+      <c r="P39" s="41" t="n"/>
+      <c r="Q39" s="42" t="n"/>
       <c r="R39" s="31" t="n"/>
-      <c r="S39" s="39" t="n"/>
-      <c r="T39" s="39" t="n"/>
-      <c r="U39" s="40" t="n"/>
+      <c r="S39" s="41" t="n"/>
+      <c r="T39" s="41" t="n"/>
+      <c r="U39" s="42" t="n"/>
       <c r="V39" s="31" t="n"/>
-      <c r="W39" s="39" t="n"/>
-      <c r="X39" s="39" t="n"/>
-      <c r="Y39" s="40" t="n"/>
+      <c r="W39" s="41" t="n"/>
+      <c r="X39" s="41" t="n"/>
+      <c r="Y39" s="42" t="n"/>
       <c r="Z39" s="31" t="n"/>
-      <c r="AA39" s="39" t="n"/>
-      <c r="AB39" s="39" t="n"/>
-      <c r="AC39" s="40" t="n"/>
+      <c r="AA39" s="41" t="n"/>
+      <c r="AB39" s="41" t="n"/>
+      <c r="AC39" s="42" t="n"/>
       <c r="AD39" s="31" t="n"/>
-      <c r="AE39" s="39" t="n"/>
-      <c r="AF39" s="39" t="n"/>
-      <c r="AG39" s="40" t="n"/>
+      <c r="AE39" s="41" t="n"/>
+      <c r="AF39" s="41" t="n"/>
+      <c r="AG39" s="42" t="n"/>
       <c r="AH39" s="31" t="n"/>
-      <c r="AI39" s="39" t="n"/>
-      <c r="AJ39" s="39" t="n"/>
-      <c r="AK39" s="40" t="n"/>
-      <c r="AL39" s="88" t="n"/>
+      <c r="AI39" s="41" t="n"/>
+      <c r="AJ39" s="41" t="n"/>
+      <c r="AK39" s="42" t="n"/>
+      <c r="AL39" s="92" t="n"/>
       <c r="AM39" s="33" t="n"/>
       <c r="AN39" s="33" t="n"/>
       <c r="AO39" s="34" t="n"/>
-      <c r="AP39" s="88" t="n"/>
+      <c r="AP39" s="92" t="n"/>
       <c r="AQ39" s="33" t="n"/>
       <c r="AR39" s="33" t="n"/>
       <c r="AS39" s="34" t="n"/>
-      <c r="AT39" s="88" t="n"/>
+      <c r="AT39" s="92" t="n"/>
       <c r="AU39" s="33" t="n"/>
       <c r="AV39" s="33" t="n"/>
       <c r="AW39" s="34" t="n"/>
-      <c r="AX39" s="56" t="inlineStr">
+      <c r="AX39" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AY39" s="33" t="n"/>
-      <c r="AZ39" s="57" t="inlineStr">
+      <c r="AZ39" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BA39" s="34" t="n"/>
-      <c r="BB39" s="88" t="n"/>
+      <c r="BB39" s="92" t="n"/>
       <c r="BC39" s="33" t="n"/>
       <c r="BD39" s="33" t="n"/>
       <c r="BE39" s="34" t="n"/>
-      <c r="BF39" s="88" t="n"/>
+      <c r="BF39" s="92" t="n"/>
       <c r="BG39" s="33" t="n"/>
       <c r="BH39" s="33" t="n"/>
       <c r="BI39" s="34" t="n"/>
-      <c r="BJ39" s="88" t="n"/>
+      <c r="BJ39" s="92" t="n"/>
       <c r="BK39" s="33" t="n"/>
       <c r="BL39" s="33" t="n"/>
       <c r="BM39" s="34" t="n"/>
-      <c r="BN39" s="88" t="n"/>
+      <c r="BN39" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BO39" s="33" t="n"/>
       <c r="BP39" s="33" t="n"/>
       <c r="BQ39" s="34" t="n"/>
       <c r="BR39" s="31" t="n"/>
-      <c r="BS39" s="39" t="n"/>
-      <c r="BT39" s="39" t="n"/>
-      <c r="BU39" s="40" t="n"/>
+      <c r="BS39" s="41" t="n"/>
+      <c r="BT39" s="41" t="n"/>
+      <c r="BU39" s="42" t="n"/>
       <c r="BV39" s="31" t="n"/>
-      <c r="BW39" s="39" t="n"/>
-      <c r="BX39" s="39" t="n"/>
-      <c r="BY39" s="40" t="n"/>
+      <c r="BW39" s="41" t="n"/>
+      <c r="BX39" s="41" t="n"/>
+      <c r="BY39" s="42" t="n"/>
       <c r="BZ39" s="31" t="n"/>
-      <c r="CA39" s="39" t="n"/>
-      <c r="CB39" s="39" t="n"/>
-      <c r="CC39" s="40" t="n"/>
+      <c r="CA39" s="41" t="n"/>
+      <c r="CB39" s="41" t="n"/>
+      <c r="CC39" s="42" t="n"/>
       <c r="CD39" s="31" t="n"/>
-      <c r="CE39" s="39" t="n"/>
-      <c r="CF39" s="39" t="n"/>
-      <c r="CG39" s="50" t="n"/>
+      <c r="CE39" s="41" t="n"/>
+      <c r="CF39" s="41" t="n"/>
+      <c r="CG39" s="54" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="29" t="inlineStr">
@@ -5680,89 +5845,97 @@
       </c>
       <c r="E40" s="30" t="inlineStr"/>
       <c r="F40" s="31" t="n"/>
-      <c r="G40" s="39" t="n"/>
-      <c r="H40" s="39" t="n"/>
-      <c r="I40" s="40" t="n"/>
+      <c r="G40" s="41" t="n"/>
+      <c r="H40" s="41" t="n"/>
+      <c r="I40" s="42" t="n"/>
       <c r="J40" s="31" t="n"/>
-      <c r="K40" s="39" t="n"/>
-      <c r="L40" s="39" t="n"/>
-      <c r="M40" s="40" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="41" t="n"/>
+      <c r="M40" s="42" t="n"/>
       <c r="N40" s="31" t="n"/>
-      <c r="O40" s="39" t="n"/>
-      <c r="P40" s="39" t="n"/>
-      <c r="Q40" s="40" t="n"/>
+      <c r="O40" s="41" t="n"/>
+      <c r="P40" s="41" t="n"/>
+      <c r="Q40" s="42" t="n"/>
       <c r="R40" s="31" t="n"/>
-      <c r="S40" s="39" t="n"/>
-      <c r="T40" s="39" t="n"/>
-      <c r="U40" s="40" t="n"/>
+      <c r="S40" s="41" t="n"/>
+      <c r="T40" s="41" t="n"/>
+      <c r="U40" s="42" t="n"/>
       <c r="V40" s="31" t="n"/>
-      <c r="W40" s="39" t="n"/>
-      <c r="X40" s="39" t="n"/>
-      <c r="Y40" s="40" t="n"/>
+      <c r="W40" s="41" t="n"/>
+      <c r="X40" s="41" t="n"/>
+      <c r="Y40" s="42" t="n"/>
       <c r="Z40" s="31" t="n"/>
-      <c r="AA40" s="39" t="n"/>
-      <c r="AB40" s="39" t="n"/>
-      <c r="AC40" s="40" t="n"/>
+      <c r="AA40" s="41" t="n"/>
+      <c r="AB40" s="41" t="n"/>
+      <c r="AC40" s="42" t="n"/>
       <c r="AD40" s="31" t="n"/>
-      <c r="AE40" s="39" t="n"/>
-      <c r="AF40" s="39" t="n"/>
-      <c r="AG40" s="40" t="n"/>
+      <c r="AE40" s="41" t="n"/>
+      <c r="AF40" s="41" t="n"/>
+      <c r="AG40" s="42" t="n"/>
       <c r="AH40" s="31" t="n"/>
-      <c r="AI40" s="39" t="n"/>
-      <c r="AJ40" s="39" t="n"/>
-      <c r="AK40" s="40" t="n"/>
+      <c r="AI40" s="41" t="n"/>
+      <c r="AJ40" s="41" t="n"/>
+      <c r="AK40" s="42" t="n"/>
       <c r="AL40" s="31" t="n"/>
-      <c r="AM40" s="39" t="n"/>
-      <c r="AN40" s="39" t="n"/>
-      <c r="AO40" s="40" t="n"/>
+      <c r="AM40" s="41" t="n"/>
+      <c r="AN40" s="41" t="n"/>
+      <c r="AO40" s="42" t="n"/>
       <c r="AP40" s="31" t="n"/>
-      <c r="AQ40" s="39" t="n"/>
-      <c r="AR40" s="39" t="n"/>
-      <c r="AS40" s="40" t="n"/>
-      <c r="AT40" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
+      <c r="AQ40" s="41" t="n"/>
+      <c r="AR40" s="41" t="n"/>
+      <c r="AS40" s="42" t="n"/>
+      <c r="AT40" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
         </is>
       </c>
       <c r="AU40" s="33" t="n"/>
       <c r="AV40" s="33" t="n"/>
       <c r="AW40" s="34" t="n"/>
-      <c r="AX40" s="82" t="n"/>
+      <c r="AX40" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="AY40" s="33" t="n"/>
       <c r="AZ40" s="33" t="n"/>
       <c r="BA40" s="34" t="n"/>
-      <c r="BB40" s="82" t="n"/>
+      <c r="BB40" s="86" t="n"/>
       <c r="BC40" s="33" t="n"/>
       <c r="BD40" s="33" t="n"/>
       <c r="BE40" s="34" t="n"/>
-      <c r="BF40" s="82" t="n"/>
+      <c r="BF40" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="BG40" s="33" t="n"/>
       <c r="BH40" s="33" t="n"/>
       <c r="BI40" s="34" t="n"/>
       <c r="BJ40" s="31" t="n"/>
-      <c r="BK40" s="39" t="n"/>
-      <c r="BL40" s="39" t="n"/>
-      <c r="BM40" s="40" t="n"/>
+      <c r="BK40" s="41" t="n"/>
+      <c r="BL40" s="41" t="n"/>
+      <c r="BM40" s="42" t="n"/>
       <c r="BN40" s="31" t="n"/>
-      <c r="BO40" s="39" t="n"/>
-      <c r="BP40" s="39" t="n"/>
-      <c r="BQ40" s="40" t="n"/>
+      <c r="BO40" s="41" t="n"/>
+      <c r="BP40" s="41" t="n"/>
+      <c r="BQ40" s="42" t="n"/>
       <c r="BR40" s="31" t="n"/>
-      <c r="BS40" s="39" t="n"/>
-      <c r="BT40" s="39" t="n"/>
-      <c r="BU40" s="40" t="n"/>
+      <c r="BS40" s="41" t="n"/>
+      <c r="BT40" s="41" t="n"/>
+      <c r="BU40" s="42" t="n"/>
       <c r="BV40" s="31" t="n"/>
-      <c r="BW40" s="39" t="n"/>
-      <c r="BX40" s="39" t="n"/>
-      <c r="BY40" s="40" t="n"/>
+      <c r="BW40" s="41" t="n"/>
+      <c r="BX40" s="41" t="n"/>
+      <c r="BY40" s="42" t="n"/>
       <c r="BZ40" s="31" t="n"/>
-      <c r="CA40" s="39" t="n"/>
-      <c r="CB40" s="39" t="n"/>
-      <c r="CC40" s="40" t="n"/>
+      <c r="CA40" s="41" t="n"/>
+      <c r="CB40" s="41" t="n"/>
+      <c r="CC40" s="42" t="n"/>
       <c r="CD40" s="31" t="n"/>
-      <c r="CE40" s="39" t="n"/>
-      <c r="CF40" s="39" t="n"/>
-      <c r="CG40" s="50" t="n"/>
+      <c r="CE40" s="41" t="n"/>
+      <c r="CF40" s="41" t="n"/>
+      <c r="CG40" s="54" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="29" t="inlineStr">
@@ -5791,97 +5964,97 @@
         </is>
       </c>
       <c r="F41" s="31" t="n"/>
-      <c r="G41" s="39" t="n"/>
-      <c r="H41" s="39" t="n"/>
-      <c r="I41" s="40" t="n"/>
+      <c r="G41" s="41" t="n"/>
+      <c r="H41" s="41" t="n"/>
+      <c r="I41" s="42" t="n"/>
       <c r="J41" s="31" t="n"/>
-      <c r="K41" s="39" t="n"/>
-      <c r="L41" s="39" t="n"/>
-      <c r="M41" s="40" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="41" t="n"/>
+      <c r="M41" s="42" t="n"/>
       <c r="N41" s="31" t="n"/>
-      <c r="O41" s="39" t="n"/>
-      <c r="P41" s="39" t="n"/>
-      <c r="Q41" s="40" t="n"/>
+      <c r="O41" s="41" t="n"/>
+      <c r="P41" s="41" t="n"/>
+      <c r="Q41" s="42" t="n"/>
       <c r="R41" s="31" t="n"/>
-      <c r="S41" s="39" t="n"/>
-      <c r="T41" s="39" t="n"/>
-      <c r="U41" s="40" t="n"/>
+      <c r="S41" s="41" t="n"/>
+      <c r="T41" s="41" t="n"/>
+      <c r="U41" s="42" t="n"/>
       <c r="V41" s="31" t="n"/>
-      <c r="W41" s="39" t="n"/>
-      <c r="X41" s="39" t="n"/>
-      <c r="Y41" s="40" t="n"/>
+      <c r="W41" s="41" t="n"/>
+      <c r="X41" s="41" t="n"/>
+      <c r="Y41" s="42" t="n"/>
       <c r="Z41" s="31" t="n"/>
-      <c r="AA41" s="39" t="n"/>
-      <c r="AB41" s="39" t="n"/>
-      <c r="AC41" s="40" t="n"/>
+      <c r="AA41" s="41" t="n"/>
+      <c r="AB41" s="41" t="n"/>
+      <c r="AC41" s="42" t="n"/>
       <c r="AD41" s="31" t="n"/>
-      <c r="AE41" s="39" t="n"/>
-      <c r="AF41" s="39" t="n"/>
-      <c r="AG41" s="40" t="n"/>
+      <c r="AE41" s="41" t="n"/>
+      <c r="AF41" s="41" t="n"/>
+      <c r="AG41" s="42" t="n"/>
       <c r="AH41" s="31" t="n"/>
-      <c r="AI41" s="39" t="n"/>
-      <c r="AJ41" s="39" t="n"/>
-      <c r="AK41" s="40" t="n"/>
+      <c r="AI41" s="41" t="n"/>
+      <c r="AJ41" s="41" t="n"/>
+      <c r="AK41" s="42" t="n"/>
       <c r="AL41" s="31" t="n"/>
-      <c r="AM41" s="39" t="n"/>
-      <c r="AN41" s="39" t="n"/>
-      <c r="AO41" s="40" t="n"/>
+      <c r="AM41" s="41" t="n"/>
+      <c r="AN41" s="41" t="n"/>
+      <c r="AO41" s="42" t="n"/>
       <c r="AP41" s="31" t="n"/>
-      <c r="AQ41" s="39" t="n"/>
-      <c r="AR41" s="39" t="n"/>
-      <c r="AS41" s="40" t="n"/>
-      <c r="AT41" s="88" t="n"/>
+      <c r="AQ41" s="41" t="n"/>
+      <c r="AR41" s="41" t="n"/>
+      <c r="AS41" s="42" t="n"/>
+      <c r="AT41" s="92" t="n"/>
       <c r="AU41" s="33" t="n"/>
       <c r="AV41" s="33" t="n"/>
       <c r="AW41" s="34" t="n"/>
-      <c r="AX41" s="88" t="n"/>
+      <c r="AX41" s="92" t="n"/>
       <c r="AY41" s="33" t="n"/>
       <c r="AZ41" s="33" t="n"/>
       <c r="BA41" s="34" t="n"/>
-      <c r="BB41" s="88" t="n"/>
+      <c r="BB41" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="BC41" s="33" t="n"/>
       <c r="BD41" s="33" t="n"/>
       <c r="BE41" s="34" t="n"/>
-      <c r="BF41" s="56" t="inlineStr">
+      <c r="BF41" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BG41" s="33" t="n"/>
-      <c r="BH41" s="57" t="inlineStr">
+      <c r="BH41" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BI41" s="34" t="n"/>
-      <c r="BJ41" s="88" t="n"/>
+      <c r="BJ41" s="92" t="n"/>
       <c r="BK41" s="33" t="n"/>
       <c r="BL41" s="33" t="n"/>
       <c r="BM41" s="34" t="n"/>
-      <c r="BN41" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BN41" s="92" t="n"/>
       <c r="BO41" s="33" t="n"/>
       <c r="BP41" s="33" t="n"/>
       <c r="BQ41" s="34" t="n"/>
-      <c r="BR41" s="88" t="n"/>
+      <c r="BR41" s="92" t="n"/>
       <c r="BS41" s="33" t="n"/>
       <c r="BT41" s="33" t="n"/>
       <c r="BU41" s="34" t="n"/>
-      <c r="BV41" s="88" t="n"/>
+      <c r="BV41" s="92" t="n"/>
       <c r="BW41" s="33" t="n"/>
       <c r="BX41" s="33" t="n"/>
       <c r="BY41" s="34" t="n"/>
       <c r="BZ41" s="31" t="n"/>
-      <c r="CA41" s="39" t="n"/>
-      <c r="CB41" s="39" t="n"/>
-      <c r="CC41" s="40" t="n"/>
+      <c r="CA41" s="41" t="n"/>
+      <c r="CB41" s="41" t="n"/>
+      <c r="CC41" s="42" t="n"/>
       <c r="CD41" s="31" t="n"/>
-      <c r="CE41" s="39" t="n"/>
-      <c r="CF41" s="39" t="n"/>
-      <c r="CG41" s="50" t="n"/>
+      <c r="CE41" s="41" t="n"/>
+      <c r="CF41" s="41" t="n"/>
+      <c r="CG41" s="54" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="29" t="inlineStr">
@@ -5906,93 +6079,97 @@
       </c>
       <c r="E42" s="30" t="inlineStr"/>
       <c r="F42" s="31" t="n"/>
-      <c r="G42" s="39" t="n"/>
-      <c r="H42" s="39" t="n"/>
-      <c r="I42" s="40" t="n"/>
+      <c r="G42" s="41" t="n"/>
+      <c r="H42" s="41" t="n"/>
+      <c r="I42" s="42" t="n"/>
       <c r="J42" s="31" t="n"/>
-      <c r="K42" s="39" t="n"/>
-      <c r="L42" s="39" t="n"/>
-      <c r="M42" s="40" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="41" t="n"/>
+      <c r="M42" s="42" t="n"/>
       <c r="N42" s="31" t="n"/>
-      <c r="O42" s="39" t="n"/>
-      <c r="P42" s="39" t="n"/>
-      <c r="Q42" s="40" t="n"/>
+      <c r="O42" s="41" t="n"/>
+      <c r="P42" s="41" t="n"/>
+      <c r="Q42" s="42" t="n"/>
       <c r="R42" s="31" t="n"/>
-      <c r="S42" s="39" t="n"/>
-      <c r="T42" s="39" t="n"/>
-      <c r="U42" s="40" t="n"/>
+      <c r="S42" s="41" t="n"/>
+      <c r="T42" s="41" t="n"/>
+      <c r="U42" s="42" t="n"/>
       <c r="V42" s="31" t="n"/>
-      <c r="W42" s="39" t="n"/>
-      <c r="X42" s="39" t="n"/>
-      <c r="Y42" s="40" t="n"/>
+      <c r="W42" s="41" t="n"/>
+      <c r="X42" s="41" t="n"/>
+      <c r="Y42" s="42" t="n"/>
       <c r="Z42" s="31" t="n"/>
-      <c r="AA42" s="39" t="n"/>
-      <c r="AB42" s="39" t="n"/>
-      <c r="AC42" s="40" t="n"/>
+      <c r="AA42" s="41" t="n"/>
+      <c r="AB42" s="41" t="n"/>
+      <c r="AC42" s="42" t="n"/>
       <c r="AD42" s="31" t="n"/>
-      <c r="AE42" s="39" t="n"/>
-      <c r="AF42" s="39" t="n"/>
-      <c r="AG42" s="40" t="n"/>
+      <c r="AE42" s="41" t="n"/>
+      <c r="AF42" s="41" t="n"/>
+      <c r="AG42" s="42" t="n"/>
       <c r="AH42" s="31" t="n"/>
-      <c r="AI42" s="39" t="n"/>
-      <c r="AJ42" s="39" t="n"/>
-      <c r="AK42" s="40" t="n"/>
+      <c r="AI42" s="41" t="n"/>
+      <c r="AJ42" s="41" t="n"/>
+      <c r="AK42" s="42" t="n"/>
       <c r="AL42" s="31" t="n"/>
-      <c r="AM42" s="39" t="n"/>
-      <c r="AN42" s="39" t="n"/>
-      <c r="AO42" s="40" t="n"/>
+      <c r="AM42" s="41" t="n"/>
+      <c r="AN42" s="41" t="n"/>
+      <c r="AO42" s="42" t="n"/>
       <c r="AP42" s="31" t="n"/>
-      <c r="AQ42" s="39" t="n"/>
-      <c r="AR42" s="39" t="n"/>
-      <c r="AS42" s="40" t="n"/>
+      <c r="AQ42" s="41" t="n"/>
+      <c r="AR42" s="41" t="n"/>
+      <c r="AS42" s="42" t="n"/>
       <c r="AT42" s="31" t="n"/>
-      <c r="AU42" s="39" t="n"/>
-      <c r="AV42" s="81" t="n"/>
+      <c r="AU42" s="41" t="n"/>
+      <c r="AV42" s="85" t="n"/>
       <c r="AW42" s="34" t="n"/>
-      <c r="AX42" s="82" t="n"/>
+      <c r="AX42" s="86" t="n"/>
       <c r="AY42" s="33" t="n"/>
       <c r="AZ42" s="33" t="n"/>
       <c r="BA42" s="34" t="n"/>
-      <c r="BB42" s="82" t="n"/>
+      <c r="BB42" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BC42" s="33" t="n"/>
       <c r="BD42" s="33" t="n"/>
       <c r="BE42" s="34" t="n"/>
-      <c r="BF42" s="82" t="n"/>
+      <c r="BF42" s="86" t="n"/>
       <c r="BG42" s="33" t="n"/>
       <c r="BH42" s="33" t="n"/>
       <c r="BI42" s="34" t="n"/>
-      <c r="BJ42" s="36" t="inlineStr">
+      <c r="BJ42" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BK42" s="33" t="n"/>
-      <c r="BL42" s="37" t="inlineStr">
+      <c r="BL42" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BM42" s="34" t="n"/>
-      <c r="BN42" s="82" t="n"/>
+      <c r="BN42" s="86" t="n"/>
       <c r="BO42" s="33" t="n"/>
       <c r="BP42" s="33" t="n"/>
       <c r="BQ42" s="34" t="n"/>
-      <c r="BR42" s="82" t="n"/>
+      <c r="BR42" s="86" t="n"/>
       <c r="BS42" s="33" t="n"/>
       <c r="BT42" s="33" t="n"/>
       <c r="BU42" s="34" t="n"/>
-      <c r="BV42" s="82" t="n"/>
+      <c r="BV42" s="86" t="n"/>
       <c r="BW42" s="33" t="n"/>
       <c r="BX42" s="33" t="n"/>
       <c r="BY42" s="34" t="n"/>
       <c r="BZ42" s="31" t="n"/>
-      <c r="CA42" s="39" t="n"/>
-      <c r="CB42" s="39" t="n"/>
-      <c r="CC42" s="40" t="n"/>
+      <c r="CA42" s="41" t="n"/>
+      <c r="CB42" s="41" t="n"/>
+      <c r="CC42" s="42" t="n"/>
       <c r="CD42" s="31" t="n"/>
-      <c r="CE42" s="39" t="n"/>
-      <c r="CF42" s="39" t="n"/>
-      <c r="CG42" s="50" t="n"/>
+      <c r="CE42" s="41" t="n"/>
+      <c r="CF42" s="41" t="n"/>
+      <c r="CG42" s="54" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="29" t="inlineStr">
@@ -6021,89 +6198,97 @@
         </is>
       </c>
       <c r="F43" s="31" t="n"/>
-      <c r="G43" s="39" t="n"/>
-      <c r="H43" s="39" t="n"/>
-      <c r="I43" s="40" t="n"/>
+      <c r="G43" s="41" t="n"/>
+      <c r="H43" s="41" t="n"/>
+      <c r="I43" s="42" t="n"/>
       <c r="J43" s="31" t="n"/>
-      <c r="K43" s="39" t="n"/>
-      <c r="L43" s="39" t="n"/>
-      <c r="M43" s="40" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="41" t="n"/>
+      <c r="M43" s="42" t="n"/>
       <c r="N43" s="31" t="n"/>
-      <c r="O43" s="39" t="n"/>
-      <c r="P43" s="39" t="n"/>
-      <c r="Q43" s="40" t="n"/>
+      <c r="O43" s="41" t="n"/>
+      <c r="P43" s="41" t="n"/>
+      <c r="Q43" s="42" t="n"/>
       <c r="R43" s="31" t="n"/>
-      <c r="S43" s="39" t="n"/>
-      <c r="T43" s="39" t="n"/>
-      <c r="U43" s="40" t="n"/>
+      <c r="S43" s="41" t="n"/>
+      <c r="T43" s="41" t="n"/>
+      <c r="U43" s="42" t="n"/>
       <c r="V43" s="31" t="n"/>
-      <c r="W43" s="39" t="n"/>
-      <c r="X43" s="39" t="n"/>
-      <c r="Y43" s="40" t="n"/>
+      <c r="W43" s="41" t="n"/>
+      <c r="X43" s="41" t="n"/>
+      <c r="Y43" s="42" t="n"/>
       <c r="Z43" s="31" t="n"/>
-      <c r="AA43" s="39" t="n"/>
-      <c r="AB43" s="39" t="n"/>
-      <c r="AC43" s="40" t="n"/>
+      <c r="AA43" s="41" t="n"/>
+      <c r="AB43" s="41" t="n"/>
+      <c r="AC43" s="42" t="n"/>
       <c r="AD43" s="31" t="n"/>
-      <c r="AE43" s="39" t="n"/>
-      <c r="AF43" s="39" t="n"/>
-      <c r="AG43" s="40" t="n"/>
+      <c r="AE43" s="41" t="n"/>
+      <c r="AF43" s="41" t="n"/>
+      <c r="AG43" s="42" t="n"/>
       <c r="AH43" s="31" t="n"/>
-      <c r="AI43" s="39" t="n"/>
-      <c r="AJ43" s="39" t="n"/>
-      <c r="AK43" s="40" t="n"/>
+      <c r="AI43" s="41" t="n"/>
+      <c r="AJ43" s="41" t="n"/>
+      <c r="AK43" s="42" t="n"/>
       <c r="AL43" s="31" t="n"/>
-      <c r="AM43" s="39" t="n"/>
-      <c r="AN43" s="39" t="n"/>
-      <c r="AO43" s="40" t="n"/>
+      <c r="AM43" s="41" t="n"/>
+      <c r="AN43" s="41" t="n"/>
+      <c r="AO43" s="42" t="n"/>
       <c r="AP43" s="31" t="n"/>
-      <c r="AQ43" s="39" t="n"/>
-      <c r="AR43" s="39" t="n"/>
-      <c r="AS43" s="40" t="n"/>
+      <c r="AQ43" s="41" t="n"/>
+      <c r="AR43" s="41" t="n"/>
+      <c r="AS43" s="42" t="n"/>
       <c r="AT43" s="31" t="n"/>
-      <c r="AU43" s="39" t="n"/>
-      <c r="AV43" s="39" t="n"/>
-      <c r="AW43" s="40" t="n"/>
-      <c r="AX43" s="88" t="n"/>
+      <c r="AU43" s="41" t="n"/>
+      <c r="AV43" s="41" t="n"/>
+      <c r="AW43" s="42" t="n"/>
+      <c r="AX43" s="92" t="n"/>
       <c r="AY43" s="33" t="n"/>
       <c r="AZ43" s="33" t="n"/>
       <c r="BA43" s="34" t="n"/>
-      <c r="BB43" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
+      <c r="BB43" s="48" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="BC43" s="33" t="n"/>
       <c r="BD43" s="33" t="n"/>
       <c r="BE43" s="34" t="n"/>
-      <c r="BF43" s="88" t="n"/>
+      <c r="BF43" s="35" t="inlineStr">
+        <is>
+          <t>Security Check</t>
+        </is>
+      </c>
       <c r="BG43" s="33" t="n"/>
       <c r="BH43" s="33" t="n"/>
       <c r="BI43" s="34" t="n"/>
-      <c r="BJ43" s="88" t="n"/>
+      <c r="BJ43" s="55" t="inlineStr">
+        <is>
+          <t>VIP/MIP</t>
+        </is>
+      </c>
       <c r="BK43" s="33" t="n"/>
       <c r="BL43" s="33" t="n"/>
       <c r="BM43" s="34" t="n"/>
       <c r="BN43" s="31" t="n"/>
-      <c r="BO43" s="39" t="n"/>
-      <c r="BP43" s="39" t="n"/>
-      <c r="BQ43" s="40" t="n"/>
+      <c r="BO43" s="41" t="n"/>
+      <c r="BP43" s="41" t="n"/>
+      <c r="BQ43" s="42" t="n"/>
       <c r="BR43" s="31" t="n"/>
-      <c r="BS43" s="39" t="n"/>
-      <c r="BT43" s="39" t="n"/>
-      <c r="BU43" s="40" t="n"/>
+      <c r="BS43" s="41" t="n"/>
+      <c r="BT43" s="41" t="n"/>
+      <c r="BU43" s="42" t="n"/>
       <c r="BV43" s="31" t="n"/>
-      <c r="BW43" s="39" t="n"/>
-      <c r="BX43" s="39" t="n"/>
-      <c r="BY43" s="40" t="n"/>
+      <c r="BW43" s="41" t="n"/>
+      <c r="BX43" s="41" t="n"/>
+      <c r="BY43" s="42" t="n"/>
       <c r="BZ43" s="31" t="n"/>
-      <c r="CA43" s="39" t="n"/>
-      <c r="CB43" s="39" t="n"/>
-      <c r="CC43" s="40" t="n"/>
+      <c r="CA43" s="41" t="n"/>
+      <c r="CB43" s="41" t="n"/>
+      <c r="CC43" s="42" t="n"/>
       <c r="CD43" s="31" t="n"/>
-      <c r="CE43" s="39" t="n"/>
-      <c r="CF43" s="39" t="n"/>
-      <c r="CG43" s="50" t="n"/>
+      <c r="CE43" s="41" t="n"/>
+      <c r="CF43" s="41" t="n"/>
+      <c r="CG43" s="54" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="29" t="inlineStr">
@@ -6132,93 +6317,97 @@
         </is>
       </c>
       <c r="F44" s="31" t="n"/>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="39" t="n"/>
-      <c r="I44" s="40" t="n"/>
+      <c r="G44" s="41" t="n"/>
+      <c r="H44" s="41" t="n"/>
+      <c r="I44" s="42" t="n"/>
       <c r="J44" s="31" t="n"/>
-      <c r="K44" s="39" t="n"/>
-      <c r="L44" s="39" t="n"/>
-      <c r="M44" s="40" t="n"/>
+      <c r="K44" s="41" t="n"/>
+      <c r="L44" s="41" t="n"/>
+      <c r="M44" s="42" t="n"/>
       <c r="N44" s="31" t="n"/>
-      <c r="O44" s="39" t="n"/>
-      <c r="P44" s="39" t="n"/>
-      <c r="Q44" s="40" t="n"/>
+      <c r="O44" s="41" t="n"/>
+      <c r="P44" s="41" t="n"/>
+      <c r="Q44" s="42" t="n"/>
       <c r="R44" s="31" t="n"/>
-      <c r="S44" s="39" t="n"/>
-      <c r="T44" s="39" t="n"/>
-      <c r="U44" s="40" t="n"/>
+      <c r="S44" s="41" t="n"/>
+      <c r="T44" s="41" t="n"/>
+      <c r="U44" s="42" t="n"/>
       <c r="V44" s="31" t="n"/>
-      <c r="W44" s="39" t="n"/>
-      <c r="X44" s="39" t="n"/>
-      <c r="Y44" s="40" t="n"/>
+      <c r="W44" s="41" t="n"/>
+      <c r="X44" s="41" t="n"/>
+      <c r="Y44" s="42" t="n"/>
       <c r="Z44" s="31" t="n"/>
-      <c r="AA44" s="39" t="n"/>
-      <c r="AB44" s="39" t="n"/>
-      <c r="AC44" s="40" t="n"/>
+      <c r="AA44" s="41" t="n"/>
+      <c r="AB44" s="41" t="n"/>
+      <c r="AC44" s="42" t="n"/>
       <c r="AD44" s="31" t="n"/>
-      <c r="AE44" s="39" t="n"/>
-      <c r="AF44" s="39" t="n"/>
-      <c r="AG44" s="40" t="n"/>
+      <c r="AE44" s="41" t="n"/>
+      <c r="AF44" s="41" t="n"/>
+      <c r="AG44" s="42" t="n"/>
       <c r="AH44" s="31" t="n"/>
-      <c r="AI44" s="39" t="n"/>
-      <c r="AJ44" s="39" t="n"/>
-      <c r="AK44" s="40" t="n"/>
+      <c r="AI44" s="41" t="n"/>
+      <c r="AJ44" s="41" t="n"/>
+      <c r="AK44" s="42" t="n"/>
       <c r="AL44" s="31" t="n"/>
-      <c r="AM44" s="39" t="n"/>
-      <c r="AN44" s="39" t="n"/>
-      <c r="AO44" s="40" t="n"/>
+      <c r="AM44" s="41" t="n"/>
+      <c r="AN44" s="41" t="n"/>
+      <c r="AO44" s="42" t="n"/>
       <c r="AP44" s="31" t="n"/>
-      <c r="AQ44" s="39" t="n"/>
-      <c r="AR44" s="39" t="n"/>
-      <c r="AS44" s="40" t="n"/>
+      <c r="AQ44" s="41" t="n"/>
+      <c r="AR44" s="41" t="n"/>
+      <c r="AS44" s="42" t="n"/>
       <c r="AT44" s="31" t="n"/>
-      <c r="AU44" s="39" t="n"/>
-      <c r="AV44" s="39" t="n"/>
-      <c r="AW44" s="40" t="n"/>
+      <c r="AU44" s="41" t="n"/>
+      <c r="AV44" s="41" t="n"/>
+      <c r="AW44" s="42" t="n"/>
       <c r="AX44" s="31" t="n"/>
-      <c r="AY44" s="39" t="n"/>
-      <c r="AZ44" s="39" t="n"/>
-      <c r="BA44" s="40" t="n"/>
-      <c r="BB44" s="88" t="n"/>
+      <c r="AY44" s="41" t="n"/>
+      <c r="AZ44" s="41" t="n"/>
+      <c r="BA44" s="42" t="n"/>
+      <c r="BB44" s="92" t="n"/>
       <c r="BC44" s="33" t="n"/>
       <c r="BD44" s="33" t="n"/>
       <c r="BE44" s="34" t="n"/>
-      <c r="BF44" s="88" t="n"/>
+      <c r="BF44" s="48" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="BG44" s="33" t="n"/>
       <c r="BH44" s="33" t="n"/>
       <c r="BI44" s="34" t="n"/>
-      <c r="BJ44" s="88" t="n"/>
+      <c r="BJ44" s="92" t="n"/>
       <c r="BK44" s="33" t="n"/>
       <c r="BL44" s="33" t="n"/>
       <c r="BM44" s="34" t="n"/>
-      <c r="BN44" s="56" t="inlineStr">
+      <c r="BN44" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BO44" s="33" t="n"/>
-      <c r="BP44" s="57" t="inlineStr">
+      <c r="BP44" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BQ44" s="34" t="n"/>
-      <c r="BR44" s="88" t="n"/>
+      <c r="BR44" s="92" t="n"/>
       <c r="BS44" s="33" t="n"/>
       <c r="BT44" s="33" t="n"/>
       <c r="BU44" s="34" t="n"/>
-      <c r="BV44" s="88" t="n"/>
+      <c r="BV44" s="92" t="n"/>
       <c r="BW44" s="33" t="n"/>
       <c r="BX44" s="33" t="n"/>
       <c r="BY44" s="34" t="n"/>
-      <c r="BZ44" s="88" t="n"/>
+      <c r="BZ44" s="92" t="n"/>
       <c r="CA44" s="33" t="n"/>
       <c r="CB44" s="33" t="n"/>
       <c r="CC44" s="34" t="n"/>
-      <c r="CD44" s="92" t="n"/>
+      <c r="CD44" s="96" t="n"/>
       <c r="CE44" s="33" t="n"/>
       <c r="CF44" s="33" t="n"/>
-      <c r="CG44" s="50" t="n"/>
+      <c r="CG44" s="54" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="29" t="inlineStr">
@@ -6247,97 +6436,93 @@
         </is>
       </c>
       <c r="F45" s="31" t="n"/>
-      <c r="G45" s="39" t="n"/>
-      <c r="H45" s="39" t="n"/>
-      <c r="I45" s="40" t="n"/>
+      <c r="G45" s="41" t="n"/>
+      <c r="H45" s="41" t="n"/>
+      <c r="I45" s="42" t="n"/>
       <c r="J45" s="31" t="n"/>
-      <c r="K45" s="39" t="n"/>
-      <c r="L45" s="39" t="n"/>
-      <c r="M45" s="40" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="41" t="n"/>
+      <c r="M45" s="42" t="n"/>
       <c r="N45" s="31" t="n"/>
-      <c r="O45" s="39" t="n"/>
-      <c r="P45" s="39" t="n"/>
-      <c r="Q45" s="40" t="n"/>
+      <c r="O45" s="41" t="n"/>
+      <c r="P45" s="41" t="n"/>
+      <c r="Q45" s="42" t="n"/>
       <c r="R45" s="31" t="n"/>
-      <c r="S45" s="39" t="n"/>
-      <c r="T45" s="39" t="n"/>
-      <c r="U45" s="40" t="n"/>
+      <c r="S45" s="41" t="n"/>
+      <c r="T45" s="41" t="n"/>
+      <c r="U45" s="42" t="n"/>
       <c r="V45" s="31" t="n"/>
-      <c r="W45" s="39" t="n"/>
-      <c r="X45" s="39" t="n"/>
-      <c r="Y45" s="40" t="n"/>
+      <c r="W45" s="41" t="n"/>
+      <c r="X45" s="41" t="n"/>
+      <c r="Y45" s="42" t="n"/>
       <c r="Z45" s="31" t="n"/>
-      <c r="AA45" s="39" t="n"/>
-      <c r="AB45" s="39" t="n"/>
-      <c r="AC45" s="40" t="n"/>
+      <c r="AA45" s="41" t="n"/>
+      <c r="AB45" s="41" t="n"/>
+      <c r="AC45" s="42" t="n"/>
       <c r="AD45" s="31" t="n"/>
-      <c r="AE45" s="39" t="n"/>
-      <c r="AF45" s="39" t="n"/>
-      <c r="AG45" s="40" t="n"/>
+      <c r="AE45" s="41" t="n"/>
+      <c r="AF45" s="41" t="n"/>
+      <c r="AG45" s="42" t="n"/>
       <c r="AH45" s="31" t="n"/>
-      <c r="AI45" s="39" t="n"/>
-      <c r="AJ45" s="39" t="n"/>
-      <c r="AK45" s="40" t="n"/>
+      <c r="AI45" s="41" t="n"/>
+      <c r="AJ45" s="41" t="n"/>
+      <c r="AK45" s="42" t="n"/>
       <c r="AL45" s="31" t="n"/>
-      <c r="AM45" s="39" t="n"/>
-      <c r="AN45" s="39" t="n"/>
-      <c r="AO45" s="40" t="n"/>
+      <c r="AM45" s="41" t="n"/>
+      <c r="AN45" s="41" t="n"/>
+      <c r="AO45" s="42" t="n"/>
       <c r="AP45" s="31" t="n"/>
-      <c r="AQ45" s="39" t="n"/>
-      <c r="AR45" s="39" t="n"/>
-      <c r="AS45" s="40" t="n"/>
+      <c r="AQ45" s="41" t="n"/>
+      <c r="AR45" s="41" t="n"/>
+      <c r="AS45" s="42" t="n"/>
       <c r="AT45" s="31" t="n"/>
-      <c r="AU45" s="39" t="n"/>
-      <c r="AV45" s="39" t="n"/>
-      <c r="AW45" s="40" t="n"/>
+      <c r="AU45" s="41" t="n"/>
+      <c r="AV45" s="41" t="n"/>
+      <c r="AW45" s="42" t="n"/>
       <c r="AX45" s="31" t="n"/>
-      <c r="AY45" s="39" t="n"/>
-      <c r="AZ45" s="39" t="n"/>
-      <c r="BA45" s="40" t="n"/>
+      <c r="AY45" s="41" t="n"/>
+      <c r="AZ45" s="41" t="n"/>
+      <c r="BA45" s="42" t="n"/>
       <c r="BB45" s="31" t="n"/>
-      <c r="BC45" s="39" t="n"/>
-      <c r="BD45" s="81" t="n"/>
+      <c r="BC45" s="41" t="n"/>
+      <c r="BD45" s="85" t="n"/>
       <c r="BE45" s="34" t="n"/>
-      <c r="BF45" s="82" t="n"/>
+      <c r="BF45" s="86" t="n"/>
       <c r="BG45" s="33" t="n"/>
       <c r="BH45" s="33" t="n"/>
       <c r="BI45" s="34" t="n"/>
-      <c r="BJ45" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BJ45" s="86" t="n"/>
       <c r="BK45" s="33" t="n"/>
       <c r="BL45" s="33" t="n"/>
       <c r="BM45" s="34" t="n"/>
-      <c r="BN45" s="82" t="n"/>
+      <c r="BN45" s="86" t="n"/>
       <c r="BO45" s="33" t="n"/>
       <c r="BP45" s="33" t="n"/>
       <c r="BQ45" s="34" t="n"/>
-      <c r="BR45" s="36" t="inlineStr">
+      <c r="BR45" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BS45" s="33" t="n"/>
-      <c r="BT45" s="37" t="inlineStr">
+      <c r="BT45" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BU45" s="34" t="n"/>
-      <c r="BV45" s="82" t="n"/>
+      <c r="BV45" s="86" t="n"/>
       <c r="BW45" s="33" t="n"/>
       <c r="BX45" s="33" t="n"/>
       <c r="BY45" s="34" t="n"/>
-      <c r="BZ45" s="82" t="n"/>
+      <c r="BZ45" s="86" t="n"/>
       <c r="CA45" s="33" t="n"/>
       <c r="CB45" s="33" t="n"/>
       <c r="CC45" s="34" t="n"/>
-      <c r="CD45" s="83" t="n"/>
+      <c r="CD45" s="87" t="n"/>
       <c r="CE45" s="33" t="n"/>
       <c r="CF45" s="33" t="n"/>
-      <c r="CG45" s="50" t="n"/>
+      <c r="CG45" s="54" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="29" t="inlineStr"/>
@@ -6346,85 +6531,85 @@
       <c r="D46" s="30" t="n"/>
       <c r="E46" s="30" t="n"/>
       <c r="F46" s="31" t="n"/>
-      <c r="G46" s="39" t="n"/>
-      <c r="H46" s="39" t="n"/>
-      <c r="I46" s="40" t="n"/>
+      <c r="G46" s="41" t="n"/>
+      <c r="H46" s="41" t="n"/>
+      <c r="I46" s="42" t="n"/>
       <c r="J46" s="31" t="n"/>
-      <c r="K46" s="39" t="n"/>
-      <c r="L46" s="39" t="n"/>
-      <c r="M46" s="40" t="n"/>
+      <c r="K46" s="41" t="n"/>
+      <c r="L46" s="41" t="n"/>
+      <c r="M46" s="42" t="n"/>
       <c r="N46" s="31" t="n"/>
-      <c r="O46" s="39" t="n"/>
-      <c r="P46" s="39" t="n"/>
-      <c r="Q46" s="40" t="n"/>
+      <c r="O46" s="41" t="n"/>
+      <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="42" t="n"/>
       <c r="R46" s="31" t="n"/>
-      <c r="S46" s="39" t="n"/>
-      <c r="T46" s="39" t="n"/>
-      <c r="U46" s="40" t="n"/>
+      <c r="S46" s="41" t="n"/>
+      <c r="T46" s="41" t="n"/>
+      <c r="U46" s="42" t="n"/>
       <c r="V46" s="31" t="n"/>
-      <c r="W46" s="39" t="n"/>
-      <c r="X46" s="39" t="n"/>
-      <c r="Y46" s="40" t="n"/>
+      <c r="W46" s="41" t="n"/>
+      <c r="X46" s="41" t="n"/>
+      <c r="Y46" s="42" t="n"/>
       <c r="Z46" s="31" t="n"/>
-      <c r="AA46" s="39" t="n"/>
-      <c r="AB46" s="39" t="n"/>
-      <c r="AC46" s="40" t="n"/>
+      <c r="AA46" s="41" t="n"/>
+      <c r="AB46" s="41" t="n"/>
+      <c r="AC46" s="42" t="n"/>
       <c r="AD46" s="31" t="n"/>
-      <c r="AE46" s="39" t="n"/>
-      <c r="AF46" s="39" t="n"/>
-      <c r="AG46" s="40" t="n"/>
+      <c r="AE46" s="41" t="n"/>
+      <c r="AF46" s="41" t="n"/>
+      <c r="AG46" s="42" t="n"/>
       <c r="AH46" s="31" t="n"/>
-      <c r="AI46" s="39" t="n"/>
-      <c r="AJ46" s="39" t="n"/>
-      <c r="AK46" s="40" t="n"/>
+      <c r="AI46" s="41" t="n"/>
+      <c r="AJ46" s="41" t="n"/>
+      <c r="AK46" s="42" t="n"/>
       <c r="AL46" s="31" t="n"/>
-      <c r="AM46" s="39" t="n"/>
-      <c r="AN46" s="39" t="n"/>
-      <c r="AO46" s="40" t="n"/>
+      <c r="AM46" s="41" t="n"/>
+      <c r="AN46" s="41" t="n"/>
+      <c r="AO46" s="42" t="n"/>
       <c r="AP46" s="31" t="n"/>
-      <c r="AQ46" s="39" t="n"/>
-      <c r="AR46" s="39" t="n"/>
-      <c r="AS46" s="40" t="n"/>
+      <c r="AQ46" s="41" t="n"/>
+      <c r="AR46" s="41" t="n"/>
+      <c r="AS46" s="42" t="n"/>
       <c r="AT46" s="31" t="n"/>
-      <c r="AU46" s="39" t="n"/>
-      <c r="AV46" s="39" t="n"/>
-      <c r="AW46" s="40" t="n"/>
+      <c r="AU46" s="41" t="n"/>
+      <c r="AV46" s="41" t="n"/>
+      <c r="AW46" s="42" t="n"/>
       <c r="AX46" s="31" t="n"/>
-      <c r="AY46" s="39" t="n"/>
-      <c r="AZ46" s="39" t="n"/>
-      <c r="BA46" s="40" t="n"/>
+      <c r="AY46" s="41" t="n"/>
+      <c r="AZ46" s="41" t="n"/>
+      <c r="BA46" s="42" t="n"/>
       <c r="BB46" s="31" t="n"/>
-      <c r="BC46" s="39" t="n"/>
-      <c r="BD46" s="39" t="n"/>
-      <c r="BE46" s="40" t="n"/>
+      <c r="BC46" s="41" t="n"/>
+      <c r="BD46" s="41" t="n"/>
+      <c r="BE46" s="42" t="n"/>
       <c r="BF46" s="31" t="n"/>
-      <c r="BG46" s="39" t="n"/>
-      <c r="BH46" s="39" t="n"/>
-      <c r="BI46" s="40" t="n"/>
+      <c r="BG46" s="41" t="n"/>
+      <c r="BH46" s="41" t="n"/>
+      <c r="BI46" s="42" t="n"/>
       <c r="BJ46" s="31" t="n"/>
-      <c r="BK46" s="39" t="n"/>
-      <c r="BL46" s="39" t="n"/>
-      <c r="BM46" s="40" t="n"/>
+      <c r="BK46" s="41" t="n"/>
+      <c r="BL46" s="41" t="n"/>
+      <c r="BM46" s="42" t="n"/>
       <c r="BN46" s="31" t="n"/>
-      <c r="BO46" s="39" t="n"/>
-      <c r="BP46" s="39" t="n"/>
-      <c r="BQ46" s="40" t="n"/>
+      <c r="BO46" s="41" t="n"/>
+      <c r="BP46" s="41" t="n"/>
+      <c r="BQ46" s="42" t="n"/>
       <c r="BR46" s="31" t="n"/>
-      <c r="BS46" s="39" t="n"/>
-      <c r="BT46" s="39" t="n"/>
-      <c r="BU46" s="40" t="n"/>
+      <c r="BS46" s="41" t="n"/>
+      <c r="BT46" s="41" t="n"/>
+      <c r="BU46" s="42" t="n"/>
       <c r="BV46" s="31" t="n"/>
-      <c r="BW46" s="39" t="n"/>
-      <c r="BX46" s="39" t="n"/>
-      <c r="BY46" s="40" t="n"/>
+      <c r="BW46" s="41" t="n"/>
+      <c r="BX46" s="41" t="n"/>
+      <c r="BY46" s="42" t="n"/>
       <c r="BZ46" s="31" t="n"/>
-      <c r="CA46" s="39" t="n"/>
-      <c r="CB46" s="39" t="n"/>
-      <c r="CC46" s="40" t="n"/>
+      <c r="CA46" s="41" t="n"/>
+      <c r="CB46" s="41" t="n"/>
+      <c r="CC46" s="42" t="n"/>
       <c r="CD46" s="31" t="n"/>
-      <c r="CE46" s="39" t="n"/>
-      <c r="CF46" s="39" t="n"/>
-      <c r="CG46" s="50" t="n"/>
+      <c r="CE46" s="41" t="n"/>
+      <c r="CF46" s="41" t="n"/>
+      <c r="CG46" s="54" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="29" t="inlineStr"/>
@@ -6433,85 +6618,85 @@
       <c r="D47" s="30" t="n"/>
       <c r="E47" s="30" t="n"/>
       <c r="F47" s="31" t="n"/>
-      <c r="G47" s="39" t="n"/>
-      <c r="H47" s="39" t="n"/>
-      <c r="I47" s="40" t="n"/>
+      <c r="G47" s="41" t="n"/>
+      <c r="H47" s="41" t="n"/>
+      <c r="I47" s="42" t="n"/>
       <c r="J47" s="31" t="n"/>
-      <c r="K47" s="39" t="n"/>
-      <c r="L47" s="39" t="n"/>
-      <c r="M47" s="40" t="n"/>
+      <c r="K47" s="41" t="n"/>
+      <c r="L47" s="41" t="n"/>
+      <c r="M47" s="42" t="n"/>
       <c r="N47" s="31" t="n"/>
-      <c r="O47" s="39" t="n"/>
-      <c r="P47" s="39" t="n"/>
-      <c r="Q47" s="40" t="n"/>
+      <c r="O47" s="41" t="n"/>
+      <c r="P47" s="41" t="n"/>
+      <c r="Q47" s="42" t="n"/>
       <c r="R47" s="31" t="n"/>
-      <c r="S47" s="39" t="n"/>
-      <c r="T47" s="39" t="n"/>
-      <c r="U47" s="40" t="n"/>
+      <c r="S47" s="41" t="n"/>
+      <c r="T47" s="41" t="n"/>
+      <c r="U47" s="42" t="n"/>
       <c r="V47" s="31" t="n"/>
-      <c r="W47" s="39" t="n"/>
-      <c r="X47" s="39" t="n"/>
-      <c r="Y47" s="40" t="n"/>
+      <c r="W47" s="41" t="n"/>
+      <c r="X47" s="41" t="n"/>
+      <c r="Y47" s="42" t="n"/>
       <c r="Z47" s="31" t="n"/>
-      <c r="AA47" s="39" t="n"/>
-      <c r="AB47" s="39" t="n"/>
-      <c r="AC47" s="40" t="n"/>
+      <c r="AA47" s="41" t="n"/>
+      <c r="AB47" s="41" t="n"/>
+      <c r="AC47" s="42" t="n"/>
       <c r="AD47" s="31" t="n"/>
-      <c r="AE47" s="39" t="n"/>
-      <c r="AF47" s="39" t="n"/>
-      <c r="AG47" s="40" t="n"/>
+      <c r="AE47" s="41" t="n"/>
+      <c r="AF47" s="41" t="n"/>
+      <c r="AG47" s="42" t="n"/>
       <c r="AH47" s="31" t="n"/>
-      <c r="AI47" s="39" t="n"/>
-      <c r="AJ47" s="39" t="n"/>
-      <c r="AK47" s="40" t="n"/>
+      <c r="AI47" s="41" t="n"/>
+      <c r="AJ47" s="41" t="n"/>
+      <c r="AK47" s="42" t="n"/>
       <c r="AL47" s="31" t="n"/>
-      <c r="AM47" s="39" t="n"/>
-      <c r="AN47" s="39" t="n"/>
-      <c r="AO47" s="40" t="n"/>
+      <c r="AM47" s="41" t="n"/>
+      <c r="AN47" s="41" t="n"/>
+      <c r="AO47" s="42" t="n"/>
       <c r="AP47" s="31" t="n"/>
-      <c r="AQ47" s="39" t="n"/>
-      <c r="AR47" s="39" t="n"/>
-      <c r="AS47" s="40" t="n"/>
+      <c r="AQ47" s="41" t="n"/>
+      <c r="AR47" s="41" t="n"/>
+      <c r="AS47" s="42" t="n"/>
       <c r="AT47" s="31" t="n"/>
-      <c r="AU47" s="39" t="n"/>
-      <c r="AV47" s="39" t="n"/>
-      <c r="AW47" s="40" t="n"/>
+      <c r="AU47" s="41" t="n"/>
+      <c r="AV47" s="41" t="n"/>
+      <c r="AW47" s="42" t="n"/>
       <c r="AX47" s="31" t="n"/>
-      <c r="AY47" s="39" t="n"/>
-      <c r="AZ47" s="39" t="n"/>
-      <c r="BA47" s="40" t="n"/>
+      <c r="AY47" s="41" t="n"/>
+      <c r="AZ47" s="41" t="n"/>
+      <c r="BA47" s="42" t="n"/>
       <c r="BB47" s="31" t="n"/>
-      <c r="BC47" s="39" t="n"/>
-      <c r="BD47" s="39" t="n"/>
-      <c r="BE47" s="40" t="n"/>
+      <c r="BC47" s="41" t="n"/>
+      <c r="BD47" s="41" t="n"/>
+      <c r="BE47" s="42" t="n"/>
       <c r="BF47" s="31" t="n"/>
-      <c r="BG47" s="39" t="n"/>
-      <c r="BH47" s="39" t="n"/>
-      <c r="BI47" s="40" t="n"/>
+      <c r="BG47" s="41" t="n"/>
+      <c r="BH47" s="41" t="n"/>
+      <c r="BI47" s="42" t="n"/>
       <c r="BJ47" s="31" t="n"/>
-      <c r="BK47" s="39" t="n"/>
-      <c r="BL47" s="39" t="n"/>
-      <c r="BM47" s="40" t="n"/>
+      <c r="BK47" s="41" t="n"/>
+      <c r="BL47" s="41" t="n"/>
+      <c r="BM47" s="42" t="n"/>
       <c r="BN47" s="31" t="n"/>
-      <c r="BO47" s="39" t="n"/>
-      <c r="BP47" s="39" t="n"/>
-      <c r="BQ47" s="40" t="n"/>
+      <c r="BO47" s="41" t="n"/>
+      <c r="BP47" s="41" t="n"/>
+      <c r="BQ47" s="42" t="n"/>
       <c r="BR47" s="31" t="n"/>
-      <c r="BS47" s="39" t="n"/>
-      <c r="BT47" s="39" t="n"/>
-      <c r="BU47" s="40" t="n"/>
+      <c r="BS47" s="41" t="n"/>
+      <c r="BT47" s="41" t="n"/>
+      <c r="BU47" s="42" t="n"/>
       <c r="BV47" s="31" t="n"/>
-      <c r="BW47" s="39" t="n"/>
-      <c r="BX47" s="39" t="n"/>
-      <c r="BY47" s="40" t="n"/>
+      <c r="BW47" s="41" t="n"/>
+      <c r="BX47" s="41" t="n"/>
+      <c r="BY47" s="42" t="n"/>
       <c r="BZ47" s="31" t="n"/>
-      <c r="CA47" s="39" t="n"/>
-      <c r="CB47" s="39" t="n"/>
-      <c r="CC47" s="40" t="n"/>
+      <c r="CA47" s="41" t="n"/>
+      <c r="CB47" s="41" t="n"/>
+      <c r="CC47" s="42" t="n"/>
       <c r="CD47" s="31" t="n"/>
-      <c r="CE47" s="39" t="n"/>
-      <c r="CF47" s="39" t="n"/>
-      <c r="CG47" s="50" t="n"/>
+      <c r="CE47" s="41" t="n"/>
+      <c r="CF47" s="41" t="n"/>
+      <c r="CG47" s="54" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="29" t="inlineStr"/>
@@ -6520,85 +6705,85 @@
       <c r="D48" s="30" t="n"/>
       <c r="E48" s="30" t="n"/>
       <c r="F48" s="31" t="n"/>
-      <c r="G48" s="39" t="n"/>
-      <c r="H48" s="39" t="n"/>
-      <c r="I48" s="40" t="n"/>
+      <c r="G48" s="41" t="n"/>
+      <c r="H48" s="41" t="n"/>
+      <c r="I48" s="42" t="n"/>
       <c r="J48" s="31" t="n"/>
-      <c r="K48" s="39" t="n"/>
-      <c r="L48" s="39" t="n"/>
-      <c r="M48" s="40" t="n"/>
+      <c r="K48" s="41" t="n"/>
+      <c r="L48" s="41" t="n"/>
+      <c r="M48" s="42" t="n"/>
       <c r="N48" s="31" t="n"/>
-      <c r="O48" s="39" t="n"/>
-      <c r="P48" s="39" t="n"/>
-      <c r="Q48" s="40" t="n"/>
+      <c r="O48" s="41" t="n"/>
+      <c r="P48" s="41" t="n"/>
+      <c r="Q48" s="42" t="n"/>
       <c r="R48" s="31" t="n"/>
-      <c r="S48" s="39" t="n"/>
-      <c r="T48" s="39" t="n"/>
-      <c r="U48" s="40" t="n"/>
+      <c r="S48" s="41" t="n"/>
+      <c r="T48" s="41" t="n"/>
+      <c r="U48" s="42" t="n"/>
       <c r="V48" s="31" t="n"/>
-      <c r="W48" s="39" t="n"/>
-      <c r="X48" s="39" t="n"/>
-      <c r="Y48" s="40" t="n"/>
+      <c r="W48" s="41" t="n"/>
+      <c r="X48" s="41" t="n"/>
+      <c r="Y48" s="42" t="n"/>
       <c r="Z48" s="31" t="n"/>
-      <c r="AA48" s="39" t="n"/>
-      <c r="AB48" s="39" t="n"/>
-      <c r="AC48" s="40" t="n"/>
+      <c r="AA48" s="41" t="n"/>
+      <c r="AB48" s="41" t="n"/>
+      <c r="AC48" s="42" t="n"/>
       <c r="AD48" s="31" t="n"/>
-      <c r="AE48" s="39" t="n"/>
-      <c r="AF48" s="39" t="n"/>
-      <c r="AG48" s="40" t="n"/>
+      <c r="AE48" s="41" t="n"/>
+      <c r="AF48" s="41" t="n"/>
+      <c r="AG48" s="42" t="n"/>
       <c r="AH48" s="31" t="n"/>
-      <c r="AI48" s="39" t="n"/>
-      <c r="AJ48" s="39" t="n"/>
-      <c r="AK48" s="40" t="n"/>
+      <c r="AI48" s="41" t="n"/>
+      <c r="AJ48" s="41" t="n"/>
+      <c r="AK48" s="42" t="n"/>
       <c r="AL48" s="31" t="n"/>
-      <c r="AM48" s="39" t="n"/>
-      <c r="AN48" s="39" t="n"/>
-      <c r="AO48" s="40" t="n"/>
+      <c r="AM48" s="41" t="n"/>
+      <c r="AN48" s="41" t="n"/>
+      <c r="AO48" s="42" t="n"/>
       <c r="AP48" s="31" t="n"/>
-      <c r="AQ48" s="39" t="n"/>
-      <c r="AR48" s="39" t="n"/>
-      <c r="AS48" s="40" t="n"/>
+      <c r="AQ48" s="41" t="n"/>
+      <c r="AR48" s="41" t="n"/>
+      <c r="AS48" s="42" t="n"/>
       <c r="AT48" s="31" t="n"/>
-      <c r="AU48" s="39" t="n"/>
-      <c r="AV48" s="39" t="n"/>
-      <c r="AW48" s="40" t="n"/>
+      <c r="AU48" s="41" t="n"/>
+      <c r="AV48" s="41" t="n"/>
+      <c r="AW48" s="42" t="n"/>
       <c r="AX48" s="31" t="n"/>
-      <c r="AY48" s="39" t="n"/>
-      <c r="AZ48" s="39" t="n"/>
-      <c r="BA48" s="40" t="n"/>
+      <c r="AY48" s="41" t="n"/>
+      <c r="AZ48" s="41" t="n"/>
+      <c r="BA48" s="42" t="n"/>
       <c r="BB48" s="31" t="n"/>
-      <c r="BC48" s="39" t="n"/>
-      <c r="BD48" s="39" t="n"/>
-      <c r="BE48" s="40" t="n"/>
+      <c r="BC48" s="41" t="n"/>
+      <c r="BD48" s="41" t="n"/>
+      <c r="BE48" s="42" t="n"/>
       <c r="BF48" s="31" t="n"/>
-      <c r="BG48" s="39" t="n"/>
-      <c r="BH48" s="39" t="n"/>
-      <c r="BI48" s="40" t="n"/>
+      <c r="BG48" s="41" t="n"/>
+      <c r="BH48" s="41" t="n"/>
+      <c r="BI48" s="42" t="n"/>
       <c r="BJ48" s="31" t="n"/>
-      <c r="BK48" s="39" t="n"/>
-      <c r="BL48" s="39" t="n"/>
-      <c r="BM48" s="40" t="n"/>
+      <c r="BK48" s="41" t="n"/>
+      <c r="BL48" s="41" t="n"/>
+      <c r="BM48" s="42" t="n"/>
       <c r="BN48" s="31" t="n"/>
-      <c r="BO48" s="39" t="n"/>
-      <c r="BP48" s="39" t="n"/>
-      <c r="BQ48" s="40" t="n"/>
+      <c r="BO48" s="41" t="n"/>
+      <c r="BP48" s="41" t="n"/>
+      <c r="BQ48" s="42" t="n"/>
       <c r="BR48" s="31" t="n"/>
-      <c r="BS48" s="39" t="n"/>
-      <c r="BT48" s="39" t="n"/>
-      <c r="BU48" s="40" t="n"/>
+      <c r="BS48" s="41" t="n"/>
+      <c r="BT48" s="41" t="n"/>
+      <c r="BU48" s="42" t="n"/>
       <c r="BV48" s="31" t="n"/>
-      <c r="BW48" s="39" t="n"/>
-      <c r="BX48" s="39" t="n"/>
-      <c r="BY48" s="40" t="n"/>
+      <c r="BW48" s="41" t="n"/>
+      <c r="BX48" s="41" t="n"/>
+      <c r="BY48" s="42" t="n"/>
       <c r="BZ48" s="31" t="n"/>
-      <c r="CA48" s="39" t="n"/>
-      <c r="CB48" s="39" t="n"/>
-      <c r="CC48" s="40" t="n"/>
+      <c r="CA48" s="41" t="n"/>
+      <c r="CB48" s="41" t="n"/>
+      <c r="CC48" s="42" t="n"/>
       <c r="CD48" s="31" t="n"/>
-      <c r="CE48" s="39" t="n"/>
-      <c r="CF48" s="39" t="n"/>
-      <c r="CG48" s="50" t="n"/>
+      <c r="CE48" s="41" t="n"/>
+      <c r="CF48" s="41" t="n"/>
+      <c r="CG48" s="54" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="29" t="inlineStr"/>
@@ -6607,172 +6792,172 @@
       <c r="D49" s="30" t="n"/>
       <c r="E49" s="30" t="n"/>
       <c r="F49" s="31" t="n"/>
-      <c r="G49" s="39" t="n"/>
-      <c r="H49" s="39" t="n"/>
-      <c r="I49" s="40" t="n"/>
+      <c r="G49" s="41" t="n"/>
+      <c r="H49" s="41" t="n"/>
+      <c r="I49" s="42" t="n"/>
       <c r="J49" s="31" t="n"/>
-      <c r="K49" s="39" t="n"/>
-      <c r="L49" s="39" t="n"/>
-      <c r="M49" s="40" t="n"/>
+      <c r="K49" s="41" t="n"/>
+      <c r="L49" s="41" t="n"/>
+      <c r="M49" s="42" t="n"/>
       <c r="N49" s="31" t="n"/>
-      <c r="O49" s="39" t="n"/>
-      <c r="P49" s="39" t="n"/>
-      <c r="Q49" s="40" t="n"/>
+      <c r="O49" s="41" t="n"/>
+      <c r="P49" s="41" t="n"/>
+      <c r="Q49" s="42" t="n"/>
       <c r="R49" s="31" t="n"/>
-      <c r="S49" s="39" t="n"/>
-      <c r="T49" s="39" t="n"/>
-      <c r="U49" s="40" t="n"/>
+      <c r="S49" s="41" t="n"/>
+      <c r="T49" s="41" t="n"/>
+      <c r="U49" s="42" t="n"/>
       <c r="V49" s="31" t="n"/>
-      <c r="W49" s="39" t="n"/>
-      <c r="X49" s="39" t="n"/>
-      <c r="Y49" s="40" t="n"/>
+      <c r="W49" s="41" t="n"/>
+      <c r="X49" s="41" t="n"/>
+      <c r="Y49" s="42" t="n"/>
       <c r="Z49" s="31" t="n"/>
-      <c r="AA49" s="39" t="n"/>
-      <c r="AB49" s="39" t="n"/>
-      <c r="AC49" s="40" t="n"/>
+      <c r="AA49" s="41" t="n"/>
+      <c r="AB49" s="41" t="n"/>
+      <c r="AC49" s="42" t="n"/>
       <c r="AD49" s="31" t="n"/>
-      <c r="AE49" s="39" t="n"/>
-      <c r="AF49" s="39" t="n"/>
-      <c r="AG49" s="40" t="n"/>
+      <c r="AE49" s="41" t="n"/>
+      <c r="AF49" s="41" t="n"/>
+      <c r="AG49" s="42" t="n"/>
       <c r="AH49" s="31" t="n"/>
-      <c r="AI49" s="39" t="n"/>
-      <c r="AJ49" s="39" t="n"/>
-      <c r="AK49" s="40" t="n"/>
+      <c r="AI49" s="41" t="n"/>
+      <c r="AJ49" s="41" t="n"/>
+      <c r="AK49" s="42" t="n"/>
       <c r="AL49" s="31" t="n"/>
-      <c r="AM49" s="39" t="n"/>
-      <c r="AN49" s="39" t="n"/>
-      <c r="AO49" s="40" t="n"/>
+      <c r="AM49" s="41" t="n"/>
+      <c r="AN49" s="41" t="n"/>
+      <c r="AO49" s="42" t="n"/>
       <c r="AP49" s="31" t="n"/>
-      <c r="AQ49" s="39" t="n"/>
-      <c r="AR49" s="39" t="n"/>
-      <c r="AS49" s="40" t="n"/>
+      <c r="AQ49" s="41" t="n"/>
+      <c r="AR49" s="41" t="n"/>
+      <c r="AS49" s="42" t="n"/>
       <c r="AT49" s="31" t="n"/>
-      <c r="AU49" s="39" t="n"/>
-      <c r="AV49" s="39" t="n"/>
-      <c r="AW49" s="40" t="n"/>
+      <c r="AU49" s="41" t="n"/>
+      <c r="AV49" s="41" t="n"/>
+      <c r="AW49" s="42" t="n"/>
       <c r="AX49" s="31" t="n"/>
-      <c r="AY49" s="39" t="n"/>
-      <c r="AZ49" s="39" t="n"/>
-      <c r="BA49" s="40" t="n"/>
+      <c r="AY49" s="41" t="n"/>
+      <c r="AZ49" s="41" t="n"/>
+      <c r="BA49" s="42" t="n"/>
       <c r="BB49" s="31" t="n"/>
-      <c r="BC49" s="39" t="n"/>
-      <c r="BD49" s="39" t="n"/>
-      <c r="BE49" s="40" t="n"/>
+      <c r="BC49" s="41" t="n"/>
+      <c r="BD49" s="41" t="n"/>
+      <c r="BE49" s="42" t="n"/>
       <c r="BF49" s="31" t="n"/>
-      <c r="BG49" s="39" t="n"/>
-      <c r="BH49" s="39" t="n"/>
-      <c r="BI49" s="40" t="n"/>
+      <c r="BG49" s="41" t="n"/>
+      <c r="BH49" s="41" t="n"/>
+      <c r="BI49" s="42" t="n"/>
       <c r="BJ49" s="31" t="n"/>
-      <c r="BK49" s="39" t="n"/>
-      <c r="BL49" s="39" t="n"/>
-      <c r="BM49" s="40" t="n"/>
+      <c r="BK49" s="41" t="n"/>
+      <c r="BL49" s="41" t="n"/>
+      <c r="BM49" s="42" t="n"/>
       <c r="BN49" s="31" t="n"/>
-      <c r="BO49" s="39" t="n"/>
-      <c r="BP49" s="39" t="n"/>
-      <c r="BQ49" s="40" t="n"/>
+      <c r="BO49" s="41" t="n"/>
+      <c r="BP49" s="41" t="n"/>
+      <c r="BQ49" s="42" t="n"/>
       <c r="BR49" s="31" t="n"/>
-      <c r="BS49" s="39" t="n"/>
-      <c r="BT49" s="39" t="n"/>
-      <c r="BU49" s="40" t="n"/>
+      <c r="BS49" s="41" t="n"/>
+      <c r="BT49" s="41" t="n"/>
+      <c r="BU49" s="42" t="n"/>
       <c r="BV49" s="31" t="n"/>
-      <c r="BW49" s="39" t="n"/>
-      <c r="BX49" s="39" t="n"/>
-      <c r="BY49" s="40" t="n"/>
+      <c r="BW49" s="41" t="n"/>
+      <c r="BX49" s="41" t="n"/>
+      <c r="BY49" s="42" t="n"/>
       <c r="BZ49" s="31" t="n"/>
-      <c r="CA49" s="39" t="n"/>
-      <c r="CB49" s="39" t="n"/>
-      <c r="CC49" s="40" t="n"/>
+      <c r="CA49" s="41" t="n"/>
+      <c r="CB49" s="41" t="n"/>
+      <c r="CC49" s="42" t="n"/>
       <c r="CD49" s="31" t="n"/>
-      <c r="CE49" s="39" t="n"/>
-      <c r="CF49" s="39" t="n"/>
-      <c r="CG49" s="50" t="n"/>
+      <c r="CE49" s="41" t="n"/>
+      <c r="CF49" s="41" t="n"/>
+      <c r="CG49" s="54" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="69" t="inlineStr"/>
-      <c r="B50" s="70" t="n"/>
-      <c r="C50" s="70" t="n"/>
-      <c r="D50" s="70" t="n"/>
-      <c r="E50" s="70" t="n"/>
-      <c r="F50" s="71" t="n"/>
-      <c r="G50" s="72" t="n"/>
-      <c r="H50" s="72" t="n"/>
-      <c r="I50" s="73" t="n"/>
-      <c r="J50" s="71" t="n"/>
-      <c r="K50" s="72" t="n"/>
-      <c r="L50" s="72" t="n"/>
-      <c r="M50" s="73" t="n"/>
-      <c r="N50" s="71" t="n"/>
-      <c r="O50" s="72" t="n"/>
-      <c r="P50" s="72" t="n"/>
-      <c r="Q50" s="73" t="n"/>
-      <c r="R50" s="71" t="n"/>
-      <c r="S50" s="72" t="n"/>
-      <c r="T50" s="72" t="n"/>
-      <c r="U50" s="73" t="n"/>
-      <c r="V50" s="71" t="n"/>
-      <c r="W50" s="72" t="n"/>
-      <c r="X50" s="72" t="n"/>
-      <c r="Y50" s="73" t="n"/>
-      <c r="Z50" s="71" t="n"/>
-      <c r="AA50" s="72" t="n"/>
-      <c r="AB50" s="72" t="n"/>
-      <c r="AC50" s="73" t="n"/>
-      <c r="AD50" s="71" t="n"/>
-      <c r="AE50" s="72" t="n"/>
-      <c r="AF50" s="72" t="n"/>
-      <c r="AG50" s="73" t="n"/>
-      <c r="AH50" s="71" t="n"/>
-      <c r="AI50" s="72" t="n"/>
-      <c r="AJ50" s="72" t="n"/>
-      <c r="AK50" s="73" t="n"/>
-      <c r="AL50" s="71" t="n"/>
-      <c r="AM50" s="72" t="n"/>
-      <c r="AN50" s="72" t="n"/>
-      <c r="AO50" s="73" t="n"/>
-      <c r="AP50" s="71" t="n"/>
-      <c r="AQ50" s="72" t="n"/>
-      <c r="AR50" s="72" t="n"/>
-      <c r="AS50" s="73" t="n"/>
-      <c r="AT50" s="71" t="n"/>
-      <c r="AU50" s="72" t="n"/>
-      <c r="AV50" s="72" t="n"/>
-      <c r="AW50" s="73" t="n"/>
-      <c r="AX50" s="71" t="n"/>
-      <c r="AY50" s="72" t="n"/>
-      <c r="AZ50" s="72" t="n"/>
-      <c r="BA50" s="73" t="n"/>
-      <c r="BB50" s="71" t="n"/>
-      <c r="BC50" s="72" t="n"/>
-      <c r="BD50" s="72" t="n"/>
-      <c r="BE50" s="73" t="n"/>
-      <c r="BF50" s="71" t="n"/>
-      <c r="BG50" s="72" t="n"/>
-      <c r="BH50" s="72" t="n"/>
-      <c r="BI50" s="73" t="n"/>
-      <c r="BJ50" s="71" t="n"/>
-      <c r="BK50" s="72" t="n"/>
-      <c r="BL50" s="72" t="n"/>
-      <c r="BM50" s="73" t="n"/>
-      <c r="BN50" s="71" t="n"/>
-      <c r="BO50" s="72" t="n"/>
-      <c r="BP50" s="72" t="n"/>
-      <c r="BQ50" s="73" t="n"/>
-      <c r="BR50" s="71" t="n"/>
-      <c r="BS50" s="72" t="n"/>
-      <c r="BT50" s="72" t="n"/>
-      <c r="BU50" s="73" t="n"/>
-      <c r="BV50" s="71" t="n"/>
-      <c r="BW50" s="72" t="n"/>
-      <c r="BX50" s="72" t="n"/>
-      <c r="BY50" s="73" t="n"/>
-      <c r="BZ50" s="71" t="n"/>
-      <c r="CA50" s="72" t="n"/>
-      <c r="CB50" s="72" t="n"/>
-      <c r="CC50" s="73" t="n"/>
-      <c r="CD50" s="71" t="n"/>
-      <c r="CE50" s="72" t="n"/>
-      <c r="CF50" s="72" t="n"/>
-      <c r="CG50" s="74" t="n"/>
+      <c r="A50" s="73" t="inlineStr"/>
+      <c r="B50" s="74" t="n"/>
+      <c r="C50" s="74" t="n"/>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="75" t="n"/>
+      <c r="G50" s="76" t="n"/>
+      <c r="H50" s="76" t="n"/>
+      <c r="I50" s="77" t="n"/>
+      <c r="J50" s="75" t="n"/>
+      <c r="K50" s="76" t="n"/>
+      <c r="L50" s="76" t="n"/>
+      <c r="M50" s="77" t="n"/>
+      <c r="N50" s="75" t="n"/>
+      <c r="O50" s="76" t="n"/>
+      <c r="P50" s="76" t="n"/>
+      <c r="Q50" s="77" t="n"/>
+      <c r="R50" s="75" t="n"/>
+      <c r="S50" s="76" t="n"/>
+      <c r="T50" s="76" t="n"/>
+      <c r="U50" s="77" t="n"/>
+      <c r="V50" s="75" t="n"/>
+      <c r="W50" s="76" t="n"/>
+      <c r="X50" s="76" t="n"/>
+      <c r="Y50" s="77" t="n"/>
+      <c r="Z50" s="75" t="n"/>
+      <c r="AA50" s="76" t="n"/>
+      <c r="AB50" s="76" t="n"/>
+      <c r="AC50" s="77" t="n"/>
+      <c r="AD50" s="75" t="n"/>
+      <c r="AE50" s="76" t="n"/>
+      <c r="AF50" s="76" t="n"/>
+      <c r="AG50" s="77" t="n"/>
+      <c r="AH50" s="75" t="n"/>
+      <c r="AI50" s="76" t="n"/>
+      <c r="AJ50" s="76" t="n"/>
+      <c r="AK50" s="77" t="n"/>
+      <c r="AL50" s="75" t="n"/>
+      <c r="AM50" s="76" t="n"/>
+      <c r="AN50" s="76" t="n"/>
+      <c r="AO50" s="77" t="n"/>
+      <c r="AP50" s="75" t="n"/>
+      <c r="AQ50" s="76" t="n"/>
+      <c r="AR50" s="76" t="n"/>
+      <c r="AS50" s="77" t="n"/>
+      <c r="AT50" s="75" t="n"/>
+      <c r="AU50" s="76" t="n"/>
+      <c r="AV50" s="76" t="n"/>
+      <c r="AW50" s="77" t="n"/>
+      <c r="AX50" s="75" t="n"/>
+      <c r="AY50" s="76" t="n"/>
+      <c r="AZ50" s="76" t="n"/>
+      <c r="BA50" s="77" t="n"/>
+      <c r="BB50" s="75" t="n"/>
+      <c r="BC50" s="76" t="n"/>
+      <c r="BD50" s="76" t="n"/>
+      <c r="BE50" s="77" t="n"/>
+      <c r="BF50" s="75" t="n"/>
+      <c r="BG50" s="76" t="n"/>
+      <c r="BH50" s="76" t="n"/>
+      <c r="BI50" s="77" t="n"/>
+      <c r="BJ50" s="75" t="n"/>
+      <c r="BK50" s="76" t="n"/>
+      <c r="BL50" s="76" t="n"/>
+      <c r="BM50" s="77" t="n"/>
+      <c r="BN50" s="75" t="n"/>
+      <c r="BO50" s="76" t="n"/>
+      <c r="BP50" s="76" t="n"/>
+      <c r="BQ50" s="77" t="n"/>
+      <c r="BR50" s="75" t="n"/>
+      <c r="BS50" s="76" t="n"/>
+      <c r="BT50" s="76" t="n"/>
+      <c r="BU50" s="77" t="n"/>
+      <c r="BV50" s="75" t="n"/>
+      <c r="BW50" s="76" t="n"/>
+      <c r="BX50" s="76" t="n"/>
+      <c r="BY50" s="77" t="n"/>
+      <c r="BZ50" s="75" t="n"/>
+      <c r="CA50" s="76" t="n"/>
+      <c r="CB50" s="76" t="n"/>
+      <c r="CC50" s="77" t="n"/>
+      <c r="CD50" s="75" t="n"/>
+      <c r="CE50" s="76" t="n"/>
+      <c r="CF50" s="76" t="n"/>
+      <c r="CG50" s="78" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
@@ -6942,111 +7127,111 @@
       <c r="CG52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="75" t="inlineStr">
+      <c r="A53" s="79" t="inlineStr">
         <is>
           <t>Duty No.</t>
         </is>
       </c>
-      <c r="B53" s="76" t="inlineStr">
+      <c r="B53" s="80" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="C53" s="76" t="inlineStr">
+      <c r="C53" s="80" t="inlineStr">
         <is>
           <t>Finish Time</t>
         </is>
       </c>
-      <c r="D53" s="76" t="inlineStr">
+      <c r="D53" s="80" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E53" s="76" t="inlineStr">
+      <c r="E53" s="80" t="inlineStr">
         <is>
           <t>Radio</t>
         </is>
       </c>
-      <c r="F53" s="77" t="n"/>
-      <c r="G53" s="78" t="n"/>
-      <c r="H53" s="78" t="n"/>
-      <c r="I53" s="79" t="n"/>
-      <c r="J53" s="77" t="n"/>
-      <c r="K53" s="78" t="n"/>
-      <c r="L53" s="78" t="n"/>
-      <c r="M53" s="79" t="n"/>
-      <c r="N53" s="77" t="n"/>
-      <c r="O53" s="78" t="n"/>
-      <c r="P53" s="78" t="n"/>
-      <c r="Q53" s="79" t="n"/>
-      <c r="R53" s="77" t="n"/>
-      <c r="S53" s="78" t="n"/>
-      <c r="T53" s="78" t="n"/>
-      <c r="U53" s="79" t="n"/>
-      <c r="V53" s="77" t="n"/>
-      <c r="W53" s="78" t="n"/>
-      <c r="X53" s="78" t="n"/>
-      <c r="Y53" s="79" t="n"/>
-      <c r="Z53" s="77" t="n"/>
-      <c r="AA53" s="78" t="n"/>
-      <c r="AB53" s="78" t="n"/>
-      <c r="AC53" s="79" t="n"/>
-      <c r="AD53" s="77" t="n"/>
-      <c r="AE53" s="78" t="n"/>
-      <c r="AF53" s="78" t="n"/>
-      <c r="AG53" s="79" t="n"/>
-      <c r="AH53" s="77" t="n"/>
-      <c r="AI53" s="78" t="n"/>
-      <c r="AJ53" s="78" t="n"/>
-      <c r="AK53" s="79" t="n"/>
-      <c r="AL53" s="77" t="n"/>
-      <c r="AM53" s="78" t="n"/>
-      <c r="AN53" s="78" t="n"/>
-      <c r="AO53" s="79" t="n"/>
-      <c r="AP53" s="77" t="n"/>
-      <c r="AQ53" s="78" t="n"/>
-      <c r="AR53" s="78" t="n"/>
-      <c r="AS53" s="79" t="n"/>
-      <c r="AT53" s="77" t="n"/>
-      <c r="AU53" s="78" t="n"/>
-      <c r="AV53" s="78" t="n"/>
-      <c r="AW53" s="79" t="n"/>
-      <c r="AX53" s="77" t="n"/>
-      <c r="AY53" s="78" t="n"/>
-      <c r="AZ53" s="78" t="n"/>
-      <c r="BA53" s="79" t="n"/>
-      <c r="BB53" s="77" t="n"/>
-      <c r="BC53" s="78" t="n"/>
-      <c r="BD53" s="78" t="n"/>
-      <c r="BE53" s="79" t="n"/>
-      <c r="BF53" s="77" t="n"/>
-      <c r="BG53" s="78" t="n"/>
-      <c r="BH53" s="78" t="n"/>
-      <c r="BI53" s="79" t="n"/>
-      <c r="BJ53" s="77" t="n"/>
-      <c r="BK53" s="78" t="n"/>
-      <c r="BL53" s="78" t="n"/>
-      <c r="BM53" s="79" t="n"/>
-      <c r="BN53" s="77" t="n"/>
-      <c r="BO53" s="78" t="n"/>
-      <c r="BP53" s="78" t="n"/>
-      <c r="BQ53" s="79" t="n"/>
-      <c r="BR53" s="77" t="n"/>
-      <c r="BS53" s="78" t="n"/>
-      <c r="BT53" s="78" t="n"/>
-      <c r="BU53" s="79" t="n"/>
-      <c r="BV53" s="77" t="n"/>
-      <c r="BW53" s="78" t="n"/>
-      <c r="BX53" s="78" t="n"/>
-      <c r="BY53" s="79" t="n"/>
-      <c r="BZ53" s="77" t="n"/>
-      <c r="CA53" s="78" t="n"/>
-      <c r="CB53" s="78" t="n"/>
-      <c r="CC53" s="79" t="n"/>
-      <c r="CD53" s="77" t="n"/>
-      <c r="CE53" s="78" t="n"/>
-      <c r="CF53" s="78" t="n"/>
-      <c r="CG53" s="80" t="n"/>
+      <c r="F53" s="81" t="n"/>
+      <c r="G53" s="82" t="n"/>
+      <c r="H53" s="82" t="n"/>
+      <c r="I53" s="83" t="n"/>
+      <c r="J53" s="81" t="n"/>
+      <c r="K53" s="82" t="n"/>
+      <c r="L53" s="82" t="n"/>
+      <c r="M53" s="83" t="n"/>
+      <c r="N53" s="81" t="n"/>
+      <c r="O53" s="82" t="n"/>
+      <c r="P53" s="82" t="n"/>
+      <c r="Q53" s="83" t="n"/>
+      <c r="R53" s="81" t="n"/>
+      <c r="S53" s="82" t="n"/>
+      <c r="T53" s="82" t="n"/>
+      <c r="U53" s="83" t="n"/>
+      <c r="V53" s="81" t="n"/>
+      <c r="W53" s="82" t="n"/>
+      <c r="X53" s="82" t="n"/>
+      <c r="Y53" s="83" t="n"/>
+      <c r="Z53" s="81" t="n"/>
+      <c r="AA53" s="82" t="n"/>
+      <c r="AB53" s="82" t="n"/>
+      <c r="AC53" s="83" t="n"/>
+      <c r="AD53" s="81" t="n"/>
+      <c r="AE53" s="82" t="n"/>
+      <c r="AF53" s="82" t="n"/>
+      <c r="AG53" s="83" t="n"/>
+      <c r="AH53" s="81" t="n"/>
+      <c r="AI53" s="82" t="n"/>
+      <c r="AJ53" s="82" t="n"/>
+      <c r="AK53" s="83" t="n"/>
+      <c r="AL53" s="81" t="n"/>
+      <c r="AM53" s="82" t="n"/>
+      <c r="AN53" s="82" t="n"/>
+      <c r="AO53" s="83" t="n"/>
+      <c r="AP53" s="81" t="n"/>
+      <c r="AQ53" s="82" t="n"/>
+      <c r="AR53" s="82" t="n"/>
+      <c r="AS53" s="83" t="n"/>
+      <c r="AT53" s="81" t="n"/>
+      <c r="AU53" s="82" t="n"/>
+      <c r="AV53" s="82" t="n"/>
+      <c r="AW53" s="83" t="n"/>
+      <c r="AX53" s="81" t="n"/>
+      <c r="AY53" s="82" t="n"/>
+      <c r="AZ53" s="82" t="n"/>
+      <c r="BA53" s="83" t="n"/>
+      <c r="BB53" s="81" t="n"/>
+      <c r="BC53" s="82" t="n"/>
+      <c r="BD53" s="82" t="n"/>
+      <c r="BE53" s="83" t="n"/>
+      <c r="BF53" s="81" t="n"/>
+      <c r="BG53" s="82" t="n"/>
+      <c r="BH53" s="82" t="n"/>
+      <c r="BI53" s="83" t="n"/>
+      <c r="BJ53" s="81" t="n"/>
+      <c r="BK53" s="82" t="n"/>
+      <c r="BL53" s="82" t="n"/>
+      <c r="BM53" s="83" t="n"/>
+      <c r="BN53" s="81" t="n"/>
+      <c r="BO53" s="82" t="n"/>
+      <c r="BP53" s="82" t="n"/>
+      <c r="BQ53" s="83" t="n"/>
+      <c r="BR53" s="81" t="n"/>
+      <c r="BS53" s="82" t="n"/>
+      <c r="BT53" s="82" t="n"/>
+      <c r="BU53" s="83" t="n"/>
+      <c r="BV53" s="81" t="n"/>
+      <c r="BW53" s="82" t="n"/>
+      <c r="BX53" s="82" t="n"/>
+      <c r="BY53" s="83" t="n"/>
+      <c r="BZ53" s="81" t="n"/>
+      <c r="CA53" s="82" t="n"/>
+      <c r="CB53" s="82" t="n"/>
+      <c r="CC53" s="83" t="n"/>
+      <c r="CD53" s="81" t="n"/>
+      <c r="CE53" s="82" t="n"/>
+      <c r="CF53" s="82" t="n"/>
+      <c r="CG53" s="84" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="29" t="inlineStr">
@@ -7075,101 +7260,105 @@
         </is>
       </c>
       <c r="F54" s="31" t="n"/>
-      <c r="G54" s="93" t="n"/>
+      <c r="G54" s="97" t="n"/>
       <c r="H54" s="33" t="n"/>
       <c r="I54" s="34" t="n"/>
-      <c r="J54" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="J54" s="98" t="n"/>
       <c r="K54" s="33" t="n"/>
       <c r="L54" s="33" t="n"/>
       <c r="M54" s="34" t="n"/>
-      <c r="N54" s="94" t="n"/>
+      <c r="N54" s="98" t="n"/>
       <c r="O54" s="33" t="n"/>
       <c r="P54" s="33" t="n"/>
       <c r="Q54" s="34" t="n"/>
-      <c r="R54" s="94" t="n"/>
+      <c r="R54" s="48" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="S54" s="33" t="n"/>
       <c r="T54" s="33" t="n"/>
       <c r="U54" s="34" t="n"/>
-      <c r="V54" s="36" t="inlineStr">
+      <c r="V54" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="W54" s="33" t="n"/>
-      <c r="X54" s="37" t="inlineStr">
+      <c r="X54" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="Y54" s="34" t="n"/>
-      <c r="Z54" s="94" t="n"/>
+      <c r="Z54" s="98" t="n"/>
       <c r="AA54" s="33" t="n"/>
       <c r="AB54" s="33" t="n"/>
       <c r="AC54" s="34" t="n"/>
-      <c r="AD54" s="94" t="n"/>
+      <c r="AD54" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="AE54" s="33" t="n"/>
       <c r="AF54" s="33" t="n"/>
       <c r="AG54" s="34" t="n"/>
-      <c r="AH54" s="94" t="n"/>
+      <c r="AH54" s="98" t="n"/>
       <c r="AI54" s="33" t="n"/>
       <c r="AJ54" s="33" t="n"/>
       <c r="AK54" s="34" t="n"/>
       <c r="AL54" s="31" t="n"/>
-      <c r="AM54" s="39" t="n"/>
-      <c r="AN54" s="39" t="n"/>
-      <c r="AO54" s="40" t="n"/>
+      <c r="AM54" s="41" t="n"/>
+      <c r="AN54" s="41" t="n"/>
+      <c r="AO54" s="42" t="n"/>
       <c r="AP54" s="31" t="n"/>
-      <c r="AQ54" s="39" t="n"/>
-      <c r="AR54" s="39" t="n"/>
-      <c r="AS54" s="40" t="n"/>
+      <c r="AQ54" s="41" t="n"/>
+      <c r="AR54" s="41" t="n"/>
+      <c r="AS54" s="42" t="n"/>
       <c r="AT54" s="31" t="n"/>
-      <c r="AU54" s="39" t="n"/>
-      <c r="AV54" s="39" t="n"/>
-      <c r="AW54" s="40" t="n"/>
+      <c r="AU54" s="41" t="n"/>
+      <c r="AV54" s="41" t="n"/>
+      <c r="AW54" s="42" t="n"/>
       <c r="AX54" s="31" t="n"/>
-      <c r="AY54" s="39" t="n"/>
-      <c r="AZ54" s="39" t="n"/>
-      <c r="BA54" s="40" t="n"/>
+      <c r="AY54" s="41" t="n"/>
+      <c r="AZ54" s="41" t="n"/>
+      <c r="BA54" s="42" t="n"/>
       <c r="BB54" s="31" t="n"/>
-      <c r="BC54" s="39" t="n"/>
-      <c r="BD54" s="39" t="n"/>
-      <c r="BE54" s="40" t="n"/>
+      <c r="BC54" s="41" t="n"/>
+      <c r="BD54" s="41" t="n"/>
+      <c r="BE54" s="42" t="n"/>
       <c r="BF54" s="31" t="n"/>
-      <c r="BG54" s="39" t="n"/>
-      <c r="BH54" s="39" t="n"/>
-      <c r="BI54" s="40" t="n"/>
-      <c r="BJ54" s="95" t="inlineStr">
+      <c r="BG54" s="41" t="n"/>
+      <c r="BH54" s="41" t="n"/>
+      <c r="BI54" s="42" t="n"/>
+      <c r="BJ54" s="99" t="inlineStr">
         <is>
           <t>CARDINAL</t>
         </is>
       </c>
-      <c r="BK54" s="96" t="n"/>
-      <c r="BL54" s="96" t="n"/>
-      <c r="BM54" s="96" t="n"/>
-      <c r="BN54" s="96" t="n"/>
-      <c r="BO54" s="96" t="n"/>
-      <c r="BP54" s="96" t="n"/>
-      <c r="BQ54" s="96" t="n"/>
-      <c r="BR54" s="96" t="n"/>
-      <c r="BS54" s="96" t="n"/>
-      <c r="BT54" s="96" t="n"/>
-      <c r="BU54" s="96" t="n"/>
-      <c r="BV54" s="96" t="n"/>
-      <c r="BW54" s="96" t="n"/>
-      <c r="BX54" s="96" t="n"/>
-      <c r="BY54" s="96" t="n"/>
-      <c r="BZ54" s="96" t="n"/>
-      <c r="CA54" s="96" t="n"/>
-      <c r="CB54" s="96" t="n"/>
-      <c r="CC54" s="96" t="n"/>
-      <c r="CD54" s="96" t="n"/>
-      <c r="CE54" s="96" t="n"/>
-      <c r="CF54" s="96" t="n"/>
-      <c r="CG54" s="97" t="n"/>
+      <c r="BK54" s="100" t="n"/>
+      <c r="BL54" s="100" t="n"/>
+      <c r="BM54" s="100" t="n"/>
+      <c r="BN54" s="100" t="n"/>
+      <c r="BO54" s="100" t="n"/>
+      <c r="BP54" s="100" t="n"/>
+      <c r="BQ54" s="100" t="n"/>
+      <c r="BR54" s="100" t="n"/>
+      <c r="BS54" s="100" t="n"/>
+      <c r="BT54" s="100" t="n"/>
+      <c r="BU54" s="100" t="n"/>
+      <c r="BV54" s="100" t="n"/>
+      <c r="BW54" s="100" t="n"/>
+      <c r="BX54" s="100" t="n"/>
+      <c r="BY54" s="100" t="n"/>
+      <c r="BZ54" s="100" t="n"/>
+      <c r="CA54" s="100" t="n"/>
+      <c r="CB54" s="100" t="n"/>
+      <c r="CC54" s="100" t="n"/>
+      <c r="CD54" s="100" t="n"/>
+      <c r="CE54" s="100" t="n"/>
+      <c r="CF54" s="100" t="n"/>
+      <c r="CG54" s="101" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="29" t="inlineStr">
@@ -7198,93 +7387,97 @@
         </is>
       </c>
       <c r="F55" s="31" t="n"/>
-      <c r="G55" s="93" t="n"/>
+      <c r="G55" s="97" t="n"/>
       <c r="H55" s="33" t="n"/>
       <c r="I55" s="34" t="n"/>
-      <c r="J55" s="94" t="n"/>
+      <c r="J55" s="98" t="n"/>
       <c r="K55" s="33" t="n"/>
       <c r="L55" s="33" t="n"/>
       <c r="M55" s="34" t="n"/>
-      <c r="N55" s="94" t="n"/>
+      <c r="N55" s="102" t="n"/>
       <c r="O55" s="33" t="n"/>
-      <c r="P55" s="33" t="n"/>
+      <c r="P55" s="53" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="Q55" s="34" t="n"/>
-      <c r="R55" s="94" t="n"/>
+      <c r="R55" s="98" t="n"/>
       <c r="S55" s="33" t="n"/>
       <c r="T55" s="33" t="n"/>
       <c r="U55" s="34" t="n"/>
-      <c r="V55" s="56" t="inlineStr">
+      <c r="V55" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="W55" s="33" t="n"/>
-      <c r="X55" s="57" t="inlineStr">
+      <c r="X55" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="Y55" s="34" t="n"/>
-      <c r="Z55" s="94" t="n"/>
+      <c r="Z55" s="98" t="n"/>
       <c r="AA55" s="33" t="n"/>
       <c r="AB55" s="33" t="n"/>
       <c r="AC55" s="34" t="n"/>
-      <c r="AD55" s="94" t="n"/>
+      <c r="AD55" s="98" t="n"/>
       <c r="AE55" s="33" t="n"/>
       <c r="AF55" s="33" t="n"/>
       <c r="AG55" s="34" t="n"/>
-      <c r="AH55" s="94" t="n"/>
+      <c r="AH55" s="98" t="n"/>
       <c r="AI55" s="33" t="n"/>
       <c r="AJ55" s="33" t="n"/>
       <c r="AK55" s="34" t="n"/>
       <c r="AL55" s="31" t="n"/>
-      <c r="AM55" s="39" t="n"/>
-      <c r="AN55" s="39" t="n"/>
-      <c r="AO55" s="40" t="n"/>
+      <c r="AM55" s="41" t="n"/>
+      <c r="AN55" s="41" t="n"/>
+      <c r="AO55" s="42" t="n"/>
       <c r="AP55" s="31" t="n"/>
-      <c r="AQ55" s="39" t="n"/>
-      <c r="AR55" s="39" t="n"/>
-      <c r="AS55" s="40" t="n"/>
+      <c r="AQ55" s="41" t="n"/>
+      <c r="AR55" s="41" t="n"/>
+      <c r="AS55" s="42" t="n"/>
       <c r="AT55" s="31" t="n"/>
-      <c r="AU55" s="39" t="n"/>
-      <c r="AV55" s="39" t="n"/>
-      <c r="AW55" s="40" t="n"/>
+      <c r="AU55" s="41" t="n"/>
+      <c r="AV55" s="41" t="n"/>
+      <c r="AW55" s="42" t="n"/>
       <c r="AX55" s="31" t="n"/>
-      <c r="AY55" s="39" t="n"/>
-      <c r="AZ55" s="39" t="n"/>
-      <c r="BA55" s="40" t="n"/>
+      <c r="AY55" s="41" t="n"/>
+      <c r="AZ55" s="41" t="n"/>
+      <c r="BA55" s="42" t="n"/>
       <c r="BB55" s="31" t="n"/>
-      <c r="BC55" s="39" t="n"/>
-      <c r="BD55" s="39" t="n"/>
-      <c r="BE55" s="40" t="n"/>
+      <c r="BC55" s="41" t="n"/>
+      <c r="BD55" s="41" t="n"/>
+      <c r="BE55" s="42" t="n"/>
       <c r="BF55" s="31" t="n"/>
-      <c r="BG55" s="39" t="n"/>
-      <c r="BH55" s="39" t="n"/>
-      <c r="BI55" s="40" t="n"/>
-      <c r="BJ55" s="98" t="n"/>
-      <c r="BK55" s="99" t="n"/>
-      <c r="BL55" s="99" t="n"/>
-      <c r="BM55" s="99" t="n"/>
-      <c r="BN55" s="99" t="n"/>
-      <c r="BO55" s="99" t="n"/>
-      <c r="BP55" s="99" t="n"/>
-      <c r="BQ55" s="99" t="n"/>
-      <c r="BR55" s="99" t="n"/>
-      <c r="BS55" s="99" t="n"/>
-      <c r="BT55" s="99" t="n"/>
-      <c r="BU55" s="99" t="n"/>
-      <c r="BV55" s="99" t="n"/>
-      <c r="BW55" s="99" t="n"/>
-      <c r="BX55" s="99" t="n"/>
-      <c r="BY55" s="99" t="n"/>
-      <c r="BZ55" s="99" t="n"/>
-      <c r="CA55" s="99" t="n"/>
-      <c r="CB55" s="99" t="n"/>
-      <c r="CC55" s="99" t="n"/>
-      <c r="CD55" s="99" t="n"/>
-      <c r="CE55" s="99" t="n"/>
-      <c r="CF55" s="99" t="n"/>
-      <c r="CG55" s="100" t="n"/>
+      <c r="BG55" s="41" t="n"/>
+      <c r="BH55" s="41" t="n"/>
+      <c r="BI55" s="42" t="n"/>
+      <c r="BJ55" s="103" t="n"/>
+      <c r="BK55" s="104" t="n"/>
+      <c r="BL55" s="104" t="n"/>
+      <c r="BM55" s="104" t="n"/>
+      <c r="BN55" s="104" t="n"/>
+      <c r="BO55" s="104" t="n"/>
+      <c r="BP55" s="104" t="n"/>
+      <c r="BQ55" s="104" t="n"/>
+      <c r="BR55" s="104" t="n"/>
+      <c r="BS55" s="104" t="n"/>
+      <c r="BT55" s="104" t="n"/>
+      <c r="BU55" s="104" t="n"/>
+      <c r="BV55" s="104" t="n"/>
+      <c r="BW55" s="104" t="n"/>
+      <c r="BX55" s="104" t="n"/>
+      <c r="BY55" s="104" t="n"/>
+      <c r="BZ55" s="104" t="n"/>
+      <c r="CA55" s="104" t="n"/>
+      <c r="CB55" s="104" t="n"/>
+      <c r="CC55" s="104" t="n"/>
+      <c r="CD55" s="104" t="n"/>
+      <c r="CE55" s="104" t="n"/>
+      <c r="CF55" s="104" t="n"/>
+      <c r="CG55" s="105" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="29" t="inlineStr">
@@ -7313,93 +7506,97 @@
         </is>
       </c>
       <c r="F56" s="31" t="n"/>
-      <c r="G56" s="39" t="n"/>
-      <c r="H56" s="39" t="n"/>
-      <c r="I56" s="40" t="n"/>
+      <c r="G56" s="41" t="n"/>
+      <c r="H56" s="41" t="n"/>
+      <c r="I56" s="42" t="n"/>
       <c r="J56" s="31" t="n"/>
-      <c r="K56" s="39" t="n"/>
-      <c r="L56" s="39" t="n"/>
-      <c r="M56" s="40" t="n"/>
+      <c r="K56" s="41" t="n"/>
+      <c r="L56" s="41" t="n"/>
+      <c r="M56" s="42" t="n"/>
       <c r="N56" s="31" t="n"/>
-      <c r="O56" s="39" t="n"/>
-      <c r="P56" s="93" t="n"/>
+      <c r="O56" s="41" t="n"/>
+      <c r="P56" s="97" t="n"/>
       <c r="Q56" s="34" t="n"/>
-      <c r="R56" s="94" t="n"/>
+      <c r="R56" s="98" t="n"/>
       <c r="S56" s="33" t="n"/>
       <c r="T56" s="33" t="n"/>
       <c r="U56" s="34" t="n"/>
-      <c r="V56" s="94" t="n"/>
+      <c r="V56" s="98" t="n"/>
       <c r="W56" s="33" t="n"/>
       <c r="X56" s="33" t="n"/>
       <c r="Y56" s="34" t="n"/>
-      <c r="Z56" s="56" t="inlineStr">
+      <c r="Z56" s="61" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="AA56" s="33" t="n"/>
-      <c r="AB56" s="57" t="inlineStr">
+      <c r="AB56" s="62" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AC56" s="34" t="n"/>
-      <c r="AD56" s="94" t="n"/>
+      <c r="AD56" s="98" t="n"/>
       <c r="AE56" s="33" t="n"/>
       <c r="AF56" s="33" t="n"/>
       <c r="AG56" s="34" t="n"/>
-      <c r="AH56" s="94" t="n"/>
+      <c r="AH56" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="AI56" s="33" t="n"/>
       <c r="AJ56" s="33" t="n"/>
       <c r="AK56" s="34" t="n"/>
-      <c r="AL56" s="94" t="n"/>
+      <c r="AL56" s="98" t="n"/>
       <c r="AM56" s="33" t="n"/>
       <c r="AN56" s="33" t="n"/>
       <c r="AO56" s="34" t="n"/>
-      <c r="AP56" s="94" t="n"/>
+      <c r="AP56" s="98" t="n"/>
       <c r="AQ56" s="33" t="n"/>
       <c r="AR56" s="33" t="n"/>
       <c r="AS56" s="34" t="n"/>
-      <c r="AT56" s="101" t="n"/>
+      <c r="AT56" s="102" t="n"/>
       <c r="AU56" s="33" t="n"/>
-      <c r="AV56" s="39" t="n"/>
-      <c r="AW56" s="40" t="n"/>
+      <c r="AV56" s="41" t="n"/>
+      <c r="AW56" s="42" t="n"/>
       <c r="AX56" s="31" t="n"/>
-      <c r="AY56" s="39" t="n"/>
-      <c r="AZ56" s="39" t="n"/>
-      <c r="BA56" s="40" t="n"/>
+      <c r="AY56" s="41" t="n"/>
+      <c r="AZ56" s="41" t="n"/>
+      <c r="BA56" s="42" t="n"/>
       <c r="BB56" s="31" t="n"/>
-      <c r="BC56" s="39" t="n"/>
-      <c r="BD56" s="39" t="n"/>
-      <c r="BE56" s="40" t="n"/>
+      <c r="BC56" s="41" t="n"/>
+      <c r="BD56" s="41" t="n"/>
+      <c r="BE56" s="42" t="n"/>
       <c r="BF56" s="31" t="n"/>
-      <c r="BG56" s="39" t="n"/>
-      <c r="BH56" s="39" t="n"/>
-      <c r="BI56" s="40" t="n"/>
+      <c r="BG56" s="41" t="n"/>
+      <c r="BH56" s="41" t="n"/>
+      <c r="BI56" s="42" t="n"/>
       <c r="BJ56" s="31" t="n"/>
-      <c r="BK56" s="39" t="n"/>
-      <c r="BL56" s="39" t="n"/>
-      <c r="BM56" s="40" t="n"/>
+      <c r="BK56" s="41" t="n"/>
+      <c r="BL56" s="41" t="n"/>
+      <c r="BM56" s="42" t="n"/>
       <c r="BN56" s="31" t="n"/>
-      <c r="BO56" s="39" t="n"/>
-      <c r="BP56" s="39" t="n"/>
-      <c r="BQ56" s="40" t="n"/>
+      <c r="BO56" s="41" t="n"/>
+      <c r="BP56" s="41" t="n"/>
+      <c r="BQ56" s="42" t="n"/>
       <c r="BR56" s="31" t="n"/>
-      <c r="BS56" s="39" t="n"/>
-      <c r="BT56" s="39" t="n"/>
-      <c r="BU56" s="40" t="n"/>
+      <c r="BS56" s="41" t="n"/>
+      <c r="BT56" s="41" t="n"/>
+      <c r="BU56" s="42" t="n"/>
       <c r="BV56" s="31" t="n"/>
-      <c r="BW56" s="39" t="n"/>
-      <c r="BX56" s="39" t="n"/>
-      <c r="BY56" s="40" t="n"/>
+      <c r="BW56" s="41" t="n"/>
+      <c r="BX56" s="41" t="n"/>
+      <c r="BY56" s="42" t="n"/>
       <c r="BZ56" s="31" t="n"/>
-      <c r="CA56" s="39" t="n"/>
-      <c r="CB56" s="39" t="n"/>
-      <c r="CC56" s="40" t="n"/>
+      <c r="CA56" s="41" t="n"/>
+      <c r="CB56" s="41" t="n"/>
+      <c r="CC56" s="42" t="n"/>
       <c r="CD56" s="31" t="n"/>
-      <c r="CE56" s="39" t="n"/>
-      <c r="CF56" s="39" t="n"/>
-      <c r="CG56" s="50" t="n"/>
+      <c r="CE56" s="41" t="n"/>
+      <c r="CF56" s="41" t="n"/>
+      <c r="CG56" s="54" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="29" t="inlineStr">
@@ -7428,97 +7625,101 @@
         </is>
       </c>
       <c r="F57" s="31" t="n"/>
-      <c r="G57" s="39" t="n"/>
-      <c r="H57" s="39" t="n"/>
-      <c r="I57" s="40" t="n"/>
+      <c r="G57" s="41" t="n"/>
+      <c r="H57" s="41" t="n"/>
+      <c r="I57" s="42" t="n"/>
       <c r="J57" s="31" t="n"/>
-      <c r="K57" s="39" t="n"/>
-      <c r="L57" s="39" t="n"/>
-      <c r="M57" s="40" t="n"/>
+      <c r="K57" s="41" t="n"/>
+      <c r="L57" s="41" t="n"/>
+      <c r="M57" s="42" t="n"/>
       <c r="N57" s="31" t="n"/>
-      <c r="O57" s="39" t="n"/>
-      <c r="P57" s="39" t="n"/>
-      <c r="Q57" s="40" t="n"/>
+      <c r="O57" s="41" t="n"/>
+      <c r="P57" s="41" t="n"/>
+      <c r="Q57" s="42" t="n"/>
       <c r="R57" s="31" t="n"/>
-      <c r="S57" s="39" t="n"/>
-      <c r="T57" s="39" t="n"/>
-      <c r="U57" s="40" t="n"/>
+      <c r="S57" s="41" t="n"/>
+      <c r="T57" s="41" t="n"/>
+      <c r="U57" s="42" t="n"/>
       <c r="V57" s="31" t="n"/>
-      <c r="W57" s="39" t="n"/>
-      <c r="X57" s="39" t="n"/>
-      <c r="Y57" s="40" t="n"/>
+      <c r="W57" s="41" t="n"/>
+      <c r="X57" s="41" t="n"/>
+      <c r="Y57" s="42" t="n"/>
       <c r="Z57" s="31" t="n"/>
-      <c r="AA57" s="39" t="n"/>
-      <c r="AB57" s="39" t="n"/>
-      <c r="AC57" s="40" t="n"/>
+      <c r="AA57" s="41" t="n"/>
+      <c r="AB57" s="41" t="n"/>
+      <c r="AC57" s="42" t="n"/>
       <c r="AD57" s="31" t="n"/>
-      <c r="AE57" s="39" t="n"/>
-      <c r="AF57" s="39" t="n"/>
-      <c r="AG57" s="40" t="n"/>
+      <c r="AE57" s="41" t="n"/>
+      <c r="AF57" s="41" t="n"/>
+      <c r="AG57" s="42" t="n"/>
       <c r="AH57" s="31" t="n"/>
-      <c r="AI57" s="39" t="n"/>
-      <c r="AJ57" s="39" t="n"/>
-      <c r="AK57" s="40" t="n"/>
-      <c r="AL57" s="94" t="n"/>
+      <c r="AI57" s="41" t="n"/>
+      <c r="AJ57" s="41" t="n"/>
+      <c r="AK57" s="42" t="n"/>
+      <c r="AL57" s="98" t="n"/>
       <c r="AM57" s="33" t="n"/>
       <c r="AN57" s="33" t="n"/>
       <c r="AO57" s="34" t="n"/>
-      <c r="AP57" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
+      <c r="AP57" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
         </is>
       </c>
       <c r="AQ57" s="33" t="n"/>
       <c r="AR57" s="33" t="n"/>
       <c r="AS57" s="34" t="n"/>
-      <c r="AT57" s="94" t="n"/>
+      <c r="AT57" s="98" t="n"/>
       <c r="AU57" s="33" t="n"/>
       <c r="AV57" s="33" t="n"/>
       <c r="AW57" s="34" t="n"/>
-      <c r="AX57" s="36" t="inlineStr">
+      <c r="AX57" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="AY57" s="33" t="n"/>
-      <c r="AZ57" s="37" t="inlineStr">
+      <c r="AZ57" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BA57" s="34" t="n"/>
-      <c r="BB57" s="94" t="n"/>
+      <c r="BB57" s="98" t="n"/>
       <c r="BC57" s="33" t="n"/>
       <c r="BD57" s="33" t="n"/>
       <c r="BE57" s="34" t="n"/>
-      <c r="BF57" s="94" t="n"/>
+      <c r="BF57" s="48" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="BG57" s="33" t="n"/>
       <c r="BH57" s="33" t="n"/>
       <c r="BI57" s="34" t="n"/>
-      <c r="BJ57" s="94" t="n"/>
+      <c r="BJ57" s="98" t="n"/>
       <c r="BK57" s="33" t="n"/>
       <c r="BL57" s="33" t="n"/>
       <c r="BM57" s="34" t="n"/>
-      <c r="BN57" s="94" t="n"/>
+      <c r="BN57" s="98" t="n"/>
       <c r="BO57" s="33" t="n"/>
       <c r="BP57" s="33" t="n"/>
       <c r="BQ57" s="34" t="n"/>
       <c r="BR57" s="31" t="n"/>
-      <c r="BS57" s="39" t="n"/>
-      <c r="BT57" s="39" t="n"/>
-      <c r="BU57" s="40" t="n"/>
+      <c r="BS57" s="41" t="n"/>
+      <c r="BT57" s="41" t="n"/>
+      <c r="BU57" s="42" t="n"/>
       <c r="BV57" s="31" t="n"/>
-      <c r="BW57" s="39" t="n"/>
-      <c r="BX57" s="39" t="n"/>
-      <c r="BY57" s="40" t="n"/>
+      <c r="BW57" s="41" t="n"/>
+      <c r="BX57" s="41" t="n"/>
+      <c r="BY57" s="42" t="n"/>
       <c r="BZ57" s="31" t="n"/>
-      <c r="CA57" s="39" t="n"/>
-      <c r="CB57" s="39" t="n"/>
-      <c r="CC57" s="40" t="n"/>
+      <c r="CA57" s="41" t="n"/>
+      <c r="CB57" s="41" t="n"/>
+      <c r="CC57" s="42" t="n"/>
       <c r="CD57" s="31" t="n"/>
-      <c r="CE57" s="39" t="n"/>
-      <c r="CF57" s="39" t="n"/>
-      <c r="CG57" s="50" t="n"/>
+      <c r="CE57" s="41" t="n"/>
+      <c r="CF57" s="41" t="n"/>
+      <c r="CG57" s="54" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="29" t="inlineStr">
@@ -7547,93 +7748,97 @@
         </is>
       </c>
       <c r="F58" s="31" t="n"/>
-      <c r="G58" s="39" t="n"/>
-      <c r="H58" s="39" t="n"/>
-      <c r="I58" s="40" t="n"/>
+      <c r="G58" s="41" t="n"/>
+      <c r="H58" s="41" t="n"/>
+      <c r="I58" s="42" t="n"/>
       <c r="J58" s="31" t="n"/>
-      <c r="K58" s="39" t="n"/>
-      <c r="L58" s="39" t="n"/>
-      <c r="M58" s="40" t="n"/>
+      <c r="K58" s="41" t="n"/>
+      <c r="L58" s="41" t="n"/>
+      <c r="M58" s="42" t="n"/>
       <c r="N58" s="31" t="n"/>
-      <c r="O58" s="39" t="n"/>
-      <c r="P58" s="39" t="n"/>
-      <c r="Q58" s="40" t="n"/>
+      <c r="O58" s="41" t="n"/>
+      <c r="P58" s="41" t="n"/>
+      <c r="Q58" s="42" t="n"/>
       <c r="R58" s="31" t="n"/>
-      <c r="S58" s="39" t="n"/>
-      <c r="T58" s="39" t="n"/>
-      <c r="U58" s="40" t="n"/>
+      <c r="S58" s="41" t="n"/>
+      <c r="T58" s="41" t="n"/>
+      <c r="U58" s="42" t="n"/>
       <c r="V58" s="31" t="n"/>
-      <c r="W58" s="39" t="n"/>
-      <c r="X58" s="39" t="n"/>
-      <c r="Y58" s="40" t="n"/>
+      <c r="W58" s="41" t="n"/>
+      <c r="X58" s="41" t="n"/>
+      <c r="Y58" s="42" t="n"/>
       <c r="Z58" s="31" t="n"/>
-      <c r="AA58" s="39" t="n"/>
-      <c r="AB58" s="39" t="n"/>
-      <c r="AC58" s="40" t="n"/>
+      <c r="AA58" s="41" t="n"/>
+      <c r="AB58" s="41" t="n"/>
+      <c r="AC58" s="42" t="n"/>
       <c r="AD58" s="31" t="n"/>
-      <c r="AE58" s="39" t="n"/>
-      <c r="AF58" s="39" t="n"/>
-      <c r="AG58" s="40" t="n"/>
+      <c r="AE58" s="41" t="n"/>
+      <c r="AF58" s="41" t="n"/>
+      <c r="AG58" s="42" t="n"/>
       <c r="AH58" s="31" t="n"/>
-      <c r="AI58" s="39" t="n"/>
-      <c r="AJ58" s="39" t="n"/>
-      <c r="AK58" s="40" t="n"/>
+      <c r="AI58" s="41" t="n"/>
+      <c r="AJ58" s="41" t="n"/>
+      <c r="AK58" s="42" t="n"/>
       <c r="AL58" s="31" t="n"/>
-      <c r="AM58" s="39" t="n"/>
-      <c r="AN58" s="39" t="n"/>
-      <c r="AO58" s="40" t="n"/>
-      <c r="AP58" s="94" t="n"/>
+      <c r="AM58" s="41" t="n"/>
+      <c r="AN58" s="41" t="n"/>
+      <c r="AO58" s="42" t="n"/>
+      <c r="AP58" s="98" t="n"/>
       <c r="AQ58" s="33" t="n"/>
       <c r="AR58" s="33" t="n"/>
       <c r="AS58" s="34" t="n"/>
-      <c r="AT58" s="94" t="n"/>
+      <c r="AT58" s="98" t="n"/>
       <c r="AU58" s="33" t="n"/>
       <c r="AV58" s="33" t="n"/>
       <c r="AW58" s="34" t="n"/>
-      <c r="AX58" s="94" t="n"/>
+      <c r="AX58" s="98" t="n"/>
       <c r="AY58" s="33" t="n"/>
       <c r="AZ58" s="33" t="n"/>
       <c r="BA58" s="34" t="n"/>
-      <c r="BB58" s="36" t="inlineStr">
+      <c r="BB58" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BC58" s="33" t="n"/>
-      <c r="BD58" s="37" t="inlineStr">
+      <c r="BD58" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BE58" s="34" t="n"/>
-      <c r="BF58" s="94" t="n"/>
+      <c r="BF58" s="98" t="n"/>
       <c r="BG58" s="33" t="n"/>
       <c r="BH58" s="33" t="n"/>
       <c r="BI58" s="34" t="n"/>
-      <c r="BJ58" s="94" t="n"/>
+      <c r="BJ58" s="98" t="n"/>
       <c r="BK58" s="33" t="n"/>
       <c r="BL58" s="33" t="n"/>
       <c r="BM58" s="34" t="n"/>
-      <c r="BN58" s="94" t="n"/>
+      <c r="BN58" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="BO58" s="33" t="n"/>
       <c r="BP58" s="33" t="n"/>
       <c r="BQ58" s="34" t="n"/>
-      <c r="BR58" s="94" t="n"/>
+      <c r="BR58" s="98" t="n"/>
       <c r="BS58" s="33" t="n"/>
       <c r="BT58" s="33" t="n"/>
       <c r="BU58" s="34" t="n"/>
       <c r="BV58" s="31" t="n"/>
-      <c r="BW58" s="39" t="n"/>
-      <c r="BX58" s="39" t="n"/>
-      <c r="BY58" s="40" t="n"/>
+      <c r="BW58" s="41" t="n"/>
+      <c r="BX58" s="41" t="n"/>
+      <c r="BY58" s="42" t="n"/>
       <c r="BZ58" s="31" t="n"/>
-      <c r="CA58" s="39" t="n"/>
-      <c r="CB58" s="39" t="n"/>
-      <c r="CC58" s="40" t="n"/>
+      <c r="CA58" s="41" t="n"/>
+      <c r="CB58" s="41" t="n"/>
+      <c r="CC58" s="42" t="n"/>
       <c r="CD58" s="31" t="n"/>
-      <c r="CE58" s="39" t="n"/>
-      <c r="CF58" s="39" t="n"/>
-      <c r="CG58" s="50" t="n"/>
+      <c r="CE58" s="41" t="n"/>
+      <c r="CF58" s="41" t="n"/>
+      <c r="CG58" s="54" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="29" t="inlineStr">
@@ -7662,97 +7867,97 @@
         </is>
       </c>
       <c r="F59" s="31" t="n"/>
-      <c r="G59" s="39" t="n"/>
-      <c r="H59" s="39" t="n"/>
-      <c r="I59" s="40" t="n"/>
+      <c r="G59" s="41" t="n"/>
+      <c r="H59" s="41" t="n"/>
+      <c r="I59" s="42" t="n"/>
       <c r="J59" s="31" t="n"/>
-      <c r="K59" s="39" t="n"/>
-      <c r="L59" s="39" t="n"/>
-      <c r="M59" s="40" t="n"/>
+      <c r="K59" s="41" t="n"/>
+      <c r="L59" s="41" t="n"/>
+      <c r="M59" s="42" t="n"/>
       <c r="N59" s="31" t="n"/>
-      <c r="O59" s="39" t="n"/>
-      <c r="P59" s="39" t="n"/>
-      <c r="Q59" s="40" t="n"/>
+      <c r="O59" s="41" t="n"/>
+      <c r="P59" s="41" t="n"/>
+      <c r="Q59" s="42" t="n"/>
       <c r="R59" s="31" t="n"/>
-      <c r="S59" s="39" t="n"/>
-      <c r="T59" s="39" t="n"/>
-      <c r="U59" s="40" t="n"/>
+      <c r="S59" s="41" t="n"/>
+      <c r="T59" s="41" t="n"/>
+      <c r="U59" s="42" t="n"/>
       <c r="V59" s="31" t="n"/>
-      <c r="W59" s="39" t="n"/>
-      <c r="X59" s="39" t="n"/>
-      <c r="Y59" s="40" t="n"/>
+      <c r="W59" s="41" t="n"/>
+      <c r="X59" s="41" t="n"/>
+      <c r="Y59" s="42" t="n"/>
       <c r="Z59" s="31" t="n"/>
-      <c r="AA59" s="39" t="n"/>
-      <c r="AB59" s="39" t="n"/>
-      <c r="AC59" s="40" t="n"/>
+      <c r="AA59" s="41" t="n"/>
+      <c r="AB59" s="41" t="n"/>
+      <c r="AC59" s="42" t="n"/>
       <c r="AD59" s="31" t="n"/>
-      <c r="AE59" s="39" t="n"/>
-      <c r="AF59" s="39" t="n"/>
-      <c r="AG59" s="40" t="n"/>
+      <c r="AE59" s="41" t="n"/>
+      <c r="AF59" s="41" t="n"/>
+      <c r="AG59" s="42" t="n"/>
       <c r="AH59" s="31" t="n"/>
-      <c r="AI59" s="39" t="n"/>
-      <c r="AJ59" s="39" t="n"/>
-      <c r="AK59" s="40" t="n"/>
+      <c r="AI59" s="41" t="n"/>
+      <c r="AJ59" s="41" t="n"/>
+      <c r="AK59" s="42" t="n"/>
       <c r="AL59" s="31" t="n"/>
-      <c r="AM59" s="39" t="n"/>
-      <c r="AN59" s="39" t="n"/>
-      <c r="AO59" s="40" t="n"/>
+      <c r="AM59" s="41" t="n"/>
+      <c r="AN59" s="41" t="n"/>
+      <c r="AO59" s="42" t="n"/>
       <c r="AP59" s="31" t="n"/>
-      <c r="AQ59" s="39" t="n"/>
-      <c r="AR59" s="39" t="n"/>
-      <c r="AS59" s="40" t="n"/>
+      <c r="AQ59" s="41" t="n"/>
+      <c r="AR59" s="41" t="n"/>
+      <c r="AS59" s="42" t="n"/>
       <c r="AT59" s="31" t="n"/>
-      <c r="AU59" s="39" t="n"/>
-      <c r="AV59" s="39" t="n"/>
-      <c r="AW59" s="40" t="n"/>
+      <c r="AU59" s="41" t="n"/>
+      <c r="AV59" s="41" t="n"/>
+      <c r="AW59" s="42" t="n"/>
       <c r="AX59" s="31" t="n"/>
-      <c r="AY59" s="39" t="n"/>
-      <c r="AZ59" s="39" t="n"/>
-      <c r="BA59" s="40" t="n"/>
-      <c r="BB59" s="94" t="n"/>
+      <c r="AY59" s="41" t="n"/>
+      <c r="AZ59" s="41" t="n"/>
+      <c r="BA59" s="42" t="n"/>
+      <c r="BB59" s="98" t="n"/>
       <c r="BC59" s="33" t="n"/>
       <c r="BD59" s="33" t="n"/>
       <c r="BE59" s="34" t="n"/>
-      <c r="BF59" s="49" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BF59" s="98" t="n"/>
       <c r="BG59" s="33" t="n"/>
       <c r="BH59" s="33" t="n"/>
       <c r="BI59" s="34" t="n"/>
-      <c r="BJ59" s="94" t="n"/>
+      <c r="BJ59" s="98" t="n"/>
       <c r="BK59" s="33" t="n"/>
       <c r="BL59" s="33" t="n"/>
       <c r="BM59" s="34" t="n"/>
-      <c r="BN59" s="36" t="inlineStr">
+      <c r="BN59" s="37" t="inlineStr">
         <is>
           <t>Meal Break</t>
         </is>
       </c>
       <c r="BO59" s="33" t="n"/>
-      <c r="BP59" s="37" t="inlineStr">
+      <c r="BP59" s="38" t="inlineStr">
         <is>
           <t>CSSI</t>
         </is>
       </c>
       <c r="BQ59" s="34" t="n"/>
-      <c r="BR59" s="94" t="n"/>
+      <c r="BR59" s="98" t="n"/>
       <c r="BS59" s="33" t="n"/>
       <c r="BT59" s="33" t="n"/>
       <c r="BU59" s="34" t="n"/>
-      <c r="BV59" s="94" t="n"/>
+      <c r="BV59" s="39" t="inlineStr">
+        <is>
+          <t>Top of Esc</t>
+        </is>
+      </c>
       <c r="BW59" s="33" t="n"/>
       <c r="BX59" s="33" t="n"/>
       <c r="BY59" s="34" t="n"/>
-      <c r="BZ59" s="94" t="n"/>
+      <c r="BZ59" s="98" t="n"/>
       <c r="CA59" s="33" t="n"/>
       <c r="CB59" s="33" t="n"/>
       <c r="CC59" s="34" t="n"/>
-      <c r="CD59" s="101" t="n"/>
+      <c r="CD59" s="102" t="n"/>
       <c r="CE59" s="33" t="n"/>
       <c r="CF59" s="33" t="n"/>
-      <c r="CG59" s="50" t="n"/>
+      <c r="CG59" s="54" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="29" t="inlineStr"/>
@@ -7761,85 +7966,85 @@
       <c r="D60" s="30" t="n"/>
       <c r="E60" s="30" t="n"/>
       <c r="F60" s="31" t="n"/>
-      <c r="G60" s="39" t="n"/>
-      <c r="H60" s="39" t="n"/>
-      <c r="I60" s="40" t="n"/>
+      <c r="G60" s="41" t="n"/>
+      <c r="H60" s="41" t="n"/>
+      <c r="I60" s="42" t="n"/>
       <c r="J60" s="31" t="n"/>
-      <c r="K60" s="39" t="n"/>
-      <c r="L60" s="39" t="n"/>
-      <c r="M60" s="40" t="n"/>
+      <c r="K60" s="41" t="n"/>
+      <c r="L60" s="41" t="n"/>
+      <c r="M60" s="42" t="n"/>
       <c r="N60" s="31" t="n"/>
-      <c r="O60" s="39" t="n"/>
-      <c r="P60" s="39" t="n"/>
-      <c r="Q60" s="40" t="n"/>
+      <c r="O60" s="41" t="n"/>
+      <c r="P60" s="41" t="n"/>
+      <c r="Q60" s="42" t="n"/>
       <c r="R60" s="31" t="n"/>
-      <c r="S60" s="39" t="n"/>
-      <c r="T60" s="39" t="n"/>
-      <c r="U60" s="40" t="n"/>
+      <c r="S60" s="41" t="n"/>
+      <c r="T60" s="41" t="n"/>
+      <c r="U60" s="42" t="n"/>
       <c r="V60" s="31" t="n"/>
-      <c r="W60" s="39" t="n"/>
-      <c r="X60" s="39" t="n"/>
-      <c r="Y60" s="40" t="n"/>
+      <c r="W60" s="41" t="n"/>
+      <c r="X60" s="41" t="n"/>
+      <c r="Y60" s="42" t="n"/>
       <c r="Z60" s="31" t="n"/>
-      <c r="AA60" s="39" t="n"/>
-      <c r="AB60" s="39" t="n"/>
-      <c r="AC60" s="40" t="n"/>
+      <c r="AA60" s="41" t="n"/>
+      <c r="AB60" s="41" t="n"/>
+      <c r="AC60" s="42" t="n"/>
       <c r="AD60" s="31" t="n"/>
-      <c r="AE60" s="39" t="n"/>
-      <c r="AF60" s="39" t="n"/>
-      <c r="AG60" s="40" t="n"/>
+      <c r="AE60" s="41" t="n"/>
+      <c r="AF60" s="41" t="n"/>
+      <c r="AG60" s="42" t="n"/>
       <c r="AH60" s="31" t="n"/>
-      <c r="AI60" s="39" t="n"/>
-      <c r="AJ60" s="39" t="n"/>
-      <c r="AK60" s="40" t="n"/>
+      <c r="AI60" s="41" t="n"/>
+      <c r="AJ60" s="41" t="n"/>
+      <c r="AK60" s="42" t="n"/>
       <c r="AL60" s="31" t="n"/>
-      <c r="AM60" s="39" t="n"/>
-      <c r="AN60" s="39" t="n"/>
-      <c r="AO60" s="40" t="n"/>
+      <c r="AM60" s="41" t="n"/>
+      <c r="AN60" s="41" t="n"/>
+      <c r="AO60" s="42" t="n"/>
       <c r="AP60" s="31" t="n"/>
-      <c r="AQ60" s="39" t="n"/>
-      <c r="AR60" s="39" t="n"/>
-      <c r="AS60" s="40" t="n"/>
+      <c r="AQ60" s="41" t="n"/>
+      <c r="AR60" s="41" t="n"/>
+      <c r="AS60" s="42" t="n"/>
       <c r="AT60" s="31" t="n"/>
-      <c r="AU60" s="39" t="n"/>
-      <c r="AV60" s="39" t="n"/>
-      <c r="AW60" s="40" t="n"/>
+      <c r="AU60" s="41" t="n"/>
+      <c r="AV60" s="41" t="n"/>
+      <c r="AW60" s="42" t="n"/>
       <c r="AX60" s="31" t="n"/>
-      <c r="AY60" s="39" t="n"/>
-      <c r="AZ60" s="39" t="n"/>
-      <c r="BA60" s="40" t="n"/>
+      <c r="AY60" s="41" t="n"/>
+      <c r="AZ60" s="41" t="n"/>
+      <c r="BA60" s="42" t="n"/>
       <c r="BB60" s="31" t="n"/>
-      <c r="BC60" s="39" t="n"/>
-      <c r="BD60" s="39" t="n"/>
-      <c r="BE60" s="40" t="n"/>
+      <c r="BC60" s="41" t="n"/>
+      <c r="BD60" s="41" t="n"/>
+      <c r="BE60" s="42" t="n"/>
       <c r="BF60" s="31" t="n"/>
-      <c r="BG60" s="39" t="n"/>
-      <c r="BH60" s="39" t="n"/>
-      <c r="BI60" s="40" t="n"/>
+      <c r="BG60" s="41" t="n"/>
+      <c r="BH60" s="41" t="n"/>
+      <c r="BI60" s="42" t="n"/>
       <c r="BJ60" s="31" t="n"/>
-      <c r="BK60" s="39" t="n"/>
-      <c r="BL60" s="39" t="n"/>
-      <c r="BM60" s="40" t="n"/>
+      <c r="BK60" s="41" t="n"/>
+      <c r="BL60" s="41" t="n"/>
+      <c r="BM60" s="42" t="n"/>
       <c r="BN60" s="31" t="n"/>
-      <c r="BO60" s="39" t="n"/>
-      <c r="BP60" s="39" t="n"/>
-      <c r="BQ60" s="40" t="n"/>
+      <c r="BO60" s="41" t="n"/>
+      <c r="BP60" s="41" t="n"/>
+      <c r="BQ60" s="42" t="n"/>
       <c r="BR60" s="31" t="n"/>
-      <c r="BS60" s="39" t="n"/>
-      <c r="BT60" s="39" t="n"/>
-      <c r="BU60" s="40" t="n"/>
+      <c r="BS60" s="41" t="n"/>
+      <c r="BT60" s="41" t="n"/>
+      <c r="BU60" s="42" t="n"/>
       <c r="BV60" s="31" t="n"/>
-      <c r="BW60" s="39" t="n"/>
-      <c r="BX60" s="39" t="n"/>
-      <c r="BY60" s="40" t="n"/>
+      <c r="BW60" s="41" t="n"/>
+      <c r="BX60" s="41" t="n"/>
+      <c r="BY60" s="42" t="n"/>
       <c r="BZ60" s="31" t="n"/>
-      <c r="CA60" s="39" t="n"/>
-      <c r="CB60" s="39" t="n"/>
-      <c r="CC60" s="40" t="n"/>
+      <c r="CA60" s="41" t="n"/>
+      <c r="CB60" s="41" t="n"/>
+      <c r="CC60" s="42" t="n"/>
       <c r="CD60" s="31" t="n"/>
-      <c r="CE60" s="39" t="n"/>
-      <c r="CF60" s="39" t="n"/>
-      <c r="CG60" s="50" t="n"/>
+      <c r="CE60" s="41" t="n"/>
+      <c r="CF60" s="41" t="n"/>
+      <c r="CG60" s="54" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="29" t="inlineStr"/>
@@ -7848,85 +8053,85 @@
       <c r="D61" s="30" t="n"/>
       <c r="E61" s="30" t="n"/>
       <c r="F61" s="31" t="n"/>
-      <c r="G61" s="39" t="n"/>
-      <c r="H61" s="39" t="n"/>
-      <c r="I61" s="40" t="n"/>
+      <c r="G61" s="41" t="n"/>
+      <c r="H61" s="41" t="n"/>
+      <c r="I61" s="42" t="n"/>
       <c r="J61" s="31" t="n"/>
-      <c r="K61" s="39" t="n"/>
-      <c r="L61" s="39" t="n"/>
-      <c r="M61" s="40" t="n"/>
+      <c r="K61" s="41" t="n"/>
+      <c r="L61" s="41" t="n"/>
+      <c r="M61" s="42" t="n"/>
       <c r="N61" s="31" t="n"/>
-      <c r="O61" s="39" t="n"/>
-      <c r="P61" s="39" t="n"/>
-      <c r="Q61" s="40" t="n"/>
+      <c r="O61" s="41" t="n"/>
+      <c r="P61" s="41" t="n"/>
+      <c r="Q61" s="42" t="n"/>
       <c r="R61" s="31" t="n"/>
-      <c r="S61" s="39" t="n"/>
-      <c r="T61" s="39" t="n"/>
-      <c r="U61" s="40" t="n"/>
+      <c r="S61" s="41" t="n"/>
+      <c r="T61" s="41" t="n"/>
+      <c r="U61" s="42" t="n"/>
       <c r="V61" s="31" t="n"/>
-      <c r="W61" s="39" t="n"/>
-      <c r="X61" s="39" t="n"/>
-      <c r="Y61" s="40" t="n"/>
+      <c r="W61" s="41" t="n"/>
+      <c r="X61" s="41" t="n"/>
+      <c r="Y61" s="42" t="n"/>
       <c r="Z61" s="31" t="n"/>
-      <c r="AA61" s="39" t="n"/>
-      <c r="AB61" s="39" t="n"/>
-      <c r="AC61" s="40" t="n"/>
+      <c r="AA61" s="41" t="n"/>
+      <c r="AB61" s="41" t="n"/>
+      <c r="AC61" s="42" t="n"/>
       <c r="AD61" s="31" t="n"/>
-      <c r="AE61" s="39" t="n"/>
-      <c r="AF61" s="39" t="n"/>
-      <c r="AG61" s="40" t="n"/>
+      <c r="AE61" s="41" t="n"/>
+      <c r="AF61" s="41" t="n"/>
+      <c r="AG61" s="42" t="n"/>
       <c r="AH61" s="31" t="n"/>
-      <c r="AI61" s="39" t="n"/>
-      <c r="AJ61" s="39" t="n"/>
-      <c r="AK61" s="40" t="n"/>
+      <c r="AI61" s="41" t="n"/>
+      <c r="AJ61" s="41" t="n"/>
+      <c r="AK61" s="42" t="n"/>
       <c r="AL61" s="31" t="n"/>
-      <c r="AM61" s="39" t="n"/>
-      <c r="AN61" s="39" t="n"/>
-      <c r="AO61" s="40" t="n"/>
+      <c r="AM61" s="41" t="n"/>
+      <c r="AN61" s="41" t="n"/>
+      <c r="AO61" s="42" t="n"/>
       <c r="AP61" s="31" t="n"/>
-      <c r="AQ61" s="39" t="n"/>
-      <c r="AR61" s="39" t="n"/>
-      <c r="AS61" s="40" t="n"/>
+      <c r="AQ61" s="41" t="n"/>
+      <c r="AR61" s="41" t="n"/>
+      <c r="AS61" s="42" t="n"/>
       <c r="AT61" s="31" t="n"/>
-      <c r="AU61" s="39" t="n"/>
-      <c r="AV61" s="39" t="n"/>
-      <c r="AW61" s="40" t="n"/>
+      <c r="AU61" s="41" t="n"/>
+      <c r="AV61" s="41" t="n"/>
+      <c r="AW61" s="42" t="n"/>
       <c r="AX61" s="31" t="n"/>
-      <c r="AY61" s="39" t="n"/>
-      <c r="AZ61" s="39" t="n"/>
-      <c r="BA61" s="40" t="n"/>
+      <c r="AY61" s="41" t="n"/>
+      <c r="AZ61" s="41" t="n"/>
+      <c r="BA61" s="42" t="n"/>
       <c r="BB61" s="31" t="n"/>
-      <c r="BC61" s="39" t="n"/>
-      <c r="BD61" s="39" t="n"/>
-      <c r="BE61" s="40" t="n"/>
+      <c r="BC61" s="41" t="n"/>
+      <c r="BD61" s="41" t="n"/>
+      <c r="BE61" s="42" t="n"/>
       <c r="BF61" s="31" t="n"/>
-      <c r="BG61" s="39" t="n"/>
-      <c r="BH61" s="39" t="n"/>
-      <c r="BI61" s="40" t="n"/>
+      <c r="BG61" s="41" t="n"/>
+      <c r="BH61" s="41" t="n"/>
+      <c r="BI61" s="42" t="n"/>
       <c r="BJ61" s="31" t="n"/>
-      <c r="BK61" s="39" t="n"/>
-      <c r="BL61" s="39" t="n"/>
-      <c r="BM61" s="40" t="n"/>
+      <c r="BK61" s="41" t="n"/>
+      <c r="BL61" s="41" t="n"/>
+      <c r="BM61" s="42" t="n"/>
       <c r="BN61" s="31" t="n"/>
-      <c r="BO61" s="39" t="n"/>
-      <c r="BP61" s="39" t="n"/>
-      <c r="BQ61" s="40" t="n"/>
+      <c r="BO61" s="41" t="n"/>
+      <c r="BP61" s="41" t="n"/>
+      <c r="BQ61" s="42" t="n"/>
       <c r="BR61" s="31" t="n"/>
-      <c r="BS61" s="39" t="n"/>
-      <c r="BT61" s="39" t="n"/>
-      <c r="BU61" s="40" t="n"/>
+      <c r="BS61" s="41" t="n"/>
+      <c r="BT61" s="41" t="n"/>
+      <c r="BU61" s="42" t="n"/>
       <c r="BV61" s="31" t="n"/>
-      <c r="BW61" s="39" t="n"/>
-      <c r="BX61" s="39" t="n"/>
-      <c r="BY61" s="40" t="n"/>
+      <c r="BW61" s="41" t="n"/>
+      <c r="BX61" s="41" t="n"/>
+      <c r="BY61" s="42" t="n"/>
       <c r="BZ61" s="31" t="n"/>
-      <c r="CA61" s="39" t="n"/>
-      <c r="CB61" s="39" t="n"/>
-      <c r="CC61" s="40" t="n"/>
+      <c r="CA61" s="41" t="n"/>
+      <c r="CB61" s="41" t="n"/>
+      <c r="CC61" s="42" t="n"/>
       <c r="CD61" s="31" t="n"/>
-      <c r="CE61" s="39" t="n"/>
-      <c r="CF61" s="39" t="n"/>
-      <c r="CG61" s="50" t="n"/>
+      <c r="CE61" s="41" t="n"/>
+      <c r="CF61" s="41" t="n"/>
+      <c r="CG61" s="54" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="29" t="inlineStr"/>
@@ -7935,85 +8140,85 @@
       <c r="D62" s="30" t="n"/>
       <c r="E62" s="30" t="n"/>
       <c r="F62" s="31" t="n"/>
-      <c r="G62" s="39" t="n"/>
-      <c r="H62" s="39" t="n"/>
-      <c r="I62" s="40" t="n"/>
+      <c r="G62" s="41" t="n"/>
+      <c r="H62" s="41" t="n"/>
+      <c r="I62" s="42" t="n"/>
       <c r="J62" s="31" t="n"/>
-      <c r="K62" s="39" t="n"/>
-      <c r="L62" s="39" t="n"/>
-      <c r="M62" s="40" t="n"/>
+      <c r="K62" s="41" t="n"/>
+      <c r="L62" s="41" t="n"/>
+      <c r="M62" s="42" t="n"/>
       <c r="N62" s="31" t="n"/>
-      <c r="O62" s="39" t="n"/>
-      <c r="P62" s="39" t="n"/>
-      <c r="Q62" s="40" t="n"/>
+      <c r="O62" s="41" t="n"/>
+      <c r="P62" s="41" t="n"/>
+      <c r="Q62" s="42" t="n"/>
       <c r="R62" s="31" t="n"/>
-      <c r="S62" s="39" t="n"/>
-      <c r="T62" s="39" t="n"/>
-      <c r="U62" s="40" t="n"/>
+      <c r="S62" s="41" t="n"/>
+      <c r="T62" s="41" t="n"/>
+      <c r="U62" s="42" t="n"/>
       <c r="V62" s="31" t="n"/>
-      <c r="W62" s="39" t="n"/>
-      <c r="X62" s="39" t="n"/>
-      <c r="Y62" s="40" t="n"/>
+      <c r="W62" s="41" t="n"/>
+      <c r="X62" s="41" t="n"/>
+      <c r="Y62" s="42" t="n"/>
       <c r="Z62" s="31" t="n"/>
-      <c r="AA62" s="39" t="n"/>
-      <c r="AB62" s="39" t="n"/>
-      <c r="AC62" s="40" t="n"/>
+      <c r="AA62" s="41" t="n"/>
+      <c r="AB62" s="41" t="n"/>
+      <c r="AC62" s="42" t="n"/>
       <c r="AD62" s="31" t="n"/>
-      <c r="AE62" s="39" t="n"/>
-      <c r="AF62" s="39" t="n"/>
-      <c r="AG62" s="40" t="n"/>
+      <c r="AE62" s="41" t="n"/>
+      <c r="AF62" s="41" t="n"/>
+      <c r="AG62" s="42" t="n"/>
       <c r="AH62" s="31" t="n"/>
-      <c r="AI62" s="39" t="n"/>
-      <c r="AJ62" s="39" t="n"/>
-      <c r="AK62" s="40" t="n"/>
+      <c r="AI62" s="41" t="n"/>
+      <c r="AJ62" s="41" t="n"/>
+      <c r="AK62" s="42" t="n"/>
       <c r="AL62" s="31" t="n"/>
-      <c r="AM62" s="39" t="n"/>
-      <c r="AN62" s="39" t="n"/>
-      <c r="AO62" s="40" t="n"/>
+      <c r="AM62" s="41" t="n"/>
+      <c r="AN62" s="41" t="n"/>
+      <c r="AO62" s="42" t="n"/>
       <c r="AP62" s="31" t="n"/>
-      <c r="AQ62" s="39" t="n"/>
-      <c r="AR62" s="39" t="n"/>
-      <c r="AS62" s="40" t="n"/>
+      <c r="AQ62" s="41" t="n"/>
+      <c r="AR62" s="41" t="n"/>
+      <c r="AS62" s="42" t="n"/>
       <c r="AT62" s="31" t="n"/>
-      <c r="AU62" s="39" t="n"/>
-      <c r="AV62" s="39" t="n"/>
-      <c r="AW62" s="40" t="n"/>
+      <c r="AU62" s="41" t="n"/>
+      <c r="AV62" s="41" t="n"/>
+      <c r="AW62" s="42" t="n"/>
       <c r="AX62" s="31" t="n"/>
-      <c r="AY62" s="39" t="n"/>
-      <c r="AZ62" s="39" t="n"/>
-      <c r="BA62" s="40" t="n"/>
+      <c r="AY62" s="41" t="n"/>
+      <c r="AZ62" s="41" t="n"/>
+      <c r="BA62" s="42" t="n"/>
       <c r="BB62" s="31" t="n"/>
-      <c r="BC62" s="39" t="n"/>
-      <c r="BD62" s="39" t="n"/>
-      <c r="BE62" s="40" t="n"/>
+      <c r="BC62" s="41" t="n"/>
+      <c r="BD62" s="41" t="n"/>
+      <c r="BE62" s="42" t="n"/>
       <c r="BF62" s="31" t="n"/>
-      <c r="BG62" s="39" t="n"/>
-      <c r="BH62" s="39" t="n"/>
-      <c r="BI62" s="40" t="n"/>
+      <c r="BG62" s="41" t="n"/>
+      <c r="BH62" s="41" t="n"/>
+      <c r="BI62" s="42" t="n"/>
       <c r="BJ62" s="31" t="n"/>
-      <c r="BK62" s="39" t="n"/>
-      <c r="BL62" s="39" t="n"/>
-      <c r="BM62" s="40" t="n"/>
+      <c r="BK62" s="41" t="n"/>
+      <c r="BL62" s="41" t="n"/>
+      <c r="BM62" s="42" t="n"/>
       <c r="BN62" s="31" t="n"/>
-      <c r="BO62" s="39" t="n"/>
-      <c r="BP62" s="39" t="n"/>
-      <c r="BQ62" s="40" t="n"/>
+      <c r="BO62" s="41" t="n"/>
+      <c r="BP62" s="41" t="n"/>
+      <c r="BQ62" s="42" t="n"/>
       <c r="BR62" s="31" t="n"/>
-      <c r="BS62" s="39" t="n"/>
-      <c r="BT62" s="39" t="n"/>
-      <c r="BU62" s="40" t="n"/>
+      <c r="BS62" s="41" t="n"/>
+      <c r="BT62" s="41" t="n"/>
+      <c r="BU62" s="42" t="n"/>
       <c r="BV62" s="31" t="n"/>
-      <c r="BW62" s="39" t="n"/>
-      <c r="BX62" s="39" t="n"/>
-      <c r="BY62" s="40" t="n"/>
+      <c r="BW62" s="41" t="n"/>
+      <c r="BX62" s="41" t="n"/>
+      <c r="BY62" s="42" t="n"/>
       <c r="BZ62" s="31" t="n"/>
-      <c r="CA62" s="39" t="n"/>
-      <c r="CB62" s="39" t="n"/>
-      <c r="CC62" s="40" t="n"/>
+      <c r="CA62" s="41" t="n"/>
+      <c r="CB62" s="41" t="n"/>
+      <c r="CC62" s="42" t="n"/>
       <c r="CD62" s="31" t="n"/>
-      <c r="CE62" s="39" t="n"/>
-      <c r="CF62" s="39" t="n"/>
-      <c r="CG62" s="50" t="n"/>
+      <c r="CE62" s="41" t="n"/>
+      <c r="CF62" s="41" t="n"/>
+      <c r="CG62" s="54" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="29" t="inlineStr"/>
@@ -8022,175 +8227,175 @@
       <c r="D63" s="30" t="n"/>
       <c r="E63" s="30" t="n"/>
       <c r="F63" s="31" t="n"/>
-      <c r="G63" s="39" t="n"/>
-      <c r="H63" s="39" t="n"/>
-      <c r="I63" s="40" t="n"/>
+      <c r="G63" s="41" t="n"/>
+      <c r="H63" s="41" t="n"/>
+      <c r="I63" s="42" t="n"/>
       <c r="J63" s="31" t="n"/>
-      <c r="K63" s="39" t="n"/>
-      <c r="L63" s="39" t="n"/>
-      <c r="M63" s="40" t="n"/>
+      <c r="K63" s="41" t="n"/>
+      <c r="L63" s="41" t="n"/>
+      <c r="M63" s="42" t="n"/>
       <c r="N63" s="31" t="n"/>
-      <c r="O63" s="39" t="n"/>
-      <c r="P63" s="39" t="n"/>
-      <c r="Q63" s="40" t="n"/>
+      <c r="O63" s="41" t="n"/>
+      <c r="P63" s="41" t="n"/>
+      <c r="Q63" s="42" t="n"/>
       <c r="R63" s="31" t="n"/>
-      <c r="S63" s="39" t="n"/>
-      <c r="T63" s="39" t="n"/>
-      <c r="U63" s="40" t="n"/>
+      <c r="S63" s="41" t="n"/>
+      <c r="T63" s="41" t="n"/>
+      <c r="U63" s="42" t="n"/>
       <c r="V63" s="31" t="n"/>
-      <c r="W63" s="39" t="n"/>
-      <c r="X63" s="39" t="n"/>
-      <c r="Y63" s="40" t="n"/>
+      <c r="W63" s="41" t="n"/>
+      <c r="X63" s="41" t="n"/>
+      <c r="Y63" s="42" t="n"/>
       <c r="Z63" s="31" t="n"/>
-      <c r="AA63" s="39" t="n"/>
-      <c r="AB63" s="39" t="n"/>
-      <c r="AC63" s="40" t="n"/>
+      <c r="AA63" s="41" t="n"/>
+      <c r="AB63" s="41" t="n"/>
+      <c r="AC63" s="42" t="n"/>
       <c r="AD63" s="31" t="n"/>
-      <c r="AE63" s="39" t="n"/>
-      <c r="AF63" s="39" t="n"/>
-      <c r="AG63" s="40" t="n"/>
+      <c r="AE63" s="41" t="n"/>
+      <c r="AF63" s="41" t="n"/>
+      <c r="AG63" s="42" t="n"/>
       <c r="AH63" s="31" t="n"/>
-      <c r="AI63" s="39" t="n"/>
-      <c r="AJ63" s="39" t="n"/>
-      <c r="AK63" s="40" t="n"/>
+      <c r="AI63" s="41" t="n"/>
+      <c r="AJ63" s="41" t="n"/>
+      <c r="AK63" s="42" t="n"/>
       <c r="AL63" s="31" t="n"/>
-      <c r="AM63" s="39" t="n"/>
-      <c r="AN63" s="39" t="n"/>
-      <c r="AO63" s="40" t="n"/>
+      <c r="AM63" s="41" t="n"/>
+      <c r="AN63" s="41" t="n"/>
+      <c r="AO63" s="42" t="n"/>
       <c r="AP63" s="31" t="n"/>
-      <c r="AQ63" s="39" t="n"/>
-      <c r="AR63" s="39" t="n"/>
-      <c r="AS63" s="40" t="n"/>
+      <c r="AQ63" s="41" t="n"/>
+      <c r="AR63" s="41" t="n"/>
+      <c r="AS63" s="42" t="n"/>
       <c r="AT63" s="31" t="n"/>
-      <c r="AU63" s="39" t="n"/>
-      <c r="AV63" s="39" t="n"/>
-      <c r="AW63" s="40" t="n"/>
+      <c r="AU63" s="41" t="n"/>
+      <c r="AV63" s="41" t="n"/>
+      <c r="AW63" s="42" t="n"/>
       <c r="AX63" s="31" t="n"/>
-      <c r="AY63" s="39" t="n"/>
-      <c r="AZ63" s="39" t="n"/>
-      <c r="BA63" s="40" t="n"/>
+      <c r="AY63" s="41" t="n"/>
+      <c r="AZ63" s="41" t="n"/>
+      <c r="BA63" s="42" t="n"/>
       <c r="BB63" s="31" t="n"/>
-      <c r="BC63" s="39" t="n"/>
-      <c r="BD63" s="39" t="n"/>
-      <c r="BE63" s="40" t="n"/>
+      <c r="BC63" s="41" t="n"/>
+      <c r="BD63" s="41" t="n"/>
+      <c r="BE63" s="42" t="n"/>
       <c r="BF63" s="31" t="n"/>
-      <c r="BG63" s="39" t="n"/>
-      <c r="BH63" s="39" t="n"/>
-      <c r="BI63" s="40" t="n"/>
+      <c r="BG63" s="41" t="n"/>
+      <c r="BH63" s="41" t="n"/>
+      <c r="BI63" s="42" t="n"/>
       <c r="BJ63" s="31" t="n"/>
-      <c r="BK63" s="39" t="n"/>
-      <c r="BL63" s="39" t="n"/>
-      <c r="BM63" s="40" t="n"/>
+      <c r="BK63" s="41" t="n"/>
+      <c r="BL63" s="41" t="n"/>
+      <c r="BM63" s="42" t="n"/>
       <c r="BN63" s="31" t="n"/>
-      <c r="BO63" s="39" t="n"/>
-      <c r="BP63" s="39" t="n"/>
-      <c r="BQ63" s="40" t="n"/>
+      <c r="BO63" s="41" t="n"/>
+      <c r="BP63" s="41" t="n"/>
+      <c r="BQ63" s="42" t="n"/>
       <c r="BR63" s="31" t="n"/>
-      <c r="BS63" s="39" t="n"/>
-      <c r="BT63" s="39" t="n"/>
-      <c r="BU63" s="40" t="n"/>
+      <c r="BS63" s="41" t="n"/>
+      <c r="BT63" s="41" t="n"/>
+      <c r="BU63" s="42" t="n"/>
       <c r="BV63" s="31" t="n"/>
-      <c r="BW63" s="39" t="n"/>
-      <c r="BX63" s="39" t="n"/>
-      <c r="BY63" s="40" t="n"/>
+      <c r="BW63" s="41" t="n"/>
+      <c r="BX63" s="41" t="n"/>
+      <c r="BY63" s="42" t="n"/>
       <c r="BZ63" s="31" t="n"/>
-      <c r="CA63" s="39" t="n"/>
-      <c r="CB63" s="39" t="n"/>
-      <c r="CC63" s="40" t="n"/>
+      <c r="CA63" s="41" t="n"/>
+      <c r="CB63" s="41" t="n"/>
+      <c r="CC63" s="42" t="n"/>
       <c r="CD63" s="31" t="n"/>
-      <c r="CE63" s="39" t="n"/>
-      <c r="CF63" s="39" t="n"/>
-      <c r="CG63" s="50" t="n"/>
+      <c r="CE63" s="41" t="n"/>
+      <c r="CF63" s="41" t="n"/>
+      <c r="CG63" s="54" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="69" t="inlineStr"/>
-      <c r="B64" s="70" t="n"/>
-      <c r="C64" s="70" t="n"/>
-      <c r="D64" s="70" t="n"/>
-      <c r="E64" s="70" t="n"/>
-      <c r="F64" s="71" t="n"/>
-      <c r="G64" s="72" t="n"/>
-      <c r="H64" s="72" t="n"/>
-      <c r="I64" s="73" t="n"/>
-      <c r="J64" s="71" t="n"/>
-      <c r="K64" s="72" t="n"/>
-      <c r="L64" s="72" t="n"/>
-      <c r="M64" s="73" t="n"/>
-      <c r="N64" s="71" t="n"/>
-      <c r="O64" s="72" t="n"/>
-      <c r="P64" s="72" t="n"/>
-      <c r="Q64" s="73" t="n"/>
-      <c r="R64" s="71" t="n"/>
-      <c r="S64" s="72" t="n"/>
-      <c r="T64" s="72" t="n"/>
-      <c r="U64" s="73" t="n"/>
-      <c r="V64" s="71" t="n"/>
-      <c r="W64" s="72" t="n"/>
-      <c r="X64" s="72" t="n"/>
-      <c r="Y64" s="73" t="n"/>
-      <c r="Z64" s="71" t="n"/>
-      <c r="AA64" s="72" t="n"/>
-      <c r="AB64" s="72" t="n"/>
-      <c r="AC64" s="73" t="n"/>
-      <c r="AD64" s="71" t="n"/>
-      <c r="AE64" s="72" t="n"/>
-      <c r="AF64" s="72" t="n"/>
-      <c r="AG64" s="73" t="n"/>
-      <c r="AH64" s="71" t="n"/>
-      <c r="AI64" s="72" t="n"/>
-      <c r="AJ64" s="72" t="n"/>
-      <c r="AK64" s="73" t="n"/>
-      <c r="AL64" s="71" t="n"/>
-      <c r="AM64" s="72" t="n"/>
-      <c r="AN64" s="72" t="n"/>
-      <c r="AO64" s="73" t="n"/>
-      <c r="AP64" s="71" t="n"/>
-      <c r="AQ64" s="72" t="n"/>
-      <c r="AR64" s="72" t="n"/>
-      <c r="AS64" s="73" t="n"/>
-      <c r="AT64" s="71" t="n"/>
-      <c r="AU64" s="72" t="n"/>
-      <c r="AV64" s="72" t="n"/>
-      <c r="AW64" s="73" t="n"/>
-      <c r="AX64" s="71" t="n"/>
-      <c r="AY64" s="72" t="n"/>
-      <c r="AZ64" s="72" t="n"/>
-      <c r="BA64" s="73" t="n"/>
-      <c r="BB64" s="71" t="n"/>
-      <c r="BC64" s="72" t="n"/>
-      <c r="BD64" s="72" t="n"/>
-      <c r="BE64" s="73" t="n"/>
-      <c r="BF64" s="71" t="n"/>
-      <c r="BG64" s="72" t="n"/>
-      <c r="BH64" s="72" t="n"/>
-      <c r="BI64" s="73" t="n"/>
-      <c r="BJ64" s="71" t="n"/>
-      <c r="BK64" s="72" t="n"/>
-      <c r="BL64" s="72" t="n"/>
-      <c r="BM64" s="73" t="n"/>
-      <c r="BN64" s="71" t="n"/>
-      <c r="BO64" s="72" t="n"/>
-      <c r="BP64" s="72" t="n"/>
-      <c r="BQ64" s="73" t="n"/>
-      <c r="BR64" s="71" t="n"/>
-      <c r="BS64" s="72" t="n"/>
-      <c r="BT64" s="72" t="n"/>
-      <c r="BU64" s="73" t="n"/>
-      <c r="BV64" s="71" t="n"/>
-      <c r="BW64" s="72" t="n"/>
-      <c r="BX64" s="72" t="n"/>
-      <c r="BY64" s="73" t="n"/>
-      <c r="BZ64" s="71" t="n"/>
-      <c r="CA64" s="72" t="n"/>
-      <c r="CB64" s="72" t="n"/>
-      <c r="CC64" s="73" t="n"/>
-      <c r="CD64" s="71" t="n"/>
-      <c r="CE64" s="72" t="n"/>
-      <c r="CF64" s="72" t="n"/>
-      <c r="CG64" s="74" t="n"/>
+      <c r="A64" s="73" t="inlineStr"/>
+      <c r="B64" s="74" t="n"/>
+      <c r="C64" s="74" t="n"/>
+      <c r="D64" s="74" t="n"/>
+      <c r="E64" s="74" t="n"/>
+      <c r="F64" s="75" t="n"/>
+      <c r="G64" s="76" t="n"/>
+      <c r="H64" s="76" t="n"/>
+      <c r="I64" s="77" t="n"/>
+      <c r="J64" s="75" t="n"/>
+      <c r="K64" s="76" t="n"/>
+      <c r="L64" s="76" t="n"/>
+      <c r="M64" s="77" t="n"/>
+      <c r="N64" s="75" t="n"/>
+      <c r="O64" s="76" t="n"/>
+      <c r="P64" s="76" t="n"/>
+      <c r="Q64" s="77" t="n"/>
+      <c r="R64" s="75" t="n"/>
+      <c r="S64" s="76" t="n"/>
+      <c r="T64" s="76" t="n"/>
+      <c r="U64" s="77" t="n"/>
+      <c r="V64" s="75" t="n"/>
+      <c r="W64" s="76" t="n"/>
+      <c r="X64" s="76" t="n"/>
+      <c r="Y64" s="77" t="n"/>
+      <c r="Z64" s="75" t="n"/>
+      <c r="AA64" s="76" t="n"/>
+      <c r="AB64" s="76" t="n"/>
+      <c r="AC64" s="77" t="n"/>
+      <c r="AD64" s="75" t="n"/>
+      <c r="AE64" s="76" t="n"/>
+      <c r="AF64" s="76" t="n"/>
+      <c r="AG64" s="77" t="n"/>
+      <c r="AH64" s="75" t="n"/>
+      <c r="AI64" s="76" t="n"/>
+      <c r="AJ64" s="76" t="n"/>
+      <c r="AK64" s="77" t="n"/>
+      <c r="AL64" s="75" t="n"/>
+      <c r="AM64" s="76" t="n"/>
+      <c r="AN64" s="76" t="n"/>
+      <c r="AO64" s="77" t="n"/>
+      <c r="AP64" s="75" t="n"/>
+      <c r="AQ64" s="76" t="n"/>
+      <c r="AR64" s="76" t="n"/>
+      <c r="AS64" s="77" t="n"/>
+      <c r="AT64" s="75" t="n"/>
+      <c r="AU64" s="76" t="n"/>
+      <c r="AV64" s="76" t="n"/>
+      <c r="AW64" s="77" t="n"/>
+      <c r="AX64" s="75" t="n"/>
+      <c r="AY64" s="76" t="n"/>
+      <c r="AZ64" s="76" t="n"/>
+      <c r="BA64" s="77" t="n"/>
+      <c r="BB64" s="75" t="n"/>
+      <c r="BC64" s="76" t="n"/>
+      <c r="BD64" s="76" t="n"/>
+      <c r="BE64" s="77" t="n"/>
+      <c r="BF64" s="75" t="n"/>
+      <c r="BG64" s="76" t="n"/>
+      <c r="BH64" s="76" t="n"/>
+      <c r="BI64" s="77" t="n"/>
+      <c r="BJ64" s="75" t="n"/>
+      <c r="BK64" s="76" t="n"/>
+      <c r="BL64" s="76" t="n"/>
+      <c r="BM64" s="77" t="n"/>
+      <c r="BN64" s="75" t="n"/>
+      <c r="BO64" s="76" t="n"/>
+      <c r="BP64" s="76" t="n"/>
+      <c r="BQ64" s="77" t="n"/>
+      <c r="BR64" s="75" t="n"/>
+      <c r="BS64" s="76" t="n"/>
+      <c r="BT64" s="76" t="n"/>
+      <c r="BU64" s="77" t="n"/>
+      <c r="BV64" s="75" t="n"/>
+      <c r="BW64" s="76" t="n"/>
+      <c r="BX64" s="76" t="n"/>
+      <c r="BY64" s="77" t="n"/>
+      <c r="BZ64" s="75" t="n"/>
+      <c r="CA64" s="76" t="n"/>
+      <c r="CB64" s="76" t="n"/>
+      <c r="CC64" s="77" t="n"/>
+      <c r="CD64" s="75" t="n"/>
+      <c r="CE64" s="76" t="n"/>
+      <c r="CF64" s="76" t="n"/>
+      <c r="CG64" s="78" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="484">
+  <mergeCells count="487">
     <mergeCell ref="BN41:BQ41"/>
     <mergeCell ref="BZ12:CG12"/>
     <mergeCell ref="BF58:BI58"/>
@@ -8298,7 +8503,6 @@
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="V55:W55"/>
     <mergeCell ref="BJ42:BK42"/>
-    <mergeCell ref="N9:Q9"/>
     <mergeCell ref="AT39:AW39"/>
     <mergeCell ref="AD53:AG53"/>
     <mergeCell ref="BB37:BC37"/>
@@ -8358,6 +8562,7 @@
     <mergeCell ref="AH30:AK30"/>
     <mergeCell ref="BV13:BY13"/>
     <mergeCell ref="BF21:BI21"/>
+    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="V56:Y56"/>
     <mergeCell ref="AX1:BA1"/>
     <mergeCell ref="BF16:BI16"/>
@@ -8404,7 +8609,6 @@
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="AZ17:BA17"/>
     <mergeCell ref="BJ7:CG8"/>
-    <mergeCell ref="N10:Q10"/>
     <mergeCell ref="Z36:AA36"/>
     <mergeCell ref="BR2:BU3"/>
     <mergeCell ref="F31:I31"/>
@@ -8475,6 +8679,7 @@
     <mergeCell ref="AD54:AG54"/>
     <mergeCell ref="AL14:AO14"/>
     <mergeCell ref="N31:Q31"/>
+    <mergeCell ref="P10:Q10"/>
     <mergeCell ref="F52:I52"/>
     <mergeCell ref="AH4:AK5"/>
     <mergeCell ref="BZ11:CG11"/>
@@ -8524,6 +8729,7 @@
     <mergeCell ref="BR41:BU41"/>
     <mergeCell ref="AT37:AW37"/>
     <mergeCell ref="BZ14:CG14"/>
+    <mergeCell ref="N9:O9"/>
     <mergeCell ref="CD4:CG5"/>
     <mergeCell ref="AT53:AW53"/>
     <mergeCell ref="BJ16:BM16"/>
@@ -8540,7 +8746,6 @@
     <mergeCell ref="BF20:BI20"/>
     <mergeCell ref="R9:U9"/>
     <mergeCell ref="AD52:AG52"/>
-    <mergeCell ref="N55:Q55"/>
     <mergeCell ref="BB4:BE5"/>
     <mergeCell ref="Z6:AC6"/>
     <mergeCell ref="AL30:AO30"/>
@@ -8627,6 +8832,8 @@
     <mergeCell ref="AH55:AK55"/>
     <mergeCell ref="BV11:BY11"/>
     <mergeCell ref="CD44:CF44"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="P55:Q55"/>
     <mergeCell ref="AL52:AO52"/>
     <mergeCell ref="J31:M31"/>
     <mergeCell ref="AL39:AO39"/>
@@ -8648,6 +8855,7 @@
     <mergeCell ref="AD33:AG33"/>
     <mergeCell ref="Z54:AC54"/>
     <mergeCell ref="BV45:BY45"/>
+    <mergeCell ref="N10:O10"/>
     <mergeCell ref="AD35:AG35"/>
     <mergeCell ref="BF57:BI57"/>
     <mergeCell ref="V2:Y3"/>

--- a/Roster_Builder/output/Final_Roster.xlsx
+++ b/Roster_Builder/output/Final_Roster.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,37 +39,12 @@
       <sz val="7"/>
     </font>
     <font>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <color rgb="00FFFFFF"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="24"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="23">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -105,74 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00101"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0060497A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009966FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A895BE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006BE181"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFF2F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00A6A6A6"/>
         <bgColor rgb="00A6A6A6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009059FB"/>
-        <bgColor rgb="009059FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A895BE"/>
-        <bgColor rgb="00A895BE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFF2F"/>
-        <bgColor rgb="00FEFF2F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DE6220"/>
-        <bgColor rgb="00DE6220"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006BE181"/>
-        <bgColor rgb="006BE181"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FABF8E"/>
-        <bgColor rgb="00FABF8E"/>
       </patternFill>
     </fill>
     <fill>
@@ -194,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -668,6 +577,30 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color rgb="00000000"/>
       </left>
@@ -725,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -779,39 +712,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -822,130 +743,96 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2089,7 +1976,7 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>James,LN</t>
+          <t>James</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
@@ -2101,102 +1988,86 @@
       <c r="G7" s="32" t="n"/>
       <c r="H7" s="33" t="n"/>
       <c r="I7" s="34" t="n"/>
-      <c r="J7" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="J7" s="35" t="n"/>
       <c r="K7" s="33" t="n"/>
       <c r="L7" s="33" t="n"/>
       <c r="M7" s="34" t="n"/>
-      <c r="N7" s="36" t="n"/>
+      <c r="N7" s="35" t="n"/>
       <c r="O7" s="33" t="n"/>
       <c r="P7" s="33" t="n"/>
       <c r="Q7" s="34" t="n"/>
-      <c r="R7" s="36" t="n"/>
+      <c r="R7" s="35" t="n"/>
       <c r="S7" s="33" t="n"/>
       <c r="T7" s="33" t="n"/>
       <c r="U7" s="34" t="n"/>
-      <c r="V7" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="V7" s="35" t="n"/>
       <c r="W7" s="33" t="n"/>
-      <c r="X7" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="X7" s="33" t="n"/>
       <c r="Y7" s="34" t="n"/>
-      <c r="Z7" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="Z7" s="35" t="n"/>
       <c r="AA7" s="33" t="n"/>
       <c r="AB7" s="33" t="n"/>
       <c r="AC7" s="34" t="n"/>
-      <c r="AD7" s="36" t="n"/>
+      <c r="AD7" s="35" t="n"/>
       <c r="AE7" s="33" t="n"/>
       <c r="AF7" s="33" t="n"/>
       <c r="AG7" s="34" t="n"/>
-      <c r="AH7" s="40" t="n"/>
+      <c r="AH7" s="36" t="n"/>
       <c r="AI7" s="33" t="n"/>
-      <c r="AJ7" s="41" t="n"/>
-      <c r="AK7" s="42" t="n"/>
+      <c r="AJ7" s="33" t="n"/>
+      <c r="AK7" s="37" t="n"/>
       <c r="AL7" s="31" t="n"/>
-      <c r="AM7" s="41" t="n"/>
-      <c r="AN7" s="41" t="n"/>
-      <c r="AO7" s="42" t="n"/>
+      <c r="AM7" s="38" t="n"/>
+      <c r="AN7" s="38" t="n"/>
+      <c r="AO7" s="37" t="n"/>
       <c r="AP7" s="31" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
-      <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
+      <c r="AQ7" s="38" t="n"/>
+      <c r="AR7" s="38" t="n"/>
+      <c r="AS7" s="37" t="n"/>
       <c r="AT7" s="31" t="n"/>
-      <c r="AU7" s="41" t="n"/>
-      <c r="AV7" s="41" t="n"/>
-      <c r="AW7" s="42" t="n"/>
+      <c r="AU7" s="38" t="n"/>
+      <c r="AV7" s="38" t="n"/>
+      <c r="AW7" s="37" t="n"/>
       <c r="AX7" s="31" t="n"/>
-      <c r="AY7" s="41" t="n"/>
-      <c r="AZ7" s="41" t="n"/>
-      <c r="BA7" s="42" t="n"/>
+      <c r="AY7" s="38" t="n"/>
+      <c r="AZ7" s="38" t="n"/>
+      <c r="BA7" s="37" t="n"/>
       <c r="BB7" s="31" t="n"/>
-      <c r="BC7" s="41" t="n"/>
-      <c r="BD7" s="41" t="n"/>
-      <c r="BE7" s="42" t="n"/>
+      <c r="BC7" s="38" t="n"/>
+      <c r="BD7" s="38" t="n"/>
+      <c r="BE7" s="37" t="n"/>
       <c r="BF7" s="31" t="n"/>
-      <c r="BG7" s="41" t="n"/>
-      <c r="BH7" s="41" t="n"/>
-      <c r="BI7" s="42" t="n"/>
-      <c r="BJ7" s="43" t="inlineStr">
+      <c r="BG7" s="38" t="n"/>
+      <c r="BH7" s="38" t="n"/>
+      <c r="BI7" s="37" t="n"/>
+      <c r="BJ7" s="39" t="inlineStr">
         <is>
           <t>VICTORIA</t>
         </is>
       </c>
-      <c r="BK7" s="44" t="n"/>
-      <c r="BL7" s="44" t="n"/>
-      <c r="BM7" s="44" t="n"/>
-      <c r="BN7" s="44" t="n"/>
-      <c r="BO7" s="44" t="n"/>
-      <c r="BP7" s="44" t="n"/>
-      <c r="BQ7" s="44" t="n"/>
-      <c r="BR7" s="44" t="n"/>
-      <c r="BS7" s="44" t="n"/>
-      <c r="BT7" s="44" t="n"/>
-      <c r="BU7" s="44" t="n"/>
-      <c r="BV7" s="44" t="n"/>
-      <c r="BW7" s="44" t="n"/>
-      <c r="BX7" s="44" t="n"/>
-      <c r="BY7" s="44" t="n"/>
-      <c r="BZ7" s="44" t="n"/>
-      <c r="CA7" s="44" t="n"/>
-      <c r="CB7" s="44" t="n"/>
-      <c r="CC7" s="44" t="n"/>
-      <c r="CD7" s="44" t="n"/>
-      <c r="CE7" s="44" t="n"/>
-      <c r="CF7" s="44" t="n"/>
-      <c r="CG7" s="45" t="n"/>
+      <c r="BK7" s="40" t="n"/>
+      <c r="BL7" s="40" t="n"/>
+      <c r="BM7" s="40" t="n"/>
+      <c r="BN7" s="40" t="n"/>
+      <c r="BO7" s="40" t="n"/>
+      <c r="BP7" s="40" t="n"/>
+      <c r="BQ7" s="40" t="n"/>
+      <c r="BR7" s="40" t="n"/>
+      <c r="BS7" s="40" t="n"/>
+      <c r="BT7" s="40" t="n"/>
+      <c r="BU7" s="40" t="n"/>
+      <c r="BV7" s="40" t="n"/>
+      <c r="BW7" s="40" t="n"/>
+      <c r="BX7" s="40" t="n"/>
+      <c r="BY7" s="40" t="n"/>
+      <c r="BZ7" s="40" t="n"/>
+      <c r="CA7" s="40" t="n"/>
+      <c r="CB7" s="40" t="n"/>
+      <c r="CC7" s="40" t="n"/>
+      <c r="CD7" s="40" t="n"/>
+      <c r="CE7" s="40" t="n"/>
+      <c r="CF7" s="40" t="n"/>
+      <c r="CG7" s="41" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
@@ -2216,7 +2087,7 @@
       </c>
       <c r="D8" s="30" t="inlineStr">
         <is>
-          <t>Havewala,AP</t>
+          <t>Havewala</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
@@ -2225,101 +2096,85 @@
         </is>
       </c>
       <c r="F8" s="31" t="n"/>
-      <c r="G8" s="46" t="n"/>
+      <c r="G8" s="42" t="n"/>
       <c r="H8" s="33" t="n"/>
       <c r="I8" s="34" t="n"/>
-      <c r="J8" s="47" t="n"/>
+      <c r="J8" s="43" t="n"/>
       <c r="K8" s="33" t="n"/>
       <c r="L8" s="33" t="n"/>
       <c r="M8" s="34" t="n"/>
-      <c r="N8" s="47" t="n"/>
+      <c r="N8" s="43" t="n"/>
       <c r="O8" s="33" t="n"/>
       <c r="P8" s="33" t="n"/>
       <c r="Q8" s="34" t="n"/>
-      <c r="R8" s="48" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="R8" s="43" t="n"/>
       <c r="S8" s="33" t="n"/>
       <c r="T8" s="33" t="n"/>
       <c r="U8" s="34" t="n"/>
-      <c r="V8" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="V8" s="43" t="n"/>
       <c r="W8" s="33" t="n"/>
-      <c r="X8" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="X8" s="33" t="n"/>
       <c r="Y8" s="34" t="n"/>
-      <c r="Z8" s="47" t="n"/>
+      <c r="Z8" s="43" t="n"/>
       <c r="AA8" s="33" t="n"/>
       <c r="AB8" s="33" t="n"/>
       <c r="AC8" s="34" t="n"/>
-      <c r="AD8" s="47" t="n"/>
+      <c r="AD8" s="43" t="n"/>
       <c r="AE8" s="33" t="n"/>
       <c r="AF8" s="33" t="n"/>
       <c r="AG8" s="34" t="n"/>
-      <c r="AH8" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AH8" s="43" t="n"/>
       <c r="AI8" s="33" t="n"/>
       <c r="AJ8" s="33" t="n"/>
       <c r="AK8" s="34" t="n"/>
-      <c r="AL8" s="31" t="n"/>
-      <c r="AM8" s="41" t="n"/>
-      <c r="AN8" s="41" t="n"/>
-      <c r="AO8" s="42" t="n"/>
+      <c r="AL8" s="44" t="n"/>
+      <c r="AM8" s="38" t="n"/>
+      <c r="AN8" s="38" t="n"/>
+      <c r="AO8" s="37" t="n"/>
       <c r="AP8" s="31" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
-      <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n"/>
+      <c r="AQ8" s="38" t="n"/>
+      <c r="AR8" s="38" t="n"/>
+      <c r="AS8" s="37" t="n"/>
       <c r="AT8" s="31" t="n"/>
-      <c r="AU8" s="41" t="n"/>
-      <c r="AV8" s="41" t="n"/>
-      <c r="AW8" s="42" t="n"/>
+      <c r="AU8" s="38" t="n"/>
+      <c r="AV8" s="38" t="n"/>
+      <c r="AW8" s="37" t="n"/>
       <c r="AX8" s="31" t="n"/>
-      <c r="AY8" s="41" t="n"/>
-      <c r="AZ8" s="41" t="n"/>
-      <c r="BA8" s="42" t="n"/>
+      <c r="AY8" s="38" t="n"/>
+      <c r="AZ8" s="38" t="n"/>
+      <c r="BA8" s="37" t="n"/>
       <c r="BB8" s="31" t="n"/>
-      <c r="BC8" s="41" t="n"/>
-      <c r="BD8" s="41" t="n"/>
-      <c r="BE8" s="42" t="n"/>
+      <c r="BC8" s="38" t="n"/>
+      <c r="BD8" s="38" t="n"/>
+      <c r="BE8" s="37" t="n"/>
       <c r="BF8" s="31" t="n"/>
-      <c r="BG8" s="41" t="n"/>
-      <c r="BH8" s="41" t="n"/>
-      <c r="BI8" s="42" t="n"/>
-      <c r="BJ8" s="49" t="n"/>
-      <c r="BK8" s="50" t="n"/>
-      <c r="BL8" s="50" t="n"/>
-      <c r="BM8" s="50" t="n"/>
-      <c r="BN8" s="50" t="n"/>
-      <c r="BO8" s="50" t="n"/>
-      <c r="BP8" s="50" t="n"/>
-      <c r="BQ8" s="50" t="n"/>
-      <c r="BR8" s="50" t="n"/>
-      <c r="BS8" s="50" t="n"/>
-      <c r="BT8" s="50" t="n"/>
-      <c r="BU8" s="50" t="n"/>
-      <c r="BV8" s="50" t="n"/>
-      <c r="BW8" s="50" t="n"/>
-      <c r="BX8" s="50" t="n"/>
-      <c r="BY8" s="50" t="n"/>
-      <c r="BZ8" s="50" t="n"/>
-      <c r="CA8" s="50" t="n"/>
-      <c r="CB8" s="50" t="n"/>
-      <c r="CC8" s="50" t="n"/>
-      <c r="CD8" s="50" t="n"/>
-      <c r="CE8" s="50" t="n"/>
-      <c r="CF8" s="50" t="n"/>
-      <c r="CG8" s="51" t="n"/>
+      <c r="BG8" s="38" t="n"/>
+      <c r="BH8" s="38" t="n"/>
+      <c r="BI8" s="37" t="n"/>
+      <c r="BJ8" s="45" t="n"/>
+      <c r="BK8" s="46" t="n"/>
+      <c r="BL8" s="46" t="n"/>
+      <c r="BM8" s="46" t="n"/>
+      <c r="BN8" s="46" t="n"/>
+      <c r="BO8" s="46" t="n"/>
+      <c r="BP8" s="46" t="n"/>
+      <c r="BQ8" s="46" t="n"/>
+      <c r="BR8" s="46" t="n"/>
+      <c r="BS8" s="46" t="n"/>
+      <c r="BT8" s="46" t="n"/>
+      <c r="BU8" s="46" t="n"/>
+      <c r="BV8" s="46" t="n"/>
+      <c r="BW8" s="46" t="n"/>
+      <c r="BX8" s="46" t="n"/>
+      <c r="BY8" s="46" t="n"/>
+      <c r="BZ8" s="46" t="n"/>
+      <c r="CA8" s="46" t="n"/>
+      <c r="CB8" s="46" t="n"/>
+      <c r="CC8" s="46" t="n"/>
+      <c r="CD8" s="46" t="n"/>
+      <c r="CE8" s="46" t="n"/>
+      <c r="CF8" s="46" t="n"/>
+      <c r="CG8" s="47" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="29" t="inlineStr">
@@ -2344,97 +2199,85 @@
       </c>
       <c r="E9" s="30" t="inlineStr"/>
       <c r="F9" s="31" t="n"/>
-      <c r="G9" s="41" t="n"/>
-      <c r="H9" s="41" t="n"/>
-      <c r="I9" s="42" t="n"/>
+      <c r="G9" s="38" t="n"/>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="37" t="n"/>
       <c r="J9" s="31" t="n"/>
-      <c r="K9" s="41" t="n"/>
-      <c r="L9" s="41" t="n"/>
-      <c r="M9" s="42" t="n"/>
-      <c r="N9" s="52" t="n"/>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="37" t="n"/>
+      <c r="N9" s="43" t="n"/>
       <c r="O9" s="33" t="n"/>
-      <c r="P9" s="53" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="P9" s="33" t="n"/>
       <c r="Q9" s="34" t="n"/>
-      <c r="R9" s="47" t="n"/>
+      <c r="R9" s="43" t="n"/>
       <c r="S9" s="33" t="n"/>
       <c r="T9" s="33" t="n"/>
       <c r="U9" s="34" t="n"/>
-      <c r="V9" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="V9" s="43" t="n"/>
       <c r="W9" s="33" t="n"/>
       <c r="X9" s="33" t="n"/>
       <c r="Y9" s="34" t="n"/>
-      <c r="Z9" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="Z9" s="43" t="n"/>
       <c r="AA9" s="33" t="n"/>
       <c r="AB9" s="33" t="n"/>
       <c r="AC9" s="34" t="n"/>
       <c r="AD9" s="31" t="n"/>
-      <c r="AE9" s="41" t="n"/>
-      <c r="AF9" s="41" t="n"/>
-      <c r="AG9" s="42" t="n"/>
+      <c r="AE9" s="38" t="n"/>
+      <c r="AF9" s="38" t="n"/>
+      <c r="AG9" s="37" t="n"/>
       <c r="AH9" s="31" t="n"/>
-      <c r="AI9" s="41" t="n"/>
-      <c r="AJ9" s="41" t="n"/>
-      <c r="AK9" s="42" t="n"/>
+      <c r="AI9" s="38" t="n"/>
+      <c r="AJ9" s="38" t="n"/>
+      <c r="AK9" s="37" t="n"/>
       <c r="AL9" s="31" t="n"/>
-      <c r="AM9" s="41" t="n"/>
-      <c r="AN9" s="41" t="n"/>
-      <c r="AO9" s="42" t="n"/>
+      <c r="AM9" s="38" t="n"/>
+      <c r="AN9" s="38" t="n"/>
+      <c r="AO9" s="37" t="n"/>
       <c r="AP9" s="31" t="n"/>
-      <c r="AQ9" s="41" t="n"/>
-      <c r="AR9" s="41" t="n"/>
-      <c r="AS9" s="42" t="n"/>
+      <c r="AQ9" s="38" t="n"/>
+      <c r="AR9" s="38" t="n"/>
+      <c r="AS9" s="37" t="n"/>
       <c r="AT9" s="31" t="n"/>
-      <c r="AU9" s="41" t="n"/>
-      <c r="AV9" s="41" t="n"/>
-      <c r="AW9" s="42" t="n"/>
+      <c r="AU9" s="38" t="n"/>
+      <c r="AV9" s="38" t="n"/>
+      <c r="AW9" s="37" t="n"/>
       <c r="AX9" s="31" t="n"/>
-      <c r="AY9" s="41" t="n"/>
-      <c r="AZ9" s="41" t="n"/>
-      <c r="BA9" s="42" t="n"/>
+      <c r="AY9" s="38" t="n"/>
+      <c r="AZ9" s="38" t="n"/>
+      <c r="BA9" s="37" t="n"/>
       <c r="BB9" s="31" t="n"/>
-      <c r="BC9" s="41" t="n"/>
-      <c r="BD9" s="41" t="n"/>
-      <c r="BE9" s="42" t="n"/>
+      <c r="BC9" s="38" t="n"/>
+      <c r="BD9" s="38" t="n"/>
+      <c r="BE9" s="37" t="n"/>
       <c r="BF9" s="31" t="n"/>
-      <c r="BG9" s="41" t="n"/>
-      <c r="BH9" s="41" t="n"/>
-      <c r="BI9" s="42" t="n"/>
+      <c r="BG9" s="38" t="n"/>
+      <c r="BH9" s="38" t="n"/>
+      <c r="BI9" s="37" t="n"/>
       <c r="BJ9" s="31" t="n"/>
-      <c r="BK9" s="41" t="n"/>
-      <c r="BL9" s="41" t="n"/>
-      <c r="BM9" s="42" t="n"/>
+      <c r="BK9" s="38" t="n"/>
+      <c r="BL9" s="38" t="n"/>
+      <c r="BM9" s="37" t="n"/>
       <c r="BN9" s="31" t="n"/>
-      <c r="BO9" s="41" t="n"/>
-      <c r="BP9" s="41" t="n"/>
-      <c r="BQ9" s="42" t="n"/>
+      <c r="BO9" s="38" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="37" t="n"/>
       <c r="BR9" s="31" t="n"/>
-      <c r="BS9" s="41" t="n"/>
-      <c r="BT9" s="41" t="n"/>
-      <c r="BU9" s="42" t="n"/>
+      <c r="BS9" s="38" t="n"/>
+      <c r="BT9" s="38" t="n"/>
+      <c r="BU9" s="37" t="n"/>
       <c r="BV9" s="31" t="n"/>
-      <c r="BW9" s="41" t="n"/>
-      <c r="BX9" s="41" t="n"/>
-      <c r="BY9" s="42" t="n"/>
+      <c r="BW9" s="38" t="n"/>
+      <c r="BX9" s="38" t="n"/>
+      <c r="BY9" s="37" t="n"/>
       <c r="BZ9" s="31" t="n"/>
-      <c r="CA9" s="41" t="n"/>
-      <c r="CB9" s="41" t="n"/>
-      <c r="CC9" s="42" t="n"/>
+      <c r="CA9" s="38" t="n"/>
+      <c r="CB9" s="38" t="n"/>
+      <c r="CC9" s="37" t="n"/>
       <c r="CD9" s="31" t="n"/>
-      <c r="CE9" s="41" t="n"/>
-      <c r="CF9" s="41" t="n"/>
-      <c r="CG9" s="54" t="n"/>
+      <c r="CE9" s="38" t="n"/>
+      <c r="CF9" s="38" t="n"/>
+      <c r="CG9" s="48" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="29" t="inlineStr">
@@ -2454,7 +2297,7 @@
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>Cooke,LE</t>
+          <t>Cooke</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -2463,107 +2306,85 @@
         </is>
       </c>
       <c r="F10" s="31" t="n"/>
-      <c r="G10" s="41" t="n"/>
-      <c r="H10" s="41" t="n"/>
-      <c r="I10" s="42" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="37" t="n"/>
       <c r="J10" s="31" t="n"/>
-      <c r="K10" s="41" t="n"/>
-      <c r="L10" s="41" t="n"/>
-      <c r="M10" s="42" t="n"/>
-      <c r="N10" s="52" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="37" t="n"/>
+      <c r="N10" s="43" t="n"/>
       <c r="O10" s="33" t="n"/>
-      <c r="P10" s="53" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="P10" s="33" t="n"/>
       <c r="Q10" s="34" t="n"/>
-      <c r="R10" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="R10" s="43" t="n"/>
       <c r="S10" s="33" t="n"/>
       <c r="T10" s="33" t="n"/>
       <c r="U10" s="34" t="n"/>
-      <c r="V10" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="V10" s="43" t="n"/>
       <c r="W10" s="33" t="n"/>
       <c r="X10" s="33" t="n"/>
       <c r="Y10" s="34" t="n"/>
-      <c r="Z10" s="47" t="n"/>
+      <c r="Z10" s="43" t="n"/>
       <c r="AA10" s="33" t="n"/>
       <c r="AB10" s="33" t="n"/>
       <c r="AC10" s="34" t="n"/>
       <c r="AD10" s="31" t="n"/>
-      <c r="AE10" s="41" t="n"/>
-      <c r="AF10" s="41" t="n"/>
-      <c r="AG10" s="42" t="n"/>
+      <c r="AE10" s="38" t="n"/>
+      <c r="AF10" s="38" t="n"/>
+      <c r="AG10" s="37" t="n"/>
       <c r="AH10" s="31" t="n"/>
-      <c r="AI10" s="41" t="n"/>
-      <c r="AJ10" s="41" t="n"/>
-      <c r="AK10" s="42" t="n"/>
+      <c r="AI10" s="38" t="n"/>
+      <c r="AJ10" s="38" t="n"/>
+      <c r="AK10" s="37" t="n"/>
       <c r="AL10" s="31" t="n"/>
-      <c r="AM10" s="41" t="n"/>
-      <c r="AN10" s="41" t="n"/>
-      <c r="AO10" s="42" t="n"/>
+      <c r="AM10" s="38" t="n"/>
+      <c r="AN10" s="38" t="n"/>
+      <c r="AO10" s="37" t="n"/>
       <c r="AP10" s="31" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
-      <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n"/>
+      <c r="AQ10" s="38" t="n"/>
+      <c r="AR10" s="38" t="n"/>
+      <c r="AS10" s="37" t="n"/>
       <c r="AT10" s="31" t="n"/>
-      <c r="AU10" s="41" t="n"/>
-      <c r="AV10" s="41" t="n"/>
-      <c r="AW10" s="42" t="n"/>
+      <c r="AU10" s="38" t="n"/>
+      <c r="AV10" s="38" t="n"/>
+      <c r="AW10" s="37" t="n"/>
       <c r="AX10" s="31" t="n"/>
-      <c r="AY10" s="41" t="n"/>
-      <c r="AZ10" s="41" t="n"/>
-      <c r="BA10" s="42" t="n"/>
+      <c r="AY10" s="38" t="n"/>
+      <c r="AZ10" s="38" t="n"/>
+      <c r="BA10" s="37" t="n"/>
       <c r="BB10" s="31" t="n"/>
-      <c r="BC10" s="41" t="n"/>
-      <c r="BD10" s="41" t="n"/>
-      <c r="BE10" s="42" t="n"/>
+      <c r="BC10" s="38" t="n"/>
+      <c r="BD10" s="38" t="n"/>
+      <c r="BE10" s="37" t="n"/>
       <c r="BF10" s="31" t="n"/>
-      <c r="BG10" s="41" t="n"/>
-      <c r="BH10" s="41" t="n"/>
-      <c r="BI10" s="42" t="n"/>
+      <c r="BG10" s="38" t="n"/>
+      <c r="BH10" s="38" t="n"/>
+      <c r="BI10" s="37" t="n"/>
       <c r="BJ10" s="31" t="n"/>
-      <c r="BK10" s="41" t="n"/>
-      <c r="BL10" s="41" t="n"/>
-      <c r="BM10" s="42" t="n"/>
+      <c r="BK10" s="38" t="n"/>
+      <c r="BL10" s="38" t="n"/>
+      <c r="BM10" s="37" t="n"/>
       <c r="BN10" s="31" t="n"/>
-      <c r="BO10" s="41" t="n"/>
-      <c r="BP10" s="41" t="n"/>
-      <c r="BQ10" s="42" t="n"/>
+      <c r="BO10" s="38" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="37" t="n"/>
       <c r="BR10" s="31" t="n"/>
-      <c r="BS10" s="41" t="n"/>
-      <c r="BT10" s="41" t="n"/>
-      <c r="BU10" s="42" t="n"/>
-      <c r="BV10" s="56" t="inlineStr">
-        <is>
-          <t>TOP OF ESC
-4–6</t>
-        </is>
-      </c>
-      <c r="BW10" s="57" t="n"/>
-      <c r="BX10" s="57" t="n"/>
-      <c r="BY10" s="58" t="n"/>
-      <c r="BZ10" s="56" t="inlineStr">
-        <is>
-          <t>AREA AT THE TOP OF ESC
-6</t>
-        </is>
-      </c>
-      <c r="CA10" s="57" t="n"/>
-      <c r="CB10" s="57" t="n"/>
-      <c r="CC10" s="57" t="n"/>
-      <c r="CD10" s="57" t="n"/>
-      <c r="CE10" s="57" t="n"/>
-      <c r="CF10" s="57" t="n"/>
-      <c r="CG10" s="28" t="n"/>
+      <c r="BS10" s="38" t="n"/>
+      <c r="BT10" s="38" t="n"/>
+      <c r="BU10" s="37" t="n"/>
+      <c r="BV10" s="31" t="n"/>
+      <c r="BW10" s="38" t="n"/>
+      <c r="BX10" s="38" t="n"/>
+      <c r="BY10" s="37" t="n"/>
+      <c r="BZ10" s="31" t="n"/>
+      <c r="CA10" s="38" t="n"/>
+      <c r="CB10" s="38" t="n"/>
+      <c r="CC10" s="37" t="n"/>
+      <c r="CD10" s="31" t="n"/>
+      <c r="CE10" s="38" t="n"/>
+      <c r="CF10" s="38" t="n"/>
+      <c r="CG10" s="48" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="29" t="inlineStr">
@@ -2588,106 +2409,85 @@
       </c>
       <c r="E11" s="30" t="inlineStr"/>
       <c r="F11" s="31" t="n"/>
-      <c r="G11" s="41" t="n"/>
-      <c r="H11" s="41" t="n"/>
-      <c r="I11" s="42" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="37" t="n"/>
       <c r="J11" s="31" t="n"/>
-      <c r="K11" s="41" t="n"/>
-      <c r="L11" s="41" t="n"/>
-      <c r="M11" s="42" t="n"/>
-      <c r="N11" s="36" t="n"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="38" t="n"/>
+      <c r="M11" s="37" t="n"/>
+      <c r="N11" s="35" t="n"/>
       <c r="O11" s="33" t="n"/>
       <c r="P11" s="33" t="n"/>
       <c r="Q11" s="34" t="n"/>
-      <c r="R11" s="36" t="n"/>
+      <c r="R11" s="35" t="n"/>
       <c r="S11" s="33" t="n"/>
       <c r="T11" s="33" t="n"/>
       <c r="U11" s="34" t="n"/>
-      <c r="V11" s="36" t="n"/>
+      <c r="V11" s="35" t="n"/>
       <c r="W11" s="33" t="n"/>
       <c r="X11" s="33" t="n"/>
       <c r="Y11" s="34" t="n"/>
-      <c r="Z11" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="Z11" s="35" t="n"/>
       <c r="AA11" s="33" t="n"/>
-      <c r="AB11" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AB11" s="33" t="n"/>
       <c r="AC11" s="34" t="n"/>
-      <c r="AD11" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AD11" s="35" t="n"/>
       <c r="AE11" s="33" t="n"/>
       <c r="AF11" s="33" t="n"/>
       <c r="AG11" s="34" t="n"/>
-      <c r="AH11" s="36" t="n"/>
+      <c r="AH11" s="35" t="n"/>
       <c r="AI11" s="33" t="n"/>
       <c r="AJ11" s="33" t="n"/>
       <c r="AK11" s="34" t="n"/>
-      <c r="AL11" s="36" t="n"/>
+      <c r="AL11" s="35" t="n"/>
       <c r="AM11" s="33" t="n"/>
       <c r="AN11" s="33" t="n"/>
       <c r="AO11" s="34" t="n"/>
-      <c r="AP11" s="40" t="n"/>
+      <c r="AP11" s="36" t="n"/>
       <c r="AQ11" s="33" t="n"/>
-      <c r="AR11" s="41" t="n"/>
-      <c r="AS11" s="42" t="n"/>
+      <c r="AR11" s="38" t="n"/>
+      <c r="AS11" s="37" t="n"/>
       <c r="AT11" s="31" t="n"/>
-      <c r="AU11" s="41" t="n"/>
-      <c r="AV11" s="41" t="n"/>
-      <c r="AW11" s="42" t="n"/>
+      <c r="AU11" s="38" t="n"/>
+      <c r="AV11" s="38" t="n"/>
+      <c r="AW11" s="37" t="n"/>
       <c r="AX11" s="31" t="n"/>
-      <c r="AY11" s="41" t="n"/>
-      <c r="AZ11" s="41" t="n"/>
-      <c r="BA11" s="42" t="n"/>
+      <c r="AY11" s="38" t="n"/>
+      <c r="AZ11" s="38" t="n"/>
+      <c r="BA11" s="37" t="n"/>
       <c r="BB11" s="31" t="n"/>
-      <c r="BC11" s="41" t="n"/>
-      <c r="BD11" s="41" t="n"/>
-      <c r="BE11" s="42" t="n"/>
+      <c r="BC11" s="38" t="n"/>
+      <c r="BD11" s="38" t="n"/>
+      <c r="BE11" s="37" t="n"/>
       <c r="BF11" s="31" t="n"/>
-      <c r="BG11" s="41" t="n"/>
-      <c r="BH11" s="41" t="n"/>
-      <c r="BI11" s="42" t="n"/>
+      <c r="BG11" s="38" t="n"/>
+      <c r="BH11" s="38" t="n"/>
+      <c r="BI11" s="37" t="n"/>
       <c r="BJ11" s="31" t="n"/>
-      <c r="BK11" s="41" t="n"/>
-      <c r="BL11" s="41" t="n"/>
-      <c r="BM11" s="42" t="n"/>
+      <c r="BK11" s="38" t="n"/>
+      <c r="BL11" s="38" t="n"/>
+      <c r="BM11" s="37" t="n"/>
       <c r="BN11" s="31" t="n"/>
-      <c r="BO11" s="41" t="n"/>
-      <c r="BP11" s="41" t="n"/>
-      <c r="BQ11" s="42" t="n"/>
+      <c r="BO11" s="38" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="37" t="n"/>
       <c r="BR11" s="31" t="n"/>
-      <c r="BS11" s="41" t="n"/>
-      <c r="BT11" s="41" t="n"/>
-      <c r="BU11" s="42" t="n"/>
-      <c r="BV11" s="59" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
-      <c r="BW11" s="57" t="n"/>
-      <c r="BX11" s="57" t="n"/>
-      <c r="BY11" s="58" t="n"/>
-      <c r="BZ11" s="59" t="inlineStr">
-        <is>
-          <t>PERSON ALLOCATED TO ASSIST
-WITH VIP/MIPs</t>
-        </is>
-      </c>
-      <c r="CA11" s="57" t="n"/>
-      <c r="CB11" s="57" t="n"/>
-      <c r="CC11" s="57" t="n"/>
-      <c r="CD11" s="57" t="n"/>
-      <c r="CE11" s="57" t="n"/>
-      <c r="CF11" s="57" t="n"/>
-      <c r="CG11" s="28" t="n"/>
+      <c r="BS11" s="38" t="n"/>
+      <c r="BT11" s="38" t="n"/>
+      <c r="BU11" s="37" t="n"/>
+      <c r="BV11" s="31" t="n"/>
+      <c r="BW11" s="38" t="n"/>
+      <c r="BX11" s="38" t="n"/>
+      <c r="BY11" s="37" t="n"/>
+      <c r="BZ11" s="31" t="n"/>
+      <c r="CA11" s="38" t="n"/>
+      <c r="CB11" s="38" t="n"/>
+      <c r="CC11" s="37" t="n"/>
+      <c r="CD11" s="31" t="n"/>
+      <c r="CE11" s="38" t="n"/>
+      <c r="CF11" s="38" t="n"/>
+      <c r="CG11" s="48" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="29" t="inlineStr">
@@ -2712,109 +2512,85 @@
       </c>
       <c r="E12" s="30" t="inlineStr"/>
       <c r="F12" s="31" t="n"/>
-      <c r="G12" s="41" t="n"/>
-      <c r="H12" s="41" t="n"/>
-      <c r="I12" s="42" t="n"/>
+      <c r="G12" s="38" t="n"/>
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="37" t="n"/>
       <c r="J12" s="31" t="n"/>
-      <c r="K12" s="41" t="n"/>
-      <c r="L12" s="41" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="47" t="n"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="38" t="n"/>
+      <c r="M12" s="37" t="n"/>
+      <c r="N12" s="43" t="n"/>
       <c r="O12" s="33" t="n"/>
       <c r="P12" s="33" t="n"/>
       <c r="Q12" s="34" t="n"/>
-      <c r="R12" s="47" t="n"/>
+      <c r="R12" s="43" t="n"/>
       <c r="S12" s="33" t="n"/>
       <c r="T12" s="33" t="n"/>
       <c r="U12" s="34" t="n"/>
-      <c r="V12" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="V12" s="43" t="n"/>
       <c r="W12" s="33" t="n"/>
       <c r="X12" s="33" t="n"/>
       <c r="Y12" s="34" t="n"/>
-      <c r="Z12" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="Z12" s="43" t="n"/>
       <c r="AA12" s="33" t="n"/>
-      <c r="AB12" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AB12" s="33" t="n"/>
       <c r="AC12" s="34" t="n"/>
-      <c r="AD12" s="47" t="n"/>
+      <c r="AD12" s="43" t="n"/>
       <c r="AE12" s="33" t="n"/>
       <c r="AF12" s="33" t="n"/>
       <c r="AG12" s="34" t="n"/>
-      <c r="AH12" s="47" t="n"/>
+      <c r="AH12" s="43" t="n"/>
       <c r="AI12" s="33" t="n"/>
       <c r="AJ12" s="33" t="n"/>
       <c r="AK12" s="34" t="n"/>
-      <c r="AL12" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="AL12" s="43" t="n"/>
       <c r="AM12" s="33" t="n"/>
       <c r="AN12" s="33" t="n"/>
       <c r="AO12" s="34" t="n"/>
-      <c r="AP12" s="47" t="n"/>
+      <c r="AP12" s="43" t="n"/>
       <c r="AQ12" s="33" t="n"/>
       <c r="AR12" s="33" t="n"/>
       <c r="AS12" s="34" t="n"/>
       <c r="AT12" s="31" t="n"/>
-      <c r="AU12" s="41" t="n"/>
-      <c r="AV12" s="41" t="n"/>
-      <c r="AW12" s="42" t="n"/>
+      <c r="AU12" s="38" t="n"/>
+      <c r="AV12" s="38" t="n"/>
+      <c r="AW12" s="37" t="n"/>
       <c r="AX12" s="31" t="n"/>
-      <c r="AY12" s="41" t="n"/>
-      <c r="AZ12" s="41" t="n"/>
-      <c r="BA12" s="42" t="n"/>
+      <c r="AY12" s="38" t="n"/>
+      <c r="AZ12" s="38" t="n"/>
+      <c r="BA12" s="37" t="n"/>
       <c r="BB12" s="31" t="n"/>
-      <c r="BC12" s="41" t="n"/>
-      <c r="BD12" s="41" t="n"/>
-      <c r="BE12" s="42" t="n"/>
+      <c r="BC12" s="38" t="n"/>
+      <c r="BD12" s="38" t="n"/>
+      <c r="BE12" s="37" t="n"/>
       <c r="BF12" s="31" t="n"/>
-      <c r="BG12" s="41" t="n"/>
-      <c r="BH12" s="41" t="n"/>
-      <c r="BI12" s="42" t="n"/>
+      <c r="BG12" s="38" t="n"/>
+      <c r="BH12" s="38" t="n"/>
+      <c r="BI12" s="37" t="n"/>
       <c r="BJ12" s="31" t="n"/>
-      <c r="BK12" s="41" t="n"/>
-      <c r="BL12" s="41" t="n"/>
-      <c r="BM12" s="42" t="n"/>
+      <c r="BK12" s="38" t="n"/>
+      <c r="BL12" s="38" t="n"/>
+      <c r="BM12" s="37" t="n"/>
       <c r="BN12" s="31" t="n"/>
-      <c r="BO12" s="41" t="n"/>
-      <c r="BP12" s="41" t="n"/>
-      <c r="BQ12" s="42" t="n"/>
+      <c r="BO12" s="38" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="37" t="n"/>
       <c r="BR12" s="31" t="n"/>
-      <c r="BS12" s="41" t="n"/>
-      <c r="BT12" s="41" t="n"/>
-      <c r="BU12" s="42" t="n"/>
-      <c r="BV12" s="60" t="inlineStr">
-        <is>
-          <t>POM SERVICING</t>
-        </is>
-      </c>
-      <c r="BW12" s="57" t="n"/>
-      <c r="BX12" s="57" t="n"/>
-      <c r="BY12" s="58" t="n"/>
-      <c r="BZ12" s="60" t="inlineStr">
-        <is>
-          <t>SERVICE ALL POMS</t>
-        </is>
-      </c>
-      <c r="CA12" s="57" t="n"/>
-      <c r="CB12" s="57" t="n"/>
-      <c r="CC12" s="57" t="n"/>
-      <c r="CD12" s="57" t="n"/>
-      <c r="CE12" s="57" t="n"/>
-      <c r="CF12" s="57" t="n"/>
-      <c r="CG12" s="28" t="n"/>
+      <c r="BS12" s="38" t="n"/>
+      <c r="BT12" s="38" t="n"/>
+      <c r="BU12" s="37" t="n"/>
+      <c r="BV12" s="31" t="n"/>
+      <c r="BW12" s="38" t="n"/>
+      <c r="BX12" s="38" t="n"/>
+      <c r="BY12" s="37" t="n"/>
+      <c r="BZ12" s="31" t="n"/>
+      <c r="CA12" s="38" t="n"/>
+      <c r="CB12" s="38" t="n"/>
+      <c r="CC12" s="37" t="n"/>
+      <c r="CD12" s="31" t="n"/>
+      <c r="CE12" s="38" t="n"/>
+      <c r="CF12" s="38" t="n"/>
+      <c r="CG12" s="48" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
@@ -2834,7 +2610,7 @@
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>Ilesanmi,KS</t>
+          <t>Ilesanmi</t>
         </is>
       </c>
       <c r="E13" s="30" t="inlineStr">
@@ -2843,109 +2619,85 @@
         </is>
       </c>
       <c r="F13" s="31" t="n"/>
-      <c r="G13" s="41" t="n"/>
-      <c r="H13" s="41" t="n"/>
-      <c r="I13" s="42" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="37" t="n"/>
       <c r="J13" s="31" t="n"/>
-      <c r="K13" s="41" t="n"/>
-      <c r="L13" s="41" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="47" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="43" t="n"/>
       <c r="O13" s="33" t="n"/>
       <c r="P13" s="33" t="n"/>
       <c r="Q13" s="34" t="n"/>
-      <c r="R13" s="47" t="n"/>
+      <c r="R13" s="43" t="n"/>
       <c r="S13" s="33" t="n"/>
       <c r="T13" s="33" t="n"/>
       <c r="U13" s="34" t="n"/>
-      <c r="V13" s="47" t="n"/>
+      <c r="V13" s="43" t="n"/>
       <c r="W13" s="33" t="n"/>
       <c r="X13" s="33" t="n"/>
       <c r="Y13" s="34" t="n"/>
-      <c r="Z13" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="Z13" s="43" t="n"/>
       <c r="AA13" s="33" t="n"/>
-      <c r="AB13" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AB13" s="33" t="n"/>
       <c r="AC13" s="34" t="n"/>
-      <c r="AD13" s="47" t="n"/>
+      <c r="AD13" s="43" t="n"/>
       <c r="AE13" s="33" t="n"/>
       <c r="AF13" s="33" t="n"/>
       <c r="AG13" s="34" t="n"/>
-      <c r="AH13" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="AH13" s="43" t="n"/>
       <c r="AI13" s="33" t="n"/>
       <c r="AJ13" s="33" t="n"/>
       <c r="AK13" s="34" t="n"/>
-      <c r="AL13" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AL13" s="43" t="n"/>
       <c r="AM13" s="33" t="n"/>
       <c r="AN13" s="33" t="n"/>
       <c r="AO13" s="34" t="n"/>
-      <c r="AP13" s="47" t="n"/>
+      <c r="AP13" s="43" t="n"/>
       <c r="AQ13" s="33" t="n"/>
       <c r="AR13" s="33" t="n"/>
       <c r="AS13" s="34" t="n"/>
       <c r="AT13" s="31" t="n"/>
-      <c r="AU13" s="41" t="n"/>
-      <c r="AV13" s="41" t="n"/>
-      <c r="AW13" s="42" t="n"/>
+      <c r="AU13" s="38" t="n"/>
+      <c r="AV13" s="38" t="n"/>
+      <c r="AW13" s="37" t="n"/>
       <c r="AX13" s="31" t="n"/>
-      <c r="AY13" s="41" t="n"/>
-      <c r="AZ13" s="41" t="n"/>
-      <c r="BA13" s="42" t="n"/>
+      <c r="AY13" s="38" t="n"/>
+      <c r="AZ13" s="38" t="n"/>
+      <c r="BA13" s="37" t="n"/>
       <c r="BB13" s="31" t="n"/>
-      <c r="BC13" s="41" t="n"/>
-      <c r="BD13" s="41" t="n"/>
-      <c r="BE13" s="42" t="n"/>
+      <c r="BC13" s="38" t="n"/>
+      <c r="BD13" s="38" t="n"/>
+      <c r="BE13" s="37" t="n"/>
       <c r="BF13" s="31" t="n"/>
-      <c r="BG13" s="41" t="n"/>
-      <c r="BH13" s="41" t="n"/>
-      <c r="BI13" s="42" t="n"/>
+      <c r="BG13" s="38" t="n"/>
+      <c r="BH13" s="38" t="n"/>
+      <c r="BI13" s="37" t="n"/>
       <c r="BJ13" s="31" t="n"/>
-      <c r="BK13" s="41" t="n"/>
-      <c r="BL13" s="41" t="n"/>
-      <c r="BM13" s="42" t="n"/>
+      <c r="BK13" s="38" t="n"/>
+      <c r="BL13" s="38" t="n"/>
+      <c r="BM13" s="37" t="n"/>
       <c r="BN13" s="31" t="n"/>
-      <c r="BO13" s="41" t="n"/>
-      <c r="BP13" s="41" t="n"/>
-      <c r="BQ13" s="42" t="n"/>
+      <c r="BO13" s="38" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="37" t="n"/>
       <c r="BR13" s="31" t="n"/>
-      <c r="BS13" s="41" t="n"/>
-      <c r="BT13" s="41" t="n"/>
-      <c r="BU13" s="42" t="n"/>
-      <c r="BV13" s="63" t="inlineStr">
-        <is>
-          <t>PLATFORM</t>
-        </is>
-      </c>
-      <c r="BW13" s="57" t="n"/>
-      <c r="BX13" s="57" t="n"/>
-      <c r="BY13" s="58" t="n"/>
-      <c r="BZ13" s="63" t="inlineStr">
-        <is>
-          <t>PLATFORM SATS</t>
-        </is>
-      </c>
-      <c r="CA13" s="57" t="n"/>
-      <c r="CB13" s="57" t="n"/>
-      <c r="CC13" s="57" t="n"/>
-      <c r="CD13" s="57" t="n"/>
-      <c r="CE13" s="57" t="n"/>
-      <c r="CF13" s="57" t="n"/>
-      <c r="CG13" s="28" t="n"/>
+      <c r="BS13" s="38" t="n"/>
+      <c r="BT13" s="38" t="n"/>
+      <c r="BU13" s="37" t="n"/>
+      <c r="BV13" s="31" t="n"/>
+      <c r="BW13" s="38" t="n"/>
+      <c r="BX13" s="38" t="n"/>
+      <c r="BY13" s="37" t="n"/>
+      <c r="BZ13" s="31" t="n"/>
+      <c r="CA13" s="38" t="n"/>
+      <c r="CB13" s="38" t="n"/>
+      <c r="CC13" s="37" t="n"/>
+      <c r="CD13" s="31" t="n"/>
+      <c r="CE13" s="38" t="n"/>
+      <c r="CF13" s="38" t="n"/>
+      <c r="CG13" s="48" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="29" t="inlineStr">
@@ -2965,7 +2717,7 @@
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>Kalisilira,KI</t>
+          <t>Kalisilira</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
@@ -2974,109 +2726,85 @@
         </is>
       </c>
       <c r="F14" s="31" t="n"/>
-      <c r="G14" s="41" t="n"/>
-      <c r="H14" s="41" t="n"/>
-      <c r="I14" s="42" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="37" t="n"/>
       <c r="J14" s="31" t="n"/>
-      <c r="K14" s="41" t="n"/>
-      <c r="L14" s="41" t="n"/>
-      <c r="M14" s="42" t="n"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="38" t="n"/>
+      <c r="M14" s="37" t="n"/>
       <c r="N14" s="31" t="n"/>
-      <c r="O14" s="41" t="n"/>
-      <c r="P14" s="41" t="n"/>
-      <c r="Q14" s="42" t="n"/>
+      <c r="O14" s="38" t="n"/>
+      <c r="P14" s="38" t="n"/>
+      <c r="Q14" s="37" t="n"/>
       <c r="R14" s="31" t="n"/>
-      <c r="S14" s="41" t="n"/>
-      <c r="T14" s="41" t="n"/>
-      <c r="U14" s="42" t="n"/>
-      <c r="V14" s="47" t="n"/>
+      <c r="S14" s="38" t="n"/>
+      <c r="T14" s="38" t="n"/>
+      <c r="U14" s="37" t="n"/>
+      <c r="V14" s="43" t="n"/>
       <c r="W14" s="33" t="n"/>
       <c r="X14" s="33" t="n"/>
       <c r="Y14" s="34" t="n"/>
-      <c r="Z14" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="Z14" s="43" t="n"/>
       <c r="AA14" s="33" t="n"/>
       <c r="AB14" s="33" t="n"/>
       <c r="AC14" s="34" t="n"/>
-      <c r="AD14" s="47" t="n"/>
+      <c r="AD14" s="43" t="n"/>
       <c r="AE14" s="33" t="n"/>
       <c r="AF14" s="33" t="n"/>
       <c r="AG14" s="34" t="n"/>
-      <c r="AH14" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AH14" s="43" t="n"/>
       <c r="AI14" s="33" t="n"/>
-      <c r="AJ14" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AJ14" s="33" t="n"/>
       <c r="AK14" s="34" t="n"/>
-      <c r="AL14" s="47" t="n"/>
+      <c r="AL14" s="43" t="n"/>
       <c r="AM14" s="33" t="n"/>
       <c r="AN14" s="33" t="n"/>
       <c r="AO14" s="34" t="n"/>
-      <c r="AP14" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="AP14" s="43" t="n"/>
       <c r="AQ14" s="33" t="n"/>
       <c r="AR14" s="33" t="n"/>
       <c r="AS14" s="34" t="n"/>
-      <c r="AT14" s="47" t="n"/>
+      <c r="AT14" s="43" t="n"/>
       <c r="AU14" s="33" t="n"/>
       <c r="AV14" s="33" t="n"/>
       <c r="AW14" s="34" t="n"/>
-      <c r="AX14" s="47" t="n"/>
+      <c r="AX14" s="43" t="n"/>
       <c r="AY14" s="33" t="n"/>
       <c r="AZ14" s="33" t="n"/>
       <c r="BA14" s="34" t="n"/>
       <c r="BB14" s="31" t="n"/>
-      <c r="BC14" s="41" t="n"/>
-      <c r="BD14" s="41" t="n"/>
-      <c r="BE14" s="42" t="n"/>
+      <c r="BC14" s="38" t="n"/>
+      <c r="BD14" s="38" t="n"/>
+      <c r="BE14" s="37" t="n"/>
       <c r="BF14" s="31" t="n"/>
-      <c r="BG14" s="41" t="n"/>
-      <c r="BH14" s="41" t="n"/>
-      <c r="BI14" s="42" t="n"/>
+      <c r="BG14" s="38" t="n"/>
+      <c r="BH14" s="38" t="n"/>
+      <c r="BI14" s="37" t="n"/>
       <c r="BJ14" s="31" t="n"/>
-      <c r="BK14" s="41" t="n"/>
-      <c r="BL14" s="41" t="n"/>
-      <c r="BM14" s="42" t="n"/>
+      <c r="BK14" s="38" t="n"/>
+      <c r="BL14" s="38" t="n"/>
+      <c r="BM14" s="37" t="n"/>
       <c r="BN14" s="31" t="n"/>
-      <c r="BO14" s="41" t="n"/>
-      <c r="BP14" s="41" t="n"/>
-      <c r="BQ14" s="42" t="n"/>
+      <c r="BO14" s="38" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="37" t="n"/>
       <c r="BR14" s="31" t="n"/>
-      <c r="BS14" s="41" t="n"/>
-      <c r="BT14" s="41" t="n"/>
-      <c r="BU14" s="42" t="n"/>
-      <c r="BV14" s="64" t="inlineStr">
-        <is>
-          <t>PTI</t>
-        </is>
-      </c>
-      <c r="BW14" s="57" t="n"/>
-      <c r="BX14" s="57" t="n"/>
-      <c r="BY14" s="58" t="n"/>
-      <c r="BZ14" s="64" t="inlineStr">
-        <is>
-          <t>PTI DUTY</t>
-        </is>
-      </c>
-      <c r="CA14" s="57" t="n"/>
-      <c r="CB14" s="57" t="n"/>
-      <c r="CC14" s="57" t="n"/>
-      <c r="CD14" s="57" t="n"/>
-      <c r="CE14" s="57" t="n"/>
-      <c r="CF14" s="57" t="n"/>
-      <c r="CG14" s="28" t="n"/>
+      <c r="BS14" s="38" t="n"/>
+      <c r="BT14" s="38" t="n"/>
+      <c r="BU14" s="37" t="n"/>
+      <c r="BV14" s="31" t="n"/>
+      <c r="BW14" s="38" t="n"/>
+      <c r="BX14" s="38" t="n"/>
+      <c r="BY14" s="37" t="n"/>
+      <c r="BZ14" s="31" t="n"/>
+      <c r="CA14" s="38" t="n"/>
+      <c r="CB14" s="38" t="n"/>
+      <c r="CC14" s="37" t="n"/>
+      <c r="CD14" s="31" t="n"/>
+      <c r="CE14" s="38" t="n"/>
+      <c r="CF14" s="38" t="n"/>
+      <c r="CG14" s="48" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
@@ -3096,7 +2824,7 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>Usman,S</t>
+          <t>Usman</t>
         </is>
       </c>
       <c r="E15" s="30" t="inlineStr">
@@ -3105,101 +2833,85 @@
         </is>
       </c>
       <c r="F15" s="31" t="n"/>
-      <c r="G15" s="41" t="n"/>
-      <c r="H15" s="41" t="n"/>
-      <c r="I15" s="42" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="37" t="n"/>
       <c r="J15" s="31" t="n"/>
-      <c r="K15" s="41" t="n"/>
-      <c r="L15" s="41" t="n"/>
-      <c r="M15" s="42" t="n"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="38" t="n"/>
+      <c r="M15" s="37" t="n"/>
       <c r="N15" s="31" t="n"/>
-      <c r="O15" s="41" t="n"/>
-      <c r="P15" s="41" t="n"/>
-      <c r="Q15" s="42" t="n"/>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="38" t="n"/>
+      <c r="Q15" s="37" t="n"/>
       <c r="R15" s="31" t="n"/>
-      <c r="S15" s="41" t="n"/>
-      <c r="T15" s="41" t="n"/>
-      <c r="U15" s="42" t="n"/>
-      <c r="V15" s="47" t="n"/>
+      <c r="S15" s="38" t="n"/>
+      <c r="T15" s="38" t="n"/>
+      <c r="U15" s="37" t="n"/>
+      <c r="V15" s="43" t="n"/>
       <c r="W15" s="33" t="n"/>
       <c r="X15" s="33" t="n"/>
       <c r="Y15" s="34" t="n"/>
-      <c r="Z15" s="47" t="n"/>
+      <c r="Z15" s="43" t="n"/>
       <c r="AA15" s="33" t="n"/>
       <c r="AB15" s="33" t="n"/>
       <c r="AC15" s="34" t="n"/>
-      <c r="AD15" s="47" t="n"/>
+      <c r="AD15" s="43" t="n"/>
       <c r="AE15" s="33" t="n"/>
       <c r="AF15" s="33" t="n"/>
       <c r="AG15" s="34" t="n"/>
-      <c r="AH15" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AH15" s="43" t="n"/>
       <c r="AI15" s="33" t="n"/>
-      <c r="AJ15" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AJ15" s="33" t="n"/>
       <c r="AK15" s="34" t="n"/>
-      <c r="AL15" s="47" t="n"/>
+      <c r="AL15" s="43" t="n"/>
       <c r="AM15" s="33" t="n"/>
       <c r="AN15" s="33" t="n"/>
       <c r="AO15" s="34" t="n"/>
-      <c r="AP15" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AP15" s="43" t="n"/>
       <c r="AQ15" s="33" t="n"/>
       <c r="AR15" s="33" t="n"/>
       <c r="AS15" s="34" t="n"/>
-      <c r="AT15" s="47" t="n"/>
+      <c r="AT15" s="43" t="n"/>
       <c r="AU15" s="33" t="n"/>
       <c r="AV15" s="33" t="n"/>
       <c r="AW15" s="34" t="n"/>
-      <c r="AX15" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="AX15" s="43" t="n"/>
       <c r="AY15" s="33" t="n"/>
       <c r="AZ15" s="33" t="n"/>
       <c r="BA15" s="34" t="n"/>
       <c r="BB15" s="31" t="n"/>
-      <c r="BC15" s="41" t="n"/>
-      <c r="BD15" s="41" t="n"/>
-      <c r="BE15" s="42" t="n"/>
+      <c r="BC15" s="38" t="n"/>
+      <c r="BD15" s="38" t="n"/>
+      <c r="BE15" s="37" t="n"/>
       <c r="BF15" s="31" t="n"/>
-      <c r="BG15" s="41" t="n"/>
-      <c r="BH15" s="41" t="n"/>
-      <c r="BI15" s="42" t="n"/>
+      <c r="BG15" s="38" t="n"/>
+      <c r="BH15" s="38" t="n"/>
+      <c r="BI15" s="37" t="n"/>
       <c r="BJ15" s="31" t="n"/>
-      <c r="BK15" s="41" t="n"/>
-      <c r="BL15" s="41" t="n"/>
-      <c r="BM15" s="42" t="n"/>
+      <c r="BK15" s="38" t="n"/>
+      <c r="BL15" s="38" t="n"/>
+      <c r="BM15" s="37" t="n"/>
       <c r="BN15" s="31" t="n"/>
-      <c r="BO15" s="41" t="n"/>
-      <c r="BP15" s="41" t="n"/>
-      <c r="BQ15" s="42" t="n"/>
+      <c r="BO15" s="38" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="37" t="n"/>
       <c r="BR15" s="31" t="n"/>
-      <c r="BS15" s="41" t="n"/>
-      <c r="BT15" s="41" t="n"/>
-      <c r="BU15" s="42" t="n"/>
+      <c r="BS15" s="38" t="n"/>
+      <c r="BT15" s="38" t="n"/>
+      <c r="BU15" s="37" t="n"/>
       <c r="BV15" s="31" t="n"/>
-      <c r="BW15" s="41" t="n"/>
-      <c r="BX15" s="41" t="n"/>
-      <c r="BY15" s="42" t="n"/>
+      <c r="BW15" s="38" t="n"/>
+      <c r="BX15" s="38" t="n"/>
+      <c r="BY15" s="37" t="n"/>
       <c r="BZ15" s="31" t="n"/>
-      <c r="CA15" s="41" t="n"/>
-      <c r="CB15" s="41" t="n"/>
-      <c r="CC15" s="42" t="n"/>
+      <c r="CA15" s="38" t="n"/>
+      <c r="CB15" s="38" t="n"/>
+      <c r="CC15" s="37" t="n"/>
       <c r="CD15" s="31" t="n"/>
-      <c r="CE15" s="41" t="n"/>
-      <c r="CF15" s="41" t="n"/>
-      <c r="CG15" s="54" t="n"/>
+      <c r="CE15" s="38" t="n"/>
+      <c r="CF15" s="38" t="n"/>
+      <c r="CG15" s="48" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
@@ -3219,7 +2931,7 @@
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>SydneyAdenekan,AA</t>
+          <t>SydneyAdenekan</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -3228,97 +2940,85 @@
         </is>
       </c>
       <c r="F16" s="31" t="n"/>
-      <c r="G16" s="41" t="n"/>
-      <c r="H16" s="41" t="n"/>
-      <c r="I16" s="42" t="n"/>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="38" t="n"/>
+      <c r="I16" s="37" t="n"/>
       <c r="J16" s="31" t="n"/>
-      <c r="K16" s="41" t="n"/>
-      <c r="L16" s="41" t="n"/>
-      <c r="M16" s="42" t="n"/>
+      <c r="K16" s="38" t="n"/>
+      <c r="L16" s="38" t="n"/>
+      <c r="M16" s="37" t="n"/>
       <c r="N16" s="31" t="n"/>
-      <c r="O16" s="41" t="n"/>
-      <c r="P16" s="41" t="n"/>
-      <c r="Q16" s="42" t="n"/>
+      <c r="O16" s="38" t="n"/>
+      <c r="P16" s="38" t="n"/>
+      <c r="Q16" s="37" t="n"/>
       <c r="R16" s="31" t="n"/>
-      <c r="S16" s="41" t="n"/>
-      <c r="T16" s="41" t="n"/>
-      <c r="U16" s="42" t="n"/>
+      <c r="S16" s="38" t="n"/>
+      <c r="T16" s="38" t="n"/>
+      <c r="U16" s="37" t="n"/>
       <c r="V16" s="31" t="n"/>
-      <c r="W16" s="41" t="n"/>
-      <c r="X16" s="41" t="n"/>
-      <c r="Y16" s="42" t="n"/>
+      <c r="W16" s="38" t="n"/>
+      <c r="X16" s="38" t="n"/>
+      <c r="Y16" s="37" t="n"/>
       <c r="Z16" s="31" t="n"/>
-      <c r="AA16" s="41" t="n"/>
-      <c r="AB16" s="41" t="n"/>
-      <c r="AC16" s="42" t="n"/>
+      <c r="AA16" s="38" t="n"/>
+      <c r="AB16" s="38" t="n"/>
+      <c r="AC16" s="37" t="n"/>
       <c r="AD16" s="31" t="n"/>
-      <c r="AE16" s="41" t="n"/>
-      <c r="AF16" s="41" t="n"/>
-      <c r="AG16" s="42" t="n"/>
+      <c r="AE16" s="38" t="n"/>
+      <c r="AF16" s="38" t="n"/>
+      <c r="AG16" s="37" t="n"/>
       <c r="AH16" s="31" t="n"/>
-      <c r="AI16" s="41" t="n"/>
+      <c r="AI16" s="38" t="n"/>
       <c r="AJ16" s="32" t="n"/>
       <c r="AK16" s="34" t="n"/>
-      <c r="AL16" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AL16" s="35" t="n"/>
       <c r="AM16" s="33" t="n"/>
-      <c r="AN16" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AN16" s="33" t="n"/>
       <c r="AO16" s="34" t="n"/>
-      <c r="AP16" s="36" t="n"/>
+      <c r="AP16" s="35" t="n"/>
       <c r="AQ16" s="33" t="n"/>
       <c r="AR16" s="33" t="n"/>
       <c r="AS16" s="34" t="n"/>
-      <c r="AT16" s="36" t="n"/>
+      <c r="AT16" s="35" t="n"/>
       <c r="AU16" s="33" t="n"/>
       <c r="AV16" s="33" t="n"/>
       <c r="AW16" s="34" t="n"/>
-      <c r="AX16" s="36" t="n"/>
+      <c r="AX16" s="35" t="n"/>
       <c r="AY16" s="33" t="n"/>
       <c r="AZ16" s="33" t="n"/>
       <c r="BA16" s="34" t="n"/>
-      <c r="BB16" s="36" t="n"/>
+      <c r="BB16" s="35" t="n"/>
       <c r="BC16" s="33" t="n"/>
       <c r="BD16" s="33" t="n"/>
       <c r="BE16" s="34" t="n"/>
-      <c r="BF16" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="BF16" s="35" t="n"/>
       <c r="BG16" s="33" t="n"/>
       <c r="BH16" s="33" t="n"/>
       <c r="BI16" s="34" t="n"/>
-      <c r="BJ16" s="36" t="n"/>
+      <c r="BJ16" s="35" t="n"/>
       <c r="BK16" s="33" t="n"/>
       <c r="BL16" s="33" t="n"/>
       <c r="BM16" s="34" t="n"/>
       <c r="BN16" s="31" t="n"/>
-      <c r="BO16" s="41" t="n"/>
-      <c r="BP16" s="41" t="n"/>
-      <c r="BQ16" s="42" t="n"/>
+      <c r="BO16" s="38" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="37" t="n"/>
       <c r="BR16" s="31" t="n"/>
-      <c r="BS16" s="41" t="n"/>
-      <c r="BT16" s="41" t="n"/>
-      <c r="BU16" s="42" t="n"/>
+      <c r="BS16" s="38" t="n"/>
+      <c r="BT16" s="38" t="n"/>
+      <c r="BU16" s="37" t="n"/>
       <c r="BV16" s="31" t="n"/>
-      <c r="BW16" s="41" t="n"/>
-      <c r="BX16" s="41" t="n"/>
-      <c r="BY16" s="42" t="n"/>
+      <c r="BW16" s="38" t="n"/>
+      <c r="BX16" s="38" t="n"/>
+      <c r="BY16" s="37" t="n"/>
       <c r="BZ16" s="31" t="n"/>
-      <c r="CA16" s="41" t="n"/>
-      <c r="CB16" s="41" t="n"/>
-      <c r="CC16" s="42" t="n"/>
+      <c r="CA16" s="38" t="n"/>
+      <c r="CB16" s="38" t="n"/>
+      <c r="CC16" s="37" t="n"/>
       <c r="CD16" s="31" t="n"/>
-      <c r="CE16" s="41" t="n"/>
-      <c r="CF16" s="41" t="n"/>
-      <c r="CG16" s="54" t="n"/>
+      <c r="CE16" s="38" t="n"/>
+      <c r="CF16" s="38" t="n"/>
+      <c r="CG16" s="48" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
@@ -3338,7 +3038,7 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>Delossantos,RP</t>
+          <t>Delossantos</t>
         </is>
       </c>
       <c r="E17" s="30" t="inlineStr">
@@ -3347,101 +3047,85 @@
         </is>
       </c>
       <c r="F17" s="31" t="n"/>
-      <c r="G17" s="41" t="n"/>
-      <c r="H17" s="41" t="n"/>
-      <c r="I17" s="42" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="37" t="n"/>
       <c r="J17" s="31" t="n"/>
-      <c r="K17" s="41" t="n"/>
-      <c r="L17" s="41" t="n"/>
-      <c r="M17" s="42" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="38" t="n"/>
+      <c r="M17" s="37" t="n"/>
       <c r="N17" s="31" t="n"/>
-      <c r="O17" s="41" t="n"/>
-      <c r="P17" s="41" t="n"/>
-      <c r="Q17" s="42" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="38" t="n"/>
+      <c r="Q17" s="37" t="n"/>
       <c r="R17" s="31" t="n"/>
-      <c r="S17" s="41" t="n"/>
-      <c r="T17" s="41" t="n"/>
-      <c r="U17" s="42" t="n"/>
+      <c r="S17" s="38" t="n"/>
+      <c r="T17" s="38" t="n"/>
+      <c r="U17" s="37" t="n"/>
       <c r="V17" s="31" t="n"/>
-      <c r="W17" s="41" t="n"/>
-      <c r="X17" s="41" t="n"/>
-      <c r="Y17" s="42" t="n"/>
+      <c r="W17" s="38" t="n"/>
+      <c r="X17" s="38" t="n"/>
+      <c r="Y17" s="37" t="n"/>
       <c r="Z17" s="31" t="n"/>
-      <c r="AA17" s="41" t="n"/>
-      <c r="AB17" s="41" t="n"/>
-      <c r="AC17" s="42" t="n"/>
+      <c r="AA17" s="38" t="n"/>
+      <c r="AB17" s="38" t="n"/>
+      <c r="AC17" s="37" t="n"/>
       <c r="AD17" s="31" t="n"/>
-      <c r="AE17" s="41" t="n"/>
-      <c r="AF17" s="41" t="n"/>
-      <c r="AG17" s="42" t="n"/>
+      <c r="AE17" s="38" t="n"/>
+      <c r="AF17" s="38" t="n"/>
+      <c r="AG17" s="37" t="n"/>
       <c r="AH17" s="31" t="n"/>
-      <c r="AI17" s="41" t="n"/>
-      <c r="AJ17" s="41" t="n"/>
-      <c r="AK17" s="42" t="n"/>
+      <c r="AI17" s="38" t="n"/>
+      <c r="AJ17" s="38" t="n"/>
+      <c r="AK17" s="37" t="n"/>
       <c r="AL17" s="31" t="n"/>
-      <c r="AM17" s="41" t="n"/>
-      <c r="AN17" s="41" t="n"/>
-      <c r="AO17" s="42" t="n"/>
-      <c r="AP17" s="36" t="n"/>
+      <c r="AM17" s="38" t="n"/>
+      <c r="AN17" s="38" t="n"/>
+      <c r="AO17" s="37" t="n"/>
+      <c r="AP17" s="35" t="n"/>
       <c r="AQ17" s="33" t="n"/>
       <c r="AR17" s="33" t="n"/>
       <c r="AS17" s="34" t="n"/>
-      <c r="AT17" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AT17" s="35" t="n"/>
       <c r="AU17" s="33" t="n"/>
       <c r="AV17" s="33" t="n"/>
       <c r="AW17" s="34" t="n"/>
-      <c r="AX17" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AX17" s="35" t="n"/>
       <c r="AY17" s="33" t="n"/>
-      <c r="AZ17" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AZ17" s="33" t="n"/>
       <c r="BA17" s="34" t="n"/>
-      <c r="BB17" s="36" t="n"/>
+      <c r="BB17" s="35" t="n"/>
       <c r="BC17" s="33" t="n"/>
       <c r="BD17" s="33" t="n"/>
       <c r="BE17" s="34" t="n"/>
-      <c r="BF17" s="36" t="n"/>
+      <c r="BF17" s="35" t="n"/>
       <c r="BG17" s="33" t="n"/>
       <c r="BH17" s="33" t="n"/>
       <c r="BI17" s="34" t="n"/>
-      <c r="BJ17" s="36" t="n"/>
+      <c r="BJ17" s="35" t="n"/>
       <c r="BK17" s="33" t="n"/>
       <c r="BL17" s="33" t="n"/>
       <c r="BM17" s="34" t="n"/>
-      <c r="BN17" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="BN17" s="35" t="n"/>
       <c r="BO17" s="33" t="n"/>
       <c r="BP17" s="33" t="n"/>
       <c r="BQ17" s="34" t="n"/>
-      <c r="BR17" s="40" t="n"/>
+      <c r="BR17" s="36" t="n"/>
       <c r="BS17" s="33" t="n"/>
-      <c r="BT17" s="41" t="n"/>
-      <c r="BU17" s="42" t="n"/>
+      <c r="BT17" s="38" t="n"/>
+      <c r="BU17" s="37" t="n"/>
       <c r="BV17" s="31" t="n"/>
-      <c r="BW17" s="41" t="n"/>
-      <c r="BX17" s="41" t="n"/>
-      <c r="BY17" s="42" t="n"/>
+      <c r="BW17" s="38" t="n"/>
+      <c r="BX17" s="38" t="n"/>
+      <c r="BY17" s="37" t="n"/>
       <c r="BZ17" s="31" t="n"/>
-      <c r="CA17" s="41" t="n"/>
-      <c r="CB17" s="41" t="n"/>
-      <c r="CC17" s="42" t="n"/>
+      <c r="CA17" s="38" t="n"/>
+      <c r="CB17" s="38" t="n"/>
+      <c r="CC17" s="37" t="n"/>
       <c r="CD17" s="31" t="n"/>
-      <c r="CE17" s="41" t="n"/>
-      <c r="CF17" s="41" t="n"/>
-      <c r="CG17" s="54" t="n"/>
+      <c r="CE17" s="38" t="n"/>
+      <c r="CF17" s="38" t="n"/>
+      <c r="CG17" s="48" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
@@ -3466,101 +3150,85 @@
       </c>
       <c r="E18" s="30" t="inlineStr"/>
       <c r="F18" s="31" t="n"/>
-      <c r="G18" s="41" t="n"/>
-      <c r="H18" s="41" t="n"/>
-      <c r="I18" s="42" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="37" t="n"/>
       <c r="J18" s="31" t="n"/>
-      <c r="K18" s="41" t="n"/>
-      <c r="L18" s="41" t="n"/>
-      <c r="M18" s="42" t="n"/>
+      <c r="K18" s="38" t="n"/>
+      <c r="L18" s="38" t="n"/>
+      <c r="M18" s="37" t="n"/>
       <c r="N18" s="31" t="n"/>
-      <c r="O18" s="41" t="n"/>
-      <c r="P18" s="41" t="n"/>
-      <c r="Q18" s="42" t="n"/>
+      <c r="O18" s="38" t="n"/>
+      <c r="P18" s="38" t="n"/>
+      <c r="Q18" s="37" t="n"/>
       <c r="R18" s="31" t="n"/>
-      <c r="S18" s="41" t="n"/>
-      <c r="T18" s="41" t="n"/>
-      <c r="U18" s="42" t="n"/>
+      <c r="S18" s="38" t="n"/>
+      <c r="T18" s="38" t="n"/>
+      <c r="U18" s="37" t="n"/>
       <c r="V18" s="31" t="n"/>
-      <c r="W18" s="41" t="n"/>
-      <c r="X18" s="41" t="n"/>
-      <c r="Y18" s="42" t="n"/>
+      <c r="W18" s="38" t="n"/>
+      <c r="X18" s="38" t="n"/>
+      <c r="Y18" s="37" t="n"/>
       <c r="Z18" s="31" t="n"/>
-      <c r="AA18" s="41" t="n"/>
-      <c r="AB18" s="41" t="n"/>
-      <c r="AC18" s="42" t="n"/>
+      <c r="AA18" s="38" t="n"/>
+      <c r="AB18" s="38" t="n"/>
+      <c r="AC18" s="37" t="n"/>
       <c r="AD18" s="31" t="n"/>
-      <c r="AE18" s="41" t="n"/>
-      <c r="AF18" s="41" t="n"/>
-      <c r="AG18" s="42" t="n"/>
+      <c r="AE18" s="38" t="n"/>
+      <c r="AF18" s="38" t="n"/>
+      <c r="AG18" s="37" t="n"/>
       <c r="AH18" s="31" t="n"/>
-      <c r="AI18" s="41" t="n"/>
-      <c r="AJ18" s="41" t="n"/>
-      <c r="AK18" s="42" t="n"/>
+      <c r="AI18" s="38" t="n"/>
+      <c r="AJ18" s="38" t="n"/>
+      <c r="AK18" s="37" t="n"/>
       <c r="AL18" s="31" t="n"/>
-      <c r="AM18" s="41" t="n"/>
-      <c r="AN18" s="41" t="n"/>
-      <c r="AO18" s="42" t="n"/>
+      <c r="AM18" s="38" t="n"/>
+      <c r="AN18" s="38" t="n"/>
+      <c r="AO18" s="37" t="n"/>
       <c r="AP18" s="31" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
-      <c r="AR18" s="41" t="n"/>
-      <c r="AS18" s="42" t="n"/>
-      <c r="AT18" s="47" t="n"/>
+      <c r="AQ18" s="38" t="n"/>
+      <c r="AR18" s="38" t="n"/>
+      <c r="AS18" s="37" t="n"/>
+      <c r="AT18" s="43" t="n"/>
       <c r="AU18" s="33" t="n"/>
       <c r="AV18" s="33" t="n"/>
       <c r="AW18" s="34" t="n"/>
-      <c r="AX18" s="47" t="n"/>
+      <c r="AX18" s="43" t="n"/>
       <c r="AY18" s="33" t="n"/>
       <c r="AZ18" s="33" t="n"/>
       <c r="BA18" s="34" t="n"/>
-      <c r="BB18" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BB18" s="43" t="n"/>
       <c r="BC18" s="33" t="n"/>
-      <c r="BD18" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BD18" s="33" t="n"/>
       <c r="BE18" s="34" t="n"/>
-      <c r="BF18" s="47" t="n"/>
+      <c r="BF18" s="43" t="n"/>
       <c r="BG18" s="33" t="n"/>
       <c r="BH18" s="33" t="n"/>
       <c r="BI18" s="34" t="n"/>
-      <c r="BJ18" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="BJ18" s="43" t="n"/>
       <c r="BK18" s="33" t="n"/>
       <c r="BL18" s="33" t="n"/>
       <c r="BM18" s="34" t="n"/>
-      <c r="BN18" s="47" t="n"/>
+      <c r="BN18" s="43" t="n"/>
       <c r="BO18" s="33" t="n"/>
       <c r="BP18" s="33" t="n"/>
       <c r="BQ18" s="34" t="n"/>
-      <c r="BR18" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BR18" s="43" t="n"/>
       <c r="BS18" s="33" t="n"/>
       <c r="BT18" s="33" t="n"/>
       <c r="BU18" s="34" t="n"/>
-      <c r="BV18" s="47" t="n"/>
+      <c r="BV18" s="43" t="n"/>
       <c r="BW18" s="33" t="n"/>
       <c r="BX18" s="33" t="n"/>
       <c r="BY18" s="34" t="n"/>
       <c r="BZ18" s="31" t="n"/>
-      <c r="CA18" s="41" t="n"/>
-      <c r="CB18" s="41" t="n"/>
-      <c r="CC18" s="42" t="n"/>
+      <c r="CA18" s="38" t="n"/>
+      <c r="CB18" s="38" t="n"/>
+      <c r="CC18" s="37" t="n"/>
       <c r="CD18" s="31" t="n"/>
-      <c r="CE18" s="41" t="n"/>
-      <c r="CF18" s="41" t="n"/>
-      <c r="CG18" s="54" t="n"/>
+      <c r="CE18" s="38" t="n"/>
+      <c r="CF18" s="38" t="n"/>
+      <c r="CG18" s="48" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
@@ -3580,7 +3248,7 @@
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>Alcindor,M</t>
+          <t>Alcindor</t>
         </is>
       </c>
       <c r="E19" s="30" t="inlineStr">
@@ -3589,101 +3257,85 @@
         </is>
       </c>
       <c r="F19" s="31" t="n"/>
-      <c r="G19" s="41" t="n"/>
-      <c r="H19" s="41" t="n"/>
-      <c r="I19" s="42" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="37" t="n"/>
       <c r="J19" s="31" t="n"/>
-      <c r="K19" s="41" t="n"/>
-      <c r="L19" s="41" t="n"/>
-      <c r="M19" s="42" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="38" t="n"/>
+      <c r="M19" s="37" t="n"/>
       <c r="N19" s="31" t="n"/>
-      <c r="O19" s="41" t="n"/>
-      <c r="P19" s="41" t="n"/>
-      <c r="Q19" s="42" t="n"/>
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="38" t="n"/>
+      <c r="Q19" s="37" t="n"/>
       <c r="R19" s="31" t="n"/>
-      <c r="S19" s="41" t="n"/>
-      <c r="T19" s="41" t="n"/>
-      <c r="U19" s="42" t="n"/>
+      <c r="S19" s="38" t="n"/>
+      <c r="T19" s="38" t="n"/>
+      <c r="U19" s="37" t="n"/>
       <c r="V19" s="31" t="n"/>
-      <c r="W19" s="41" t="n"/>
-      <c r="X19" s="41" t="n"/>
-      <c r="Y19" s="42" t="n"/>
+      <c r="W19" s="38" t="n"/>
+      <c r="X19" s="38" t="n"/>
+      <c r="Y19" s="37" t="n"/>
       <c r="Z19" s="31" t="n"/>
-      <c r="AA19" s="41" t="n"/>
-      <c r="AB19" s="41" t="n"/>
-      <c r="AC19" s="42" t="n"/>
+      <c r="AA19" s="38" t="n"/>
+      <c r="AB19" s="38" t="n"/>
+      <c r="AC19" s="37" t="n"/>
       <c r="AD19" s="31" t="n"/>
-      <c r="AE19" s="41" t="n"/>
-      <c r="AF19" s="41" t="n"/>
-      <c r="AG19" s="42" t="n"/>
+      <c r="AE19" s="38" t="n"/>
+      <c r="AF19" s="38" t="n"/>
+      <c r="AG19" s="37" t="n"/>
       <c r="AH19" s="31" t="n"/>
-      <c r="AI19" s="41" t="n"/>
-      <c r="AJ19" s="41" t="n"/>
-      <c r="AK19" s="42" t="n"/>
+      <c r="AI19" s="38" t="n"/>
+      <c r="AJ19" s="38" t="n"/>
+      <c r="AK19" s="37" t="n"/>
       <c r="AL19" s="31" t="n"/>
-      <c r="AM19" s="41" t="n"/>
-      <c r="AN19" s="41" t="n"/>
-      <c r="AO19" s="42" t="n"/>
+      <c r="AM19" s="38" t="n"/>
+      <c r="AN19" s="38" t="n"/>
+      <c r="AO19" s="37" t="n"/>
       <c r="AP19" s="31" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
-      <c r="AR19" s="41" t="n"/>
-      <c r="AS19" s="42" t="n"/>
-      <c r="AT19" s="47" t="n"/>
+      <c r="AQ19" s="38" t="n"/>
+      <c r="AR19" s="38" t="n"/>
+      <c r="AS19" s="37" t="n"/>
+      <c r="AT19" s="43" t="n"/>
       <c r="AU19" s="33" t="n"/>
       <c r="AV19" s="33" t="n"/>
       <c r="AW19" s="34" t="n"/>
-      <c r="AX19" s="47" t="n"/>
+      <c r="AX19" s="43" t="n"/>
       <c r="AY19" s="33" t="n"/>
       <c r="AZ19" s="33" t="n"/>
       <c r="BA19" s="34" t="n"/>
-      <c r="BB19" s="48" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="BB19" s="43" t="n"/>
       <c r="BC19" s="33" t="n"/>
       <c r="BD19" s="33" t="n"/>
       <c r="BE19" s="34" t="n"/>
-      <c r="BF19" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BF19" s="43" t="n"/>
       <c r="BG19" s="33" t="n"/>
-      <c r="BH19" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BH19" s="33" t="n"/>
       <c r="BI19" s="34" t="n"/>
-      <c r="BJ19" s="47" t="n"/>
+      <c r="BJ19" s="43" t="n"/>
       <c r="BK19" s="33" t="n"/>
       <c r="BL19" s="33" t="n"/>
       <c r="BM19" s="34" t="n"/>
-      <c r="BN19" s="47" t="n"/>
+      <c r="BN19" s="43" t="n"/>
       <c r="BO19" s="33" t="n"/>
       <c r="BP19" s="33" t="n"/>
       <c r="BQ19" s="34" t="n"/>
-      <c r="BR19" s="47" t="n"/>
+      <c r="BR19" s="43" t="n"/>
       <c r="BS19" s="33" t="n"/>
       <c r="BT19" s="33" t="n"/>
       <c r="BU19" s="34" t="n"/>
-      <c r="BV19" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BV19" s="43" t="n"/>
       <c r="BW19" s="33" t="n"/>
       <c r="BX19" s="33" t="n"/>
       <c r="BY19" s="34" t="n"/>
       <c r="BZ19" s="31" t="n"/>
-      <c r="CA19" s="41" t="n"/>
-      <c r="CB19" s="41" t="n"/>
-      <c r="CC19" s="42" t="n"/>
+      <c r="CA19" s="38" t="n"/>
+      <c r="CB19" s="38" t="n"/>
+      <c r="CC19" s="37" t="n"/>
       <c r="CD19" s="31" t="n"/>
-      <c r="CE19" s="41" t="n"/>
-      <c r="CF19" s="41" t="n"/>
-      <c r="CG19" s="54" t="n"/>
+      <c r="CE19" s="38" t="n"/>
+      <c r="CF19" s="38" t="n"/>
+      <c r="CG19" s="48" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="29" t="inlineStr">
@@ -3703,7 +3355,7 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>Gorial,G</t>
+          <t>Gorial</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -3712,97 +3364,85 @@
         </is>
       </c>
       <c r="F20" s="31" t="n"/>
-      <c r="G20" s="41" t="n"/>
-      <c r="H20" s="41" t="n"/>
-      <c r="I20" s="42" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="37" t="n"/>
       <c r="J20" s="31" t="n"/>
-      <c r="K20" s="41" t="n"/>
-      <c r="L20" s="41" t="n"/>
-      <c r="M20" s="42" t="n"/>
+      <c r="K20" s="38" t="n"/>
+      <c r="L20" s="38" t="n"/>
+      <c r="M20" s="37" t="n"/>
       <c r="N20" s="31" t="n"/>
-      <c r="O20" s="41" t="n"/>
-      <c r="P20" s="41" t="n"/>
-      <c r="Q20" s="42" t="n"/>
+      <c r="O20" s="38" t="n"/>
+      <c r="P20" s="38" t="n"/>
+      <c r="Q20" s="37" t="n"/>
       <c r="R20" s="31" t="n"/>
-      <c r="S20" s="41" t="n"/>
-      <c r="T20" s="41" t="n"/>
-      <c r="U20" s="42" t="n"/>
+      <c r="S20" s="38" t="n"/>
+      <c r="T20" s="38" t="n"/>
+      <c r="U20" s="37" t="n"/>
       <c r="V20" s="31" t="n"/>
-      <c r="W20" s="41" t="n"/>
-      <c r="X20" s="41" t="n"/>
-      <c r="Y20" s="42" t="n"/>
+      <c r="W20" s="38" t="n"/>
+      <c r="X20" s="38" t="n"/>
+      <c r="Y20" s="37" t="n"/>
       <c r="Z20" s="31" t="n"/>
-      <c r="AA20" s="41" t="n"/>
-      <c r="AB20" s="41" t="n"/>
-      <c r="AC20" s="42" t="n"/>
+      <c r="AA20" s="38" t="n"/>
+      <c r="AB20" s="38" t="n"/>
+      <c r="AC20" s="37" t="n"/>
       <c r="AD20" s="31" t="n"/>
-      <c r="AE20" s="41" t="n"/>
-      <c r="AF20" s="41" t="n"/>
-      <c r="AG20" s="42" t="n"/>
+      <c r="AE20" s="38" t="n"/>
+      <c r="AF20" s="38" t="n"/>
+      <c r="AG20" s="37" t="n"/>
       <c r="AH20" s="31" t="n"/>
-      <c r="AI20" s="41" t="n"/>
-      <c r="AJ20" s="41" t="n"/>
-      <c r="AK20" s="42" t="n"/>
+      <c r="AI20" s="38" t="n"/>
+      <c r="AJ20" s="38" t="n"/>
+      <c r="AK20" s="37" t="n"/>
       <c r="AL20" s="31" t="n"/>
-      <c r="AM20" s="41" t="n"/>
-      <c r="AN20" s="41" t="n"/>
-      <c r="AO20" s="42" t="n"/>
+      <c r="AM20" s="38" t="n"/>
+      <c r="AN20" s="38" t="n"/>
+      <c r="AO20" s="37" t="n"/>
       <c r="AP20" s="31" t="n"/>
-      <c r="AQ20" s="41" t="n"/>
-      <c r="AR20" s="41" t="n"/>
-      <c r="AS20" s="42" t="n"/>
+      <c r="AQ20" s="38" t="n"/>
+      <c r="AR20" s="38" t="n"/>
+      <c r="AS20" s="37" t="n"/>
       <c r="AT20" s="31" t="n"/>
-      <c r="AU20" s="41" t="n"/>
-      <c r="AV20" s="41" t="n"/>
-      <c r="AW20" s="42" t="n"/>
-      <c r="AX20" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AU20" s="38" t="n"/>
+      <c r="AV20" s="38" t="n"/>
+      <c r="AW20" s="37" t="n"/>
+      <c r="AX20" s="43" t="n"/>
       <c r="AY20" s="33" t="n"/>
       <c r="AZ20" s="33" t="n"/>
       <c r="BA20" s="34" t="n"/>
-      <c r="BB20" s="48" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+      <c r="BB20" s="43" t="n"/>
       <c r="BC20" s="33" t="n"/>
       <c r="BD20" s="33" t="n"/>
       <c r="BE20" s="34" t="n"/>
-      <c r="BF20" s="47" t="n"/>
+      <c r="BF20" s="43" t="n"/>
       <c r="BG20" s="33" t="n"/>
       <c r="BH20" s="33" t="n"/>
       <c r="BI20" s="34" t="n"/>
-      <c r="BJ20" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BJ20" s="43" t="n"/>
       <c r="BK20" s="33" t="n"/>
       <c r="BL20" s="33" t="n"/>
       <c r="BM20" s="34" t="n"/>
       <c r="BN20" s="31" t="n"/>
-      <c r="BO20" s="41" t="n"/>
-      <c r="BP20" s="41" t="n"/>
-      <c r="BQ20" s="42" t="n"/>
+      <c r="BO20" s="38" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="37" t="n"/>
       <c r="BR20" s="31" t="n"/>
-      <c r="BS20" s="41" t="n"/>
-      <c r="BT20" s="41" t="n"/>
-      <c r="BU20" s="42" t="n"/>
+      <c r="BS20" s="38" t="n"/>
+      <c r="BT20" s="38" t="n"/>
+      <c r="BU20" s="37" t="n"/>
       <c r="BV20" s="31" t="n"/>
-      <c r="BW20" s="41" t="n"/>
-      <c r="BX20" s="41" t="n"/>
-      <c r="BY20" s="42" t="n"/>
+      <c r="BW20" s="38" t="n"/>
+      <c r="BX20" s="38" t="n"/>
+      <c r="BY20" s="37" t="n"/>
       <c r="BZ20" s="31" t="n"/>
-      <c r="CA20" s="41" t="n"/>
-      <c r="CB20" s="41" t="n"/>
-      <c r="CC20" s="42" t="n"/>
+      <c r="CA20" s="38" t="n"/>
+      <c r="CB20" s="38" t="n"/>
+      <c r="CC20" s="37" t="n"/>
       <c r="CD20" s="31" t="n"/>
-      <c r="CE20" s="41" t="n"/>
-      <c r="CF20" s="41" t="n"/>
-      <c r="CG20" s="54" t="n"/>
+      <c r="CE20" s="38" t="n"/>
+      <c r="CF20" s="38" t="n"/>
+      <c r="CG20" s="48" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="29" t="inlineStr">
@@ -3822,7 +3462,7 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>Ciarico,A</t>
+          <t>Ciarico</t>
         </is>
       </c>
       <c r="E21" s="30" t="inlineStr">
@@ -3831,101 +3471,85 @@
         </is>
       </c>
       <c r="F21" s="31" t="n"/>
-      <c r="G21" s="41" t="n"/>
-      <c r="H21" s="41" t="n"/>
-      <c r="I21" s="42" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="37" t="n"/>
       <c r="J21" s="31" t="n"/>
-      <c r="K21" s="41" t="n"/>
-      <c r="L21" s="41" t="n"/>
-      <c r="M21" s="42" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="38" t="n"/>
+      <c r="M21" s="37" t="n"/>
       <c r="N21" s="31" t="n"/>
-      <c r="O21" s="41" t="n"/>
-      <c r="P21" s="41" t="n"/>
-      <c r="Q21" s="42" t="n"/>
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="38" t="n"/>
+      <c r="Q21" s="37" t="n"/>
       <c r="R21" s="31" t="n"/>
-      <c r="S21" s="41" t="n"/>
-      <c r="T21" s="41" t="n"/>
-      <c r="U21" s="42" t="n"/>
+      <c r="S21" s="38" t="n"/>
+      <c r="T21" s="38" t="n"/>
+      <c r="U21" s="37" t="n"/>
       <c r="V21" s="31" t="n"/>
-      <c r="W21" s="41" t="n"/>
-      <c r="X21" s="41" t="n"/>
-      <c r="Y21" s="42" t="n"/>
+      <c r="W21" s="38" t="n"/>
+      <c r="X21" s="38" t="n"/>
+      <c r="Y21" s="37" t="n"/>
       <c r="Z21" s="31" t="n"/>
-      <c r="AA21" s="41" t="n"/>
-      <c r="AB21" s="41" t="n"/>
-      <c r="AC21" s="42" t="n"/>
+      <c r="AA21" s="38" t="n"/>
+      <c r="AB21" s="38" t="n"/>
+      <c r="AC21" s="37" t="n"/>
       <c r="AD21" s="31" t="n"/>
-      <c r="AE21" s="41" t="n"/>
-      <c r="AF21" s="41" t="n"/>
-      <c r="AG21" s="42" t="n"/>
+      <c r="AE21" s="38" t="n"/>
+      <c r="AF21" s="38" t="n"/>
+      <c r="AG21" s="37" t="n"/>
       <c r="AH21" s="31" t="n"/>
-      <c r="AI21" s="41" t="n"/>
-      <c r="AJ21" s="41" t="n"/>
-      <c r="AK21" s="42" t="n"/>
+      <c r="AI21" s="38" t="n"/>
+      <c r="AJ21" s="38" t="n"/>
+      <c r="AK21" s="37" t="n"/>
       <c r="AL21" s="31" t="n"/>
-      <c r="AM21" s="41" t="n"/>
-      <c r="AN21" s="41" t="n"/>
-      <c r="AO21" s="42" t="n"/>
+      <c r="AM21" s="38" t="n"/>
+      <c r="AN21" s="38" t="n"/>
+      <c r="AO21" s="37" t="n"/>
       <c r="AP21" s="31" t="n"/>
-      <c r="AQ21" s="41" t="n"/>
-      <c r="AR21" s="41" t="n"/>
-      <c r="AS21" s="42" t="n"/>
+      <c r="AQ21" s="38" t="n"/>
+      <c r="AR21" s="38" t="n"/>
+      <c r="AS21" s="37" t="n"/>
       <c r="AT21" s="31" t="n"/>
-      <c r="AU21" s="41" t="n"/>
-      <c r="AV21" s="41" t="n"/>
-      <c r="AW21" s="42" t="n"/>
+      <c r="AU21" s="38" t="n"/>
+      <c r="AV21" s="38" t="n"/>
+      <c r="AW21" s="37" t="n"/>
       <c r="AX21" s="31" t="n"/>
-      <c r="AY21" s="41" t="n"/>
-      <c r="AZ21" s="41" t="n"/>
-      <c r="BA21" s="42" t="n"/>
-      <c r="BB21" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AY21" s="38" t="n"/>
+      <c r="AZ21" s="38" t="n"/>
+      <c r="BA21" s="37" t="n"/>
+      <c r="BB21" s="43" t="n"/>
       <c r="BC21" s="33" t="n"/>
       <c r="BD21" s="33" t="n"/>
       <c r="BE21" s="34" t="n"/>
-      <c r="BF21" s="47" t="n"/>
+      <c r="BF21" s="43" t="n"/>
       <c r="BG21" s="33" t="n"/>
       <c r="BH21" s="33" t="n"/>
       <c r="BI21" s="34" t="n"/>
-      <c r="BJ21" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BJ21" s="43" t="n"/>
       <c r="BK21" s="33" t="n"/>
-      <c r="BL21" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BL21" s="33" t="n"/>
       <c r="BM21" s="34" t="n"/>
-      <c r="BN21" s="47" t="n"/>
+      <c r="BN21" s="43" t="n"/>
       <c r="BO21" s="33" t="n"/>
       <c r="BP21" s="33" t="n"/>
       <c r="BQ21" s="34" t="n"/>
-      <c r="BR21" s="47" t="n"/>
+      <c r="BR21" s="43" t="n"/>
       <c r="BS21" s="33" t="n"/>
       <c r="BT21" s="33" t="n"/>
       <c r="BU21" s="34" t="n"/>
-      <c r="BV21" s="47" t="n"/>
+      <c r="BV21" s="43" t="n"/>
       <c r="BW21" s="33" t="n"/>
       <c r="BX21" s="33" t="n"/>
       <c r="BY21" s="34" t="n"/>
-      <c r="BZ21" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BZ21" s="43" t="n"/>
       <c r="CA21" s="33" t="n"/>
       <c r="CB21" s="33" t="n"/>
       <c r="CC21" s="34" t="n"/>
-      <c r="CD21" s="52" t="n"/>
+      <c r="CD21" s="43" t="n"/>
       <c r="CE21" s="33" t="n"/>
       <c r="CF21" s="33" t="n"/>
-      <c r="CG21" s="54" t="n"/>
+      <c r="CG21" s="49" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="29" t="inlineStr">
@@ -3945,7 +3569,7 @@
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>Owusu,MK</t>
+          <t>Owusu</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -3954,101 +3578,85 @@
         </is>
       </c>
       <c r="F22" s="31" t="n"/>
-      <c r="G22" s="41" t="n"/>
-      <c r="H22" s="41" t="n"/>
-      <c r="I22" s="42" t="n"/>
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="38" t="n"/>
+      <c r="I22" s="37" t="n"/>
       <c r="J22" s="31" t="n"/>
-      <c r="K22" s="41" t="n"/>
-      <c r="L22" s="41" t="n"/>
-      <c r="M22" s="42" t="n"/>
+      <c r="K22" s="38" t="n"/>
+      <c r="L22" s="38" t="n"/>
+      <c r="M22" s="37" t="n"/>
       <c r="N22" s="31" t="n"/>
-      <c r="O22" s="41" t="n"/>
-      <c r="P22" s="41" t="n"/>
-      <c r="Q22" s="42" t="n"/>
+      <c r="O22" s="38" t="n"/>
+      <c r="P22" s="38" t="n"/>
+      <c r="Q22" s="37" t="n"/>
       <c r="R22" s="31" t="n"/>
-      <c r="S22" s="41" t="n"/>
-      <c r="T22" s="41" t="n"/>
-      <c r="U22" s="42" t="n"/>
+      <c r="S22" s="38" t="n"/>
+      <c r="T22" s="38" t="n"/>
+      <c r="U22" s="37" t="n"/>
       <c r="V22" s="31" t="n"/>
-      <c r="W22" s="41" t="n"/>
-      <c r="X22" s="41" t="n"/>
-      <c r="Y22" s="42" t="n"/>
+      <c r="W22" s="38" t="n"/>
+      <c r="X22" s="38" t="n"/>
+      <c r="Y22" s="37" t="n"/>
       <c r="Z22" s="31" t="n"/>
-      <c r="AA22" s="41" t="n"/>
-      <c r="AB22" s="41" t="n"/>
-      <c r="AC22" s="42" t="n"/>
+      <c r="AA22" s="38" t="n"/>
+      <c r="AB22" s="38" t="n"/>
+      <c r="AC22" s="37" t="n"/>
       <c r="AD22" s="31" t="n"/>
-      <c r="AE22" s="41" t="n"/>
-      <c r="AF22" s="41" t="n"/>
-      <c r="AG22" s="42" t="n"/>
+      <c r="AE22" s="38" t="n"/>
+      <c r="AF22" s="38" t="n"/>
+      <c r="AG22" s="37" t="n"/>
       <c r="AH22" s="31" t="n"/>
-      <c r="AI22" s="41" t="n"/>
-      <c r="AJ22" s="41" t="n"/>
-      <c r="AK22" s="42" t="n"/>
+      <c r="AI22" s="38" t="n"/>
+      <c r="AJ22" s="38" t="n"/>
+      <c r="AK22" s="37" t="n"/>
       <c r="AL22" s="31" t="n"/>
-      <c r="AM22" s="41" t="n"/>
-      <c r="AN22" s="41" t="n"/>
-      <c r="AO22" s="42" t="n"/>
+      <c r="AM22" s="38" t="n"/>
+      <c r="AN22" s="38" t="n"/>
+      <c r="AO22" s="37" t="n"/>
       <c r="AP22" s="31" t="n"/>
-      <c r="AQ22" s="41" t="n"/>
-      <c r="AR22" s="41" t="n"/>
-      <c r="AS22" s="42" t="n"/>
+      <c r="AQ22" s="38" t="n"/>
+      <c r="AR22" s="38" t="n"/>
+      <c r="AS22" s="37" t="n"/>
       <c r="AT22" s="31" t="n"/>
-      <c r="AU22" s="41" t="n"/>
-      <c r="AV22" s="41" t="n"/>
-      <c r="AW22" s="42" t="n"/>
+      <c r="AU22" s="38" t="n"/>
+      <c r="AV22" s="38" t="n"/>
+      <c r="AW22" s="37" t="n"/>
       <c r="AX22" s="31" t="n"/>
-      <c r="AY22" s="41" t="n"/>
-      <c r="AZ22" s="41" t="n"/>
-      <c r="BA22" s="42" t="n"/>
-      <c r="BB22" s="47" t="n"/>
+      <c r="AY22" s="38" t="n"/>
+      <c r="AZ22" s="38" t="n"/>
+      <c r="BA22" s="37" t="n"/>
+      <c r="BB22" s="43" t="n"/>
       <c r="BC22" s="33" t="n"/>
       <c r="BD22" s="33" t="n"/>
       <c r="BE22" s="34" t="n"/>
-      <c r="BF22" s="48" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="BF22" s="43" t="n"/>
       <c r="BG22" s="33" t="n"/>
       <c r="BH22" s="33" t="n"/>
       <c r="BI22" s="34" t="n"/>
-      <c r="BJ22" s="47" t="n"/>
+      <c r="BJ22" s="43" t="n"/>
       <c r="BK22" s="33" t="n"/>
       <c r="BL22" s="33" t="n"/>
       <c r="BM22" s="34" t="n"/>
-      <c r="BN22" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BN22" s="43" t="n"/>
       <c r="BO22" s="33" t="n"/>
-      <c r="BP22" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BP22" s="33" t="n"/>
       <c r="BQ22" s="34" t="n"/>
-      <c r="BR22" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="BR22" s="43" t="n"/>
       <c r="BS22" s="33" t="n"/>
       <c r="BT22" s="33" t="n"/>
       <c r="BU22" s="34" t="n"/>
-      <c r="BV22" s="47" t="n"/>
+      <c r="BV22" s="43" t="n"/>
       <c r="BW22" s="33" t="n"/>
       <c r="BX22" s="33" t="n"/>
       <c r="BY22" s="34" t="n"/>
-      <c r="BZ22" s="47" t="n"/>
+      <c r="BZ22" s="43" t="n"/>
       <c r="CA22" s="33" t="n"/>
       <c r="CB22" s="33" t="n"/>
       <c r="CC22" s="34" t="n"/>
-      <c r="CD22" s="52" t="n"/>
+      <c r="CD22" s="43" t="n"/>
       <c r="CE22" s="33" t="n"/>
       <c r="CF22" s="33" t="n"/>
-      <c r="CG22" s="54" t="n"/>
+      <c r="CG22" s="49" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="29" t="inlineStr">
@@ -4068,7 +3676,7 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>Aboobacker,M</t>
+          <t>Aboobacker</t>
         </is>
       </c>
       <c r="E23" s="30" t="inlineStr">
@@ -4077,97 +3685,85 @@
         </is>
       </c>
       <c r="F23" s="31" t="n"/>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="41" t="n"/>
-      <c r="I23" s="42" t="n"/>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="37" t="n"/>
       <c r="J23" s="31" t="n"/>
-      <c r="K23" s="41" t="n"/>
-      <c r="L23" s="41" t="n"/>
-      <c r="M23" s="42" t="n"/>
+      <c r="K23" s="38" t="n"/>
+      <c r="L23" s="38" t="n"/>
+      <c r="M23" s="37" t="n"/>
       <c r="N23" s="31" t="n"/>
-      <c r="O23" s="41" t="n"/>
-      <c r="P23" s="41" t="n"/>
-      <c r="Q23" s="42" t="n"/>
+      <c r="O23" s="38" t="n"/>
+      <c r="P23" s="38" t="n"/>
+      <c r="Q23" s="37" t="n"/>
       <c r="R23" s="31" t="n"/>
-      <c r="S23" s="41" t="n"/>
-      <c r="T23" s="41" t="n"/>
-      <c r="U23" s="42" t="n"/>
+      <c r="S23" s="38" t="n"/>
+      <c r="T23" s="38" t="n"/>
+      <c r="U23" s="37" t="n"/>
       <c r="V23" s="31" t="n"/>
-      <c r="W23" s="41" t="n"/>
-      <c r="X23" s="41" t="n"/>
-      <c r="Y23" s="42" t="n"/>
+      <c r="W23" s="38" t="n"/>
+      <c r="X23" s="38" t="n"/>
+      <c r="Y23" s="37" t="n"/>
       <c r="Z23" s="31" t="n"/>
-      <c r="AA23" s="41" t="n"/>
-      <c r="AB23" s="41" t="n"/>
-      <c r="AC23" s="42" t="n"/>
+      <c r="AA23" s="38" t="n"/>
+      <c r="AB23" s="38" t="n"/>
+      <c r="AC23" s="37" t="n"/>
       <c r="AD23" s="31" t="n"/>
-      <c r="AE23" s="41" t="n"/>
-      <c r="AF23" s="41" t="n"/>
-      <c r="AG23" s="42" t="n"/>
+      <c r="AE23" s="38" t="n"/>
+      <c r="AF23" s="38" t="n"/>
+      <c r="AG23" s="37" t="n"/>
       <c r="AH23" s="31" t="n"/>
-      <c r="AI23" s="41" t="n"/>
-      <c r="AJ23" s="41" t="n"/>
-      <c r="AK23" s="42" t="n"/>
+      <c r="AI23" s="38" t="n"/>
+      <c r="AJ23" s="38" t="n"/>
+      <c r="AK23" s="37" t="n"/>
       <c r="AL23" s="31" t="n"/>
-      <c r="AM23" s="41" t="n"/>
-      <c r="AN23" s="41" t="n"/>
-      <c r="AO23" s="42" t="n"/>
+      <c r="AM23" s="38" t="n"/>
+      <c r="AN23" s="38" t="n"/>
+      <c r="AO23" s="37" t="n"/>
       <c r="AP23" s="31" t="n"/>
-      <c r="AQ23" s="41" t="n"/>
-      <c r="AR23" s="41" t="n"/>
-      <c r="AS23" s="42" t="n"/>
+      <c r="AQ23" s="38" t="n"/>
+      <c r="AR23" s="38" t="n"/>
+      <c r="AS23" s="37" t="n"/>
       <c r="AT23" s="31" t="n"/>
-      <c r="AU23" s="41" t="n"/>
-      <c r="AV23" s="41" t="n"/>
-      <c r="AW23" s="42" t="n"/>
+      <c r="AU23" s="38" t="n"/>
+      <c r="AV23" s="38" t="n"/>
+      <c r="AW23" s="37" t="n"/>
       <c r="AX23" s="31" t="n"/>
-      <c r="AY23" s="41" t="n"/>
-      <c r="AZ23" s="41" t="n"/>
-      <c r="BA23" s="42" t="n"/>
+      <c r="AY23" s="38" t="n"/>
+      <c r="AZ23" s="38" t="n"/>
+      <c r="BA23" s="37" t="n"/>
       <c r="BB23" s="31" t="n"/>
-      <c r="BC23" s="41" t="n"/>
+      <c r="BC23" s="38" t="n"/>
       <c r="BD23" s="32" t="n"/>
       <c r="BE23" s="34" t="n"/>
-      <c r="BF23" s="36" t="n"/>
+      <c r="BF23" s="35" t="n"/>
       <c r="BG23" s="33" t="n"/>
       <c r="BH23" s="33" t="n"/>
       <c r="BI23" s="34" t="n"/>
-      <c r="BJ23" s="36" t="n"/>
+      <c r="BJ23" s="35" t="n"/>
       <c r="BK23" s="33" t="n"/>
       <c r="BL23" s="33" t="n"/>
       <c r="BM23" s="34" t="n"/>
-      <c r="BN23" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BN23" s="35" t="n"/>
       <c r="BO23" s="33" t="n"/>
-      <c r="BP23" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BP23" s="33" t="n"/>
       <c r="BQ23" s="34" t="n"/>
-      <c r="BR23" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="BR23" s="35" t="n"/>
       <c r="BS23" s="33" t="n"/>
       <c r="BT23" s="33" t="n"/>
       <c r="BU23" s="34" t="n"/>
-      <c r="BV23" s="36" t="n"/>
+      <c r="BV23" s="35" t="n"/>
       <c r="BW23" s="33" t="n"/>
       <c r="BX23" s="33" t="n"/>
       <c r="BY23" s="34" t="n"/>
-      <c r="BZ23" s="36" t="n"/>
+      <c r="BZ23" s="35" t="n"/>
       <c r="CA23" s="33" t="n"/>
       <c r="CB23" s="33" t="n"/>
       <c r="CC23" s="34" t="n"/>
-      <c r="CD23" s="40" t="n"/>
+      <c r="CD23" s="35" t="n"/>
       <c r="CE23" s="33" t="n"/>
       <c r="CF23" s="33" t="n"/>
-      <c r="CG23" s="54" t="n"/>
+      <c r="CG23" s="49" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="29" t="inlineStr"/>
@@ -4176,91 +3772,85 @@
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="30" t="n"/>
       <c r="F24" s="31" t="n"/>
-      <c r="G24" s="41" t="n"/>
-      <c r="H24" s="41" t="n"/>
-      <c r="I24" s="42" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="37" t="n"/>
       <c r="J24" s="31" t="n"/>
-      <c r="K24" s="41" t="n"/>
-      <c r="L24" s="41" t="n"/>
-      <c r="M24" s="42" t="n"/>
+      <c r="K24" s="38" t="n"/>
+      <c r="L24" s="38" t="n"/>
+      <c r="M24" s="37" t="n"/>
       <c r="N24" s="31" t="n"/>
-      <c r="O24" s="41" t="n"/>
-      <c r="P24" s="41" t="n"/>
-      <c r="Q24" s="42" t="n"/>
+      <c r="O24" s="38" t="n"/>
+      <c r="P24" s="38" t="n"/>
+      <c r="Q24" s="37" t="n"/>
       <c r="R24" s="31" t="n"/>
-      <c r="S24" s="41" t="n"/>
-      <c r="T24" s="41" t="n"/>
-      <c r="U24" s="42" t="n"/>
+      <c r="S24" s="38" t="n"/>
+      <c r="T24" s="38" t="n"/>
+      <c r="U24" s="37" t="n"/>
       <c r="V24" s="31" t="n"/>
-      <c r="W24" s="41" t="n"/>
-      <c r="X24" s="41" t="n"/>
-      <c r="Y24" s="42" t="n"/>
+      <c r="W24" s="38" t="n"/>
+      <c r="X24" s="38" t="n"/>
+      <c r="Y24" s="37" t="n"/>
       <c r="Z24" s="31" t="n"/>
-      <c r="AA24" s="41" t="n"/>
-      <c r="AB24" s="41" t="n"/>
-      <c r="AC24" s="42" t="n"/>
+      <c r="AA24" s="38" t="n"/>
+      <c r="AB24" s="38" t="n"/>
+      <c r="AC24" s="37" t="n"/>
       <c r="AD24" s="31" t="n"/>
-      <c r="AE24" s="41" t="n"/>
-      <c r="AF24" s="41" t="n"/>
-      <c r="AG24" s="42" t="n"/>
+      <c r="AE24" s="38" t="n"/>
+      <c r="AF24" s="38" t="n"/>
+      <c r="AG24" s="37" t="n"/>
       <c r="AH24" s="31" t="n"/>
-      <c r="AI24" s="41" t="n"/>
-      <c r="AJ24" s="41" t="n"/>
-      <c r="AK24" s="42" t="n"/>
-      <c r="AL24" s="65" t="inlineStr">
-        <is>
-          <t>PLEASE NOTE: CSSI INDICATES
-THAT YOU MUST BE ON THE
-STATION DURING THIS TIME.</t>
-        </is>
-      </c>
-      <c r="AM24" s="66" t="n"/>
-      <c r="AN24" s="66" t="n"/>
-      <c r="AO24" s="66" t="n"/>
-      <c r="AP24" s="66" t="n"/>
-      <c r="AQ24" s="66" t="n"/>
-      <c r="AR24" s="66" t="n"/>
-      <c r="AS24" s="66" t="n"/>
-      <c r="AT24" s="66" t="n"/>
-      <c r="AU24" s="66" t="n"/>
-      <c r="AV24" s="66" t="n"/>
-      <c r="AW24" s="66" t="n"/>
-      <c r="AX24" s="66" t="n"/>
-      <c r="AY24" s="66" t="n"/>
-      <c r="AZ24" s="66" t="n"/>
-      <c r="BA24" s="66" t="n"/>
-      <c r="BB24" s="66" t="n"/>
-      <c r="BC24" s="66" t="n"/>
-      <c r="BD24" s="66" t="n"/>
-      <c r="BE24" s="67" t="n"/>
+      <c r="AI24" s="38" t="n"/>
+      <c r="AJ24" s="38" t="n"/>
+      <c r="AK24" s="37" t="n"/>
+      <c r="AL24" s="31" t="n"/>
+      <c r="AM24" s="38" t="n"/>
+      <c r="AN24" s="38" t="n"/>
+      <c r="AO24" s="37" t="n"/>
+      <c r="AP24" s="31" t="n"/>
+      <c r="AQ24" s="38" t="n"/>
+      <c r="AR24" s="38" t="n"/>
+      <c r="AS24" s="37" t="n"/>
+      <c r="AT24" s="31" t="n"/>
+      <c r="AU24" s="38" t="n"/>
+      <c r="AV24" s="38" t="n"/>
+      <c r="AW24" s="37" t="n"/>
+      <c r="AX24" s="31" t="n"/>
+      <c r="AY24" s="38" t="n"/>
+      <c r="AZ24" s="38" t="n"/>
+      <c r="BA24" s="37" t="n"/>
+      <c r="BB24" s="31" t="n"/>
+      <c r="BC24" s="38" t="n"/>
+      <c r="BD24" s="38" t="n"/>
+      <c r="BE24" s="37" t="n"/>
       <c r="BF24" s="31" t="n"/>
-      <c r="BG24" s="41" t="n"/>
-      <c r="BH24" s="41" t="n"/>
-      <c r="BI24" s="42" t="n"/>
+      <c r="BG24" s="38" t="n"/>
+      <c r="BH24" s="38" t="n"/>
+      <c r="BI24" s="37" t="n"/>
       <c r="BJ24" s="31" t="n"/>
-      <c r="BK24" s="41" t="n"/>
-      <c r="BL24" s="41" t="n"/>
-      <c r="BM24" s="42" t="n"/>
+      <c r="BK24" s="38" t="n"/>
+      <c r="BL24" s="38" t="n"/>
+      <c r="BM24" s="37" t="n"/>
       <c r="BN24" s="31" t="n"/>
-      <c r="BO24" s="41" t="n"/>
-      <c r="BP24" s="41" t="n"/>
-      <c r="BQ24" s="42" t="n"/>
+      <c r="BO24" s="38" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="37" t="n"/>
       <c r="BR24" s="31" t="n"/>
-      <c r="BS24" s="41" t="n"/>
-      <c r="BT24" s="41" t="n"/>
-      <c r="BU24" s="42" t="n"/>
+      <c r="BS24" s="38" t="n"/>
+      <c r="BT24" s="38" t="n"/>
+      <c r="BU24" s="37" t="n"/>
       <c r="BV24" s="31" t="n"/>
-      <c r="BW24" s="41" t="n"/>
-      <c r="BX24" s="41" t="n"/>
-      <c r="BY24" s="42" t="n"/>
+      <c r="BW24" s="38" t="n"/>
+      <c r="BX24" s="38" t="n"/>
+      <c r="BY24" s="37" t="n"/>
       <c r="BZ24" s="31" t="n"/>
-      <c r="CA24" s="41" t="n"/>
-      <c r="CB24" s="41" t="n"/>
-      <c r="CC24" s="42" t="n"/>
+      <c r="CA24" s="38" t="n"/>
+      <c r="CB24" s="38" t="n"/>
+      <c r="CC24" s="37" t="n"/>
       <c r="CD24" s="31" t="n"/>
-      <c r="CE24" s="41" t="n"/>
-      <c r="CF24" s="41" t="n"/>
-      <c r="CG24" s="54" t="n"/>
+      <c r="CE24" s="38" t="n"/>
+      <c r="CF24" s="38" t="n"/>
+      <c r="CG24" s="48" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="29" t="inlineStr"/>
@@ -4269,67 +3859,85 @@
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="30" t="n"/>
       <c r="F25" s="31" t="n"/>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="41" t="n"/>
-      <c r="I25" s="42" t="n"/>
+      <c r="G25" s="38" t="n"/>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="37" t="n"/>
       <c r="J25" s="31" t="n"/>
-      <c r="K25" s="41" t="n"/>
-      <c r="L25" s="41" t="n"/>
-      <c r="M25" s="42" t="n"/>
+      <c r="K25" s="38" t="n"/>
+      <c r="L25" s="38" t="n"/>
+      <c r="M25" s="37" t="n"/>
       <c r="N25" s="31" t="n"/>
-      <c r="O25" s="41" t="n"/>
-      <c r="P25" s="41" t="n"/>
-      <c r="Q25" s="42" t="n"/>
+      <c r="O25" s="38" t="n"/>
+      <c r="P25" s="38" t="n"/>
+      <c r="Q25" s="37" t="n"/>
       <c r="R25" s="31" t="n"/>
-      <c r="S25" s="41" t="n"/>
-      <c r="T25" s="41" t="n"/>
-      <c r="U25" s="42" t="n"/>
+      <c r="S25" s="38" t="n"/>
+      <c r="T25" s="38" t="n"/>
+      <c r="U25" s="37" t="n"/>
       <c r="V25" s="31" t="n"/>
-      <c r="W25" s="41" t="n"/>
-      <c r="X25" s="41" t="n"/>
-      <c r="Y25" s="42" t="n"/>
+      <c r="W25" s="38" t="n"/>
+      <c r="X25" s="38" t="n"/>
+      <c r="Y25" s="37" t="n"/>
       <c r="Z25" s="31" t="n"/>
-      <c r="AA25" s="41" t="n"/>
-      <c r="AB25" s="41" t="n"/>
-      <c r="AC25" s="42" t="n"/>
+      <c r="AA25" s="38" t="n"/>
+      <c r="AB25" s="38" t="n"/>
+      <c r="AC25" s="37" t="n"/>
       <c r="AD25" s="31" t="n"/>
-      <c r="AE25" s="41" t="n"/>
-      <c r="AF25" s="41" t="n"/>
-      <c r="AG25" s="42" t="n"/>
+      <c r="AE25" s="38" t="n"/>
+      <c r="AF25" s="38" t="n"/>
+      <c r="AG25" s="37" t="n"/>
       <c r="AH25" s="31" t="n"/>
-      <c r="AI25" s="41" t="n"/>
-      <c r="AJ25" s="41" t="n"/>
-      <c r="AK25" s="42" t="n"/>
-      <c r="AL25" s="68" t="n"/>
-      <c r="BE25" s="69" t="n"/>
+      <c r="AI25" s="38" t="n"/>
+      <c r="AJ25" s="38" t="n"/>
+      <c r="AK25" s="37" t="n"/>
+      <c r="AL25" s="31" t="n"/>
+      <c r="AM25" s="38" t="n"/>
+      <c r="AN25" s="38" t="n"/>
+      <c r="AO25" s="37" t="n"/>
+      <c r="AP25" s="31" t="n"/>
+      <c r="AQ25" s="38" t="n"/>
+      <c r="AR25" s="38" t="n"/>
+      <c r="AS25" s="37" t="n"/>
+      <c r="AT25" s="31" t="n"/>
+      <c r="AU25" s="38" t="n"/>
+      <c r="AV25" s="38" t="n"/>
+      <c r="AW25" s="37" t="n"/>
+      <c r="AX25" s="31" t="n"/>
+      <c r="AY25" s="38" t="n"/>
+      <c r="AZ25" s="38" t="n"/>
+      <c r="BA25" s="37" t="n"/>
+      <c r="BB25" s="31" t="n"/>
+      <c r="BC25" s="38" t="n"/>
+      <c r="BD25" s="38" t="n"/>
+      <c r="BE25" s="37" t="n"/>
       <c r="BF25" s="31" t="n"/>
-      <c r="BG25" s="41" t="n"/>
-      <c r="BH25" s="41" t="n"/>
-      <c r="BI25" s="42" t="n"/>
+      <c r="BG25" s="38" t="n"/>
+      <c r="BH25" s="38" t="n"/>
+      <c r="BI25" s="37" t="n"/>
       <c r="BJ25" s="31" t="n"/>
-      <c r="BK25" s="41" t="n"/>
-      <c r="BL25" s="41" t="n"/>
-      <c r="BM25" s="42" t="n"/>
+      <c r="BK25" s="38" t="n"/>
+      <c r="BL25" s="38" t="n"/>
+      <c r="BM25" s="37" t="n"/>
       <c r="BN25" s="31" t="n"/>
-      <c r="BO25" s="41" t="n"/>
-      <c r="BP25" s="41" t="n"/>
-      <c r="BQ25" s="42" t="n"/>
+      <c r="BO25" s="38" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="37" t="n"/>
       <c r="BR25" s="31" t="n"/>
-      <c r="BS25" s="41" t="n"/>
-      <c r="BT25" s="41" t="n"/>
-      <c r="BU25" s="42" t="n"/>
+      <c r="BS25" s="38" t="n"/>
+      <c r="BT25" s="38" t="n"/>
+      <c r="BU25" s="37" t="n"/>
       <c r="BV25" s="31" t="n"/>
-      <c r="BW25" s="41" t="n"/>
-      <c r="BX25" s="41" t="n"/>
-      <c r="BY25" s="42" t="n"/>
+      <c r="BW25" s="38" t="n"/>
+      <c r="BX25" s="38" t="n"/>
+      <c r="BY25" s="37" t="n"/>
       <c r="BZ25" s="31" t="n"/>
-      <c r="CA25" s="41" t="n"/>
-      <c r="CB25" s="41" t="n"/>
-      <c r="CC25" s="42" t="n"/>
+      <c r="CA25" s="38" t="n"/>
+      <c r="CB25" s="38" t="n"/>
+      <c r="CC25" s="37" t="n"/>
       <c r="CD25" s="31" t="n"/>
-      <c r="CE25" s="41" t="n"/>
-      <c r="CF25" s="41" t="n"/>
-      <c r="CG25" s="54" t="n"/>
+      <c r="CE25" s="38" t="n"/>
+      <c r="CF25" s="38" t="n"/>
+      <c r="CG25" s="48" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="29" t="inlineStr"/>
@@ -4338,85 +3946,85 @@
       <c r="D26" s="30" t="n"/>
       <c r="E26" s="30" t="n"/>
       <c r="F26" s="31" t="n"/>
-      <c r="G26" s="41" t="n"/>
-      <c r="H26" s="41" t="n"/>
-      <c r="I26" s="42" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="37" t="n"/>
       <c r="J26" s="31" t="n"/>
-      <c r="K26" s="41" t="n"/>
-      <c r="L26" s="41" t="n"/>
-      <c r="M26" s="42" t="n"/>
+      <c r="K26" s="38" t="n"/>
+      <c r="L26" s="38" t="n"/>
+      <c r="M26" s="37" t="n"/>
       <c r="N26" s="31" t="n"/>
-      <c r="O26" s="41" t="n"/>
-      <c r="P26" s="41" t="n"/>
-      <c r="Q26" s="42" t="n"/>
+      <c r="O26" s="38" t="n"/>
+      <c r="P26" s="38" t="n"/>
+      <c r="Q26" s="37" t="n"/>
       <c r="R26" s="31" t="n"/>
-      <c r="S26" s="41" t="n"/>
-      <c r="T26" s="41" t="n"/>
-      <c r="U26" s="42" t="n"/>
+      <c r="S26" s="38" t="n"/>
+      <c r="T26" s="38" t="n"/>
+      <c r="U26" s="37" t="n"/>
       <c r="V26" s="31" t="n"/>
-      <c r="W26" s="41" t="n"/>
-      <c r="X26" s="41" t="n"/>
-      <c r="Y26" s="42" t="n"/>
+      <c r="W26" s="38" t="n"/>
+      <c r="X26" s="38" t="n"/>
+      <c r="Y26" s="37" t="n"/>
       <c r="Z26" s="31" t="n"/>
-      <c r="AA26" s="41" t="n"/>
-      <c r="AB26" s="41" t="n"/>
-      <c r="AC26" s="42" t="n"/>
+      <c r="AA26" s="38" t="n"/>
+      <c r="AB26" s="38" t="n"/>
+      <c r="AC26" s="37" t="n"/>
       <c r="AD26" s="31" t="n"/>
-      <c r="AE26" s="41" t="n"/>
-      <c r="AF26" s="41" t="n"/>
-      <c r="AG26" s="42" t="n"/>
+      <c r="AE26" s="38" t="n"/>
+      <c r="AF26" s="38" t="n"/>
+      <c r="AG26" s="37" t="n"/>
       <c r="AH26" s="31" t="n"/>
-      <c r="AI26" s="41" t="n"/>
-      <c r="AJ26" s="41" t="n"/>
-      <c r="AK26" s="42" t="n"/>
-      <c r="AL26" s="70" t="n"/>
-      <c r="AM26" s="71" t="n"/>
-      <c r="AN26" s="71" t="n"/>
-      <c r="AO26" s="71" t="n"/>
-      <c r="AP26" s="71" t="n"/>
-      <c r="AQ26" s="71" t="n"/>
-      <c r="AR26" s="71" t="n"/>
-      <c r="AS26" s="71" t="n"/>
-      <c r="AT26" s="71" t="n"/>
-      <c r="AU26" s="71" t="n"/>
-      <c r="AV26" s="71" t="n"/>
-      <c r="AW26" s="71" t="n"/>
-      <c r="AX26" s="71" t="n"/>
-      <c r="AY26" s="71" t="n"/>
-      <c r="AZ26" s="71" t="n"/>
-      <c r="BA26" s="71" t="n"/>
-      <c r="BB26" s="71" t="n"/>
-      <c r="BC26" s="71" t="n"/>
-      <c r="BD26" s="71" t="n"/>
-      <c r="BE26" s="72" t="n"/>
+      <c r="AI26" s="38" t="n"/>
+      <c r="AJ26" s="38" t="n"/>
+      <c r="AK26" s="37" t="n"/>
+      <c r="AL26" s="31" t="n"/>
+      <c r="AM26" s="38" t="n"/>
+      <c r="AN26" s="38" t="n"/>
+      <c r="AO26" s="37" t="n"/>
+      <c r="AP26" s="31" t="n"/>
+      <c r="AQ26" s="38" t="n"/>
+      <c r="AR26" s="38" t="n"/>
+      <c r="AS26" s="37" t="n"/>
+      <c r="AT26" s="31" t="n"/>
+      <c r="AU26" s="38" t="n"/>
+      <c r="AV26" s="38" t="n"/>
+      <c r="AW26" s="37" t="n"/>
+      <c r="AX26" s="31" t="n"/>
+      <c r="AY26" s="38" t="n"/>
+      <c r="AZ26" s="38" t="n"/>
+      <c r="BA26" s="37" t="n"/>
+      <c r="BB26" s="31" t="n"/>
+      <c r="BC26" s="38" t="n"/>
+      <c r="BD26" s="38" t="n"/>
+      <c r="BE26" s="37" t="n"/>
       <c r="BF26" s="31" t="n"/>
-      <c r="BG26" s="41" t="n"/>
-      <c r="BH26" s="41" t="n"/>
-      <c r="BI26" s="42" t="n"/>
+      <c r="BG26" s="38" t="n"/>
+      <c r="BH26" s="38" t="n"/>
+      <c r="BI26" s="37" t="n"/>
       <c r="BJ26" s="31" t="n"/>
-      <c r="BK26" s="41" t="n"/>
-      <c r="BL26" s="41" t="n"/>
-      <c r="BM26" s="42" t="n"/>
+      <c r="BK26" s="38" t="n"/>
+      <c r="BL26" s="38" t="n"/>
+      <c r="BM26" s="37" t="n"/>
       <c r="BN26" s="31" t="n"/>
-      <c r="BO26" s="41" t="n"/>
-      <c r="BP26" s="41" t="n"/>
-      <c r="BQ26" s="42" t="n"/>
+      <c r="BO26" s="38" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="37" t="n"/>
       <c r="BR26" s="31" t="n"/>
-      <c r="BS26" s="41" t="n"/>
-      <c r="BT26" s="41" t="n"/>
-      <c r="BU26" s="42" t="n"/>
+      <c r="BS26" s="38" t="n"/>
+      <c r="BT26" s="38" t="n"/>
+      <c r="BU26" s="37" t="n"/>
       <c r="BV26" s="31" t="n"/>
-      <c r="BW26" s="41" t="n"/>
-      <c r="BX26" s="41" t="n"/>
-      <c r="BY26" s="42" t="n"/>
+      <c r="BW26" s="38" t="n"/>
+      <c r="BX26" s="38" t="n"/>
+      <c r="BY26" s="37" t="n"/>
       <c r="BZ26" s="31" t="n"/>
-      <c r="CA26" s="41" t="n"/>
-      <c r="CB26" s="41" t="n"/>
-      <c r="CC26" s="42" t="n"/>
+      <c r="CA26" s="38" t="n"/>
+      <c r="CB26" s="38" t="n"/>
+      <c r="CC26" s="37" t="n"/>
       <c r="CD26" s="31" t="n"/>
-      <c r="CE26" s="41" t="n"/>
-      <c r="CF26" s="41" t="n"/>
-      <c r="CG26" s="54" t="n"/>
+      <c r="CE26" s="38" t="n"/>
+      <c r="CF26" s="38" t="n"/>
+      <c r="CG26" s="48" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="29" t="inlineStr"/>
@@ -4425,172 +4033,172 @@
       <c r="D27" s="30" t="n"/>
       <c r="E27" s="30" t="n"/>
       <c r="F27" s="31" t="n"/>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="42" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="37" t="n"/>
       <c r="J27" s="31" t="n"/>
-      <c r="K27" s="41" t="n"/>
-      <c r="L27" s="41" t="n"/>
-      <c r="M27" s="42" t="n"/>
+      <c r="K27" s="38" t="n"/>
+      <c r="L27" s="38" t="n"/>
+      <c r="M27" s="37" t="n"/>
       <c r="N27" s="31" t="n"/>
-      <c r="O27" s="41" t="n"/>
-      <c r="P27" s="41" t="n"/>
-      <c r="Q27" s="42" t="n"/>
+      <c r="O27" s="38" t="n"/>
+      <c r="P27" s="38" t="n"/>
+      <c r="Q27" s="37" t="n"/>
       <c r="R27" s="31" t="n"/>
-      <c r="S27" s="41" t="n"/>
-      <c r="T27" s="41" t="n"/>
-      <c r="U27" s="42" t="n"/>
+      <c r="S27" s="38" t="n"/>
+      <c r="T27" s="38" t="n"/>
+      <c r="U27" s="37" t="n"/>
       <c r="V27" s="31" t="n"/>
-      <c r="W27" s="41" t="n"/>
-      <c r="X27" s="41" t="n"/>
-      <c r="Y27" s="42" t="n"/>
+      <c r="W27" s="38" t="n"/>
+      <c r="X27" s="38" t="n"/>
+      <c r="Y27" s="37" t="n"/>
       <c r="Z27" s="31" t="n"/>
-      <c r="AA27" s="41" t="n"/>
-      <c r="AB27" s="41" t="n"/>
-      <c r="AC27" s="42" t="n"/>
+      <c r="AA27" s="38" t="n"/>
+      <c r="AB27" s="38" t="n"/>
+      <c r="AC27" s="37" t="n"/>
       <c r="AD27" s="31" t="n"/>
-      <c r="AE27" s="41" t="n"/>
-      <c r="AF27" s="41" t="n"/>
-      <c r="AG27" s="42" t="n"/>
+      <c r="AE27" s="38" t="n"/>
+      <c r="AF27" s="38" t="n"/>
+      <c r="AG27" s="37" t="n"/>
       <c r="AH27" s="31" t="n"/>
-      <c r="AI27" s="41" t="n"/>
-      <c r="AJ27" s="41" t="n"/>
-      <c r="AK27" s="42" t="n"/>
+      <c r="AI27" s="38" t="n"/>
+      <c r="AJ27" s="38" t="n"/>
+      <c r="AK27" s="37" t="n"/>
       <c r="AL27" s="31" t="n"/>
-      <c r="AM27" s="41" t="n"/>
-      <c r="AN27" s="41" t="n"/>
-      <c r="AO27" s="42" t="n"/>
+      <c r="AM27" s="38" t="n"/>
+      <c r="AN27" s="38" t="n"/>
+      <c r="AO27" s="37" t="n"/>
       <c r="AP27" s="31" t="n"/>
-      <c r="AQ27" s="41" t="n"/>
-      <c r="AR27" s="41" t="n"/>
-      <c r="AS27" s="42" t="n"/>
+      <c r="AQ27" s="38" t="n"/>
+      <c r="AR27" s="38" t="n"/>
+      <c r="AS27" s="37" t="n"/>
       <c r="AT27" s="31" t="n"/>
-      <c r="AU27" s="41" t="n"/>
-      <c r="AV27" s="41" t="n"/>
-      <c r="AW27" s="42" t="n"/>
+      <c r="AU27" s="38" t="n"/>
+      <c r="AV27" s="38" t="n"/>
+      <c r="AW27" s="37" t="n"/>
       <c r="AX27" s="31" t="n"/>
-      <c r="AY27" s="41" t="n"/>
-      <c r="AZ27" s="41" t="n"/>
-      <c r="BA27" s="42" t="n"/>
+      <c r="AY27" s="38" t="n"/>
+      <c r="AZ27" s="38" t="n"/>
+      <c r="BA27" s="37" t="n"/>
       <c r="BB27" s="31" t="n"/>
-      <c r="BC27" s="41" t="n"/>
-      <c r="BD27" s="41" t="n"/>
-      <c r="BE27" s="42" t="n"/>
+      <c r="BC27" s="38" t="n"/>
+      <c r="BD27" s="38" t="n"/>
+      <c r="BE27" s="37" t="n"/>
       <c r="BF27" s="31" t="n"/>
-      <c r="BG27" s="41" t="n"/>
-      <c r="BH27" s="41" t="n"/>
-      <c r="BI27" s="42" t="n"/>
+      <c r="BG27" s="38" t="n"/>
+      <c r="BH27" s="38" t="n"/>
+      <c r="BI27" s="37" t="n"/>
       <c r="BJ27" s="31" t="n"/>
-      <c r="BK27" s="41" t="n"/>
-      <c r="BL27" s="41" t="n"/>
-      <c r="BM27" s="42" t="n"/>
+      <c r="BK27" s="38" t="n"/>
+      <c r="BL27" s="38" t="n"/>
+      <c r="BM27" s="37" t="n"/>
       <c r="BN27" s="31" t="n"/>
-      <c r="BO27" s="41" t="n"/>
-      <c r="BP27" s="41" t="n"/>
-      <c r="BQ27" s="42" t="n"/>
+      <c r="BO27" s="38" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="37" t="n"/>
       <c r="BR27" s="31" t="n"/>
-      <c r="BS27" s="41" t="n"/>
-      <c r="BT27" s="41" t="n"/>
-      <c r="BU27" s="42" t="n"/>
+      <c r="BS27" s="38" t="n"/>
+      <c r="BT27" s="38" t="n"/>
+      <c r="BU27" s="37" t="n"/>
       <c r="BV27" s="31" t="n"/>
-      <c r="BW27" s="41" t="n"/>
-      <c r="BX27" s="41" t="n"/>
-      <c r="BY27" s="42" t="n"/>
+      <c r="BW27" s="38" t="n"/>
+      <c r="BX27" s="38" t="n"/>
+      <c r="BY27" s="37" t="n"/>
       <c r="BZ27" s="31" t="n"/>
-      <c r="CA27" s="41" t="n"/>
-      <c r="CB27" s="41" t="n"/>
-      <c r="CC27" s="42" t="n"/>
+      <c r="CA27" s="38" t="n"/>
+      <c r="CB27" s="38" t="n"/>
+      <c r="CC27" s="37" t="n"/>
       <c r="CD27" s="31" t="n"/>
-      <c r="CE27" s="41" t="n"/>
-      <c r="CF27" s="41" t="n"/>
-      <c r="CG27" s="54" t="n"/>
+      <c r="CE27" s="38" t="n"/>
+      <c r="CF27" s="38" t="n"/>
+      <c r="CG27" s="48" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="73" t="inlineStr"/>
-      <c r="B28" s="74" t="n"/>
-      <c r="C28" s="74" t="n"/>
-      <c r="D28" s="74" t="n"/>
-      <c r="E28" s="74" t="n"/>
-      <c r="F28" s="75" t="n"/>
-      <c r="G28" s="76" t="n"/>
-      <c r="H28" s="76" t="n"/>
-      <c r="I28" s="77" t="n"/>
-      <c r="J28" s="75" t="n"/>
-      <c r="K28" s="76" t="n"/>
-      <c r="L28" s="76" t="n"/>
-      <c r="M28" s="77" t="n"/>
-      <c r="N28" s="75" t="n"/>
-      <c r="O28" s="76" t="n"/>
-      <c r="P28" s="76" t="n"/>
-      <c r="Q28" s="77" t="n"/>
-      <c r="R28" s="75" t="n"/>
-      <c r="S28" s="76" t="n"/>
-      <c r="T28" s="76" t="n"/>
-      <c r="U28" s="77" t="n"/>
-      <c r="V28" s="75" t="n"/>
-      <c r="W28" s="76" t="n"/>
-      <c r="X28" s="76" t="n"/>
-      <c r="Y28" s="77" t="n"/>
-      <c r="Z28" s="75" t="n"/>
-      <c r="AA28" s="76" t="n"/>
-      <c r="AB28" s="76" t="n"/>
-      <c r="AC28" s="77" t="n"/>
-      <c r="AD28" s="75" t="n"/>
-      <c r="AE28" s="76" t="n"/>
-      <c r="AF28" s="76" t="n"/>
-      <c r="AG28" s="77" t="n"/>
-      <c r="AH28" s="75" t="n"/>
-      <c r="AI28" s="76" t="n"/>
-      <c r="AJ28" s="76" t="n"/>
-      <c r="AK28" s="77" t="n"/>
-      <c r="AL28" s="75" t="n"/>
-      <c r="AM28" s="76" t="n"/>
-      <c r="AN28" s="76" t="n"/>
-      <c r="AO28" s="77" t="n"/>
-      <c r="AP28" s="75" t="n"/>
-      <c r="AQ28" s="76" t="n"/>
-      <c r="AR28" s="76" t="n"/>
-      <c r="AS28" s="77" t="n"/>
-      <c r="AT28" s="75" t="n"/>
-      <c r="AU28" s="76" t="n"/>
-      <c r="AV28" s="76" t="n"/>
-      <c r="AW28" s="77" t="n"/>
-      <c r="AX28" s="75" t="n"/>
-      <c r="AY28" s="76" t="n"/>
-      <c r="AZ28" s="76" t="n"/>
-      <c r="BA28" s="77" t="n"/>
-      <c r="BB28" s="75" t="n"/>
-      <c r="BC28" s="76" t="n"/>
-      <c r="BD28" s="76" t="n"/>
-      <c r="BE28" s="77" t="n"/>
-      <c r="BF28" s="75" t="n"/>
-      <c r="BG28" s="76" t="n"/>
-      <c r="BH28" s="76" t="n"/>
-      <c r="BI28" s="77" t="n"/>
-      <c r="BJ28" s="75" t="n"/>
-      <c r="BK28" s="76" t="n"/>
-      <c r="BL28" s="76" t="n"/>
-      <c r="BM28" s="77" t="n"/>
-      <c r="BN28" s="75" t="n"/>
-      <c r="BO28" s="76" t="n"/>
-      <c r="BP28" s="76" t="n"/>
-      <c r="BQ28" s="77" t="n"/>
-      <c r="BR28" s="75" t="n"/>
-      <c r="BS28" s="76" t="n"/>
-      <c r="BT28" s="76" t="n"/>
-      <c r="BU28" s="77" t="n"/>
-      <c r="BV28" s="75" t="n"/>
-      <c r="BW28" s="76" t="n"/>
-      <c r="BX28" s="76" t="n"/>
-      <c r="BY28" s="77" t="n"/>
-      <c r="BZ28" s="75" t="n"/>
-      <c r="CA28" s="76" t="n"/>
-      <c r="CB28" s="76" t="n"/>
-      <c r="CC28" s="77" t="n"/>
-      <c r="CD28" s="75" t="n"/>
-      <c r="CE28" s="76" t="n"/>
-      <c r="CF28" s="76" t="n"/>
-      <c r="CG28" s="78" t="n"/>
+      <c r="A28" s="50" t="inlineStr"/>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+      <c r="E28" s="51" t="n"/>
+      <c r="F28" s="52" t="n"/>
+      <c r="G28" s="53" t="n"/>
+      <c r="H28" s="53" t="n"/>
+      <c r="I28" s="54" t="n"/>
+      <c r="J28" s="52" t="n"/>
+      <c r="K28" s="53" t="n"/>
+      <c r="L28" s="53" t="n"/>
+      <c r="M28" s="54" t="n"/>
+      <c r="N28" s="52" t="n"/>
+      <c r="O28" s="53" t="n"/>
+      <c r="P28" s="53" t="n"/>
+      <c r="Q28" s="54" t="n"/>
+      <c r="R28" s="52" t="n"/>
+      <c r="S28" s="53" t="n"/>
+      <c r="T28" s="53" t="n"/>
+      <c r="U28" s="54" t="n"/>
+      <c r="V28" s="52" t="n"/>
+      <c r="W28" s="53" t="n"/>
+      <c r="X28" s="53" t="n"/>
+      <c r="Y28" s="54" t="n"/>
+      <c r="Z28" s="52" t="n"/>
+      <c r="AA28" s="53" t="n"/>
+      <c r="AB28" s="53" t="n"/>
+      <c r="AC28" s="54" t="n"/>
+      <c r="AD28" s="52" t="n"/>
+      <c r="AE28" s="53" t="n"/>
+      <c r="AF28" s="53" t="n"/>
+      <c r="AG28" s="54" t="n"/>
+      <c r="AH28" s="52" t="n"/>
+      <c r="AI28" s="53" t="n"/>
+      <c r="AJ28" s="53" t="n"/>
+      <c r="AK28" s="54" t="n"/>
+      <c r="AL28" s="52" t="n"/>
+      <c r="AM28" s="53" t="n"/>
+      <c r="AN28" s="53" t="n"/>
+      <c r="AO28" s="54" t="n"/>
+      <c r="AP28" s="52" t="n"/>
+      <c r="AQ28" s="53" t="n"/>
+      <c r="AR28" s="53" t="n"/>
+      <c r="AS28" s="54" t="n"/>
+      <c r="AT28" s="52" t="n"/>
+      <c r="AU28" s="53" t="n"/>
+      <c r="AV28" s="53" t="n"/>
+      <c r="AW28" s="54" t="n"/>
+      <c r="AX28" s="52" t="n"/>
+      <c r="AY28" s="53" t="n"/>
+      <c r="AZ28" s="53" t="n"/>
+      <c r="BA28" s="54" t="n"/>
+      <c r="BB28" s="52" t="n"/>
+      <c r="BC28" s="53" t="n"/>
+      <c r="BD28" s="53" t="n"/>
+      <c r="BE28" s="54" t="n"/>
+      <c r="BF28" s="52" t="n"/>
+      <c r="BG28" s="53" t="n"/>
+      <c r="BH28" s="53" t="n"/>
+      <c r="BI28" s="54" t="n"/>
+      <c r="BJ28" s="52" t="n"/>
+      <c r="BK28" s="53" t="n"/>
+      <c r="BL28" s="53" t="n"/>
+      <c r="BM28" s="54" t="n"/>
+      <c r="BN28" s="52" t="n"/>
+      <c r="BO28" s="53" t="n"/>
+      <c r="BP28" s="53" t="n"/>
+      <c r="BQ28" s="54" t="n"/>
+      <c r="BR28" s="52" t="n"/>
+      <c r="BS28" s="53" t="n"/>
+      <c r="BT28" s="53" t="n"/>
+      <c r="BU28" s="54" t="n"/>
+      <c r="BV28" s="52" t="n"/>
+      <c r="BW28" s="53" t="n"/>
+      <c r="BX28" s="53" t="n"/>
+      <c r="BY28" s="54" t="n"/>
+      <c r="BZ28" s="52" t="n"/>
+      <c r="CA28" s="53" t="n"/>
+      <c r="CB28" s="53" t="n"/>
+      <c r="CC28" s="54" t="n"/>
+      <c r="CD28" s="52" t="n"/>
+      <c r="CE28" s="53" t="n"/>
+      <c r="CF28" s="53" t="n"/>
+      <c r="CG28" s="55" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -4760,111 +4368,91 @@
       <c r="CG30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="79" t="inlineStr">
-        <is>
-          <t>Duty No.</t>
-        </is>
-      </c>
-      <c r="B31" s="80" t="inlineStr">
-        <is>
-          <t>Start Time</t>
-        </is>
-      </c>
-      <c r="C31" s="80" t="inlineStr">
-        <is>
-          <t>Finish Time</t>
-        </is>
-      </c>
-      <c r="D31" s="80" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E31" s="80" t="inlineStr">
-        <is>
-          <t>Radio</t>
-        </is>
-      </c>
-      <c r="F31" s="81" t="n"/>
-      <c r="G31" s="82" t="n"/>
-      <c r="H31" s="82" t="n"/>
-      <c r="I31" s="83" t="n"/>
-      <c r="J31" s="81" t="n"/>
-      <c r="K31" s="82" t="n"/>
-      <c r="L31" s="82" t="n"/>
-      <c r="M31" s="83" t="n"/>
-      <c r="N31" s="81" t="n"/>
-      <c r="O31" s="82" t="n"/>
-      <c r="P31" s="82" t="n"/>
-      <c r="Q31" s="83" t="n"/>
-      <c r="R31" s="81" t="n"/>
-      <c r="S31" s="82" t="n"/>
-      <c r="T31" s="82" t="n"/>
-      <c r="U31" s="83" t="n"/>
-      <c r="V31" s="81" t="n"/>
-      <c r="W31" s="82" t="n"/>
-      <c r="X31" s="82" t="n"/>
-      <c r="Y31" s="83" t="n"/>
-      <c r="Z31" s="81" t="n"/>
-      <c r="AA31" s="82" t="n"/>
-      <c r="AB31" s="82" t="n"/>
-      <c r="AC31" s="83" t="n"/>
-      <c r="AD31" s="81" t="n"/>
-      <c r="AE31" s="82" t="n"/>
-      <c r="AF31" s="82" t="n"/>
-      <c r="AG31" s="83" t="n"/>
-      <c r="AH31" s="81" t="n"/>
-      <c r="AI31" s="82" t="n"/>
-      <c r="AJ31" s="82" t="n"/>
-      <c r="AK31" s="83" t="n"/>
-      <c r="AL31" s="81" t="n"/>
-      <c r="AM31" s="82" t="n"/>
-      <c r="AN31" s="82" t="n"/>
-      <c r="AO31" s="83" t="n"/>
-      <c r="AP31" s="81" t="n"/>
-      <c r="AQ31" s="82" t="n"/>
-      <c r="AR31" s="82" t="n"/>
-      <c r="AS31" s="83" t="n"/>
-      <c r="AT31" s="81" t="n"/>
-      <c r="AU31" s="82" t="n"/>
-      <c r="AV31" s="82" t="n"/>
-      <c r="AW31" s="83" t="n"/>
-      <c r="AX31" s="81" t="n"/>
-      <c r="AY31" s="82" t="n"/>
-      <c r="AZ31" s="82" t="n"/>
-      <c r="BA31" s="83" t="n"/>
-      <c r="BB31" s="81" t="n"/>
-      <c r="BC31" s="82" t="n"/>
-      <c r="BD31" s="82" t="n"/>
-      <c r="BE31" s="83" t="n"/>
-      <c r="BF31" s="81" t="n"/>
-      <c r="BG31" s="82" t="n"/>
-      <c r="BH31" s="82" t="n"/>
-      <c r="BI31" s="83" t="n"/>
-      <c r="BJ31" s="81" t="n"/>
-      <c r="BK31" s="82" t="n"/>
-      <c r="BL31" s="82" t="n"/>
-      <c r="BM31" s="83" t="n"/>
-      <c r="BN31" s="81" t="n"/>
-      <c r="BO31" s="82" t="n"/>
-      <c r="BP31" s="82" t="n"/>
-      <c r="BQ31" s="83" t="n"/>
-      <c r="BR31" s="81" t="n"/>
-      <c r="BS31" s="82" t="n"/>
-      <c r="BT31" s="82" t="n"/>
-      <c r="BU31" s="83" t="n"/>
-      <c r="BV31" s="81" t="n"/>
-      <c r="BW31" s="82" t="n"/>
-      <c r="BX31" s="82" t="n"/>
-      <c r="BY31" s="83" t="n"/>
-      <c r="BZ31" s="81" t="n"/>
-      <c r="CA31" s="82" t="n"/>
-      <c r="CB31" s="82" t="n"/>
-      <c r="CC31" s="83" t="n"/>
-      <c r="CD31" s="81" t="n"/>
-      <c r="CE31" s="82" t="n"/>
-      <c r="CF31" s="82" t="n"/>
-      <c r="CG31" s="84" t="n"/>
+      <c r="A31" s="56" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="10" t="n"/>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="n"/>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="10" t="n"/>
+      <c r="Y31" s="10" t="n"/>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="10" t="n"/>
+      <c r="AC31" s="10" t="n"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="10" t="n"/>
+      <c r="AF31" s="10" t="n"/>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="10" t="n"/>
+      <c r="AL31" s="10" t="n"/>
+      <c r="AM31" s="10" t="n"/>
+      <c r="AN31" s="10" t="n"/>
+      <c r="AO31" s="10" t="n"/>
+      <c r="AP31" s="10" t="n"/>
+      <c r="AQ31" s="10" t="n"/>
+      <c r="AR31" s="10" t="n"/>
+      <c r="AS31" s="10" t="n"/>
+      <c r="AT31" s="10" t="n"/>
+      <c r="AU31" s="10" t="n"/>
+      <c r="AV31" s="10" t="n"/>
+      <c r="AW31" s="10" t="n"/>
+      <c r="AX31" s="10" t="n"/>
+      <c r="AY31" s="10" t="n"/>
+      <c r="AZ31" s="10" t="n"/>
+      <c r="BA31" s="10" t="n"/>
+      <c r="BB31" s="10" t="n"/>
+      <c r="BC31" s="10" t="n"/>
+      <c r="BD31" s="10" t="n"/>
+      <c r="BE31" s="10" t="n"/>
+      <c r="BF31" s="10" t="n"/>
+      <c r="BG31" s="10" t="n"/>
+      <c r="BH31" s="10" t="n"/>
+      <c r="BI31" s="10" t="n"/>
+      <c r="BJ31" s="10" t="n"/>
+      <c r="BK31" s="10" t="n"/>
+      <c r="BL31" s="10" t="n"/>
+      <c r="BM31" s="10" t="n"/>
+      <c r="BN31" s="10" t="n"/>
+      <c r="BO31" s="10" t="n"/>
+      <c r="BP31" s="10" t="n"/>
+      <c r="BQ31" s="10" t="n"/>
+      <c r="BR31" s="10" t="n"/>
+      <c r="BS31" s="10" t="n"/>
+      <c r="BT31" s="10" t="n"/>
+      <c r="BU31" s="10" t="n"/>
+      <c r="BV31" s="10" t="n"/>
+      <c r="BW31" s="10" t="n"/>
+      <c r="BX31" s="10" t="n"/>
+      <c r="BY31" s="10" t="n"/>
+      <c r="BZ31" s="10" t="n"/>
+      <c r="CA31" s="10" t="n"/>
+      <c r="CB31" s="10" t="n"/>
+      <c r="CC31" s="10" t="n"/>
+      <c r="CD31" s="10" t="n"/>
+      <c r="CE31" s="10" t="n"/>
+      <c r="CF31" s="10" t="n"/>
+      <c r="CG31" s="12" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
@@ -4884,7 +4472,7 @@
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
-          <t>Bar-On,E</t>
+          <t>Bar-On</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
@@ -4893,101 +4481,89 @@
         </is>
       </c>
       <c r="F32" s="31" t="n"/>
-      <c r="G32" s="85" t="n"/>
+      <c r="G32" s="57" t="n"/>
       <c r="H32" s="33" t="n"/>
       <c r="I32" s="34" t="n"/>
-      <c r="J32" s="86" t="n"/>
+      <c r="J32" s="58" t="n"/>
       <c r="K32" s="33" t="n"/>
       <c r="L32" s="33" t="n"/>
       <c r="M32" s="34" t="n"/>
-      <c r="N32" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="N32" s="58" t="n"/>
       <c r="O32" s="33" t="n"/>
       <c r="P32" s="33" t="n"/>
       <c r="Q32" s="34" t="n"/>
-      <c r="R32" s="86" t="n"/>
+      <c r="R32" s="58" t="n"/>
       <c r="S32" s="33" t="n"/>
       <c r="T32" s="33" t="n"/>
       <c r="U32" s="34" t="n"/>
-      <c r="V32" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="V32" s="58" t="n"/>
       <c r="W32" s="33" t="n"/>
-      <c r="X32" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="X32" s="33" t="n"/>
       <c r="Y32" s="34" t="n"/>
-      <c r="Z32" s="86" t="n"/>
+      <c r="Z32" s="58" t="n"/>
       <c r="AA32" s="33" t="n"/>
       <c r="AB32" s="33" t="n"/>
       <c r="AC32" s="34" t="n"/>
-      <c r="AD32" s="86" t="n"/>
+      <c r="AD32" s="58" t="n"/>
       <c r="AE32" s="33" t="n"/>
       <c r="AF32" s="33" t="n"/>
       <c r="AG32" s="34" t="n"/>
-      <c r="AH32" s="87" t="n"/>
+      <c r="AH32" s="59" t="n"/>
       <c r="AI32" s="33" t="n"/>
-      <c r="AJ32" s="41" t="n"/>
-      <c r="AK32" s="42" t="n"/>
+      <c r="AJ32" s="33" t="n"/>
+      <c r="AK32" s="37" t="n"/>
       <c r="AL32" s="31" t="n"/>
-      <c r="AM32" s="41" t="n"/>
-      <c r="AN32" s="41" t="n"/>
-      <c r="AO32" s="42" t="n"/>
+      <c r="AM32" s="38" t="n"/>
+      <c r="AN32" s="38" t="n"/>
+      <c r="AO32" s="37" t="n"/>
       <c r="AP32" s="31" t="n"/>
-      <c r="AQ32" s="41" t="n"/>
-      <c r="AR32" s="41" t="n"/>
-      <c r="AS32" s="42" t="n"/>
+      <c r="AQ32" s="38" t="n"/>
+      <c r="AR32" s="38" t="n"/>
+      <c r="AS32" s="37" t="n"/>
       <c r="AT32" s="31" t="n"/>
-      <c r="AU32" s="41" t="n"/>
-      <c r="AV32" s="41" t="n"/>
-      <c r="AW32" s="42" t="n"/>
+      <c r="AU32" s="38" t="n"/>
+      <c r="AV32" s="38" t="n"/>
+      <c r="AW32" s="37" t="n"/>
       <c r="AX32" s="31" t="n"/>
-      <c r="AY32" s="41" t="n"/>
-      <c r="AZ32" s="41" t="n"/>
-      <c r="BA32" s="42" t="n"/>
+      <c r="AY32" s="38" t="n"/>
+      <c r="AZ32" s="38" t="n"/>
+      <c r="BA32" s="37" t="n"/>
       <c r="BB32" s="31" t="n"/>
-      <c r="BC32" s="41" t="n"/>
-      <c r="BD32" s="41" t="n"/>
-      <c r="BE32" s="42" t="n"/>
+      <c r="BC32" s="38" t="n"/>
+      <c r="BD32" s="38" t="n"/>
+      <c r="BE32" s="37" t="n"/>
       <c r="BF32" s="31" t="n"/>
-      <c r="BG32" s="41" t="n"/>
-      <c r="BH32" s="41" t="n"/>
-      <c r="BI32" s="42" t="n"/>
-      <c r="BJ32" s="88" t="inlineStr">
+      <c r="BG32" s="38" t="n"/>
+      <c r="BH32" s="38" t="n"/>
+      <c r="BI32" s="37" t="n"/>
+      <c r="BJ32" s="60" t="inlineStr">
         <is>
           <t>DISTRICT</t>
         </is>
       </c>
-      <c r="BK32" s="89" t="n"/>
-      <c r="BL32" s="89" t="n"/>
-      <c r="BM32" s="89" t="n"/>
-      <c r="BN32" s="89" t="n"/>
-      <c r="BO32" s="89" t="n"/>
-      <c r="BP32" s="89" t="n"/>
-      <c r="BQ32" s="89" t="n"/>
-      <c r="BR32" s="89" t="n"/>
-      <c r="BS32" s="89" t="n"/>
-      <c r="BT32" s="89" t="n"/>
-      <c r="BU32" s="89" t="n"/>
-      <c r="BV32" s="89" t="n"/>
-      <c r="BW32" s="89" t="n"/>
-      <c r="BX32" s="89" t="n"/>
-      <c r="BY32" s="89" t="n"/>
-      <c r="BZ32" s="89" t="n"/>
-      <c r="CA32" s="89" t="n"/>
-      <c r="CB32" s="89" t="n"/>
-      <c r="CC32" s="89" t="n"/>
-      <c r="CD32" s="89" t="n"/>
-      <c r="CE32" s="89" t="n"/>
-      <c r="CF32" s="89" t="n"/>
-      <c r="CG32" s="90" t="n"/>
+      <c r="BK32" s="61" t="n"/>
+      <c r="BL32" s="61" t="n"/>
+      <c r="BM32" s="61" t="n"/>
+      <c r="BN32" s="61" t="n"/>
+      <c r="BO32" s="61" t="n"/>
+      <c r="BP32" s="61" t="n"/>
+      <c r="BQ32" s="61" t="n"/>
+      <c r="BR32" s="61" t="n"/>
+      <c r="BS32" s="61" t="n"/>
+      <c r="BT32" s="61" t="n"/>
+      <c r="BU32" s="61" t="n"/>
+      <c r="BV32" s="61" t="n"/>
+      <c r="BW32" s="61" t="n"/>
+      <c r="BX32" s="61" t="n"/>
+      <c r="BY32" s="61" t="n"/>
+      <c r="BZ32" s="61" t="n"/>
+      <c r="CA32" s="61" t="n"/>
+      <c r="CB32" s="61" t="n"/>
+      <c r="CC32" s="61" t="n"/>
+      <c r="CD32" s="61" t="n"/>
+      <c r="CE32" s="61" t="n"/>
+      <c r="CF32" s="61" t="n"/>
+      <c r="CG32" s="62" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="29" t="inlineStr">
@@ -5007,7 +4583,7 @@
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
-          <t>Yousaf,N</t>
+          <t>Yousaf</t>
         </is>
       </c>
       <c r="E33" s="30" t="inlineStr">
@@ -5016,101 +4592,85 @@
         </is>
       </c>
       <c r="F33" s="31" t="n"/>
-      <c r="G33" s="91" t="n"/>
+      <c r="G33" s="63" t="n"/>
       <c r="H33" s="33" t="n"/>
       <c r="I33" s="34" t="n"/>
-      <c r="J33" s="92" t="n"/>
+      <c r="J33" s="64" t="n"/>
       <c r="K33" s="33" t="n"/>
       <c r="L33" s="33" t="n"/>
       <c r="M33" s="34" t="n"/>
-      <c r="N33" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="N33" s="64" t="n"/>
       <c r="O33" s="33" t="n"/>
       <c r="P33" s="33" t="n"/>
       <c r="Q33" s="34" t="n"/>
-      <c r="R33" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="R33" s="64" t="n"/>
       <c r="S33" s="33" t="n"/>
       <c r="T33" s="33" t="n"/>
       <c r="U33" s="34" t="n"/>
-      <c r="V33" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="V33" s="64" t="n"/>
       <c r="W33" s="33" t="n"/>
-      <c r="X33" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="X33" s="33" t="n"/>
       <c r="Y33" s="34" t="n"/>
-      <c r="Z33" s="92" t="n"/>
+      <c r="Z33" s="64" t="n"/>
       <c r="AA33" s="33" t="n"/>
       <c r="AB33" s="33" t="n"/>
       <c r="AC33" s="34" t="n"/>
-      <c r="AD33" s="92" t="n"/>
+      <c r="AD33" s="64" t="n"/>
       <c r="AE33" s="33" t="n"/>
       <c r="AF33" s="33" t="n"/>
       <c r="AG33" s="34" t="n"/>
-      <c r="AH33" s="92" t="n"/>
+      <c r="AH33" s="64" t="n"/>
       <c r="AI33" s="33" t="n"/>
       <c r="AJ33" s="33" t="n"/>
       <c r="AK33" s="34" t="n"/>
-      <c r="AL33" s="31" t="n"/>
-      <c r="AM33" s="41" t="n"/>
-      <c r="AN33" s="41" t="n"/>
-      <c r="AO33" s="42" t="n"/>
+      <c r="AL33" s="65" t="n"/>
+      <c r="AM33" s="38" t="n"/>
+      <c r="AN33" s="38" t="n"/>
+      <c r="AO33" s="37" t="n"/>
       <c r="AP33" s="31" t="n"/>
-      <c r="AQ33" s="41" t="n"/>
-      <c r="AR33" s="41" t="n"/>
-      <c r="AS33" s="42" t="n"/>
+      <c r="AQ33" s="38" t="n"/>
+      <c r="AR33" s="38" t="n"/>
+      <c r="AS33" s="37" t="n"/>
       <c r="AT33" s="31" t="n"/>
-      <c r="AU33" s="41" t="n"/>
-      <c r="AV33" s="41" t="n"/>
-      <c r="AW33" s="42" t="n"/>
+      <c r="AU33" s="38" t="n"/>
+      <c r="AV33" s="38" t="n"/>
+      <c r="AW33" s="37" t="n"/>
       <c r="AX33" s="31" t="n"/>
-      <c r="AY33" s="41" t="n"/>
-      <c r="AZ33" s="41" t="n"/>
-      <c r="BA33" s="42" t="n"/>
+      <c r="AY33" s="38" t="n"/>
+      <c r="AZ33" s="38" t="n"/>
+      <c r="BA33" s="37" t="n"/>
       <c r="BB33" s="31" t="n"/>
-      <c r="BC33" s="41" t="n"/>
-      <c r="BD33" s="41" t="n"/>
-      <c r="BE33" s="42" t="n"/>
+      <c r="BC33" s="38" t="n"/>
+      <c r="BD33" s="38" t="n"/>
+      <c r="BE33" s="37" t="n"/>
       <c r="BF33" s="31" t="n"/>
-      <c r="BG33" s="41" t="n"/>
-      <c r="BH33" s="41" t="n"/>
-      <c r="BI33" s="42" t="n"/>
-      <c r="BJ33" s="93" t="n"/>
-      <c r="BK33" s="94" t="n"/>
-      <c r="BL33" s="94" t="n"/>
-      <c r="BM33" s="94" t="n"/>
-      <c r="BN33" s="94" t="n"/>
-      <c r="BO33" s="94" t="n"/>
-      <c r="BP33" s="94" t="n"/>
-      <c r="BQ33" s="94" t="n"/>
-      <c r="BR33" s="94" t="n"/>
-      <c r="BS33" s="94" t="n"/>
-      <c r="BT33" s="94" t="n"/>
-      <c r="BU33" s="94" t="n"/>
-      <c r="BV33" s="94" t="n"/>
-      <c r="BW33" s="94" t="n"/>
-      <c r="BX33" s="94" t="n"/>
-      <c r="BY33" s="94" t="n"/>
-      <c r="BZ33" s="94" t="n"/>
-      <c r="CA33" s="94" t="n"/>
-      <c r="CB33" s="94" t="n"/>
-      <c r="CC33" s="94" t="n"/>
-      <c r="CD33" s="94" t="n"/>
-      <c r="CE33" s="94" t="n"/>
-      <c r="CF33" s="94" t="n"/>
-      <c r="CG33" s="95" t="n"/>
+      <c r="BG33" s="38" t="n"/>
+      <c r="BH33" s="38" t="n"/>
+      <c r="BI33" s="37" t="n"/>
+      <c r="BJ33" s="66" t="n"/>
+      <c r="BK33" s="67" t="n"/>
+      <c r="BL33" s="67" t="n"/>
+      <c r="BM33" s="67" t="n"/>
+      <c r="BN33" s="67" t="n"/>
+      <c r="BO33" s="67" t="n"/>
+      <c r="BP33" s="67" t="n"/>
+      <c r="BQ33" s="67" t="n"/>
+      <c r="BR33" s="67" t="n"/>
+      <c r="BS33" s="67" t="n"/>
+      <c r="BT33" s="67" t="n"/>
+      <c r="BU33" s="67" t="n"/>
+      <c r="BV33" s="67" t="n"/>
+      <c r="BW33" s="67" t="n"/>
+      <c r="BX33" s="67" t="n"/>
+      <c r="BY33" s="67" t="n"/>
+      <c r="BZ33" s="67" t="n"/>
+      <c r="CA33" s="67" t="n"/>
+      <c r="CB33" s="67" t="n"/>
+      <c r="CC33" s="67" t="n"/>
+      <c r="CD33" s="67" t="n"/>
+      <c r="CE33" s="67" t="n"/>
+      <c r="CF33" s="67" t="n"/>
+      <c r="CG33" s="68" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="29" t="inlineStr">
@@ -5130,7 +4690,7 @@
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>Bird,VE</t>
+          <t>Bird</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
@@ -5139,89 +4699,85 @@
         </is>
       </c>
       <c r="F34" s="31" t="n"/>
-      <c r="G34" s="41" t="n"/>
-      <c r="H34" s="41" t="n"/>
-      <c r="I34" s="42" t="n"/>
+      <c r="G34" s="38" t="n"/>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="37" t="n"/>
       <c r="J34" s="31" t="n"/>
-      <c r="K34" s="41" t="n"/>
-      <c r="L34" s="41" t="n"/>
-      <c r="M34" s="42" t="n"/>
-      <c r="N34" s="86" t="n"/>
+      <c r="K34" s="38" t="n"/>
+      <c r="L34" s="38" t="n"/>
+      <c r="M34" s="37" t="n"/>
+      <c r="N34" s="58" t="n"/>
       <c r="O34" s="33" t="n"/>
       <c r="P34" s="33" t="n"/>
       <c r="Q34" s="34" t="n"/>
-      <c r="R34" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="R34" s="58" t="n"/>
       <c r="S34" s="33" t="n"/>
       <c r="T34" s="33" t="n"/>
       <c r="U34" s="34" t="n"/>
-      <c r="V34" s="86" t="n"/>
+      <c r="V34" s="58" t="n"/>
       <c r="W34" s="33" t="n"/>
       <c r="X34" s="33" t="n"/>
       <c r="Y34" s="34" t="n"/>
-      <c r="Z34" s="86" t="n"/>
+      <c r="Z34" s="58" t="n"/>
       <c r="AA34" s="33" t="n"/>
       <c r="AB34" s="33" t="n"/>
       <c r="AC34" s="34" t="n"/>
       <c r="AD34" s="31" t="n"/>
-      <c r="AE34" s="41" t="n"/>
-      <c r="AF34" s="41" t="n"/>
-      <c r="AG34" s="42" t="n"/>
+      <c r="AE34" s="38" t="n"/>
+      <c r="AF34" s="38" t="n"/>
+      <c r="AG34" s="37" t="n"/>
       <c r="AH34" s="31" t="n"/>
-      <c r="AI34" s="41" t="n"/>
-      <c r="AJ34" s="41" t="n"/>
-      <c r="AK34" s="42" t="n"/>
+      <c r="AI34" s="38" t="n"/>
+      <c r="AJ34" s="38" t="n"/>
+      <c r="AK34" s="37" t="n"/>
       <c r="AL34" s="31" t="n"/>
-      <c r="AM34" s="41" t="n"/>
-      <c r="AN34" s="41" t="n"/>
-      <c r="AO34" s="42" t="n"/>
+      <c r="AM34" s="38" t="n"/>
+      <c r="AN34" s="38" t="n"/>
+      <c r="AO34" s="37" t="n"/>
       <c r="AP34" s="31" t="n"/>
-      <c r="AQ34" s="41" t="n"/>
-      <c r="AR34" s="41" t="n"/>
-      <c r="AS34" s="42" t="n"/>
+      <c r="AQ34" s="38" t="n"/>
+      <c r="AR34" s="38" t="n"/>
+      <c r="AS34" s="37" t="n"/>
       <c r="AT34" s="31" t="n"/>
-      <c r="AU34" s="41" t="n"/>
-      <c r="AV34" s="41" t="n"/>
-      <c r="AW34" s="42" t="n"/>
+      <c r="AU34" s="38" t="n"/>
+      <c r="AV34" s="38" t="n"/>
+      <c r="AW34" s="37" t="n"/>
       <c r="AX34" s="31" t="n"/>
-      <c r="AY34" s="41" t="n"/>
-      <c r="AZ34" s="41" t="n"/>
-      <c r="BA34" s="42" t="n"/>
+      <c r="AY34" s="38" t="n"/>
+      <c r="AZ34" s="38" t="n"/>
+      <c r="BA34" s="37" t="n"/>
       <c r="BB34" s="31" t="n"/>
-      <c r="BC34" s="41" t="n"/>
-      <c r="BD34" s="41" t="n"/>
-      <c r="BE34" s="42" t="n"/>
+      <c r="BC34" s="38" t="n"/>
+      <c r="BD34" s="38" t="n"/>
+      <c r="BE34" s="37" t="n"/>
       <c r="BF34" s="31" t="n"/>
-      <c r="BG34" s="41" t="n"/>
-      <c r="BH34" s="41" t="n"/>
-      <c r="BI34" s="42" t="n"/>
+      <c r="BG34" s="38" t="n"/>
+      <c r="BH34" s="38" t="n"/>
+      <c r="BI34" s="37" t="n"/>
       <c r="BJ34" s="31" t="n"/>
-      <c r="BK34" s="41" t="n"/>
-      <c r="BL34" s="41" t="n"/>
-      <c r="BM34" s="42" t="n"/>
+      <c r="BK34" s="38" t="n"/>
+      <c r="BL34" s="38" t="n"/>
+      <c r="BM34" s="37" t="n"/>
       <c r="BN34" s="31" t="n"/>
-      <c r="BO34" s="41" t="n"/>
-      <c r="BP34" s="41" t="n"/>
-      <c r="BQ34" s="42" t="n"/>
+      <c r="BO34" s="38" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="37" t="n"/>
       <c r="BR34" s="31" t="n"/>
-      <c r="BS34" s="41" t="n"/>
-      <c r="BT34" s="41" t="n"/>
-      <c r="BU34" s="42" t="n"/>
+      <c r="BS34" s="38" t="n"/>
+      <c r="BT34" s="38" t="n"/>
+      <c r="BU34" s="37" t="n"/>
       <c r="BV34" s="31" t="n"/>
-      <c r="BW34" s="41" t="n"/>
-      <c r="BX34" s="41" t="n"/>
-      <c r="BY34" s="42" t="n"/>
+      <c r="BW34" s="38" t="n"/>
+      <c r="BX34" s="38" t="n"/>
+      <c r="BY34" s="37" t="n"/>
       <c r="BZ34" s="31" t="n"/>
-      <c r="CA34" s="41" t="n"/>
-      <c r="CB34" s="41" t="n"/>
-      <c r="CC34" s="42" t="n"/>
+      <c r="CA34" s="38" t="n"/>
+      <c r="CB34" s="38" t="n"/>
+      <c r="CC34" s="37" t="n"/>
       <c r="CD34" s="31" t="n"/>
-      <c r="CE34" s="41" t="n"/>
-      <c r="CF34" s="41" t="n"/>
-      <c r="CG34" s="54" t="n"/>
+      <c r="CE34" s="38" t="n"/>
+      <c r="CF34" s="38" t="n"/>
+      <c r="CG34" s="48" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="29" t="inlineStr">
@@ -5241,7 +4797,7 @@
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
-          <t>Mendes,AJ</t>
+          <t>Mendes</t>
         </is>
       </c>
       <c r="E35" s="30" t="inlineStr">
@@ -5250,101 +4806,85 @@
         </is>
       </c>
       <c r="F35" s="31" t="n"/>
-      <c r="G35" s="41" t="n"/>
-      <c r="H35" s="41" t="n"/>
-      <c r="I35" s="42" t="n"/>
+      <c r="G35" s="38" t="n"/>
+      <c r="H35" s="38" t="n"/>
+      <c r="I35" s="37" t="n"/>
       <c r="J35" s="31" t="n"/>
-      <c r="K35" s="41" t="n"/>
-      <c r="L35" s="41" t="n"/>
-      <c r="M35" s="42" t="n"/>
-      <c r="N35" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="K35" s="38" t="n"/>
+      <c r="L35" s="38" t="n"/>
+      <c r="M35" s="37" t="n"/>
+      <c r="N35" s="58" t="n"/>
       <c r="O35" s="33" t="n"/>
       <c r="P35" s="33" t="n"/>
       <c r="Q35" s="34" t="n"/>
-      <c r="R35" s="86" t="n"/>
+      <c r="R35" s="58" t="n"/>
       <c r="S35" s="33" t="n"/>
       <c r="T35" s="33" t="n"/>
       <c r="U35" s="34" t="n"/>
-      <c r="V35" s="86" t="n"/>
+      <c r="V35" s="58" t="n"/>
       <c r="W35" s="33" t="n"/>
       <c r="X35" s="33" t="n"/>
       <c r="Y35" s="34" t="n"/>
-      <c r="Z35" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="Z35" s="58" t="n"/>
       <c r="AA35" s="33" t="n"/>
-      <c r="AB35" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AB35" s="33" t="n"/>
       <c r="AC35" s="34" t="n"/>
-      <c r="AD35" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="AD35" s="58" t="n"/>
       <c r="AE35" s="33" t="n"/>
       <c r="AF35" s="33" t="n"/>
       <c r="AG35" s="34" t="n"/>
-      <c r="AH35" s="86" t="n"/>
+      <c r="AH35" s="58" t="n"/>
       <c r="AI35" s="33" t="n"/>
       <c r="AJ35" s="33" t="n"/>
       <c r="AK35" s="34" t="n"/>
-      <c r="AL35" s="86" t="n"/>
+      <c r="AL35" s="58" t="n"/>
       <c r="AM35" s="33" t="n"/>
       <c r="AN35" s="33" t="n"/>
       <c r="AO35" s="34" t="n"/>
-      <c r="AP35" s="87" t="n"/>
+      <c r="AP35" s="59" t="n"/>
       <c r="AQ35" s="33" t="n"/>
-      <c r="AR35" s="41" t="n"/>
-      <c r="AS35" s="42" t="n"/>
+      <c r="AR35" s="38" t="n"/>
+      <c r="AS35" s="37" t="n"/>
       <c r="AT35" s="31" t="n"/>
-      <c r="AU35" s="41" t="n"/>
-      <c r="AV35" s="41" t="n"/>
-      <c r="AW35" s="42" t="n"/>
+      <c r="AU35" s="38" t="n"/>
+      <c r="AV35" s="38" t="n"/>
+      <c r="AW35" s="37" t="n"/>
       <c r="AX35" s="31" t="n"/>
-      <c r="AY35" s="41" t="n"/>
-      <c r="AZ35" s="41" t="n"/>
-      <c r="BA35" s="42" t="n"/>
+      <c r="AY35" s="38" t="n"/>
+      <c r="AZ35" s="38" t="n"/>
+      <c r="BA35" s="37" t="n"/>
       <c r="BB35" s="31" t="n"/>
-      <c r="BC35" s="41" t="n"/>
-      <c r="BD35" s="41" t="n"/>
-      <c r="BE35" s="42" t="n"/>
+      <c r="BC35" s="38" t="n"/>
+      <c r="BD35" s="38" t="n"/>
+      <c r="BE35" s="37" t="n"/>
       <c r="BF35" s="31" t="n"/>
-      <c r="BG35" s="41" t="n"/>
-      <c r="BH35" s="41" t="n"/>
-      <c r="BI35" s="42" t="n"/>
+      <c r="BG35" s="38" t="n"/>
+      <c r="BH35" s="38" t="n"/>
+      <c r="BI35" s="37" t="n"/>
       <c r="BJ35" s="31" t="n"/>
-      <c r="BK35" s="41" t="n"/>
-      <c r="BL35" s="41" t="n"/>
-      <c r="BM35" s="42" t="n"/>
+      <c r="BK35" s="38" t="n"/>
+      <c r="BL35" s="38" t="n"/>
+      <c r="BM35" s="37" t="n"/>
       <c r="BN35" s="31" t="n"/>
-      <c r="BO35" s="41" t="n"/>
-      <c r="BP35" s="41" t="n"/>
-      <c r="BQ35" s="42" t="n"/>
+      <c r="BO35" s="38" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="37" t="n"/>
       <c r="BR35" s="31" t="n"/>
-      <c r="BS35" s="41" t="n"/>
-      <c r="BT35" s="41" t="n"/>
-      <c r="BU35" s="42" t="n"/>
+      <c r="BS35" s="38" t="n"/>
+      <c r="BT35" s="38" t="n"/>
+      <c r="BU35" s="37" t="n"/>
       <c r="BV35" s="31" t="n"/>
-      <c r="BW35" s="41" t="n"/>
-      <c r="BX35" s="41" t="n"/>
-      <c r="BY35" s="42" t="n"/>
+      <c r="BW35" s="38" t="n"/>
+      <c r="BX35" s="38" t="n"/>
+      <c r="BY35" s="37" t="n"/>
       <c r="BZ35" s="31" t="n"/>
-      <c r="CA35" s="41" t="n"/>
-      <c r="CB35" s="41" t="n"/>
-      <c r="CC35" s="42" t="n"/>
+      <c r="CA35" s="38" t="n"/>
+      <c r="CB35" s="38" t="n"/>
+      <c r="CC35" s="37" t="n"/>
       <c r="CD35" s="31" t="n"/>
-      <c r="CE35" s="41" t="n"/>
-      <c r="CF35" s="41" t="n"/>
-      <c r="CG35" s="54" t="n"/>
+      <c r="CE35" s="38" t="n"/>
+      <c r="CF35" s="38" t="n"/>
+      <c r="CG35" s="48" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
@@ -5364,7 +4904,7 @@
       </c>
       <c r="D36" s="30" t="inlineStr">
         <is>
-          <t>Patel,S</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
@@ -5373,97 +4913,85 @@
         </is>
       </c>
       <c r="F36" s="31" t="n"/>
-      <c r="G36" s="41" t="n"/>
-      <c r="H36" s="41" t="n"/>
-      <c r="I36" s="42" t="n"/>
+      <c r="G36" s="38" t="n"/>
+      <c r="H36" s="38" t="n"/>
+      <c r="I36" s="37" t="n"/>
       <c r="J36" s="31" t="n"/>
-      <c r="K36" s="41" t="n"/>
-      <c r="L36" s="41" t="n"/>
-      <c r="M36" s="42" t="n"/>
-      <c r="N36" s="92" t="n"/>
+      <c r="K36" s="38" t="n"/>
+      <c r="L36" s="38" t="n"/>
+      <c r="M36" s="37" t="n"/>
+      <c r="N36" s="64" t="n"/>
       <c r="O36" s="33" t="n"/>
       <c r="P36" s="33" t="n"/>
       <c r="Q36" s="34" t="n"/>
-      <c r="R36" s="48" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="R36" s="64" t="n"/>
       <c r="S36" s="33" t="n"/>
       <c r="T36" s="33" t="n"/>
       <c r="U36" s="34" t="n"/>
-      <c r="V36" s="92" t="n"/>
+      <c r="V36" s="64" t="n"/>
       <c r="W36" s="33" t="n"/>
       <c r="X36" s="33" t="n"/>
       <c r="Y36" s="34" t="n"/>
-      <c r="Z36" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="Z36" s="64" t="n"/>
       <c r="AA36" s="33" t="n"/>
-      <c r="AB36" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AB36" s="33" t="n"/>
       <c r="AC36" s="34" t="n"/>
-      <c r="AD36" s="92" t="n"/>
+      <c r="AD36" s="64" t="n"/>
       <c r="AE36" s="33" t="n"/>
       <c r="AF36" s="33" t="n"/>
       <c r="AG36" s="34" t="n"/>
-      <c r="AH36" s="92" t="n"/>
+      <c r="AH36" s="64" t="n"/>
       <c r="AI36" s="33" t="n"/>
       <c r="AJ36" s="33" t="n"/>
       <c r="AK36" s="34" t="n"/>
-      <c r="AL36" s="92" t="n"/>
+      <c r="AL36" s="64" t="n"/>
       <c r="AM36" s="33" t="n"/>
       <c r="AN36" s="33" t="n"/>
       <c r="AO36" s="34" t="n"/>
-      <c r="AP36" s="92" t="n"/>
+      <c r="AP36" s="64" t="n"/>
       <c r="AQ36" s="33" t="n"/>
       <c r="AR36" s="33" t="n"/>
       <c r="AS36" s="34" t="n"/>
       <c r="AT36" s="31" t="n"/>
-      <c r="AU36" s="41" t="n"/>
-      <c r="AV36" s="41" t="n"/>
-      <c r="AW36" s="42" t="n"/>
+      <c r="AU36" s="38" t="n"/>
+      <c r="AV36" s="38" t="n"/>
+      <c r="AW36" s="37" t="n"/>
       <c r="AX36" s="31" t="n"/>
-      <c r="AY36" s="41" t="n"/>
-      <c r="AZ36" s="41" t="n"/>
-      <c r="BA36" s="42" t="n"/>
+      <c r="AY36" s="38" t="n"/>
+      <c r="AZ36" s="38" t="n"/>
+      <c r="BA36" s="37" t="n"/>
       <c r="BB36" s="31" t="n"/>
-      <c r="BC36" s="41" t="n"/>
-      <c r="BD36" s="41" t="n"/>
-      <c r="BE36" s="42" t="n"/>
+      <c r="BC36" s="38" t="n"/>
+      <c r="BD36" s="38" t="n"/>
+      <c r="BE36" s="37" t="n"/>
       <c r="BF36" s="31" t="n"/>
-      <c r="BG36" s="41" t="n"/>
-      <c r="BH36" s="41" t="n"/>
-      <c r="BI36" s="42" t="n"/>
+      <c r="BG36" s="38" t="n"/>
+      <c r="BH36" s="38" t="n"/>
+      <c r="BI36" s="37" t="n"/>
       <c r="BJ36" s="31" t="n"/>
-      <c r="BK36" s="41" t="n"/>
-      <c r="BL36" s="41" t="n"/>
-      <c r="BM36" s="42" t="n"/>
+      <c r="BK36" s="38" t="n"/>
+      <c r="BL36" s="38" t="n"/>
+      <c r="BM36" s="37" t="n"/>
       <c r="BN36" s="31" t="n"/>
-      <c r="BO36" s="41" t="n"/>
-      <c r="BP36" s="41" t="n"/>
-      <c r="BQ36" s="42" t="n"/>
+      <c r="BO36" s="38" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="37" t="n"/>
       <c r="BR36" s="31" t="n"/>
-      <c r="BS36" s="41" t="n"/>
-      <c r="BT36" s="41" t="n"/>
-      <c r="BU36" s="42" t="n"/>
+      <c r="BS36" s="38" t="n"/>
+      <c r="BT36" s="38" t="n"/>
+      <c r="BU36" s="37" t="n"/>
       <c r="BV36" s="31" t="n"/>
-      <c r="BW36" s="41" t="n"/>
-      <c r="BX36" s="41" t="n"/>
-      <c r="BY36" s="42" t="n"/>
+      <c r="BW36" s="38" t="n"/>
+      <c r="BX36" s="38" t="n"/>
+      <c r="BY36" s="37" t="n"/>
       <c r="BZ36" s="31" t="n"/>
-      <c r="CA36" s="41" t="n"/>
-      <c r="CB36" s="41" t="n"/>
-      <c r="CC36" s="42" t="n"/>
+      <c r="CA36" s="38" t="n"/>
+      <c r="CB36" s="38" t="n"/>
+      <c r="CC36" s="37" t="n"/>
       <c r="CD36" s="31" t="n"/>
-      <c r="CE36" s="41" t="n"/>
-      <c r="CF36" s="41" t="n"/>
-      <c r="CG36" s="54" t="n"/>
+      <c r="CE36" s="38" t="n"/>
+      <c r="CF36" s="38" t="n"/>
+      <c r="CG36" s="48" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="29" t="inlineStr">
@@ -5483,7 +5011,7 @@
       </c>
       <c r="D37" s="30" t="inlineStr">
         <is>
-          <t>Etem,S</t>
+          <t>Etem</t>
         </is>
       </c>
       <c r="E37" s="30" t="inlineStr">
@@ -5492,97 +5020,85 @@
         </is>
       </c>
       <c r="F37" s="31" t="n"/>
-      <c r="G37" s="41" t="n"/>
-      <c r="H37" s="41" t="n"/>
-      <c r="I37" s="42" t="n"/>
+      <c r="G37" s="38" t="n"/>
+      <c r="H37" s="38" t="n"/>
+      <c r="I37" s="37" t="n"/>
       <c r="J37" s="31" t="n"/>
-      <c r="K37" s="41" t="n"/>
-      <c r="L37" s="41" t="n"/>
-      <c r="M37" s="42" t="n"/>
+      <c r="K37" s="38" t="n"/>
+      <c r="L37" s="38" t="n"/>
+      <c r="M37" s="37" t="n"/>
       <c r="N37" s="31" t="n"/>
-      <c r="O37" s="41" t="n"/>
-      <c r="P37" s="41" t="n"/>
-      <c r="Q37" s="42" t="n"/>
+      <c r="O37" s="38" t="n"/>
+      <c r="P37" s="38" t="n"/>
+      <c r="Q37" s="37" t="n"/>
       <c r="R37" s="31" t="n"/>
-      <c r="S37" s="41" t="n"/>
-      <c r="T37" s="41" t="n"/>
-      <c r="U37" s="42" t="n"/>
+      <c r="S37" s="38" t="n"/>
+      <c r="T37" s="38" t="n"/>
+      <c r="U37" s="37" t="n"/>
       <c r="V37" s="31" t="n"/>
-      <c r="W37" s="41" t="n"/>
-      <c r="X37" s="91" t="n"/>
+      <c r="W37" s="38" t="n"/>
+      <c r="X37" s="63" t="n"/>
       <c r="Y37" s="34" t="n"/>
-      <c r="Z37" s="92" t="n"/>
+      <c r="Z37" s="64" t="n"/>
       <c r="AA37" s="33" t="n"/>
       <c r="AB37" s="33" t="n"/>
       <c r="AC37" s="34" t="n"/>
-      <c r="AD37" s="92" t="n"/>
+      <c r="AD37" s="64" t="n"/>
       <c r="AE37" s="33" t="n"/>
       <c r="AF37" s="33" t="n"/>
       <c r="AG37" s="34" t="n"/>
-      <c r="AH37" s="92" t="n"/>
+      <c r="AH37" s="64" t="n"/>
       <c r="AI37" s="33" t="n"/>
       <c r="AJ37" s="33" t="n"/>
       <c r="AK37" s="34" t="n"/>
-      <c r="AL37" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AL37" s="64" t="n"/>
       <c r="AM37" s="33" t="n"/>
-      <c r="AN37" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AN37" s="33" t="n"/>
       <c r="AO37" s="34" t="n"/>
-      <c r="AP37" s="92" t="n"/>
+      <c r="AP37" s="64" t="n"/>
       <c r="AQ37" s="33" t="n"/>
       <c r="AR37" s="33" t="n"/>
       <c r="AS37" s="34" t="n"/>
-      <c r="AT37" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AT37" s="64" t="n"/>
       <c r="AU37" s="33" t="n"/>
       <c r="AV37" s="33" t="n"/>
       <c r="AW37" s="34" t="n"/>
-      <c r="AX37" s="92" t="n"/>
+      <c r="AX37" s="64" t="n"/>
       <c r="AY37" s="33" t="n"/>
       <c r="AZ37" s="33" t="n"/>
       <c r="BA37" s="34" t="n"/>
-      <c r="BB37" s="96" t="n"/>
+      <c r="BB37" s="69" t="n"/>
       <c r="BC37" s="33" t="n"/>
-      <c r="BD37" s="41" t="n"/>
-      <c r="BE37" s="42" t="n"/>
+      <c r="BD37" s="38" t="n"/>
+      <c r="BE37" s="37" t="n"/>
       <c r="BF37" s="31" t="n"/>
-      <c r="BG37" s="41" t="n"/>
-      <c r="BH37" s="41" t="n"/>
-      <c r="BI37" s="42" t="n"/>
+      <c r="BG37" s="38" t="n"/>
+      <c r="BH37" s="38" t="n"/>
+      <c r="BI37" s="37" t="n"/>
       <c r="BJ37" s="31" t="n"/>
-      <c r="BK37" s="41" t="n"/>
-      <c r="BL37" s="41" t="n"/>
-      <c r="BM37" s="42" t="n"/>
+      <c r="BK37" s="38" t="n"/>
+      <c r="BL37" s="38" t="n"/>
+      <c r="BM37" s="37" t="n"/>
       <c r="BN37" s="31" t="n"/>
-      <c r="BO37" s="41" t="n"/>
-      <c r="BP37" s="41" t="n"/>
-      <c r="BQ37" s="42" t="n"/>
+      <c r="BO37" s="38" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="37" t="n"/>
       <c r="BR37" s="31" t="n"/>
-      <c r="BS37" s="41" t="n"/>
-      <c r="BT37" s="41" t="n"/>
-      <c r="BU37" s="42" t="n"/>
+      <c r="BS37" s="38" t="n"/>
+      <c r="BT37" s="38" t="n"/>
+      <c r="BU37" s="37" t="n"/>
       <c r="BV37" s="31" t="n"/>
-      <c r="BW37" s="41" t="n"/>
-      <c r="BX37" s="41" t="n"/>
-      <c r="BY37" s="42" t="n"/>
+      <c r="BW37" s="38" t="n"/>
+      <c r="BX37" s="38" t="n"/>
+      <c r="BY37" s="37" t="n"/>
       <c r="BZ37" s="31" t="n"/>
-      <c r="CA37" s="41" t="n"/>
-      <c r="CB37" s="41" t="n"/>
-      <c r="CC37" s="42" t="n"/>
+      <c r="CA37" s="38" t="n"/>
+      <c r="CB37" s="38" t="n"/>
+      <c r="CC37" s="37" t="n"/>
       <c r="CD37" s="31" t="n"/>
-      <c r="CE37" s="41" t="n"/>
-      <c r="CF37" s="41" t="n"/>
-      <c r="CG37" s="54" t="n"/>
+      <c r="CE37" s="38" t="n"/>
+      <c r="CF37" s="38" t="n"/>
+      <c r="CG37" s="48" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="29" t="inlineStr">
@@ -5602,7 +5118,7 @@
       </c>
       <c r="D38" s="30" t="inlineStr">
         <is>
-          <t>Sheikh,M</t>
+          <t>Sheikh</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
@@ -5611,97 +5127,85 @@
         </is>
       </c>
       <c r="F38" s="31" t="n"/>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="41" t="n"/>
-      <c r="I38" s="42" t="n"/>
+      <c r="G38" s="38" t="n"/>
+      <c r="H38" s="38" t="n"/>
+      <c r="I38" s="37" t="n"/>
       <c r="J38" s="31" t="n"/>
-      <c r="K38" s="41" t="n"/>
-      <c r="L38" s="41" t="n"/>
-      <c r="M38" s="42" t="n"/>
+      <c r="K38" s="38" t="n"/>
+      <c r="L38" s="38" t="n"/>
+      <c r="M38" s="37" t="n"/>
       <c r="N38" s="31" t="n"/>
-      <c r="O38" s="41" t="n"/>
-      <c r="P38" s="41" t="n"/>
-      <c r="Q38" s="42" t="n"/>
+      <c r="O38" s="38" t="n"/>
+      <c r="P38" s="38" t="n"/>
+      <c r="Q38" s="37" t="n"/>
       <c r="R38" s="31" t="n"/>
-      <c r="S38" s="41" t="n"/>
-      <c r="T38" s="41" t="n"/>
-      <c r="U38" s="42" t="n"/>
+      <c r="S38" s="38" t="n"/>
+      <c r="T38" s="38" t="n"/>
+      <c r="U38" s="37" t="n"/>
       <c r="V38" s="31" t="n"/>
-      <c r="W38" s="41" t="n"/>
-      <c r="X38" s="41" t="n"/>
-      <c r="Y38" s="42" t="n"/>
+      <c r="W38" s="38" t="n"/>
+      <c r="X38" s="38" t="n"/>
+      <c r="Y38" s="37" t="n"/>
       <c r="Z38" s="31" t="n"/>
-      <c r="AA38" s="41" t="n"/>
-      <c r="AB38" s="41" t="n"/>
-      <c r="AC38" s="42" t="n"/>
+      <c r="AA38" s="38" t="n"/>
+      <c r="AB38" s="38" t="n"/>
+      <c r="AC38" s="37" t="n"/>
       <c r="AD38" s="31" t="n"/>
-      <c r="AE38" s="41" t="n"/>
-      <c r="AF38" s="41" t="n"/>
-      <c r="AG38" s="42" t="n"/>
+      <c r="AE38" s="38" t="n"/>
+      <c r="AF38" s="38" t="n"/>
+      <c r="AG38" s="37" t="n"/>
       <c r="AH38" s="31" t="n"/>
-      <c r="AI38" s="41" t="n"/>
-      <c r="AJ38" s="85" t="n"/>
+      <c r="AI38" s="38" t="n"/>
+      <c r="AJ38" s="57" t="n"/>
       <c r="AK38" s="34" t="n"/>
-      <c r="AL38" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AL38" s="58" t="n"/>
       <c r="AM38" s="33" t="n"/>
       <c r="AN38" s="33" t="n"/>
       <c r="AO38" s="34" t="n"/>
-      <c r="AP38" s="86" t="n"/>
+      <c r="AP38" s="58" t="n"/>
       <c r="AQ38" s="33" t="n"/>
       <c r="AR38" s="33" t="n"/>
       <c r="AS38" s="34" t="n"/>
-      <c r="AT38" s="86" t="n"/>
+      <c r="AT38" s="58" t="n"/>
       <c r="AU38" s="33" t="n"/>
       <c r="AV38" s="33" t="n"/>
       <c r="AW38" s="34" t="n"/>
-      <c r="AX38" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AX38" s="58" t="n"/>
       <c r="AY38" s="33" t="n"/>
-      <c r="AZ38" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AZ38" s="33" t="n"/>
       <c r="BA38" s="34" t="n"/>
-      <c r="BB38" s="86" t="n"/>
+      <c r="BB38" s="58" t="n"/>
       <c r="BC38" s="33" t="n"/>
       <c r="BD38" s="33" t="n"/>
       <c r="BE38" s="34" t="n"/>
-      <c r="BF38" s="86" t="n"/>
+      <c r="BF38" s="58" t="n"/>
       <c r="BG38" s="33" t="n"/>
       <c r="BH38" s="33" t="n"/>
       <c r="BI38" s="34" t="n"/>
-      <c r="BJ38" s="86" t="n"/>
+      <c r="BJ38" s="58" t="n"/>
       <c r="BK38" s="33" t="n"/>
       <c r="BL38" s="33" t="n"/>
       <c r="BM38" s="34" t="n"/>
       <c r="BN38" s="31" t="n"/>
-      <c r="BO38" s="41" t="n"/>
-      <c r="BP38" s="41" t="n"/>
-      <c r="BQ38" s="42" t="n"/>
+      <c r="BO38" s="38" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="37" t="n"/>
       <c r="BR38" s="31" t="n"/>
-      <c r="BS38" s="41" t="n"/>
-      <c r="BT38" s="41" t="n"/>
-      <c r="BU38" s="42" t="n"/>
+      <c r="BS38" s="38" t="n"/>
+      <c r="BT38" s="38" t="n"/>
+      <c r="BU38" s="37" t="n"/>
       <c r="BV38" s="31" t="n"/>
-      <c r="BW38" s="41" t="n"/>
-      <c r="BX38" s="41" t="n"/>
-      <c r="BY38" s="42" t="n"/>
+      <c r="BW38" s="38" t="n"/>
+      <c r="BX38" s="38" t="n"/>
+      <c r="BY38" s="37" t="n"/>
       <c r="BZ38" s="31" t="n"/>
-      <c r="CA38" s="41" t="n"/>
-      <c r="CB38" s="41" t="n"/>
-      <c r="CC38" s="42" t="n"/>
+      <c r="CA38" s="38" t="n"/>
+      <c r="CB38" s="38" t="n"/>
+      <c r="CC38" s="37" t="n"/>
       <c r="CD38" s="31" t="n"/>
-      <c r="CE38" s="41" t="n"/>
-      <c r="CF38" s="41" t="n"/>
-      <c r="CG38" s="54" t="n"/>
+      <c r="CE38" s="38" t="n"/>
+      <c r="CF38" s="38" t="n"/>
+      <c r="CG38" s="48" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="29" t="inlineStr">
@@ -5721,7 +5225,7 @@
       </c>
       <c r="D39" s="30" t="inlineStr">
         <is>
-          <t>Coldwell,NA</t>
+          <t>Coldwell</t>
         </is>
       </c>
       <c r="E39" s="30" t="inlineStr">
@@ -5730,97 +5234,85 @@
         </is>
       </c>
       <c r="F39" s="31" t="n"/>
-      <c r="G39" s="41" t="n"/>
-      <c r="H39" s="41" t="n"/>
-      <c r="I39" s="42" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="37" t="n"/>
       <c r="J39" s="31" t="n"/>
-      <c r="K39" s="41" t="n"/>
-      <c r="L39" s="41" t="n"/>
-      <c r="M39" s="42" t="n"/>
+      <c r="K39" s="38" t="n"/>
+      <c r="L39" s="38" t="n"/>
+      <c r="M39" s="37" t="n"/>
       <c r="N39" s="31" t="n"/>
-      <c r="O39" s="41" t="n"/>
-      <c r="P39" s="41" t="n"/>
-      <c r="Q39" s="42" t="n"/>
+      <c r="O39" s="38" t="n"/>
+      <c r="P39" s="38" t="n"/>
+      <c r="Q39" s="37" t="n"/>
       <c r="R39" s="31" t="n"/>
-      <c r="S39" s="41" t="n"/>
-      <c r="T39" s="41" t="n"/>
-      <c r="U39" s="42" t="n"/>
+      <c r="S39" s="38" t="n"/>
+      <c r="T39" s="38" t="n"/>
+      <c r="U39" s="37" t="n"/>
       <c r="V39" s="31" t="n"/>
-      <c r="W39" s="41" t="n"/>
-      <c r="X39" s="41" t="n"/>
-      <c r="Y39" s="42" t="n"/>
+      <c r="W39" s="38" t="n"/>
+      <c r="X39" s="38" t="n"/>
+      <c r="Y39" s="37" t="n"/>
       <c r="Z39" s="31" t="n"/>
-      <c r="AA39" s="41" t="n"/>
-      <c r="AB39" s="41" t="n"/>
-      <c r="AC39" s="42" t="n"/>
+      <c r="AA39" s="38" t="n"/>
+      <c r="AB39" s="38" t="n"/>
+      <c r="AC39" s="37" t="n"/>
       <c r="AD39" s="31" t="n"/>
-      <c r="AE39" s="41" t="n"/>
-      <c r="AF39" s="41" t="n"/>
-      <c r="AG39" s="42" t="n"/>
+      <c r="AE39" s="38" t="n"/>
+      <c r="AF39" s="38" t="n"/>
+      <c r="AG39" s="37" t="n"/>
       <c r="AH39" s="31" t="n"/>
-      <c r="AI39" s="41" t="n"/>
-      <c r="AJ39" s="41" t="n"/>
-      <c r="AK39" s="42" t="n"/>
-      <c r="AL39" s="92" t="n"/>
+      <c r="AI39" s="38" t="n"/>
+      <c r="AJ39" s="38" t="n"/>
+      <c r="AK39" s="37" t="n"/>
+      <c r="AL39" s="64" t="n"/>
       <c r="AM39" s="33" t="n"/>
       <c r="AN39" s="33" t="n"/>
       <c r="AO39" s="34" t="n"/>
-      <c r="AP39" s="92" t="n"/>
+      <c r="AP39" s="64" t="n"/>
       <c r="AQ39" s="33" t="n"/>
       <c r="AR39" s="33" t="n"/>
       <c r="AS39" s="34" t="n"/>
-      <c r="AT39" s="92" t="n"/>
+      <c r="AT39" s="64" t="n"/>
       <c r="AU39" s="33" t="n"/>
       <c r="AV39" s="33" t="n"/>
       <c r="AW39" s="34" t="n"/>
-      <c r="AX39" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AX39" s="64" t="n"/>
       <c r="AY39" s="33" t="n"/>
-      <c r="AZ39" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AZ39" s="33" t="n"/>
       <c r="BA39" s="34" t="n"/>
-      <c r="BB39" s="92" t="n"/>
+      <c r="BB39" s="64" t="n"/>
       <c r="BC39" s="33" t="n"/>
       <c r="BD39" s="33" t="n"/>
       <c r="BE39" s="34" t="n"/>
-      <c r="BF39" s="92" t="n"/>
+      <c r="BF39" s="64" t="n"/>
       <c r="BG39" s="33" t="n"/>
       <c r="BH39" s="33" t="n"/>
       <c r="BI39" s="34" t="n"/>
-      <c r="BJ39" s="92" t="n"/>
+      <c r="BJ39" s="64" t="n"/>
       <c r="BK39" s="33" t="n"/>
       <c r="BL39" s="33" t="n"/>
       <c r="BM39" s="34" t="n"/>
-      <c r="BN39" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BN39" s="64" t="n"/>
       <c r="BO39" s="33" t="n"/>
       <c r="BP39" s="33" t="n"/>
       <c r="BQ39" s="34" t="n"/>
       <c r="BR39" s="31" t="n"/>
-      <c r="BS39" s="41" t="n"/>
-      <c r="BT39" s="41" t="n"/>
-      <c r="BU39" s="42" t="n"/>
+      <c r="BS39" s="38" t="n"/>
+      <c r="BT39" s="38" t="n"/>
+      <c r="BU39" s="37" t="n"/>
       <c r="BV39" s="31" t="n"/>
-      <c r="BW39" s="41" t="n"/>
-      <c r="BX39" s="41" t="n"/>
-      <c r="BY39" s="42" t="n"/>
+      <c r="BW39" s="38" t="n"/>
+      <c r="BX39" s="38" t="n"/>
+      <c r="BY39" s="37" t="n"/>
       <c r="BZ39" s="31" t="n"/>
-      <c r="CA39" s="41" t="n"/>
-      <c r="CB39" s="41" t="n"/>
-      <c r="CC39" s="42" t="n"/>
+      <c r="CA39" s="38" t="n"/>
+      <c r="CB39" s="38" t="n"/>
+      <c r="CC39" s="37" t="n"/>
       <c r="CD39" s="31" t="n"/>
-      <c r="CE39" s="41" t="n"/>
-      <c r="CF39" s="41" t="n"/>
-      <c r="CG39" s="54" t="n"/>
+      <c r="CE39" s="38" t="n"/>
+      <c r="CF39" s="38" t="n"/>
+      <c r="CG39" s="48" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="29" t="inlineStr">
@@ -5845,97 +5337,85 @@
       </c>
       <c r="E40" s="30" t="inlineStr"/>
       <c r="F40" s="31" t="n"/>
-      <c r="G40" s="41" t="n"/>
-      <c r="H40" s="41" t="n"/>
-      <c r="I40" s="42" t="n"/>
+      <c r="G40" s="38" t="n"/>
+      <c r="H40" s="38" t="n"/>
+      <c r="I40" s="37" t="n"/>
       <c r="J40" s="31" t="n"/>
-      <c r="K40" s="41" t="n"/>
-      <c r="L40" s="41" t="n"/>
-      <c r="M40" s="42" t="n"/>
+      <c r="K40" s="38" t="n"/>
+      <c r="L40" s="38" t="n"/>
+      <c r="M40" s="37" t="n"/>
       <c r="N40" s="31" t="n"/>
-      <c r="O40" s="41" t="n"/>
-      <c r="P40" s="41" t="n"/>
-      <c r="Q40" s="42" t="n"/>
+      <c r="O40" s="38" t="n"/>
+      <c r="P40" s="38" t="n"/>
+      <c r="Q40" s="37" t="n"/>
       <c r="R40" s="31" t="n"/>
-      <c r="S40" s="41" t="n"/>
-      <c r="T40" s="41" t="n"/>
-      <c r="U40" s="42" t="n"/>
+      <c r="S40" s="38" t="n"/>
+      <c r="T40" s="38" t="n"/>
+      <c r="U40" s="37" t="n"/>
       <c r="V40" s="31" t="n"/>
-      <c r="W40" s="41" t="n"/>
-      <c r="X40" s="41" t="n"/>
-      <c r="Y40" s="42" t="n"/>
+      <c r="W40" s="38" t="n"/>
+      <c r="X40" s="38" t="n"/>
+      <c r="Y40" s="37" t="n"/>
       <c r="Z40" s="31" t="n"/>
-      <c r="AA40" s="41" t="n"/>
-      <c r="AB40" s="41" t="n"/>
-      <c r="AC40" s="42" t="n"/>
+      <c r="AA40" s="38" t="n"/>
+      <c r="AB40" s="38" t="n"/>
+      <c r="AC40" s="37" t="n"/>
       <c r="AD40" s="31" t="n"/>
-      <c r="AE40" s="41" t="n"/>
-      <c r="AF40" s="41" t="n"/>
-      <c r="AG40" s="42" t="n"/>
+      <c r="AE40" s="38" t="n"/>
+      <c r="AF40" s="38" t="n"/>
+      <c r="AG40" s="37" t="n"/>
       <c r="AH40" s="31" t="n"/>
-      <c r="AI40" s="41" t="n"/>
-      <c r="AJ40" s="41" t="n"/>
-      <c r="AK40" s="42" t="n"/>
+      <c r="AI40" s="38" t="n"/>
+      <c r="AJ40" s="38" t="n"/>
+      <c r="AK40" s="37" t="n"/>
       <c r="AL40" s="31" t="n"/>
-      <c r="AM40" s="41" t="n"/>
-      <c r="AN40" s="41" t="n"/>
-      <c r="AO40" s="42" t="n"/>
+      <c r="AM40" s="38" t="n"/>
+      <c r="AN40" s="38" t="n"/>
+      <c r="AO40" s="37" t="n"/>
       <c r="AP40" s="31" t="n"/>
-      <c r="AQ40" s="41" t="n"/>
-      <c r="AR40" s="41" t="n"/>
-      <c r="AS40" s="42" t="n"/>
-      <c r="AT40" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="AQ40" s="38" t="n"/>
+      <c r="AR40" s="38" t="n"/>
+      <c r="AS40" s="37" t="n"/>
+      <c r="AT40" s="58" t="n"/>
       <c r="AU40" s="33" t="n"/>
       <c r="AV40" s="33" t="n"/>
       <c r="AW40" s="34" t="n"/>
-      <c r="AX40" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="AX40" s="58" t="n"/>
       <c r="AY40" s="33" t="n"/>
       <c r="AZ40" s="33" t="n"/>
       <c r="BA40" s="34" t="n"/>
-      <c r="BB40" s="86" t="n"/>
+      <c r="BB40" s="58" t="n"/>
       <c r="BC40" s="33" t="n"/>
       <c r="BD40" s="33" t="n"/>
       <c r="BE40" s="34" t="n"/>
-      <c r="BF40" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="BF40" s="58" t="n"/>
       <c r="BG40" s="33" t="n"/>
       <c r="BH40" s="33" t="n"/>
       <c r="BI40" s="34" t="n"/>
       <c r="BJ40" s="31" t="n"/>
-      <c r="BK40" s="41" t="n"/>
-      <c r="BL40" s="41" t="n"/>
-      <c r="BM40" s="42" t="n"/>
+      <c r="BK40" s="38" t="n"/>
+      <c r="BL40" s="38" t="n"/>
+      <c r="BM40" s="37" t="n"/>
       <c r="BN40" s="31" t="n"/>
-      <c r="BO40" s="41" t="n"/>
-      <c r="BP40" s="41" t="n"/>
-      <c r="BQ40" s="42" t="n"/>
+      <c r="BO40" s="38" t="n"/>
+      <c r="BP40" s="38" t="n"/>
+      <c r="BQ40" s="37" t="n"/>
       <c r="BR40" s="31" t="n"/>
-      <c r="BS40" s="41" t="n"/>
-      <c r="BT40" s="41" t="n"/>
-      <c r="BU40" s="42" t="n"/>
+      <c r="BS40" s="38" t="n"/>
+      <c r="BT40" s="38" t="n"/>
+      <c r="BU40" s="37" t="n"/>
       <c r="BV40" s="31" t="n"/>
-      <c r="BW40" s="41" t="n"/>
-      <c r="BX40" s="41" t="n"/>
-      <c r="BY40" s="42" t="n"/>
+      <c r="BW40" s="38" t="n"/>
+      <c r="BX40" s="38" t="n"/>
+      <c r="BY40" s="37" t="n"/>
       <c r="BZ40" s="31" t="n"/>
-      <c r="CA40" s="41" t="n"/>
-      <c r="CB40" s="41" t="n"/>
-      <c r="CC40" s="42" t="n"/>
+      <c r="CA40" s="38" t="n"/>
+      <c r="CB40" s="38" t="n"/>
+      <c r="CC40" s="37" t="n"/>
       <c r="CD40" s="31" t="n"/>
-      <c r="CE40" s="41" t="n"/>
-      <c r="CF40" s="41" t="n"/>
-      <c r="CG40" s="54" t="n"/>
+      <c r="CE40" s="38" t="n"/>
+      <c r="CF40" s="38" t="n"/>
+      <c r="CG40" s="48" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="29" t="inlineStr">
@@ -5955,7 +5435,7 @@
       </c>
       <c r="D41" s="30" t="inlineStr">
         <is>
-          <t>Chwal,KP</t>
+          <t>Chwal</t>
         </is>
       </c>
       <c r="E41" s="30" t="inlineStr">
@@ -5964,97 +5444,85 @@
         </is>
       </c>
       <c r="F41" s="31" t="n"/>
-      <c r="G41" s="41" t="n"/>
-      <c r="H41" s="41" t="n"/>
-      <c r="I41" s="42" t="n"/>
+      <c r="G41" s="38" t="n"/>
+      <c r="H41" s="38" t="n"/>
+      <c r="I41" s="37" t="n"/>
       <c r="J41" s="31" t="n"/>
-      <c r="K41" s="41" t="n"/>
-      <c r="L41" s="41" t="n"/>
-      <c r="M41" s="42" t="n"/>
+      <c r="K41" s="38" t="n"/>
+      <c r="L41" s="38" t="n"/>
+      <c r="M41" s="37" t="n"/>
       <c r="N41" s="31" t="n"/>
-      <c r="O41" s="41" t="n"/>
-      <c r="P41" s="41" t="n"/>
-      <c r="Q41" s="42" t="n"/>
+      <c r="O41" s="38" t="n"/>
+      <c r="P41" s="38" t="n"/>
+      <c r="Q41" s="37" t="n"/>
       <c r="R41" s="31" t="n"/>
-      <c r="S41" s="41" t="n"/>
-      <c r="T41" s="41" t="n"/>
-      <c r="U41" s="42" t="n"/>
+      <c r="S41" s="38" t="n"/>
+      <c r="T41" s="38" t="n"/>
+      <c r="U41" s="37" t="n"/>
       <c r="V41" s="31" t="n"/>
-      <c r="W41" s="41" t="n"/>
-      <c r="X41" s="41" t="n"/>
-      <c r="Y41" s="42" t="n"/>
+      <c r="W41" s="38" t="n"/>
+      <c r="X41" s="38" t="n"/>
+      <c r="Y41" s="37" t="n"/>
       <c r="Z41" s="31" t="n"/>
-      <c r="AA41" s="41" t="n"/>
-      <c r="AB41" s="41" t="n"/>
-      <c r="AC41" s="42" t="n"/>
+      <c r="AA41" s="38" t="n"/>
+      <c r="AB41" s="38" t="n"/>
+      <c r="AC41" s="37" t="n"/>
       <c r="AD41" s="31" t="n"/>
-      <c r="AE41" s="41" t="n"/>
-      <c r="AF41" s="41" t="n"/>
-      <c r="AG41" s="42" t="n"/>
+      <c r="AE41" s="38" t="n"/>
+      <c r="AF41" s="38" t="n"/>
+      <c r="AG41" s="37" t="n"/>
       <c r="AH41" s="31" t="n"/>
-      <c r="AI41" s="41" t="n"/>
-      <c r="AJ41" s="41" t="n"/>
-      <c r="AK41" s="42" t="n"/>
+      <c r="AI41" s="38" t="n"/>
+      <c r="AJ41" s="38" t="n"/>
+      <c r="AK41" s="37" t="n"/>
       <c r="AL41" s="31" t="n"/>
-      <c r="AM41" s="41" t="n"/>
-      <c r="AN41" s="41" t="n"/>
-      <c r="AO41" s="42" t="n"/>
+      <c r="AM41" s="38" t="n"/>
+      <c r="AN41" s="38" t="n"/>
+      <c r="AO41" s="37" t="n"/>
       <c r="AP41" s="31" t="n"/>
-      <c r="AQ41" s="41" t="n"/>
-      <c r="AR41" s="41" t="n"/>
-      <c r="AS41" s="42" t="n"/>
-      <c r="AT41" s="92" t="n"/>
+      <c r="AQ41" s="38" t="n"/>
+      <c r="AR41" s="38" t="n"/>
+      <c r="AS41" s="37" t="n"/>
+      <c r="AT41" s="64" t="n"/>
       <c r="AU41" s="33" t="n"/>
       <c r="AV41" s="33" t="n"/>
       <c r="AW41" s="34" t="n"/>
-      <c r="AX41" s="92" t="n"/>
+      <c r="AX41" s="64" t="n"/>
       <c r="AY41" s="33" t="n"/>
       <c r="AZ41" s="33" t="n"/>
       <c r="BA41" s="34" t="n"/>
-      <c r="BB41" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="BB41" s="64" t="n"/>
       <c r="BC41" s="33" t="n"/>
       <c r="BD41" s="33" t="n"/>
       <c r="BE41" s="34" t="n"/>
-      <c r="BF41" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BF41" s="64" t="n"/>
       <c r="BG41" s="33" t="n"/>
-      <c r="BH41" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BH41" s="33" t="n"/>
       <c r="BI41" s="34" t="n"/>
-      <c r="BJ41" s="92" t="n"/>
+      <c r="BJ41" s="64" t="n"/>
       <c r="BK41" s="33" t="n"/>
       <c r="BL41" s="33" t="n"/>
       <c r="BM41" s="34" t="n"/>
-      <c r="BN41" s="92" t="n"/>
+      <c r="BN41" s="64" t="n"/>
       <c r="BO41" s="33" t="n"/>
       <c r="BP41" s="33" t="n"/>
       <c r="BQ41" s="34" t="n"/>
-      <c r="BR41" s="92" t="n"/>
+      <c r="BR41" s="64" t="n"/>
       <c r="BS41" s="33" t="n"/>
       <c r="BT41" s="33" t="n"/>
       <c r="BU41" s="34" t="n"/>
-      <c r="BV41" s="92" t="n"/>
+      <c r="BV41" s="64" t="n"/>
       <c r="BW41" s="33" t="n"/>
       <c r="BX41" s="33" t="n"/>
       <c r="BY41" s="34" t="n"/>
       <c r="BZ41" s="31" t="n"/>
-      <c r="CA41" s="41" t="n"/>
-      <c r="CB41" s="41" t="n"/>
-      <c r="CC41" s="42" t="n"/>
+      <c r="CA41" s="38" t="n"/>
+      <c r="CB41" s="38" t="n"/>
+      <c r="CC41" s="37" t="n"/>
       <c r="CD41" s="31" t="n"/>
-      <c r="CE41" s="41" t="n"/>
-      <c r="CF41" s="41" t="n"/>
-      <c r="CG41" s="54" t="n"/>
+      <c r="CE41" s="38" t="n"/>
+      <c r="CF41" s="38" t="n"/>
+      <c r="CG41" s="48" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="29" t="inlineStr">
@@ -6079,97 +5547,85 @@
       </c>
       <c r="E42" s="30" t="inlineStr"/>
       <c r="F42" s="31" t="n"/>
-      <c r="G42" s="41" t="n"/>
-      <c r="H42" s="41" t="n"/>
-      <c r="I42" s="42" t="n"/>
+      <c r="G42" s="38" t="n"/>
+      <c r="H42" s="38" t="n"/>
+      <c r="I42" s="37" t="n"/>
       <c r="J42" s="31" t="n"/>
-      <c r="K42" s="41" t="n"/>
-      <c r="L42" s="41" t="n"/>
-      <c r="M42" s="42" t="n"/>
+      <c r="K42" s="38" t="n"/>
+      <c r="L42" s="38" t="n"/>
+      <c r="M42" s="37" t="n"/>
       <c r="N42" s="31" t="n"/>
-      <c r="O42" s="41" t="n"/>
-      <c r="P42" s="41" t="n"/>
-      <c r="Q42" s="42" t="n"/>
+      <c r="O42" s="38" t="n"/>
+      <c r="P42" s="38" t="n"/>
+      <c r="Q42" s="37" t="n"/>
       <c r="R42" s="31" t="n"/>
-      <c r="S42" s="41" t="n"/>
-      <c r="T42" s="41" t="n"/>
-      <c r="U42" s="42" t="n"/>
+      <c r="S42" s="38" t="n"/>
+      <c r="T42" s="38" t="n"/>
+      <c r="U42" s="37" t="n"/>
       <c r="V42" s="31" t="n"/>
-      <c r="W42" s="41" t="n"/>
-      <c r="X42" s="41" t="n"/>
-      <c r="Y42" s="42" t="n"/>
+      <c r="W42" s="38" t="n"/>
+      <c r="X42" s="38" t="n"/>
+      <c r="Y42" s="37" t="n"/>
       <c r="Z42" s="31" t="n"/>
-      <c r="AA42" s="41" t="n"/>
-      <c r="AB42" s="41" t="n"/>
-      <c r="AC42" s="42" t="n"/>
+      <c r="AA42" s="38" t="n"/>
+      <c r="AB42" s="38" t="n"/>
+      <c r="AC42" s="37" t="n"/>
       <c r="AD42" s="31" t="n"/>
-      <c r="AE42" s="41" t="n"/>
-      <c r="AF42" s="41" t="n"/>
-      <c r="AG42" s="42" t="n"/>
+      <c r="AE42" s="38" t="n"/>
+      <c r="AF42" s="38" t="n"/>
+      <c r="AG42" s="37" t="n"/>
       <c r="AH42" s="31" t="n"/>
-      <c r="AI42" s="41" t="n"/>
-      <c r="AJ42" s="41" t="n"/>
-      <c r="AK42" s="42" t="n"/>
+      <c r="AI42" s="38" t="n"/>
+      <c r="AJ42" s="38" t="n"/>
+      <c r="AK42" s="37" t="n"/>
       <c r="AL42" s="31" t="n"/>
-      <c r="AM42" s="41" t="n"/>
-      <c r="AN42" s="41" t="n"/>
-      <c r="AO42" s="42" t="n"/>
+      <c r="AM42" s="38" t="n"/>
+      <c r="AN42" s="38" t="n"/>
+      <c r="AO42" s="37" t="n"/>
       <c r="AP42" s="31" t="n"/>
-      <c r="AQ42" s="41" t="n"/>
-      <c r="AR42" s="41" t="n"/>
-      <c r="AS42" s="42" t="n"/>
+      <c r="AQ42" s="38" t="n"/>
+      <c r="AR42" s="38" t="n"/>
+      <c r="AS42" s="37" t="n"/>
       <c r="AT42" s="31" t="n"/>
-      <c r="AU42" s="41" t="n"/>
-      <c r="AV42" s="85" t="n"/>
+      <c r="AU42" s="38" t="n"/>
+      <c r="AV42" s="57" t="n"/>
       <c r="AW42" s="34" t="n"/>
-      <c r="AX42" s="86" t="n"/>
+      <c r="AX42" s="58" t="n"/>
       <c r="AY42" s="33" t="n"/>
       <c r="AZ42" s="33" t="n"/>
       <c r="BA42" s="34" t="n"/>
-      <c r="BB42" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BB42" s="58" t="n"/>
       <c r="BC42" s="33" t="n"/>
       <c r="BD42" s="33" t="n"/>
       <c r="BE42" s="34" t="n"/>
-      <c r="BF42" s="86" t="n"/>
+      <c r="BF42" s="58" t="n"/>
       <c r="BG42" s="33" t="n"/>
       <c r="BH42" s="33" t="n"/>
       <c r="BI42" s="34" t="n"/>
-      <c r="BJ42" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BJ42" s="58" t="n"/>
       <c r="BK42" s="33" t="n"/>
-      <c r="BL42" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BL42" s="33" t="n"/>
       <c r="BM42" s="34" t="n"/>
-      <c r="BN42" s="86" t="n"/>
+      <c r="BN42" s="58" t="n"/>
       <c r="BO42" s="33" t="n"/>
       <c r="BP42" s="33" t="n"/>
       <c r="BQ42" s="34" t="n"/>
-      <c r="BR42" s="86" t="n"/>
+      <c r="BR42" s="58" t="n"/>
       <c r="BS42" s="33" t="n"/>
       <c r="BT42" s="33" t="n"/>
       <c r="BU42" s="34" t="n"/>
-      <c r="BV42" s="86" t="n"/>
+      <c r="BV42" s="58" t="n"/>
       <c r="BW42" s="33" t="n"/>
       <c r="BX42" s="33" t="n"/>
       <c r="BY42" s="34" t="n"/>
       <c r="BZ42" s="31" t="n"/>
-      <c r="CA42" s="41" t="n"/>
-      <c r="CB42" s="41" t="n"/>
-      <c r="CC42" s="42" t="n"/>
+      <c r="CA42" s="38" t="n"/>
+      <c r="CB42" s="38" t="n"/>
+      <c r="CC42" s="37" t="n"/>
       <c r="CD42" s="31" t="n"/>
-      <c r="CE42" s="41" t="n"/>
-      <c r="CF42" s="41" t="n"/>
-      <c r="CG42" s="54" t="n"/>
+      <c r="CE42" s="38" t="n"/>
+      <c r="CF42" s="38" t="n"/>
+      <c r="CG42" s="48" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="29" t="inlineStr">
@@ -6189,7 +5645,7 @@
       </c>
       <c r="D43" s="30" t="inlineStr">
         <is>
-          <t>Facinon,TS</t>
+          <t>Facinon</t>
         </is>
       </c>
       <c r="E43" s="30" t="inlineStr">
@@ -6198,97 +5654,85 @@
         </is>
       </c>
       <c r="F43" s="31" t="n"/>
-      <c r="G43" s="41" t="n"/>
-      <c r="H43" s="41" t="n"/>
-      <c r="I43" s="42" t="n"/>
+      <c r="G43" s="38" t="n"/>
+      <c r="H43" s="38" t="n"/>
+      <c r="I43" s="37" t="n"/>
       <c r="J43" s="31" t="n"/>
-      <c r="K43" s="41" t="n"/>
-      <c r="L43" s="41" t="n"/>
-      <c r="M43" s="42" t="n"/>
+      <c r="K43" s="38" t="n"/>
+      <c r="L43" s="38" t="n"/>
+      <c r="M43" s="37" t="n"/>
       <c r="N43" s="31" t="n"/>
-      <c r="O43" s="41" t="n"/>
-      <c r="P43" s="41" t="n"/>
-      <c r="Q43" s="42" t="n"/>
+      <c r="O43" s="38" t="n"/>
+      <c r="P43" s="38" t="n"/>
+      <c r="Q43" s="37" t="n"/>
       <c r="R43" s="31" t="n"/>
-      <c r="S43" s="41" t="n"/>
-      <c r="T43" s="41" t="n"/>
-      <c r="U43" s="42" t="n"/>
+      <c r="S43" s="38" t="n"/>
+      <c r="T43" s="38" t="n"/>
+      <c r="U43" s="37" t="n"/>
       <c r="V43" s="31" t="n"/>
-      <c r="W43" s="41" t="n"/>
-      <c r="X43" s="41" t="n"/>
-      <c r="Y43" s="42" t="n"/>
+      <c r="W43" s="38" t="n"/>
+      <c r="X43" s="38" t="n"/>
+      <c r="Y43" s="37" t="n"/>
       <c r="Z43" s="31" t="n"/>
-      <c r="AA43" s="41" t="n"/>
-      <c r="AB43" s="41" t="n"/>
-      <c r="AC43" s="42" t="n"/>
+      <c r="AA43" s="38" t="n"/>
+      <c r="AB43" s="38" t="n"/>
+      <c r="AC43" s="37" t="n"/>
       <c r="AD43" s="31" t="n"/>
-      <c r="AE43" s="41" t="n"/>
-      <c r="AF43" s="41" t="n"/>
-      <c r="AG43" s="42" t="n"/>
+      <c r="AE43" s="38" t="n"/>
+      <c r="AF43" s="38" t="n"/>
+      <c r="AG43" s="37" t="n"/>
       <c r="AH43" s="31" t="n"/>
-      <c r="AI43" s="41" t="n"/>
-      <c r="AJ43" s="41" t="n"/>
-      <c r="AK43" s="42" t="n"/>
+      <c r="AI43" s="38" t="n"/>
+      <c r="AJ43" s="38" t="n"/>
+      <c r="AK43" s="37" t="n"/>
       <c r="AL43" s="31" t="n"/>
-      <c r="AM43" s="41" t="n"/>
-      <c r="AN43" s="41" t="n"/>
-      <c r="AO43" s="42" t="n"/>
+      <c r="AM43" s="38" t="n"/>
+      <c r="AN43" s="38" t="n"/>
+      <c r="AO43" s="37" t="n"/>
       <c r="AP43" s="31" t="n"/>
-      <c r="AQ43" s="41" t="n"/>
-      <c r="AR43" s="41" t="n"/>
-      <c r="AS43" s="42" t="n"/>
+      <c r="AQ43" s="38" t="n"/>
+      <c r="AR43" s="38" t="n"/>
+      <c r="AS43" s="37" t="n"/>
       <c r="AT43" s="31" t="n"/>
-      <c r="AU43" s="41" t="n"/>
-      <c r="AV43" s="41" t="n"/>
-      <c r="AW43" s="42" t="n"/>
-      <c r="AX43" s="92" t="n"/>
+      <c r="AU43" s="38" t="n"/>
+      <c r="AV43" s="38" t="n"/>
+      <c r="AW43" s="37" t="n"/>
+      <c r="AX43" s="64" t="n"/>
       <c r="AY43" s="33" t="n"/>
       <c r="AZ43" s="33" t="n"/>
       <c r="BA43" s="34" t="n"/>
-      <c r="BB43" s="48" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="BB43" s="64" t="n"/>
       <c r="BC43" s="33" t="n"/>
       <c r="BD43" s="33" t="n"/>
       <c r="BE43" s="34" t="n"/>
-      <c r="BF43" s="35" t="inlineStr">
-        <is>
-          <t>Security Check</t>
-        </is>
-      </c>
+      <c r="BF43" s="64" t="n"/>
       <c r="BG43" s="33" t="n"/>
       <c r="BH43" s="33" t="n"/>
       <c r="BI43" s="34" t="n"/>
-      <c r="BJ43" s="55" t="inlineStr">
-        <is>
-          <t>VIP/MIP</t>
-        </is>
-      </c>
+      <c r="BJ43" s="64" t="n"/>
       <c r="BK43" s="33" t="n"/>
       <c r="BL43" s="33" t="n"/>
       <c r="BM43" s="34" t="n"/>
       <c r="BN43" s="31" t="n"/>
-      <c r="BO43" s="41" t="n"/>
-      <c r="BP43" s="41" t="n"/>
-      <c r="BQ43" s="42" t="n"/>
+      <c r="BO43" s="38" t="n"/>
+      <c r="BP43" s="38" t="n"/>
+      <c r="BQ43" s="37" t="n"/>
       <c r="BR43" s="31" t="n"/>
-      <c r="BS43" s="41" t="n"/>
-      <c r="BT43" s="41" t="n"/>
-      <c r="BU43" s="42" t="n"/>
+      <c r="BS43" s="38" t="n"/>
+      <c r="BT43" s="38" t="n"/>
+      <c r="BU43" s="37" t="n"/>
       <c r="BV43" s="31" t="n"/>
-      <c r="BW43" s="41" t="n"/>
-      <c r="BX43" s="41" t="n"/>
-      <c r="BY43" s="42" t="n"/>
+      <c r="BW43" s="38" t="n"/>
+      <c r="BX43" s="38" t="n"/>
+      <c r="BY43" s="37" t="n"/>
       <c r="BZ43" s="31" t="n"/>
-      <c r="CA43" s="41" t="n"/>
-      <c r="CB43" s="41" t="n"/>
-      <c r="CC43" s="42" t="n"/>
+      <c r="CA43" s="38" t="n"/>
+      <c r="CB43" s="38" t="n"/>
+      <c r="CC43" s="37" t="n"/>
       <c r="CD43" s="31" t="n"/>
-      <c r="CE43" s="41" t="n"/>
-      <c r="CF43" s="41" t="n"/>
-      <c r="CG43" s="54" t="n"/>
+      <c r="CE43" s="38" t="n"/>
+      <c r="CF43" s="38" t="n"/>
+      <c r="CG43" s="48" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="29" t="inlineStr">
@@ -6308,7 +5752,7 @@
       </c>
       <c r="D44" s="30" t="inlineStr">
         <is>
-          <t>Madarbukus,I</t>
+          <t>Madarbukus</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -6317,97 +5761,85 @@
         </is>
       </c>
       <c r="F44" s="31" t="n"/>
-      <c r="G44" s="41" t="n"/>
-      <c r="H44" s="41" t="n"/>
-      <c r="I44" s="42" t="n"/>
+      <c r="G44" s="38" t="n"/>
+      <c r="H44" s="38" t="n"/>
+      <c r="I44" s="37" t="n"/>
       <c r="J44" s="31" t="n"/>
-      <c r="K44" s="41" t="n"/>
-      <c r="L44" s="41" t="n"/>
-      <c r="M44" s="42" t="n"/>
+      <c r="K44" s="38" t="n"/>
+      <c r="L44" s="38" t="n"/>
+      <c r="M44" s="37" t="n"/>
       <c r="N44" s="31" t="n"/>
-      <c r="O44" s="41" t="n"/>
-      <c r="P44" s="41" t="n"/>
-      <c r="Q44" s="42" t="n"/>
+      <c r="O44" s="38" t="n"/>
+      <c r="P44" s="38" t="n"/>
+      <c r="Q44" s="37" t="n"/>
       <c r="R44" s="31" t="n"/>
-      <c r="S44" s="41" t="n"/>
-      <c r="T44" s="41" t="n"/>
-      <c r="U44" s="42" t="n"/>
+      <c r="S44" s="38" t="n"/>
+      <c r="T44" s="38" t="n"/>
+      <c r="U44" s="37" t="n"/>
       <c r="V44" s="31" t="n"/>
-      <c r="W44" s="41" t="n"/>
-      <c r="X44" s="41" t="n"/>
-      <c r="Y44" s="42" t="n"/>
+      <c r="W44" s="38" t="n"/>
+      <c r="X44" s="38" t="n"/>
+      <c r="Y44" s="37" t="n"/>
       <c r="Z44" s="31" t="n"/>
-      <c r="AA44" s="41" t="n"/>
-      <c r="AB44" s="41" t="n"/>
-      <c r="AC44" s="42" t="n"/>
+      <c r="AA44" s="38" t="n"/>
+      <c r="AB44" s="38" t="n"/>
+      <c r="AC44" s="37" t="n"/>
       <c r="AD44" s="31" t="n"/>
-      <c r="AE44" s="41" t="n"/>
-      <c r="AF44" s="41" t="n"/>
-      <c r="AG44" s="42" t="n"/>
+      <c r="AE44" s="38" t="n"/>
+      <c r="AF44" s="38" t="n"/>
+      <c r="AG44" s="37" t="n"/>
       <c r="AH44" s="31" t="n"/>
-      <c r="AI44" s="41" t="n"/>
-      <c r="AJ44" s="41" t="n"/>
-      <c r="AK44" s="42" t="n"/>
+      <c r="AI44" s="38" t="n"/>
+      <c r="AJ44" s="38" t="n"/>
+      <c r="AK44" s="37" t="n"/>
       <c r="AL44" s="31" t="n"/>
-      <c r="AM44" s="41" t="n"/>
-      <c r="AN44" s="41" t="n"/>
-      <c r="AO44" s="42" t="n"/>
+      <c r="AM44" s="38" t="n"/>
+      <c r="AN44" s="38" t="n"/>
+      <c r="AO44" s="37" t="n"/>
       <c r="AP44" s="31" t="n"/>
-      <c r="AQ44" s="41" t="n"/>
-      <c r="AR44" s="41" t="n"/>
-      <c r="AS44" s="42" t="n"/>
+      <c r="AQ44" s="38" t="n"/>
+      <c r="AR44" s="38" t="n"/>
+      <c r="AS44" s="37" t="n"/>
       <c r="AT44" s="31" t="n"/>
-      <c r="AU44" s="41" t="n"/>
-      <c r="AV44" s="41" t="n"/>
-      <c r="AW44" s="42" t="n"/>
+      <c r="AU44" s="38" t="n"/>
+      <c r="AV44" s="38" t="n"/>
+      <c r="AW44" s="37" t="n"/>
       <c r="AX44" s="31" t="n"/>
-      <c r="AY44" s="41" t="n"/>
-      <c r="AZ44" s="41" t="n"/>
-      <c r="BA44" s="42" t="n"/>
-      <c r="BB44" s="92" t="n"/>
+      <c r="AY44" s="38" t="n"/>
+      <c r="AZ44" s="38" t="n"/>
+      <c r="BA44" s="37" t="n"/>
+      <c r="BB44" s="64" t="n"/>
       <c r="BC44" s="33" t="n"/>
       <c r="BD44" s="33" t="n"/>
       <c r="BE44" s="34" t="n"/>
-      <c r="BF44" s="48" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+      <c r="BF44" s="64" t="n"/>
       <c r="BG44" s="33" t="n"/>
       <c r="BH44" s="33" t="n"/>
       <c r="BI44" s="34" t="n"/>
-      <c r="BJ44" s="92" t="n"/>
+      <c r="BJ44" s="64" t="n"/>
       <c r="BK44" s="33" t="n"/>
       <c r="BL44" s="33" t="n"/>
       <c r="BM44" s="34" t="n"/>
-      <c r="BN44" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BN44" s="64" t="n"/>
       <c r="BO44" s="33" t="n"/>
-      <c r="BP44" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BP44" s="33" t="n"/>
       <c r="BQ44" s="34" t="n"/>
-      <c r="BR44" s="92" t="n"/>
+      <c r="BR44" s="64" t="n"/>
       <c r="BS44" s="33" t="n"/>
       <c r="BT44" s="33" t="n"/>
       <c r="BU44" s="34" t="n"/>
-      <c r="BV44" s="92" t="n"/>
+      <c r="BV44" s="64" t="n"/>
       <c r="BW44" s="33" t="n"/>
       <c r="BX44" s="33" t="n"/>
       <c r="BY44" s="34" t="n"/>
-      <c r="BZ44" s="92" t="n"/>
+      <c r="BZ44" s="64" t="n"/>
       <c r="CA44" s="33" t="n"/>
       <c r="CB44" s="33" t="n"/>
       <c r="CC44" s="34" t="n"/>
-      <c r="CD44" s="96" t="n"/>
+      <c r="CD44" s="64" t="n"/>
       <c r="CE44" s="33" t="n"/>
       <c r="CF44" s="33" t="n"/>
-      <c r="CG44" s="54" t="n"/>
+      <c r="CG44" s="49" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="29" t="inlineStr">
@@ -6427,7 +5859,7 @@
       </c>
       <c r="D45" s="30" t="inlineStr">
         <is>
-          <t>Gomes,JE</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="E45" s="30" t="inlineStr">
@@ -6436,93 +5868,85 @@
         </is>
       </c>
       <c r="F45" s="31" t="n"/>
-      <c r="G45" s="41" t="n"/>
-      <c r="H45" s="41" t="n"/>
-      <c r="I45" s="42" t="n"/>
+      <c r="G45" s="38" t="n"/>
+      <c r="H45" s="38" t="n"/>
+      <c r="I45" s="37" t="n"/>
       <c r="J45" s="31" t="n"/>
-      <c r="K45" s="41" t="n"/>
-      <c r="L45" s="41" t="n"/>
-      <c r="M45" s="42" t="n"/>
+      <c r="K45" s="38" t="n"/>
+      <c r="L45" s="38" t="n"/>
+      <c r="M45" s="37" t="n"/>
       <c r="N45" s="31" t="n"/>
-      <c r="O45" s="41" t="n"/>
-      <c r="P45" s="41" t="n"/>
-      <c r="Q45" s="42" t="n"/>
+      <c r="O45" s="38" t="n"/>
+      <c r="P45" s="38" t="n"/>
+      <c r="Q45" s="37" t="n"/>
       <c r="R45" s="31" t="n"/>
-      <c r="S45" s="41" t="n"/>
-      <c r="T45" s="41" t="n"/>
-      <c r="U45" s="42" t="n"/>
+      <c r="S45" s="38" t="n"/>
+      <c r="T45" s="38" t="n"/>
+      <c r="U45" s="37" t="n"/>
       <c r="V45" s="31" t="n"/>
-      <c r="W45" s="41" t="n"/>
-      <c r="X45" s="41" t="n"/>
-      <c r="Y45" s="42" t="n"/>
+      <c r="W45" s="38" t="n"/>
+      <c r="X45" s="38" t="n"/>
+      <c r="Y45" s="37" t="n"/>
       <c r="Z45" s="31" t="n"/>
-      <c r="AA45" s="41" t="n"/>
-      <c r="AB45" s="41" t="n"/>
-      <c r="AC45" s="42" t="n"/>
+      <c r="AA45" s="38" t="n"/>
+      <c r="AB45" s="38" t="n"/>
+      <c r="AC45" s="37" t="n"/>
       <c r="AD45" s="31" t="n"/>
-      <c r="AE45" s="41" t="n"/>
-      <c r="AF45" s="41" t="n"/>
-      <c r="AG45" s="42" t="n"/>
+      <c r="AE45" s="38" t="n"/>
+      <c r="AF45" s="38" t="n"/>
+      <c r="AG45" s="37" t="n"/>
       <c r="AH45" s="31" t="n"/>
-      <c r="AI45" s="41" t="n"/>
-      <c r="AJ45" s="41" t="n"/>
-      <c r="AK45" s="42" t="n"/>
+      <c r="AI45" s="38" t="n"/>
+      <c r="AJ45" s="38" t="n"/>
+      <c r="AK45" s="37" t="n"/>
       <c r="AL45" s="31" t="n"/>
-      <c r="AM45" s="41" t="n"/>
-      <c r="AN45" s="41" t="n"/>
-      <c r="AO45" s="42" t="n"/>
+      <c r="AM45" s="38" t="n"/>
+      <c r="AN45" s="38" t="n"/>
+      <c r="AO45" s="37" t="n"/>
       <c r="AP45" s="31" t="n"/>
-      <c r="AQ45" s="41" t="n"/>
-      <c r="AR45" s="41" t="n"/>
-      <c r="AS45" s="42" t="n"/>
+      <c r="AQ45" s="38" t="n"/>
+      <c r="AR45" s="38" t="n"/>
+      <c r="AS45" s="37" t="n"/>
       <c r="AT45" s="31" t="n"/>
-      <c r="AU45" s="41" t="n"/>
-      <c r="AV45" s="41" t="n"/>
-      <c r="AW45" s="42" t="n"/>
+      <c r="AU45" s="38" t="n"/>
+      <c r="AV45" s="38" t="n"/>
+      <c r="AW45" s="37" t="n"/>
       <c r="AX45" s="31" t="n"/>
-      <c r="AY45" s="41" t="n"/>
-      <c r="AZ45" s="41" t="n"/>
-      <c r="BA45" s="42" t="n"/>
+      <c r="AY45" s="38" t="n"/>
+      <c r="AZ45" s="38" t="n"/>
+      <c r="BA45" s="37" t="n"/>
       <c r="BB45" s="31" t="n"/>
-      <c r="BC45" s="41" t="n"/>
-      <c r="BD45" s="85" t="n"/>
+      <c r="BC45" s="38" t="n"/>
+      <c r="BD45" s="57" t="n"/>
       <c r="BE45" s="34" t="n"/>
-      <c r="BF45" s="86" t="n"/>
+      <c r="BF45" s="58" t="n"/>
       <c r="BG45" s="33" t="n"/>
       <c r="BH45" s="33" t="n"/>
       <c r="BI45" s="34" t="n"/>
-      <c r="BJ45" s="86" t="n"/>
+      <c r="BJ45" s="58" t="n"/>
       <c r="BK45" s="33" t="n"/>
       <c r="BL45" s="33" t="n"/>
       <c r="BM45" s="34" t="n"/>
-      <c r="BN45" s="86" t="n"/>
+      <c r="BN45" s="58" t="n"/>
       <c r="BO45" s="33" t="n"/>
       <c r="BP45" s="33" t="n"/>
       <c r="BQ45" s="34" t="n"/>
-      <c r="BR45" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BR45" s="58" t="n"/>
       <c r="BS45" s="33" t="n"/>
-      <c r="BT45" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BT45" s="33" t="n"/>
       <c r="BU45" s="34" t="n"/>
-      <c r="BV45" s="86" t="n"/>
+      <c r="BV45" s="58" t="n"/>
       <c r="BW45" s="33" t="n"/>
       <c r="BX45" s="33" t="n"/>
       <c r="BY45" s="34" t="n"/>
-      <c r="BZ45" s="86" t="n"/>
+      <c r="BZ45" s="58" t="n"/>
       <c r="CA45" s="33" t="n"/>
       <c r="CB45" s="33" t="n"/>
       <c r="CC45" s="34" t="n"/>
-      <c r="CD45" s="87" t="n"/>
+      <c r="CD45" s="58" t="n"/>
       <c r="CE45" s="33" t="n"/>
       <c r="CF45" s="33" t="n"/>
-      <c r="CG45" s="54" t="n"/>
+      <c r="CG45" s="49" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="29" t="inlineStr"/>
@@ -6531,85 +5955,85 @@
       <c r="D46" s="30" t="n"/>
       <c r="E46" s="30" t="n"/>
       <c r="F46" s="31" t="n"/>
-      <c r="G46" s="41" t="n"/>
-      <c r="H46" s="41" t="n"/>
-      <c r="I46" s="42" t="n"/>
+      <c r="G46" s="38" t="n"/>
+      <c r="H46" s="38" t="n"/>
+      <c r="I46" s="37" t="n"/>
       <c r="J46" s="31" t="n"/>
-      <c r="K46" s="41" t="n"/>
-      <c r="L46" s="41" t="n"/>
-      <c r="M46" s="42" t="n"/>
+      <c r="K46" s="38" t="n"/>
+      <c r="L46" s="38" t="n"/>
+      <c r="M46" s="37" t="n"/>
       <c r="N46" s="31" t="n"/>
-      <c r="O46" s="41" t="n"/>
-      <c r="P46" s="41" t="n"/>
-      <c r="Q46" s="42" t="n"/>
+      <c r="O46" s="38" t="n"/>
+      <c r="P46" s="38" t="n"/>
+      <c r="Q46" s="37" t="n"/>
       <c r="R46" s="31" t="n"/>
-      <c r="S46" s="41" t="n"/>
-      <c r="T46" s="41" t="n"/>
-      <c r="U46" s="42" t="n"/>
+      <c r="S46" s="38" t="n"/>
+      <c r="T46" s="38" t="n"/>
+      <c r="U46" s="37" t="n"/>
       <c r="V46" s="31" t="n"/>
-      <c r="W46" s="41" t="n"/>
-      <c r="X46" s="41" t="n"/>
-      <c r="Y46" s="42" t="n"/>
+      <c r="W46" s="38" t="n"/>
+      <c r="X46" s="38" t="n"/>
+      <c r="Y46" s="37" t="n"/>
       <c r="Z46" s="31" t="n"/>
-      <c r="AA46" s="41" t="n"/>
-      <c r="AB46" s="41" t="n"/>
-      <c r="AC46" s="42" t="n"/>
+      <c r="AA46" s="38" t="n"/>
+      <c r="AB46" s="38" t="n"/>
+      <c r="AC46" s="37" t="n"/>
       <c r="AD46" s="31" t="n"/>
-      <c r="AE46" s="41" t="n"/>
-      <c r="AF46" s="41" t="n"/>
-      <c r="AG46" s="42" t="n"/>
+      <c r="AE46" s="38" t="n"/>
+      <c r="AF46" s="38" t="n"/>
+      <c r="AG46" s="37" t="n"/>
       <c r="AH46" s="31" t="n"/>
-      <c r="AI46" s="41" t="n"/>
-      <c r="AJ46" s="41" t="n"/>
-      <c r="AK46" s="42" t="n"/>
+      <c r="AI46" s="38" t="n"/>
+      <c r="AJ46" s="38" t="n"/>
+      <c r="AK46" s="37" t="n"/>
       <c r="AL46" s="31" t="n"/>
-      <c r="AM46" s="41" t="n"/>
-      <c r="AN46" s="41" t="n"/>
-      <c r="AO46" s="42" t="n"/>
+      <c r="AM46" s="38" t="n"/>
+      <c r="AN46" s="38" t="n"/>
+      <c r="AO46" s="37" t="n"/>
       <c r="AP46" s="31" t="n"/>
-      <c r="AQ46" s="41" t="n"/>
-      <c r="AR46" s="41" t="n"/>
-      <c r="AS46" s="42" t="n"/>
+      <c r="AQ46" s="38" t="n"/>
+      <c r="AR46" s="38" t="n"/>
+      <c r="AS46" s="37" t="n"/>
       <c r="AT46" s="31" t="n"/>
-      <c r="AU46" s="41" t="n"/>
-      <c r="AV46" s="41" t="n"/>
-      <c r="AW46" s="42" t="n"/>
+      <c r="AU46" s="38" t="n"/>
+      <c r="AV46" s="38" t="n"/>
+      <c r="AW46" s="37" t="n"/>
       <c r="AX46" s="31" t="n"/>
-      <c r="AY46" s="41" t="n"/>
-      <c r="AZ46" s="41" t="n"/>
-      <c r="BA46" s="42" t="n"/>
+      <c r="AY46" s="38" t="n"/>
+      <c r="AZ46" s="38" t="n"/>
+      <c r="BA46" s="37" t="n"/>
       <c r="BB46" s="31" t="n"/>
-      <c r="BC46" s="41" t="n"/>
-      <c r="BD46" s="41" t="n"/>
-      <c r="BE46" s="42" t="n"/>
+      <c r="BC46" s="38" t="n"/>
+      <c r="BD46" s="38" t="n"/>
+      <c r="BE46" s="37" t="n"/>
       <c r="BF46" s="31" t="n"/>
-      <c r="BG46" s="41" t="n"/>
-      <c r="BH46" s="41" t="n"/>
-      <c r="BI46" s="42" t="n"/>
+      <c r="BG46" s="38" t="n"/>
+      <c r="BH46" s="38" t="n"/>
+      <c r="BI46" s="37" t="n"/>
       <c r="BJ46" s="31" t="n"/>
-      <c r="BK46" s="41" t="n"/>
-      <c r="BL46" s="41" t="n"/>
-      <c r="BM46" s="42" t="n"/>
+      <c r="BK46" s="38" t="n"/>
+      <c r="BL46" s="38" t="n"/>
+      <c r="BM46" s="37" t="n"/>
       <c r="BN46" s="31" t="n"/>
-      <c r="BO46" s="41" t="n"/>
-      <c r="BP46" s="41" t="n"/>
-      <c r="BQ46" s="42" t="n"/>
+      <c r="BO46" s="38" t="n"/>
+      <c r="BP46" s="38" t="n"/>
+      <c r="BQ46" s="37" t="n"/>
       <c r="BR46" s="31" t="n"/>
-      <c r="BS46" s="41" t="n"/>
-      <c r="BT46" s="41" t="n"/>
-      <c r="BU46" s="42" t="n"/>
+      <c r="BS46" s="38" t="n"/>
+      <c r="BT46" s="38" t="n"/>
+      <c r="BU46" s="37" t="n"/>
       <c r="BV46" s="31" t="n"/>
-      <c r="BW46" s="41" t="n"/>
-      <c r="BX46" s="41" t="n"/>
-      <c r="BY46" s="42" t="n"/>
+      <c r="BW46" s="38" t="n"/>
+      <c r="BX46" s="38" t="n"/>
+      <c r="BY46" s="37" t="n"/>
       <c r="BZ46" s="31" t="n"/>
-      <c r="CA46" s="41" t="n"/>
-      <c r="CB46" s="41" t="n"/>
-      <c r="CC46" s="42" t="n"/>
+      <c r="CA46" s="38" t="n"/>
+      <c r="CB46" s="38" t="n"/>
+      <c r="CC46" s="37" t="n"/>
       <c r="CD46" s="31" t="n"/>
-      <c r="CE46" s="41" t="n"/>
-      <c r="CF46" s="41" t="n"/>
-      <c r="CG46" s="54" t="n"/>
+      <c r="CE46" s="38" t="n"/>
+      <c r="CF46" s="38" t="n"/>
+      <c r="CG46" s="48" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="29" t="inlineStr"/>
@@ -6618,85 +6042,85 @@
       <c r="D47" s="30" t="n"/>
       <c r="E47" s="30" t="n"/>
       <c r="F47" s="31" t="n"/>
-      <c r="G47" s="41" t="n"/>
-      <c r="H47" s="41" t="n"/>
-      <c r="I47" s="42" t="n"/>
+      <c r="G47" s="38" t="n"/>
+      <c r="H47" s="38" t="n"/>
+      <c r="I47" s="37" t="n"/>
       <c r="J47" s="31" t="n"/>
-      <c r="K47" s="41" t="n"/>
-      <c r="L47" s="41" t="n"/>
-      <c r="M47" s="42" t="n"/>
+      <c r="K47" s="38" t="n"/>
+      <c r="L47" s="38" t="n"/>
+      <c r="M47" s="37" t="n"/>
       <c r="N47" s="31" t="n"/>
-      <c r="O47" s="41" t="n"/>
-      <c r="P47" s="41" t="n"/>
-      <c r="Q47" s="42" t="n"/>
+      <c r="O47" s="38" t="n"/>
+      <c r="P47" s="38" t="n"/>
+      <c r="Q47" s="37" t="n"/>
       <c r="R47" s="31" t="n"/>
-      <c r="S47" s="41" t="n"/>
-      <c r="T47" s="41" t="n"/>
-      <c r="U47" s="42" t="n"/>
+      <c r="S47" s="38" t="n"/>
+      <c r="T47" s="38" t="n"/>
+      <c r="U47" s="37" t="n"/>
       <c r="V47" s="31" t="n"/>
-      <c r="W47" s="41" t="n"/>
-      <c r="X47" s="41" t="n"/>
-      <c r="Y47" s="42" t="n"/>
+      <c r="W47" s="38" t="n"/>
+      <c r="X47" s="38" t="n"/>
+      <c r="Y47" s="37" t="n"/>
       <c r="Z47" s="31" t="n"/>
-      <c r="AA47" s="41" t="n"/>
-      <c r="AB47" s="41" t="n"/>
-      <c r="AC47" s="42" t="n"/>
+      <c r="AA47" s="38" t="n"/>
+      <c r="AB47" s="38" t="n"/>
+      <c r="AC47" s="37" t="n"/>
       <c r="AD47" s="31" t="n"/>
-      <c r="AE47" s="41" t="n"/>
-      <c r="AF47" s="41" t="n"/>
-      <c r="AG47" s="42" t="n"/>
+      <c r="AE47" s="38" t="n"/>
+      <c r="AF47" s="38" t="n"/>
+      <c r="AG47" s="37" t="n"/>
       <c r="AH47" s="31" t="n"/>
-      <c r="AI47" s="41" t="n"/>
-      <c r="AJ47" s="41" t="n"/>
-      <c r="AK47" s="42" t="n"/>
+      <c r="AI47" s="38" t="n"/>
+      <c r="AJ47" s="38" t="n"/>
+      <c r="AK47" s="37" t="n"/>
       <c r="AL47" s="31" t="n"/>
-      <c r="AM47" s="41" t="n"/>
-      <c r="AN47" s="41" t="n"/>
-      <c r="AO47" s="42" t="n"/>
+      <c r="AM47" s="38" t="n"/>
+      <c r="AN47" s="38" t="n"/>
+      <c r="AO47" s="37" t="n"/>
       <c r="AP47" s="31" t="n"/>
-      <c r="AQ47" s="41" t="n"/>
-      <c r="AR47" s="41" t="n"/>
-      <c r="AS47" s="42" t="n"/>
+      <c r="AQ47" s="38" t="n"/>
+      <c r="AR47" s="38" t="n"/>
+      <c r="AS47" s="37" t="n"/>
       <c r="AT47" s="31" t="n"/>
-      <c r="AU47" s="41" t="n"/>
-      <c r="AV47" s="41" t="n"/>
-      <c r="AW47" s="42" t="n"/>
+      <c r="AU47" s="38" t="n"/>
+      <c r="AV47" s="38" t="n"/>
+      <c r="AW47" s="37" t="n"/>
       <c r="AX47" s="31" t="n"/>
-      <c r="AY47" s="41" t="n"/>
-      <c r="AZ47" s="41" t="n"/>
-      <c r="BA47" s="42" t="n"/>
+      <c r="AY47" s="38" t="n"/>
+      <c r="AZ47" s="38" t="n"/>
+      <c r="BA47" s="37" t="n"/>
       <c r="BB47" s="31" t="n"/>
-      <c r="BC47" s="41" t="n"/>
-      <c r="BD47" s="41" t="n"/>
-      <c r="BE47" s="42" t="n"/>
+      <c r="BC47" s="38" t="n"/>
+      <c r="BD47" s="38" t="n"/>
+      <c r="BE47" s="37" t="n"/>
       <c r="BF47" s="31" t="n"/>
-      <c r="BG47" s="41" t="n"/>
-      <c r="BH47" s="41" t="n"/>
-      <c r="BI47" s="42" t="n"/>
+      <c r="BG47" s="38" t="n"/>
+      <c r="BH47" s="38" t="n"/>
+      <c r="BI47" s="37" t="n"/>
       <c r="BJ47" s="31" t="n"/>
-      <c r="BK47" s="41" t="n"/>
-      <c r="BL47" s="41" t="n"/>
-      <c r="BM47" s="42" t="n"/>
+      <c r="BK47" s="38" t="n"/>
+      <c r="BL47" s="38" t="n"/>
+      <c r="BM47" s="37" t="n"/>
       <c r="BN47" s="31" t="n"/>
-      <c r="BO47" s="41" t="n"/>
-      <c r="BP47" s="41" t="n"/>
-      <c r="BQ47" s="42" t="n"/>
+      <c r="BO47" s="38" t="n"/>
+      <c r="BP47" s="38" t="n"/>
+      <c r="BQ47" s="37" t="n"/>
       <c r="BR47" s="31" t="n"/>
-      <c r="BS47" s="41" t="n"/>
-      <c r="BT47" s="41" t="n"/>
-      <c r="BU47" s="42" t="n"/>
+      <c r="BS47" s="38" t="n"/>
+      <c r="BT47" s="38" t="n"/>
+      <c r="BU47" s="37" t="n"/>
       <c r="BV47" s="31" t="n"/>
-      <c r="BW47" s="41" t="n"/>
-      <c r="BX47" s="41" t="n"/>
-      <c r="BY47" s="42" t="n"/>
+      <c r="BW47" s="38" t="n"/>
+      <c r="BX47" s="38" t="n"/>
+      <c r="BY47" s="37" t="n"/>
       <c r="BZ47" s="31" t="n"/>
-      <c r="CA47" s="41" t="n"/>
-      <c r="CB47" s="41" t="n"/>
-      <c r="CC47" s="42" t="n"/>
+      <c r="CA47" s="38" t="n"/>
+      <c r="CB47" s="38" t="n"/>
+      <c r="CC47" s="37" t="n"/>
       <c r="CD47" s="31" t="n"/>
-      <c r="CE47" s="41" t="n"/>
-      <c r="CF47" s="41" t="n"/>
-      <c r="CG47" s="54" t="n"/>
+      <c r="CE47" s="38" t="n"/>
+      <c r="CF47" s="38" t="n"/>
+      <c r="CG47" s="48" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="29" t="inlineStr"/>
@@ -6705,85 +6129,85 @@
       <c r="D48" s="30" t="n"/>
       <c r="E48" s="30" t="n"/>
       <c r="F48" s="31" t="n"/>
-      <c r="G48" s="41" t="n"/>
-      <c r="H48" s="41" t="n"/>
-      <c r="I48" s="42" t="n"/>
+      <c r="G48" s="38" t="n"/>
+      <c r="H48" s="38" t="n"/>
+      <c r="I48" s="37" t="n"/>
       <c r="J48" s="31" t="n"/>
-      <c r="K48" s="41" t="n"/>
-      <c r="L48" s="41" t="n"/>
-      <c r="M48" s="42" t="n"/>
+      <c r="K48" s="38" t="n"/>
+      <c r="L48" s="38" t="n"/>
+      <c r="M48" s="37" t="n"/>
       <c r="N48" s="31" t="n"/>
-      <c r="O48" s="41" t="n"/>
-      <c r="P48" s="41" t="n"/>
-      <c r="Q48" s="42" t="n"/>
+      <c r="O48" s="38" t="n"/>
+      <c r="P48" s="38" t="n"/>
+      <c r="Q48" s="37" t="n"/>
       <c r="R48" s="31" t="n"/>
-      <c r="S48" s="41" t="n"/>
-      <c r="T48" s="41" t="n"/>
-      <c r="U48" s="42" t="n"/>
+      <c r="S48" s="38" t="n"/>
+      <c r="T48" s="38" t="n"/>
+      <c r="U48" s="37" t="n"/>
       <c r="V48" s="31" t="n"/>
-      <c r="W48" s="41" t="n"/>
-      <c r="X48" s="41" t="n"/>
-      <c r="Y48" s="42" t="n"/>
+      <c r="W48" s="38" t="n"/>
+      <c r="X48" s="38" t="n"/>
+      <c r="Y48" s="37" t="n"/>
       <c r="Z48" s="31" t="n"/>
-      <c r="AA48" s="41" t="n"/>
-      <c r="AB48" s="41" t="n"/>
-      <c r="AC48" s="42" t="n"/>
+      <c r="AA48" s="38" t="n"/>
+      <c r="AB48" s="38" t="n"/>
+      <c r="AC48" s="37" t="n"/>
       <c r="AD48" s="31" t="n"/>
-      <c r="AE48" s="41" t="n"/>
-      <c r="AF48" s="41" t="n"/>
-      <c r="AG48" s="42" t="n"/>
+      <c r="AE48" s="38" t="n"/>
+      <c r="AF48" s="38" t="n"/>
+      <c r="AG48" s="37" t="n"/>
       <c r="AH48" s="31" t="n"/>
-      <c r="AI48" s="41" t="n"/>
-      <c r="AJ48" s="41" t="n"/>
-      <c r="AK48" s="42" t="n"/>
+      <c r="AI48" s="38" t="n"/>
+      <c r="AJ48" s="38" t="n"/>
+      <c r="AK48" s="37" t="n"/>
       <c r="AL48" s="31" t="n"/>
-      <c r="AM48" s="41" t="n"/>
-      <c r="AN48" s="41" t="n"/>
-      <c r="AO48" s="42" t="n"/>
+      <c r="AM48" s="38" t="n"/>
+      <c r="AN48" s="38" t="n"/>
+      <c r="AO48" s="37" t="n"/>
       <c r="AP48" s="31" t="n"/>
-      <c r="AQ48" s="41" t="n"/>
-      <c r="AR48" s="41" t="n"/>
-      <c r="AS48" s="42" t="n"/>
+      <c r="AQ48" s="38" t="n"/>
+      <c r="AR48" s="38" t="n"/>
+      <c r="AS48" s="37" t="n"/>
       <c r="AT48" s="31" t="n"/>
-      <c r="AU48" s="41" t="n"/>
-      <c r="AV48" s="41" t="n"/>
-      <c r="AW48" s="42" t="n"/>
+      <c r="AU48" s="38" t="n"/>
+      <c r="AV48" s="38" t="n"/>
+      <c r="AW48" s="37" t="n"/>
       <c r="AX48" s="31" t="n"/>
-      <c r="AY48" s="41" t="n"/>
-      <c r="AZ48" s="41" t="n"/>
-      <c r="BA48" s="42" t="n"/>
+      <c r="AY48" s="38" t="n"/>
+      <c r="AZ48" s="38" t="n"/>
+      <c r="BA48" s="37" t="n"/>
       <c r="BB48" s="31" t="n"/>
-      <c r="BC48" s="41" t="n"/>
-      <c r="BD48" s="41" t="n"/>
-      <c r="BE48" s="42" t="n"/>
+      <c r="BC48" s="38" t="n"/>
+      <c r="BD48" s="38" t="n"/>
+      <c r="BE48" s="37" t="n"/>
       <c r="BF48" s="31" t="n"/>
-      <c r="BG48" s="41" t="n"/>
-      <c r="BH48" s="41" t="n"/>
-      <c r="BI48" s="42" t="n"/>
+      <c r="BG48" s="38" t="n"/>
+      <c r="BH48" s="38" t="n"/>
+      <c r="BI48" s="37" t="n"/>
       <c r="BJ48" s="31" t="n"/>
-      <c r="BK48" s="41" t="n"/>
-      <c r="BL48" s="41" t="n"/>
-      <c r="BM48" s="42" t="n"/>
+      <c r="BK48" s="38" t="n"/>
+      <c r="BL48" s="38" t="n"/>
+      <c r="BM48" s="37" t="n"/>
       <c r="BN48" s="31" t="n"/>
-      <c r="BO48" s="41" t="n"/>
-      <c r="BP48" s="41" t="n"/>
-      <c r="BQ48" s="42" t="n"/>
+      <c r="BO48" s="38" t="n"/>
+      <c r="BP48" s="38" t="n"/>
+      <c r="BQ48" s="37" t="n"/>
       <c r="BR48" s="31" t="n"/>
-      <c r="BS48" s="41" t="n"/>
-      <c r="BT48" s="41" t="n"/>
-      <c r="BU48" s="42" t="n"/>
+      <c r="BS48" s="38" t="n"/>
+      <c r="BT48" s="38" t="n"/>
+      <c r="BU48" s="37" t="n"/>
       <c r="BV48" s="31" t="n"/>
-      <c r="BW48" s="41" t="n"/>
-      <c r="BX48" s="41" t="n"/>
-      <c r="BY48" s="42" t="n"/>
+      <c r="BW48" s="38" t="n"/>
+      <c r="BX48" s="38" t="n"/>
+      <c r="BY48" s="37" t="n"/>
       <c r="BZ48" s="31" t="n"/>
-      <c r="CA48" s="41" t="n"/>
-      <c r="CB48" s="41" t="n"/>
-      <c r="CC48" s="42" t="n"/>
+      <c r="CA48" s="38" t="n"/>
+      <c r="CB48" s="38" t="n"/>
+      <c r="CC48" s="37" t="n"/>
       <c r="CD48" s="31" t="n"/>
-      <c r="CE48" s="41" t="n"/>
-      <c r="CF48" s="41" t="n"/>
-      <c r="CG48" s="54" t="n"/>
+      <c r="CE48" s="38" t="n"/>
+      <c r="CF48" s="38" t="n"/>
+      <c r="CG48" s="48" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="29" t="inlineStr"/>
@@ -6792,172 +6216,172 @@
       <c r="D49" s="30" t="n"/>
       <c r="E49" s="30" t="n"/>
       <c r="F49" s="31" t="n"/>
-      <c r="G49" s="41" t="n"/>
-      <c r="H49" s="41" t="n"/>
-      <c r="I49" s="42" t="n"/>
+      <c r="G49" s="38" t="n"/>
+      <c r="H49" s="38" t="n"/>
+      <c r="I49" s="37" t="n"/>
       <c r="J49" s="31" t="n"/>
-      <c r="K49" s="41" t="n"/>
-      <c r="L49" s="41" t="n"/>
-      <c r="M49" s="42" t="n"/>
+      <c r="K49" s="38" t="n"/>
+      <c r="L49" s="38" t="n"/>
+      <c r="M49" s="37" t="n"/>
       <c r="N49" s="31" t="n"/>
-      <c r="O49" s="41" t="n"/>
-      <c r="P49" s="41" t="n"/>
-      <c r="Q49" s="42" t="n"/>
+      <c r="O49" s="38" t="n"/>
+      <c r="P49" s="38" t="n"/>
+      <c r="Q49" s="37" t="n"/>
       <c r="R49" s="31" t="n"/>
-      <c r="S49" s="41" t="n"/>
-      <c r="T49" s="41" t="n"/>
-      <c r="U49" s="42" t="n"/>
+      <c r="S49" s="38" t="n"/>
+      <c r="T49" s="38" t="n"/>
+      <c r="U49" s="37" t="n"/>
       <c r="V49" s="31" t="n"/>
-      <c r="W49" s="41" t="n"/>
-      <c r="X49" s="41" t="n"/>
-      <c r="Y49" s="42" t="n"/>
+      <c r="W49" s="38" t="n"/>
+      <c r="X49" s="38" t="n"/>
+      <c r="Y49" s="37" t="n"/>
       <c r="Z49" s="31" t="n"/>
-      <c r="AA49" s="41" t="n"/>
-      <c r="AB49" s="41" t="n"/>
-      <c r="AC49" s="42" t="n"/>
+      <c r="AA49" s="38" t="n"/>
+      <c r="AB49" s="38" t="n"/>
+      <c r="AC49" s="37" t="n"/>
       <c r="AD49" s="31" t="n"/>
-      <c r="AE49" s="41" t="n"/>
-      <c r="AF49" s="41" t="n"/>
-      <c r="AG49" s="42" t="n"/>
+      <c r="AE49" s="38" t="n"/>
+      <c r="AF49" s="38" t="n"/>
+      <c r="AG49" s="37" t="n"/>
       <c r="AH49" s="31" t="n"/>
-      <c r="AI49" s="41" t="n"/>
-      <c r="AJ49" s="41" t="n"/>
-      <c r="AK49" s="42" t="n"/>
+      <c r="AI49" s="38" t="n"/>
+      <c r="AJ49" s="38" t="n"/>
+      <c r="AK49" s="37" t="n"/>
       <c r="AL49" s="31" t="n"/>
-      <c r="AM49" s="41" t="n"/>
-      <c r="AN49" s="41" t="n"/>
-      <c r="AO49" s="42" t="n"/>
+      <c r="AM49" s="38" t="n"/>
+      <c r="AN49" s="38" t="n"/>
+      <c r="AO49" s="37" t="n"/>
       <c r="AP49" s="31" t="n"/>
-      <c r="AQ49" s="41" t="n"/>
-      <c r="AR49" s="41" t="n"/>
-      <c r="AS49" s="42" t="n"/>
+      <c r="AQ49" s="38" t="n"/>
+      <c r="AR49" s="38" t="n"/>
+      <c r="AS49" s="37" t="n"/>
       <c r="AT49" s="31" t="n"/>
-      <c r="AU49" s="41" t="n"/>
-      <c r="AV49" s="41" t="n"/>
-      <c r="AW49" s="42" t="n"/>
+      <c r="AU49" s="38" t="n"/>
+      <c r="AV49" s="38" t="n"/>
+      <c r="AW49" s="37" t="n"/>
       <c r="AX49" s="31" t="n"/>
-      <c r="AY49" s="41" t="n"/>
-      <c r="AZ49" s="41" t="n"/>
-      <c r="BA49" s="42" t="n"/>
+      <c r="AY49" s="38" t="n"/>
+      <c r="AZ49" s="38" t="n"/>
+      <c r="BA49" s="37" t="n"/>
       <c r="BB49" s="31" t="n"/>
-      <c r="BC49" s="41" t="n"/>
-      <c r="BD49" s="41" t="n"/>
-      <c r="BE49" s="42" t="n"/>
+      <c r="BC49" s="38" t="n"/>
+      <c r="BD49" s="38" t="n"/>
+      <c r="BE49" s="37" t="n"/>
       <c r="BF49" s="31" t="n"/>
-      <c r="BG49" s="41" t="n"/>
-      <c r="BH49" s="41" t="n"/>
-      <c r="BI49" s="42" t="n"/>
+      <c r="BG49" s="38" t="n"/>
+      <c r="BH49" s="38" t="n"/>
+      <c r="BI49" s="37" t="n"/>
       <c r="BJ49" s="31" t="n"/>
-      <c r="BK49" s="41" t="n"/>
-      <c r="BL49" s="41" t="n"/>
-      <c r="BM49" s="42" t="n"/>
+      <c r="BK49" s="38" t="n"/>
+      <c r="BL49" s="38" t="n"/>
+      <c r="BM49" s="37" t="n"/>
       <c r="BN49" s="31" t="n"/>
-      <c r="BO49" s="41" t="n"/>
-      <c r="BP49" s="41" t="n"/>
-      <c r="BQ49" s="42" t="n"/>
+      <c r="BO49" s="38" t="n"/>
+      <c r="BP49" s="38" t="n"/>
+      <c r="BQ49" s="37" t="n"/>
       <c r="BR49" s="31" t="n"/>
-      <c r="BS49" s="41" t="n"/>
-      <c r="BT49" s="41" t="n"/>
-      <c r="BU49" s="42" t="n"/>
+      <c r="BS49" s="38" t="n"/>
+      <c r="BT49" s="38" t="n"/>
+      <c r="BU49" s="37" t="n"/>
       <c r="BV49" s="31" t="n"/>
-      <c r="BW49" s="41" t="n"/>
-      <c r="BX49" s="41" t="n"/>
-      <c r="BY49" s="42" t="n"/>
+      <c r="BW49" s="38" t="n"/>
+      <c r="BX49" s="38" t="n"/>
+      <c r="BY49" s="37" t="n"/>
       <c r="BZ49" s="31" t="n"/>
-      <c r="CA49" s="41" t="n"/>
-      <c r="CB49" s="41" t="n"/>
-      <c r="CC49" s="42" t="n"/>
+      <c r="CA49" s="38" t="n"/>
+      <c r="CB49" s="38" t="n"/>
+      <c r="CC49" s="37" t="n"/>
       <c r="CD49" s="31" t="n"/>
-      <c r="CE49" s="41" t="n"/>
-      <c r="CF49" s="41" t="n"/>
-      <c r="CG49" s="54" t="n"/>
+      <c r="CE49" s="38" t="n"/>
+      <c r="CF49" s="38" t="n"/>
+      <c r="CG49" s="48" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="73" t="inlineStr"/>
-      <c r="B50" s="74" t="n"/>
-      <c r="C50" s="74" t="n"/>
-      <c r="D50" s="74" t="n"/>
-      <c r="E50" s="74" t="n"/>
-      <c r="F50" s="75" t="n"/>
-      <c r="G50" s="76" t="n"/>
-      <c r="H50" s="76" t="n"/>
-      <c r="I50" s="77" t="n"/>
-      <c r="J50" s="75" t="n"/>
-      <c r="K50" s="76" t="n"/>
-      <c r="L50" s="76" t="n"/>
-      <c r="M50" s="77" t="n"/>
-      <c r="N50" s="75" t="n"/>
-      <c r="O50" s="76" t="n"/>
-      <c r="P50" s="76" t="n"/>
-      <c r="Q50" s="77" t="n"/>
-      <c r="R50" s="75" t="n"/>
-      <c r="S50" s="76" t="n"/>
-      <c r="T50" s="76" t="n"/>
-      <c r="U50" s="77" t="n"/>
-      <c r="V50" s="75" t="n"/>
-      <c r="W50" s="76" t="n"/>
-      <c r="X50" s="76" t="n"/>
-      <c r="Y50" s="77" t="n"/>
-      <c r="Z50" s="75" t="n"/>
-      <c r="AA50" s="76" t="n"/>
-      <c r="AB50" s="76" t="n"/>
-      <c r="AC50" s="77" t="n"/>
-      <c r="AD50" s="75" t="n"/>
-      <c r="AE50" s="76" t="n"/>
-      <c r="AF50" s="76" t="n"/>
-      <c r="AG50" s="77" t="n"/>
-      <c r="AH50" s="75" t="n"/>
-      <c r="AI50" s="76" t="n"/>
-      <c r="AJ50" s="76" t="n"/>
-      <c r="AK50" s="77" t="n"/>
-      <c r="AL50" s="75" t="n"/>
-      <c r="AM50" s="76" t="n"/>
-      <c r="AN50" s="76" t="n"/>
-      <c r="AO50" s="77" t="n"/>
-      <c r="AP50" s="75" t="n"/>
-      <c r="AQ50" s="76" t="n"/>
-      <c r="AR50" s="76" t="n"/>
-      <c r="AS50" s="77" t="n"/>
-      <c r="AT50" s="75" t="n"/>
-      <c r="AU50" s="76" t="n"/>
-      <c r="AV50" s="76" t="n"/>
-      <c r="AW50" s="77" t="n"/>
-      <c r="AX50" s="75" t="n"/>
-      <c r="AY50" s="76" t="n"/>
-      <c r="AZ50" s="76" t="n"/>
-      <c r="BA50" s="77" t="n"/>
-      <c r="BB50" s="75" t="n"/>
-      <c r="BC50" s="76" t="n"/>
-      <c r="BD50" s="76" t="n"/>
-      <c r="BE50" s="77" t="n"/>
-      <c r="BF50" s="75" t="n"/>
-      <c r="BG50" s="76" t="n"/>
-      <c r="BH50" s="76" t="n"/>
-      <c r="BI50" s="77" t="n"/>
-      <c r="BJ50" s="75" t="n"/>
-      <c r="BK50" s="76" t="n"/>
-      <c r="BL50" s="76" t="n"/>
-      <c r="BM50" s="77" t="n"/>
-      <c r="BN50" s="75" t="n"/>
-      <c r="BO50" s="76" t="n"/>
-      <c r="BP50" s="76" t="n"/>
-      <c r="BQ50" s="77" t="n"/>
-      <c r="BR50" s="75" t="n"/>
-      <c r="BS50" s="76" t="n"/>
-      <c r="BT50" s="76" t="n"/>
-      <c r="BU50" s="77" t="n"/>
-      <c r="BV50" s="75" t="n"/>
-      <c r="BW50" s="76" t="n"/>
-      <c r="BX50" s="76" t="n"/>
-      <c r="BY50" s="77" t="n"/>
-      <c r="BZ50" s="75" t="n"/>
-      <c r="CA50" s="76" t="n"/>
-      <c r="CB50" s="76" t="n"/>
-      <c r="CC50" s="77" t="n"/>
-      <c r="CD50" s="75" t="n"/>
-      <c r="CE50" s="76" t="n"/>
-      <c r="CF50" s="76" t="n"/>
-      <c r="CG50" s="78" t="n"/>
+      <c r="A50" s="50" t="inlineStr"/>
+      <c r="B50" s="51" t="n"/>
+      <c r="C50" s="51" t="n"/>
+      <c r="D50" s="51" t="n"/>
+      <c r="E50" s="51" t="n"/>
+      <c r="F50" s="52" t="n"/>
+      <c r="G50" s="53" t="n"/>
+      <c r="H50" s="53" t="n"/>
+      <c r="I50" s="54" t="n"/>
+      <c r="J50" s="52" t="n"/>
+      <c r="K50" s="53" t="n"/>
+      <c r="L50" s="53" t="n"/>
+      <c r="M50" s="54" t="n"/>
+      <c r="N50" s="52" t="n"/>
+      <c r="O50" s="53" t="n"/>
+      <c r="P50" s="53" t="n"/>
+      <c r="Q50" s="54" t="n"/>
+      <c r="R50" s="52" t="n"/>
+      <c r="S50" s="53" t="n"/>
+      <c r="T50" s="53" t="n"/>
+      <c r="U50" s="54" t="n"/>
+      <c r="V50" s="52" t="n"/>
+      <c r="W50" s="53" t="n"/>
+      <c r="X50" s="53" t="n"/>
+      <c r="Y50" s="54" t="n"/>
+      <c r="Z50" s="52" t="n"/>
+      <c r="AA50" s="53" t="n"/>
+      <c r="AB50" s="53" t="n"/>
+      <c r="AC50" s="54" t="n"/>
+      <c r="AD50" s="52" t="n"/>
+      <c r="AE50" s="53" t="n"/>
+      <c r="AF50" s="53" t="n"/>
+      <c r="AG50" s="54" t="n"/>
+      <c r="AH50" s="52" t="n"/>
+      <c r="AI50" s="53" t="n"/>
+      <c r="AJ50" s="53" t="n"/>
+      <c r="AK50" s="54" t="n"/>
+      <c r="AL50" s="52" t="n"/>
+      <c r="AM50" s="53" t="n"/>
+      <c r="AN50" s="53" t="n"/>
+      <c r="AO50" s="54" t="n"/>
+      <c r="AP50" s="52" t="n"/>
+      <c r="AQ50" s="53" t="n"/>
+      <c r="AR50" s="53" t="n"/>
+      <c r="AS50" s="54" t="n"/>
+      <c r="AT50" s="52" t="n"/>
+      <c r="AU50" s="53" t="n"/>
+      <c r="AV50" s="53" t="n"/>
+      <c r="AW50" s="54" t="n"/>
+      <c r="AX50" s="52" t="n"/>
+      <c r="AY50" s="53" t="n"/>
+      <c r="AZ50" s="53" t="n"/>
+      <c r="BA50" s="54" t="n"/>
+      <c r="BB50" s="52" t="n"/>
+      <c r="BC50" s="53" t="n"/>
+      <c r="BD50" s="53" t="n"/>
+      <c r="BE50" s="54" t="n"/>
+      <c r="BF50" s="52" t="n"/>
+      <c r="BG50" s="53" t="n"/>
+      <c r="BH50" s="53" t="n"/>
+      <c r="BI50" s="54" t="n"/>
+      <c r="BJ50" s="52" t="n"/>
+      <c r="BK50" s="53" t="n"/>
+      <c r="BL50" s="53" t="n"/>
+      <c r="BM50" s="54" t="n"/>
+      <c r="BN50" s="52" t="n"/>
+      <c r="BO50" s="53" t="n"/>
+      <c r="BP50" s="53" t="n"/>
+      <c r="BQ50" s="54" t="n"/>
+      <c r="BR50" s="52" t="n"/>
+      <c r="BS50" s="53" t="n"/>
+      <c r="BT50" s="53" t="n"/>
+      <c r="BU50" s="54" t="n"/>
+      <c r="BV50" s="52" t="n"/>
+      <c r="BW50" s="53" t="n"/>
+      <c r="BX50" s="53" t="n"/>
+      <c r="BY50" s="54" t="n"/>
+      <c r="BZ50" s="52" t="n"/>
+      <c r="CA50" s="53" t="n"/>
+      <c r="CB50" s="53" t="n"/>
+      <c r="CC50" s="54" t="n"/>
+      <c r="CD50" s="52" t="n"/>
+      <c r="CE50" s="53" t="n"/>
+      <c r="CF50" s="53" t="n"/>
+      <c r="CG50" s="55" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
@@ -7127,111 +6551,111 @@
       <c r="CG52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="79" t="inlineStr">
+      <c r="A53" s="70" t="inlineStr">
         <is>
           <t>Duty No.</t>
         </is>
       </c>
-      <c r="B53" s="80" t="inlineStr">
+      <c r="B53" s="71" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="C53" s="80" t="inlineStr">
+      <c r="C53" s="71" t="inlineStr">
         <is>
           <t>Finish Time</t>
         </is>
       </c>
-      <c r="D53" s="80" t="inlineStr">
+      <c r="D53" s="71" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E53" s="80" t="inlineStr">
+      <c r="E53" s="71" t="inlineStr">
         <is>
           <t>Radio</t>
         </is>
       </c>
-      <c r="F53" s="81" t="n"/>
-      <c r="G53" s="82" t="n"/>
-      <c r="H53" s="82" t="n"/>
-      <c r="I53" s="83" t="n"/>
-      <c r="J53" s="81" t="n"/>
-      <c r="K53" s="82" t="n"/>
-      <c r="L53" s="82" t="n"/>
-      <c r="M53" s="83" t="n"/>
-      <c r="N53" s="81" t="n"/>
-      <c r="O53" s="82" t="n"/>
-      <c r="P53" s="82" t="n"/>
-      <c r="Q53" s="83" t="n"/>
-      <c r="R53" s="81" t="n"/>
-      <c r="S53" s="82" t="n"/>
-      <c r="T53" s="82" t="n"/>
-      <c r="U53" s="83" t="n"/>
-      <c r="V53" s="81" t="n"/>
-      <c r="W53" s="82" t="n"/>
-      <c r="X53" s="82" t="n"/>
-      <c r="Y53" s="83" t="n"/>
-      <c r="Z53" s="81" t="n"/>
-      <c r="AA53" s="82" t="n"/>
-      <c r="AB53" s="82" t="n"/>
-      <c r="AC53" s="83" t="n"/>
-      <c r="AD53" s="81" t="n"/>
-      <c r="AE53" s="82" t="n"/>
-      <c r="AF53" s="82" t="n"/>
-      <c r="AG53" s="83" t="n"/>
-      <c r="AH53" s="81" t="n"/>
-      <c r="AI53" s="82" t="n"/>
-      <c r="AJ53" s="82" t="n"/>
-      <c r="AK53" s="83" t="n"/>
-      <c r="AL53" s="81" t="n"/>
-      <c r="AM53" s="82" t="n"/>
-      <c r="AN53" s="82" t="n"/>
-      <c r="AO53" s="83" t="n"/>
-      <c r="AP53" s="81" t="n"/>
-      <c r="AQ53" s="82" t="n"/>
-      <c r="AR53" s="82" t="n"/>
-      <c r="AS53" s="83" t="n"/>
-      <c r="AT53" s="81" t="n"/>
-      <c r="AU53" s="82" t="n"/>
-      <c r="AV53" s="82" t="n"/>
-      <c r="AW53" s="83" t="n"/>
-      <c r="AX53" s="81" t="n"/>
-      <c r="AY53" s="82" t="n"/>
-      <c r="AZ53" s="82" t="n"/>
-      <c r="BA53" s="83" t="n"/>
-      <c r="BB53" s="81" t="n"/>
-      <c r="BC53" s="82" t="n"/>
-      <c r="BD53" s="82" t="n"/>
-      <c r="BE53" s="83" t="n"/>
-      <c r="BF53" s="81" t="n"/>
-      <c r="BG53" s="82" t="n"/>
-      <c r="BH53" s="82" t="n"/>
-      <c r="BI53" s="83" t="n"/>
-      <c r="BJ53" s="81" t="n"/>
-      <c r="BK53" s="82" t="n"/>
-      <c r="BL53" s="82" t="n"/>
-      <c r="BM53" s="83" t="n"/>
-      <c r="BN53" s="81" t="n"/>
-      <c r="BO53" s="82" t="n"/>
-      <c r="BP53" s="82" t="n"/>
-      <c r="BQ53" s="83" t="n"/>
-      <c r="BR53" s="81" t="n"/>
-      <c r="BS53" s="82" t="n"/>
-      <c r="BT53" s="82" t="n"/>
-      <c r="BU53" s="83" t="n"/>
-      <c r="BV53" s="81" t="n"/>
-      <c r="BW53" s="82" t="n"/>
-      <c r="BX53" s="82" t="n"/>
-      <c r="BY53" s="83" t="n"/>
-      <c r="BZ53" s="81" t="n"/>
-      <c r="CA53" s="82" t="n"/>
-      <c r="CB53" s="82" t="n"/>
-      <c r="CC53" s="83" t="n"/>
-      <c r="CD53" s="81" t="n"/>
-      <c r="CE53" s="82" t="n"/>
-      <c r="CF53" s="82" t="n"/>
-      <c r="CG53" s="84" t="n"/>
+      <c r="F53" s="72" t="n"/>
+      <c r="G53" s="73" t="n"/>
+      <c r="H53" s="73" t="n"/>
+      <c r="I53" s="74" t="n"/>
+      <c r="J53" s="72" t="n"/>
+      <c r="K53" s="73" t="n"/>
+      <c r="L53" s="73" t="n"/>
+      <c r="M53" s="74" t="n"/>
+      <c r="N53" s="72" t="n"/>
+      <c r="O53" s="73" t="n"/>
+      <c r="P53" s="73" t="n"/>
+      <c r="Q53" s="74" t="n"/>
+      <c r="R53" s="72" t="n"/>
+      <c r="S53" s="73" t="n"/>
+      <c r="T53" s="73" t="n"/>
+      <c r="U53" s="74" t="n"/>
+      <c r="V53" s="72" t="n"/>
+      <c r="W53" s="73" t="n"/>
+      <c r="X53" s="73" t="n"/>
+      <c r="Y53" s="74" t="n"/>
+      <c r="Z53" s="72" t="n"/>
+      <c r="AA53" s="73" t="n"/>
+      <c r="AB53" s="73" t="n"/>
+      <c r="AC53" s="74" t="n"/>
+      <c r="AD53" s="72" t="n"/>
+      <c r="AE53" s="73" t="n"/>
+      <c r="AF53" s="73" t="n"/>
+      <c r="AG53" s="74" t="n"/>
+      <c r="AH53" s="72" t="n"/>
+      <c r="AI53" s="73" t="n"/>
+      <c r="AJ53" s="73" t="n"/>
+      <c r="AK53" s="74" t="n"/>
+      <c r="AL53" s="72" t="n"/>
+      <c r="AM53" s="73" t="n"/>
+      <c r="AN53" s="73" t="n"/>
+      <c r="AO53" s="74" t="n"/>
+      <c r="AP53" s="72" t="n"/>
+      <c r="AQ53" s="73" t="n"/>
+      <c r="AR53" s="73" t="n"/>
+      <c r="AS53" s="74" t="n"/>
+      <c r="AT53" s="72" t="n"/>
+      <c r="AU53" s="73" t="n"/>
+      <c r="AV53" s="73" t="n"/>
+      <c r="AW53" s="74" t="n"/>
+      <c r="AX53" s="72" t="n"/>
+      <c r="AY53" s="73" t="n"/>
+      <c r="AZ53" s="73" t="n"/>
+      <c r="BA53" s="74" t="n"/>
+      <c r="BB53" s="72" t="n"/>
+      <c r="BC53" s="73" t="n"/>
+      <c r="BD53" s="73" t="n"/>
+      <c r="BE53" s="74" t="n"/>
+      <c r="BF53" s="72" t="n"/>
+      <c r="BG53" s="73" t="n"/>
+      <c r="BH53" s="73" t="n"/>
+      <c r="BI53" s="74" t="n"/>
+      <c r="BJ53" s="72" t="n"/>
+      <c r="BK53" s="73" t="n"/>
+      <c r="BL53" s="73" t="n"/>
+      <c r="BM53" s="74" t="n"/>
+      <c r="BN53" s="72" t="n"/>
+      <c r="BO53" s="73" t="n"/>
+      <c r="BP53" s="73" t="n"/>
+      <c r="BQ53" s="74" t="n"/>
+      <c r="BR53" s="72" t="n"/>
+      <c r="BS53" s="73" t="n"/>
+      <c r="BT53" s="73" t="n"/>
+      <c r="BU53" s="74" t="n"/>
+      <c r="BV53" s="72" t="n"/>
+      <c r="BW53" s="73" t="n"/>
+      <c r="BX53" s="73" t="n"/>
+      <c r="BY53" s="74" t="n"/>
+      <c r="BZ53" s="72" t="n"/>
+      <c r="CA53" s="73" t="n"/>
+      <c r="CB53" s="73" t="n"/>
+      <c r="CC53" s="74" t="n"/>
+      <c r="CD53" s="72" t="n"/>
+      <c r="CE53" s="73" t="n"/>
+      <c r="CF53" s="73" t="n"/>
+      <c r="CG53" s="75" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="29" t="inlineStr">
@@ -7251,7 +6675,7 @@
       </c>
       <c r="D54" s="30" t="inlineStr">
         <is>
-          <t>Pearce,J</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
@@ -7260,105 +6684,89 @@
         </is>
       </c>
       <c r="F54" s="31" t="n"/>
-      <c r="G54" s="97" t="n"/>
+      <c r="G54" s="76" t="n"/>
       <c r="H54" s="33" t="n"/>
       <c r="I54" s="34" t="n"/>
-      <c r="J54" s="98" t="n"/>
+      <c r="J54" s="77" t="n"/>
       <c r="K54" s="33" t="n"/>
       <c r="L54" s="33" t="n"/>
       <c r="M54" s="34" t="n"/>
-      <c r="N54" s="98" t="n"/>
+      <c r="N54" s="77" t="n"/>
       <c r="O54" s="33" t="n"/>
       <c r="P54" s="33" t="n"/>
       <c r="Q54" s="34" t="n"/>
-      <c r="R54" s="48" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+      <c r="R54" s="77" t="n"/>
       <c r="S54" s="33" t="n"/>
       <c r="T54" s="33" t="n"/>
       <c r="U54" s="34" t="n"/>
-      <c r="V54" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="V54" s="77" t="n"/>
       <c r="W54" s="33" t="n"/>
-      <c r="X54" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="X54" s="33" t="n"/>
       <c r="Y54" s="34" t="n"/>
-      <c r="Z54" s="98" t="n"/>
+      <c r="Z54" s="77" t="n"/>
       <c r="AA54" s="33" t="n"/>
       <c r="AB54" s="33" t="n"/>
       <c r="AC54" s="34" t="n"/>
-      <c r="AD54" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AD54" s="77" t="n"/>
       <c r="AE54" s="33" t="n"/>
       <c r="AF54" s="33" t="n"/>
       <c r="AG54" s="34" t="n"/>
-      <c r="AH54" s="98" t="n"/>
+      <c r="AH54" s="77" t="n"/>
       <c r="AI54" s="33" t="n"/>
       <c r="AJ54" s="33" t="n"/>
       <c r="AK54" s="34" t="n"/>
-      <c r="AL54" s="31" t="n"/>
-      <c r="AM54" s="41" t="n"/>
-      <c r="AN54" s="41" t="n"/>
-      <c r="AO54" s="42" t="n"/>
+      <c r="AL54" s="78" t="n"/>
+      <c r="AM54" s="38" t="n"/>
+      <c r="AN54" s="38" t="n"/>
+      <c r="AO54" s="37" t="n"/>
       <c r="AP54" s="31" t="n"/>
-      <c r="AQ54" s="41" t="n"/>
-      <c r="AR54" s="41" t="n"/>
-      <c r="AS54" s="42" t="n"/>
+      <c r="AQ54" s="38" t="n"/>
+      <c r="AR54" s="38" t="n"/>
+      <c r="AS54" s="37" t="n"/>
       <c r="AT54" s="31" t="n"/>
-      <c r="AU54" s="41" t="n"/>
-      <c r="AV54" s="41" t="n"/>
-      <c r="AW54" s="42" t="n"/>
+      <c r="AU54" s="38" t="n"/>
+      <c r="AV54" s="38" t="n"/>
+      <c r="AW54" s="37" t="n"/>
       <c r="AX54" s="31" t="n"/>
-      <c r="AY54" s="41" t="n"/>
-      <c r="AZ54" s="41" t="n"/>
-      <c r="BA54" s="42" t="n"/>
+      <c r="AY54" s="38" t="n"/>
+      <c r="AZ54" s="38" t="n"/>
+      <c r="BA54" s="37" t="n"/>
       <c r="BB54" s="31" t="n"/>
-      <c r="BC54" s="41" t="n"/>
-      <c r="BD54" s="41" t="n"/>
-      <c r="BE54" s="42" t="n"/>
+      <c r="BC54" s="38" t="n"/>
+      <c r="BD54" s="38" t="n"/>
+      <c r="BE54" s="37" t="n"/>
       <c r="BF54" s="31" t="n"/>
-      <c r="BG54" s="41" t="n"/>
-      <c r="BH54" s="41" t="n"/>
-      <c r="BI54" s="42" t="n"/>
-      <c r="BJ54" s="99" t="inlineStr">
+      <c r="BG54" s="38" t="n"/>
+      <c r="BH54" s="38" t="n"/>
+      <c r="BI54" s="37" t="n"/>
+      <c r="BJ54" s="79" t="inlineStr">
         <is>
           <t>CARDINAL</t>
         </is>
       </c>
-      <c r="BK54" s="100" t="n"/>
-      <c r="BL54" s="100" t="n"/>
-      <c r="BM54" s="100" t="n"/>
-      <c r="BN54" s="100" t="n"/>
-      <c r="BO54" s="100" t="n"/>
-      <c r="BP54" s="100" t="n"/>
-      <c r="BQ54" s="100" t="n"/>
-      <c r="BR54" s="100" t="n"/>
-      <c r="BS54" s="100" t="n"/>
-      <c r="BT54" s="100" t="n"/>
-      <c r="BU54" s="100" t="n"/>
-      <c r="BV54" s="100" t="n"/>
-      <c r="BW54" s="100" t="n"/>
-      <c r="BX54" s="100" t="n"/>
-      <c r="BY54" s="100" t="n"/>
-      <c r="BZ54" s="100" t="n"/>
-      <c r="CA54" s="100" t="n"/>
-      <c r="CB54" s="100" t="n"/>
-      <c r="CC54" s="100" t="n"/>
-      <c r="CD54" s="100" t="n"/>
-      <c r="CE54" s="100" t="n"/>
-      <c r="CF54" s="100" t="n"/>
-      <c r="CG54" s="101" t="n"/>
+      <c r="BK54" s="80" t="n"/>
+      <c r="BL54" s="80" t="n"/>
+      <c r="BM54" s="80" t="n"/>
+      <c r="BN54" s="80" t="n"/>
+      <c r="BO54" s="80" t="n"/>
+      <c r="BP54" s="80" t="n"/>
+      <c r="BQ54" s="80" t="n"/>
+      <c r="BR54" s="80" t="n"/>
+      <c r="BS54" s="80" t="n"/>
+      <c r="BT54" s="80" t="n"/>
+      <c r="BU54" s="80" t="n"/>
+      <c r="BV54" s="80" t="n"/>
+      <c r="BW54" s="80" t="n"/>
+      <c r="BX54" s="80" t="n"/>
+      <c r="BY54" s="80" t="n"/>
+      <c r="BZ54" s="80" t="n"/>
+      <c r="CA54" s="80" t="n"/>
+      <c r="CB54" s="80" t="n"/>
+      <c r="CC54" s="80" t="n"/>
+      <c r="CD54" s="80" t="n"/>
+      <c r="CE54" s="80" t="n"/>
+      <c r="CF54" s="80" t="n"/>
+      <c r="CG54" s="81" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="29" t="inlineStr">
@@ -7378,7 +6786,7 @@
       </c>
       <c r="D55" s="30" t="inlineStr">
         <is>
-          <t>Miah,S</t>
+          <t>Miah</t>
         </is>
       </c>
       <c r="E55" s="30" t="inlineStr">
@@ -7387,97 +6795,85 @@
         </is>
       </c>
       <c r="F55" s="31" t="n"/>
-      <c r="G55" s="97" t="n"/>
+      <c r="G55" s="76" t="n"/>
       <c r="H55" s="33" t="n"/>
       <c r="I55" s="34" t="n"/>
-      <c r="J55" s="98" t="n"/>
+      <c r="J55" s="77" t="n"/>
       <c r="K55" s="33" t="n"/>
       <c r="L55" s="33" t="n"/>
       <c r="M55" s="34" t="n"/>
-      <c r="N55" s="102" t="n"/>
+      <c r="N55" s="77" t="n"/>
       <c r="O55" s="33" t="n"/>
-      <c r="P55" s="53" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+      <c r="P55" s="33" t="n"/>
       <c r="Q55" s="34" t="n"/>
-      <c r="R55" s="98" t="n"/>
+      <c r="R55" s="77" t="n"/>
       <c r="S55" s="33" t="n"/>
       <c r="T55" s="33" t="n"/>
       <c r="U55" s="34" t="n"/>
-      <c r="V55" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="V55" s="77" t="n"/>
       <c r="W55" s="33" t="n"/>
-      <c r="X55" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="X55" s="33" t="n"/>
       <c r="Y55" s="34" t="n"/>
-      <c r="Z55" s="98" t="n"/>
+      <c r="Z55" s="77" t="n"/>
       <c r="AA55" s="33" t="n"/>
       <c r="AB55" s="33" t="n"/>
       <c r="AC55" s="34" t="n"/>
-      <c r="AD55" s="98" t="n"/>
+      <c r="AD55" s="77" t="n"/>
       <c r="AE55" s="33" t="n"/>
       <c r="AF55" s="33" t="n"/>
       <c r="AG55" s="34" t="n"/>
-      <c r="AH55" s="98" t="n"/>
+      <c r="AH55" s="77" t="n"/>
       <c r="AI55" s="33" t="n"/>
       <c r="AJ55" s="33" t="n"/>
       <c r="AK55" s="34" t="n"/>
-      <c r="AL55" s="31" t="n"/>
-      <c r="AM55" s="41" t="n"/>
-      <c r="AN55" s="41" t="n"/>
-      <c r="AO55" s="42" t="n"/>
+      <c r="AL55" s="78" t="n"/>
+      <c r="AM55" s="38" t="n"/>
+      <c r="AN55" s="38" t="n"/>
+      <c r="AO55" s="37" t="n"/>
       <c r="AP55" s="31" t="n"/>
-      <c r="AQ55" s="41" t="n"/>
-      <c r="AR55" s="41" t="n"/>
-      <c r="AS55" s="42" t="n"/>
+      <c r="AQ55" s="38" t="n"/>
+      <c r="AR55" s="38" t="n"/>
+      <c r="AS55" s="37" t="n"/>
       <c r="AT55" s="31" t="n"/>
-      <c r="AU55" s="41" t="n"/>
-      <c r="AV55" s="41" t="n"/>
-      <c r="AW55" s="42" t="n"/>
+      <c r="AU55" s="38" t="n"/>
+      <c r="AV55" s="38" t="n"/>
+      <c r="AW55" s="37" t="n"/>
       <c r="AX55" s="31" t="n"/>
-      <c r="AY55" s="41" t="n"/>
-      <c r="AZ55" s="41" t="n"/>
-      <c r="BA55" s="42" t="n"/>
+      <c r="AY55" s="38" t="n"/>
+      <c r="AZ55" s="38" t="n"/>
+      <c r="BA55" s="37" t="n"/>
       <c r="BB55" s="31" t="n"/>
-      <c r="BC55" s="41" t="n"/>
-      <c r="BD55" s="41" t="n"/>
-      <c r="BE55" s="42" t="n"/>
+      <c r="BC55" s="38" t="n"/>
+      <c r="BD55" s="38" t="n"/>
+      <c r="BE55" s="37" t="n"/>
       <c r="BF55" s="31" t="n"/>
-      <c r="BG55" s="41" t="n"/>
-      <c r="BH55" s="41" t="n"/>
-      <c r="BI55" s="42" t="n"/>
-      <c r="BJ55" s="103" t="n"/>
-      <c r="BK55" s="104" t="n"/>
-      <c r="BL55" s="104" t="n"/>
-      <c r="BM55" s="104" t="n"/>
-      <c r="BN55" s="104" t="n"/>
-      <c r="BO55" s="104" t="n"/>
-      <c r="BP55" s="104" t="n"/>
-      <c r="BQ55" s="104" t="n"/>
-      <c r="BR55" s="104" t="n"/>
-      <c r="BS55" s="104" t="n"/>
-      <c r="BT55" s="104" t="n"/>
-      <c r="BU55" s="104" t="n"/>
-      <c r="BV55" s="104" t="n"/>
-      <c r="BW55" s="104" t="n"/>
-      <c r="BX55" s="104" t="n"/>
-      <c r="BY55" s="104" t="n"/>
-      <c r="BZ55" s="104" t="n"/>
-      <c r="CA55" s="104" t="n"/>
-      <c r="CB55" s="104" t="n"/>
-      <c r="CC55" s="104" t="n"/>
-      <c r="CD55" s="104" t="n"/>
-      <c r="CE55" s="104" t="n"/>
-      <c r="CF55" s="104" t="n"/>
-      <c r="CG55" s="105" t="n"/>
+      <c r="BG55" s="38" t="n"/>
+      <c r="BH55" s="38" t="n"/>
+      <c r="BI55" s="37" t="n"/>
+      <c r="BJ55" s="82" t="n"/>
+      <c r="BK55" s="83" t="n"/>
+      <c r="BL55" s="83" t="n"/>
+      <c r="BM55" s="83" t="n"/>
+      <c r="BN55" s="83" t="n"/>
+      <c r="BO55" s="83" t="n"/>
+      <c r="BP55" s="83" t="n"/>
+      <c r="BQ55" s="83" t="n"/>
+      <c r="BR55" s="83" t="n"/>
+      <c r="BS55" s="83" t="n"/>
+      <c r="BT55" s="83" t="n"/>
+      <c r="BU55" s="83" t="n"/>
+      <c r="BV55" s="83" t="n"/>
+      <c r="BW55" s="83" t="n"/>
+      <c r="BX55" s="83" t="n"/>
+      <c r="BY55" s="83" t="n"/>
+      <c r="BZ55" s="83" t="n"/>
+      <c r="CA55" s="83" t="n"/>
+      <c r="CB55" s="83" t="n"/>
+      <c r="CC55" s="83" t="n"/>
+      <c r="CD55" s="83" t="n"/>
+      <c r="CE55" s="83" t="n"/>
+      <c r="CF55" s="83" t="n"/>
+      <c r="CG55" s="84" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="29" t="inlineStr">
@@ -7497,7 +6893,7 @@
       </c>
       <c r="D56" s="30" t="inlineStr">
         <is>
-          <t>Mussie,JHA</t>
+          <t>Mussie</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -7506,97 +6902,85 @@
         </is>
       </c>
       <c r="F56" s="31" t="n"/>
-      <c r="G56" s="41" t="n"/>
-      <c r="H56" s="41" t="n"/>
-      <c r="I56" s="42" t="n"/>
+      <c r="G56" s="38" t="n"/>
+      <c r="H56" s="38" t="n"/>
+      <c r="I56" s="37" t="n"/>
       <c r="J56" s="31" t="n"/>
-      <c r="K56" s="41" t="n"/>
-      <c r="L56" s="41" t="n"/>
-      <c r="M56" s="42" t="n"/>
+      <c r="K56" s="38" t="n"/>
+      <c r="L56" s="38" t="n"/>
+      <c r="M56" s="37" t="n"/>
       <c r="N56" s="31" t="n"/>
-      <c r="O56" s="41" t="n"/>
-      <c r="P56" s="97" t="n"/>
+      <c r="O56" s="38" t="n"/>
+      <c r="P56" s="76" t="n"/>
       <c r="Q56" s="34" t="n"/>
-      <c r="R56" s="98" t="n"/>
+      <c r="R56" s="77" t="n"/>
       <c r="S56" s="33" t="n"/>
       <c r="T56" s="33" t="n"/>
       <c r="U56" s="34" t="n"/>
-      <c r="V56" s="98" t="n"/>
+      <c r="V56" s="77" t="n"/>
       <c r="W56" s="33" t="n"/>
       <c r="X56" s="33" t="n"/>
       <c r="Y56" s="34" t="n"/>
-      <c r="Z56" s="61" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="Z56" s="77" t="n"/>
       <c r="AA56" s="33" t="n"/>
-      <c r="AB56" s="62" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AB56" s="33" t="n"/>
       <c r="AC56" s="34" t="n"/>
-      <c r="AD56" s="98" t="n"/>
+      <c r="AD56" s="77" t="n"/>
       <c r="AE56" s="33" t="n"/>
       <c r="AF56" s="33" t="n"/>
       <c r="AG56" s="34" t="n"/>
-      <c r="AH56" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AH56" s="77" t="n"/>
       <c r="AI56" s="33" t="n"/>
       <c r="AJ56" s="33" t="n"/>
       <c r="AK56" s="34" t="n"/>
-      <c r="AL56" s="98" t="n"/>
+      <c r="AL56" s="77" t="n"/>
       <c r="AM56" s="33" t="n"/>
       <c r="AN56" s="33" t="n"/>
       <c r="AO56" s="34" t="n"/>
-      <c r="AP56" s="98" t="n"/>
+      <c r="AP56" s="77" t="n"/>
       <c r="AQ56" s="33" t="n"/>
       <c r="AR56" s="33" t="n"/>
       <c r="AS56" s="34" t="n"/>
-      <c r="AT56" s="102" t="n"/>
+      <c r="AT56" s="85" t="n"/>
       <c r="AU56" s="33" t="n"/>
-      <c r="AV56" s="41" t="n"/>
-      <c r="AW56" s="42" t="n"/>
+      <c r="AV56" s="38" t="n"/>
+      <c r="AW56" s="37" t="n"/>
       <c r="AX56" s="31" t="n"/>
-      <c r="AY56" s="41" t="n"/>
-      <c r="AZ56" s="41" t="n"/>
-      <c r="BA56" s="42" t="n"/>
+      <c r="AY56" s="38" t="n"/>
+      <c r="AZ56" s="38" t="n"/>
+      <c r="BA56" s="37" t="n"/>
       <c r="BB56" s="31" t="n"/>
-      <c r="BC56" s="41" t="n"/>
-      <c r="BD56" s="41" t="n"/>
-      <c r="BE56" s="42" t="n"/>
+      <c r="BC56" s="38" t="n"/>
+      <c r="BD56" s="38" t="n"/>
+      <c r="BE56" s="37" t="n"/>
       <c r="BF56" s="31" t="n"/>
-      <c r="BG56" s="41" t="n"/>
-      <c r="BH56" s="41" t="n"/>
-      <c r="BI56" s="42" t="n"/>
+      <c r="BG56" s="38" t="n"/>
+      <c r="BH56" s="38" t="n"/>
+      <c r="BI56" s="37" t="n"/>
       <c r="BJ56" s="31" t="n"/>
-      <c r="BK56" s="41" t="n"/>
-      <c r="BL56" s="41" t="n"/>
-      <c r="BM56" s="42" t="n"/>
+      <c r="BK56" s="38" t="n"/>
+      <c r="BL56" s="38" t="n"/>
+      <c r="BM56" s="37" t="n"/>
       <c r="BN56" s="31" t="n"/>
-      <c r="BO56" s="41" t="n"/>
-      <c r="BP56" s="41" t="n"/>
-      <c r="BQ56" s="42" t="n"/>
+      <c r="BO56" s="38" t="n"/>
+      <c r="BP56" s="38" t="n"/>
+      <c r="BQ56" s="37" t="n"/>
       <c r="BR56" s="31" t="n"/>
-      <c r="BS56" s="41" t="n"/>
-      <c r="BT56" s="41" t="n"/>
-      <c r="BU56" s="42" t="n"/>
+      <c r="BS56" s="38" t="n"/>
+      <c r="BT56" s="38" t="n"/>
+      <c r="BU56" s="37" t="n"/>
       <c r="BV56" s="31" t="n"/>
-      <c r="BW56" s="41" t="n"/>
-      <c r="BX56" s="41" t="n"/>
-      <c r="BY56" s="42" t="n"/>
+      <c r="BW56" s="38" t="n"/>
+      <c r="BX56" s="38" t="n"/>
+      <c r="BY56" s="37" t="n"/>
       <c r="BZ56" s="31" t="n"/>
-      <c r="CA56" s="41" t="n"/>
-      <c r="CB56" s="41" t="n"/>
-      <c r="CC56" s="42" t="n"/>
+      <c r="CA56" s="38" t="n"/>
+      <c r="CB56" s="38" t="n"/>
+      <c r="CC56" s="37" t="n"/>
       <c r="CD56" s="31" t="n"/>
-      <c r="CE56" s="41" t="n"/>
-      <c r="CF56" s="41" t="n"/>
-      <c r="CG56" s="54" t="n"/>
+      <c r="CE56" s="38" t="n"/>
+      <c r="CF56" s="38" t="n"/>
+      <c r="CG56" s="48" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="29" t="inlineStr">
@@ -7616,7 +7000,7 @@
       </c>
       <c r="D57" s="30" t="inlineStr">
         <is>
-          <t>Hansen,L</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="E57" s="30" t="inlineStr">
@@ -7625,101 +7009,85 @@
         </is>
       </c>
       <c r="F57" s="31" t="n"/>
-      <c r="G57" s="41" t="n"/>
-      <c r="H57" s="41" t="n"/>
-      <c r="I57" s="42" t="n"/>
+      <c r="G57" s="38" t="n"/>
+      <c r="H57" s="38" t="n"/>
+      <c r="I57" s="37" t="n"/>
       <c r="J57" s="31" t="n"/>
-      <c r="K57" s="41" t="n"/>
-      <c r="L57" s="41" t="n"/>
-      <c r="M57" s="42" t="n"/>
+      <c r="K57" s="38" t="n"/>
+      <c r="L57" s="38" t="n"/>
+      <c r="M57" s="37" t="n"/>
       <c r="N57" s="31" t="n"/>
-      <c r="O57" s="41" t="n"/>
-      <c r="P57" s="41" t="n"/>
-      <c r="Q57" s="42" t="n"/>
+      <c r="O57" s="38" t="n"/>
+      <c r="P57" s="38" t="n"/>
+      <c r="Q57" s="37" t="n"/>
       <c r="R57" s="31" t="n"/>
-      <c r="S57" s="41" t="n"/>
-      <c r="T57" s="41" t="n"/>
-      <c r="U57" s="42" t="n"/>
+      <c r="S57" s="38" t="n"/>
+      <c r="T57" s="38" t="n"/>
+      <c r="U57" s="37" t="n"/>
       <c r="V57" s="31" t="n"/>
-      <c r="W57" s="41" t="n"/>
-      <c r="X57" s="41" t="n"/>
-      <c r="Y57" s="42" t="n"/>
+      <c r="W57" s="38" t="n"/>
+      <c r="X57" s="38" t="n"/>
+      <c r="Y57" s="37" t="n"/>
       <c r="Z57" s="31" t="n"/>
-      <c r="AA57" s="41" t="n"/>
-      <c r="AB57" s="41" t="n"/>
-      <c r="AC57" s="42" t="n"/>
+      <c r="AA57" s="38" t="n"/>
+      <c r="AB57" s="38" t="n"/>
+      <c r="AC57" s="37" t="n"/>
       <c r="AD57" s="31" t="n"/>
-      <c r="AE57" s="41" t="n"/>
-      <c r="AF57" s="41" t="n"/>
-      <c r="AG57" s="42" t="n"/>
+      <c r="AE57" s="38" t="n"/>
+      <c r="AF57" s="38" t="n"/>
+      <c r="AG57" s="37" t="n"/>
       <c r="AH57" s="31" t="n"/>
-      <c r="AI57" s="41" t="n"/>
-      <c r="AJ57" s="41" t="n"/>
-      <c r="AK57" s="42" t="n"/>
-      <c r="AL57" s="98" t="n"/>
+      <c r="AI57" s="38" t="n"/>
+      <c r="AJ57" s="38" t="n"/>
+      <c r="AK57" s="37" t="n"/>
+      <c r="AL57" s="77" t="n"/>
       <c r="AM57" s="33" t="n"/>
       <c r="AN57" s="33" t="n"/>
       <c r="AO57" s="34" t="n"/>
-      <c r="AP57" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="AP57" s="77" t="n"/>
       <c r="AQ57" s="33" t="n"/>
       <c r="AR57" s="33" t="n"/>
       <c r="AS57" s="34" t="n"/>
-      <c r="AT57" s="98" t="n"/>
+      <c r="AT57" s="77" t="n"/>
       <c r="AU57" s="33" t="n"/>
       <c r="AV57" s="33" t="n"/>
       <c r="AW57" s="34" t="n"/>
-      <c r="AX57" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="AX57" s="77" t="n"/>
       <c r="AY57" s="33" t="n"/>
-      <c r="AZ57" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="AZ57" s="33" t="n"/>
       <c r="BA57" s="34" t="n"/>
-      <c r="BB57" s="98" t="n"/>
+      <c r="BB57" s="77" t="n"/>
       <c r="BC57" s="33" t="n"/>
       <c r="BD57" s="33" t="n"/>
       <c r="BE57" s="34" t="n"/>
-      <c r="BF57" s="48" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="BF57" s="77" t="n"/>
       <c r="BG57" s="33" t="n"/>
       <c r="BH57" s="33" t="n"/>
       <c r="BI57" s="34" t="n"/>
-      <c r="BJ57" s="98" t="n"/>
+      <c r="BJ57" s="77" t="n"/>
       <c r="BK57" s="33" t="n"/>
       <c r="BL57" s="33" t="n"/>
       <c r="BM57" s="34" t="n"/>
-      <c r="BN57" s="98" t="n"/>
+      <c r="BN57" s="77" t="n"/>
       <c r="BO57" s="33" t="n"/>
       <c r="BP57" s="33" t="n"/>
       <c r="BQ57" s="34" t="n"/>
       <c r="BR57" s="31" t="n"/>
-      <c r="BS57" s="41" t="n"/>
-      <c r="BT57" s="41" t="n"/>
-      <c r="BU57" s="42" t="n"/>
+      <c r="BS57" s="38" t="n"/>
+      <c r="BT57" s="38" t="n"/>
+      <c r="BU57" s="37" t="n"/>
       <c r="BV57" s="31" t="n"/>
-      <c r="BW57" s="41" t="n"/>
-      <c r="BX57" s="41" t="n"/>
-      <c r="BY57" s="42" t="n"/>
+      <c r="BW57" s="38" t="n"/>
+      <c r="BX57" s="38" t="n"/>
+      <c r="BY57" s="37" t="n"/>
       <c r="BZ57" s="31" t="n"/>
-      <c r="CA57" s="41" t="n"/>
-      <c r="CB57" s="41" t="n"/>
-      <c r="CC57" s="42" t="n"/>
+      <c r="CA57" s="38" t="n"/>
+      <c r="CB57" s="38" t="n"/>
+      <c r="CC57" s="37" t="n"/>
       <c r="CD57" s="31" t="n"/>
-      <c r="CE57" s="41" t="n"/>
-      <c r="CF57" s="41" t="n"/>
-      <c r="CG57" s="54" t="n"/>
+      <c r="CE57" s="38" t="n"/>
+      <c r="CF57" s="38" t="n"/>
+      <c r="CG57" s="48" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="29" t="inlineStr">
@@ -7739,7 +7107,7 @@
       </c>
       <c r="D58" s="30" t="inlineStr">
         <is>
-          <t>Kalsey,PS</t>
+          <t>Kalsey</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
@@ -7748,97 +7116,85 @@
         </is>
       </c>
       <c r="F58" s="31" t="n"/>
-      <c r="G58" s="41" t="n"/>
-      <c r="H58" s="41" t="n"/>
-      <c r="I58" s="42" t="n"/>
+      <c r="G58" s="38" t="n"/>
+      <c r="H58" s="38" t="n"/>
+      <c r="I58" s="37" t="n"/>
       <c r="J58" s="31" t="n"/>
-      <c r="K58" s="41" t="n"/>
-      <c r="L58" s="41" t="n"/>
-      <c r="M58" s="42" t="n"/>
+      <c r="K58" s="38" t="n"/>
+      <c r="L58" s="38" t="n"/>
+      <c r="M58" s="37" t="n"/>
       <c r="N58" s="31" t="n"/>
-      <c r="O58" s="41" t="n"/>
-      <c r="P58" s="41" t="n"/>
-      <c r="Q58" s="42" t="n"/>
+      <c r="O58" s="38" t="n"/>
+      <c r="P58" s="38" t="n"/>
+      <c r="Q58" s="37" t="n"/>
       <c r="R58" s="31" t="n"/>
-      <c r="S58" s="41" t="n"/>
-      <c r="T58" s="41" t="n"/>
-      <c r="U58" s="42" t="n"/>
+      <c r="S58" s="38" t="n"/>
+      <c r="T58" s="38" t="n"/>
+      <c r="U58" s="37" t="n"/>
       <c r="V58" s="31" t="n"/>
-      <c r="W58" s="41" t="n"/>
-      <c r="X58" s="41" t="n"/>
-      <c r="Y58" s="42" t="n"/>
+      <c r="W58" s="38" t="n"/>
+      <c r="X58" s="38" t="n"/>
+      <c r="Y58" s="37" t="n"/>
       <c r="Z58" s="31" t="n"/>
-      <c r="AA58" s="41" t="n"/>
-      <c r="AB58" s="41" t="n"/>
-      <c r="AC58" s="42" t="n"/>
+      <c r="AA58" s="38" t="n"/>
+      <c r="AB58" s="38" t="n"/>
+      <c r="AC58" s="37" t="n"/>
       <c r="AD58" s="31" t="n"/>
-      <c r="AE58" s="41" t="n"/>
-      <c r="AF58" s="41" t="n"/>
-      <c r="AG58" s="42" t="n"/>
+      <c r="AE58" s="38" t="n"/>
+      <c r="AF58" s="38" t="n"/>
+      <c r="AG58" s="37" t="n"/>
       <c r="AH58" s="31" t="n"/>
-      <c r="AI58" s="41" t="n"/>
-      <c r="AJ58" s="41" t="n"/>
-      <c r="AK58" s="42" t="n"/>
+      <c r="AI58" s="38" t="n"/>
+      <c r="AJ58" s="38" t="n"/>
+      <c r="AK58" s="37" t="n"/>
       <c r="AL58" s="31" t="n"/>
-      <c r="AM58" s="41" t="n"/>
-      <c r="AN58" s="41" t="n"/>
-      <c r="AO58" s="42" t="n"/>
-      <c r="AP58" s="98" t="n"/>
+      <c r="AM58" s="38" t="n"/>
+      <c r="AN58" s="38" t="n"/>
+      <c r="AO58" s="37" t="n"/>
+      <c r="AP58" s="77" t="n"/>
       <c r="AQ58" s="33" t="n"/>
       <c r="AR58" s="33" t="n"/>
       <c r="AS58" s="34" t="n"/>
-      <c r="AT58" s="98" t="n"/>
+      <c r="AT58" s="77" t="n"/>
       <c r="AU58" s="33" t="n"/>
       <c r="AV58" s="33" t="n"/>
       <c r="AW58" s="34" t="n"/>
-      <c r="AX58" s="98" t="n"/>
+      <c r="AX58" s="77" t="n"/>
       <c r="AY58" s="33" t="n"/>
       <c r="AZ58" s="33" t="n"/>
       <c r="BA58" s="34" t="n"/>
-      <c r="BB58" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BB58" s="77" t="n"/>
       <c r="BC58" s="33" t="n"/>
-      <c r="BD58" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BD58" s="33" t="n"/>
       <c r="BE58" s="34" t="n"/>
-      <c r="BF58" s="98" t="n"/>
+      <c r="BF58" s="77" t="n"/>
       <c r="BG58" s="33" t="n"/>
       <c r="BH58" s="33" t="n"/>
       <c r="BI58" s="34" t="n"/>
-      <c r="BJ58" s="98" t="n"/>
+      <c r="BJ58" s="77" t="n"/>
       <c r="BK58" s="33" t="n"/>
       <c r="BL58" s="33" t="n"/>
       <c r="BM58" s="34" t="n"/>
-      <c r="BN58" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="BN58" s="77" t="n"/>
       <c r="BO58" s="33" t="n"/>
       <c r="BP58" s="33" t="n"/>
       <c r="BQ58" s="34" t="n"/>
-      <c r="BR58" s="98" t="n"/>
+      <c r="BR58" s="77" t="n"/>
       <c r="BS58" s="33" t="n"/>
       <c r="BT58" s="33" t="n"/>
       <c r="BU58" s="34" t="n"/>
       <c r="BV58" s="31" t="n"/>
-      <c r="BW58" s="41" t="n"/>
-      <c r="BX58" s="41" t="n"/>
-      <c r="BY58" s="42" t="n"/>
+      <c r="BW58" s="38" t="n"/>
+      <c r="BX58" s="38" t="n"/>
+      <c r="BY58" s="37" t="n"/>
       <c r="BZ58" s="31" t="n"/>
-      <c r="CA58" s="41" t="n"/>
-      <c r="CB58" s="41" t="n"/>
-      <c r="CC58" s="42" t="n"/>
+      <c r="CA58" s="38" t="n"/>
+      <c r="CB58" s="38" t="n"/>
+      <c r="CC58" s="37" t="n"/>
       <c r="CD58" s="31" t="n"/>
-      <c r="CE58" s="41" t="n"/>
-      <c r="CF58" s="41" t="n"/>
-      <c r="CG58" s="54" t="n"/>
+      <c r="CE58" s="38" t="n"/>
+      <c r="CF58" s="38" t="n"/>
+      <c r="CG58" s="48" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="29" t="inlineStr">
@@ -7858,7 +7214,7 @@
       </c>
       <c r="D59" s="30" t="inlineStr">
         <is>
-          <t>McIntyre,W</t>
+          <t>McIntyre</t>
         </is>
       </c>
       <c r="E59" s="30" t="inlineStr">
@@ -7867,97 +7223,85 @@
         </is>
       </c>
       <c r="F59" s="31" t="n"/>
-      <c r="G59" s="41" t="n"/>
-      <c r="H59" s="41" t="n"/>
-      <c r="I59" s="42" t="n"/>
+      <c r="G59" s="38" t="n"/>
+      <c r="H59" s="38" t="n"/>
+      <c r="I59" s="37" t="n"/>
       <c r="J59" s="31" t="n"/>
-      <c r="K59" s="41" t="n"/>
-      <c r="L59" s="41" t="n"/>
-      <c r="M59" s="42" t="n"/>
+      <c r="K59" s="38" t="n"/>
+      <c r="L59" s="38" t="n"/>
+      <c r="M59" s="37" t="n"/>
       <c r="N59" s="31" t="n"/>
-      <c r="O59" s="41" t="n"/>
-      <c r="P59" s="41" t="n"/>
-      <c r="Q59" s="42" t="n"/>
+      <c r="O59" s="38" t="n"/>
+      <c r="P59" s="38" t="n"/>
+      <c r="Q59" s="37" t="n"/>
       <c r="R59" s="31" t="n"/>
-      <c r="S59" s="41" t="n"/>
-      <c r="T59" s="41" t="n"/>
-      <c r="U59" s="42" t="n"/>
+      <c r="S59" s="38" t="n"/>
+      <c r="T59" s="38" t="n"/>
+      <c r="U59" s="37" t="n"/>
       <c r="V59" s="31" t="n"/>
-      <c r="W59" s="41" t="n"/>
-      <c r="X59" s="41" t="n"/>
-      <c r="Y59" s="42" t="n"/>
+      <c r="W59" s="38" t="n"/>
+      <c r="X59" s="38" t="n"/>
+      <c r="Y59" s="37" t="n"/>
       <c r="Z59" s="31" t="n"/>
-      <c r="AA59" s="41" t="n"/>
-      <c r="AB59" s="41" t="n"/>
-      <c r="AC59" s="42" t="n"/>
+      <c r="AA59" s="38" t="n"/>
+      <c r="AB59" s="38" t="n"/>
+      <c r="AC59" s="37" t="n"/>
       <c r="AD59" s="31" t="n"/>
-      <c r="AE59" s="41" t="n"/>
-      <c r="AF59" s="41" t="n"/>
-      <c r="AG59" s="42" t="n"/>
+      <c r="AE59" s="38" t="n"/>
+      <c r="AF59" s="38" t="n"/>
+      <c r="AG59" s="37" t="n"/>
       <c r="AH59" s="31" t="n"/>
-      <c r="AI59" s="41" t="n"/>
-      <c r="AJ59" s="41" t="n"/>
-      <c r="AK59" s="42" t="n"/>
+      <c r="AI59" s="38" t="n"/>
+      <c r="AJ59" s="38" t="n"/>
+      <c r="AK59" s="37" t="n"/>
       <c r="AL59" s="31" t="n"/>
-      <c r="AM59" s="41" t="n"/>
-      <c r="AN59" s="41" t="n"/>
-      <c r="AO59" s="42" t="n"/>
+      <c r="AM59" s="38" t="n"/>
+      <c r="AN59" s="38" t="n"/>
+      <c r="AO59" s="37" t="n"/>
       <c r="AP59" s="31" t="n"/>
-      <c r="AQ59" s="41" t="n"/>
-      <c r="AR59" s="41" t="n"/>
-      <c r="AS59" s="42" t="n"/>
+      <c r="AQ59" s="38" t="n"/>
+      <c r="AR59" s="38" t="n"/>
+      <c r="AS59" s="37" t="n"/>
       <c r="AT59" s="31" t="n"/>
-      <c r="AU59" s="41" t="n"/>
-      <c r="AV59" s="41" t="n"/>
-      <c r="AW59" s="42" t="n"/>
+      <c r="AU59" s="38" t="n"/>
+      <c r="AV59" s="38" t="n"/>
+      <c r="AW59" s="37" t="n"/>
       <c r="AX59" s="31" t="n"/>
-      <c r="AY59" s="41" t="n"/>
-      <c r="AZ59" s="41" t="n"/>
-      <c r="BA59" s="42" t="n"/>
-      <c r="BB59" s="98" t="n"/>
+      <c r="AY59" s="38" t="n"/>
+      <c r="AZ59" s="38" t="n"/>
+      <c r="BA59" s="37" t="n"/>
+      <c r="BB59" s="77" t="n"/>
       <c r="BC59" s="33" t="n"/>
       <c r="BD59" s="33" t="n"/>
       <c r="BE59" s="34" t="n"/>
-      <c r="BF59" s="98" t="n"/>
+      <c r="BF59" s="77" t="n"/>
       <c r="BG59" s="33" t="n"/>
       <c r="BH59" s="33" t="n"/>
       <c r="BI59" s="34" t="n"/>
-      <c r="BJ59" s="98" t="n"/>
+      <c r="BJ59" s="77" t="n"/>
       <c r="BK59" s="33" t="n"/>
       <c r="BL59" s="33" t="n"/>
       <c r="BM59" s="34" t="n"/>
-      <c r="BN59" s="37" t="inlineStr">
-        <is>
-          <t>Meal Break</t>
-        </is>
-      </c>
+      <c r="BN59" s="77" t="n"/>
       <c r="BO59" s="33" t="n"/>
-      <c r="BP59" s="38" t="inlineStr">
-        <is>
-          <t>CSSI</t>
-        </is>
-      </c>
+      <c r="BP59" s="33" t="n"/>
       <c r="BQ59" s="34" t="n"/>
-      <c r="BR59" s="98" t="n"/>
+      <c r="BR59" s="77" t="n"/>
       <c r="BS59" s="33" t="n"/>
       <c r="BT59" s="33" t="n"/>
       <c r="BU59" s="34" t="n"/>
-      <c r="BV59" s="39" t="inlineStr">
-        <is>
-          <t>Top of Esc</t>
-        </is>
-      </c>
+      <c r="BV59" s="77" t="n"/>
       <c r="BW59" s="33" t="n"/>
       <c r="BX59" s="33" t="n"/>
       <c r="BY59" s="34" t="n"/>
-      <c r="BZ59" s="98" t="n"/>
+      <c r="BZ59" s="77" t="n"/>
       <c r="CA59" s="33" t="n"/>
       <c r="CB59" s="33" t="n"/>
       <c r="CC59" s="34" t="n"/>
-      <c r="CD59" s="102" t="n"/>
+      <c r="CD59" s="77" t="n"/>
       <c r="CE59" s="33" t="n"/>
       <c r="CF59" s="33" t="n"/>
-      <c r="CG59" s="54" t="n"/>
+      <c r="CG59" s="49" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="29" t="inlineStr"/>
@@ -7966,85 +7310,85 @@
       <c r="D60" s="30" t="n"/>
       <c r="E60" s="30" t="n"/>
       <c r="F60" s="31" t="n"/>
-      <c r="G60" s="41" t="n"/>
-      <c r="H60" s="41" t="n"/>
-      <c r="I60" s="42" t="n"/>
+      <c r="G60" s="38" t="n"/>
+      <c r="H60" s="38" t="n"/>
+      <c r="I60" s="37" t="n"/>
       <c r="J60" s="31" t="n"/>
-      <c r="K60" s="41" t="n"/>
-      <c r="L60" s="41" t="n"/>
-      <c r="M60" s="42" t="n"/>
+      <c r="K60" s="38" t="n"/>
+      <c r="L60" s="38" t="n"/>
+      <c r="M60" s="37" t="n"/>
       <c r="N60" s="31" t="n"/>
-      <c r="O60" s="41" t="n"/>
-      <c r="P60" s="41" t="n"/>
-      <c r="Q60" s="42" t="n"/>
+      <c r="O60" s="38" t="n"/>
+      <c r="P60" s="38" t="n"/>
+      <c r="Q60" s="37" t="n"/>
       <c r="R60" s="31" t="n"/>
-      <c r="S60" s="41" t="n"/>
-      <c r="T60" s="41" t="n"/>
-      <c r="U60" s="42" t="n"/>
+      <c r="S60" s="38" t="n"/>
+      <c r="T60" s="38" t="n"/>
+      <c r="U60" s="37" t="n"/>
       <c r="V60" s="31" t="n"/>
-      <c r="W60" s="41" t="n"/>
-      <c r="X60" s="41" t="n"/>
-      <c r="Y60" s="42" t="n"/>
+      <c r="W60" s="38" t="n"/>
+      <c r="X60" s="38" t="n"/>
+      <c r="Y60" s="37" t="n"/>
       <c r="Z60" s="31" t="n"/>
-      <c r="AA60" s="41" t="n"/>
-      <c r="AB60" s="41" t="n"/>
-      <c r="AC60" s="42" t="n"/>
+      <c r="AA60" s="38" t="n"/>
+      <c r="AB60" s="38" t="n"/>
+      <c r="AC60" s="37" t="n"/>
       <c r="AD60" s="31" t="n"/>
-      <c r="AE60" s="41" t="n"/>
-      <c r="AF60" s="41" t="n"/>
-      <c r="AG60" s="42" t="n"/>
+      <c r="AE60" s="38" t="n"/>
+      <c r="AF60" s="38" t="n"/>
+      <c r="AG60" s="37" t="n"/>
       <c r="AH60" s="31" t="n"/>
-      <c r="AI60" s="41" t="n"/>
-      <c r="AJ60" s="41" t="n"/>
-      <c r="AK60" s="42" t="n"/>
+      <c r="AI60" s="38" t="n"/>
+      <c r="AJ60" s="38" t="n"/>
+      <c r="AK60" s="37" t="n"/>
       <c r="AL60" s="31" t="n"/>
-      <c r="AM60" s="41" t="n"/>
-      <c r="AN60" s="41" t="n"/>
-      <c r="AO60" s="42" t="n"/>
+      <c r="AM60" s="38" t="n"/>
+      <c r="AN60" s="38" t="n"/>
+      <c r="AO60" s="37" t="n"/>
       <c r="AP60" s="31" t="n"/>
-      <c r="AQ60" s="41" t="n"/>
-      <c r="AR60" s="41" t="n"/>
-      <c r="AS60" s="42" t="n"/>
+      <c r="AQ60" s="38" t="n"/>
+      <c r="AR60" s="38" t="n"/>
+      <c r="AS60" s="37" t="n"/>
       <c r="AT60" s="31" t="n"/>
-      <c r="AU60" s="41" t="n"/>
-      <c r="AV60" s="41" t="n"/>
-      <c r="AW60" s="42" t="n"/>
+      <c r="AU60" s="38" t="n"/>
+      <c r="AV60" s="38" t="n"/>
+      <c r="AW60" s="37" t="n"/>
       <c r="AX60" s="31" t="n"/>
-      <c r="AY60" s="41" t="n"/>
-      <c r="AZ60" s="41" t="n"/>
-      <c r="BA60" s="42" t="n"/>
+      <c r="AY60" s="38" t="n"/>
+      <c r="AZ60" s="38" t="n"/>
+      <c r="BA60" s="37" t="n"/>
       <c r="BB60" s="31" t="n"/>
-      <c r="BC60" s="41" t="n"/>
-      <c r="BD60" s="41" t="n"/>
-      <c r="BE60" s="42" t="n"/>
+      <c r="BC60" s="38" t="n"/>
+      <c r="BD60" s="38" t="n"/>
+      <c r="BE60" s="37" t="n"/>
       <c r="BF60" s="31" t="n"/>
-      <c r="BG60" s="41" t="n"/>
-      <c r="BH60" s="41" t="n"/>
-      <c r="BI60" s="42" t="n"/>
+      <c r="BG60" s="38" t="n"/>
+      <c r="BH60" s="38" t="n"/>
+      <c r="BI60" s="37" t="n"/>
       <c r="BJ60" s="31" t="n"/>
-      <c r="BK60" s="41" t="n"/>
-      <c r="BL60" s="41" t="n"/>
-      <c r="BM60" s="42" t="n"/>
+      <c r="BK60" s="38" t="n"/>
+      <c r="BL60" s="38" t="n"/>
+      <c r="BM60" s="37" t="n"/>
       <c r="BN60" s="31" t="n"/>
-      <c r="BO60" s="41" t="n"/>
-      <c r="BP60" s="41" t="n"/>
-      <c r="BQ60" s="42" t="n"/>
+      <c r="BO60" s="38" t="n"/>
+      <c r="BP60" s="38" t="n"/>
+      <c r="BQ60" s="37" t="n"/>
       <c r="BR60" s="31" t="n"/>
-      <c r="BS60" s="41" t="n"/>
-      <c r="BT60" s="41" t="n"/>
-      <c r="BU60" s="42" t="n"/>
+      <c r="BS60" s="38" t="n"/>
+      <c r="BT60" s="38" t="n"/>
+      <c r="BU60" s="37" t="n"/>
       <c r="BV60" s="31" t="n"/>
-      <c r="BW60" s="41" t="n"/>
-      <c r="BX60" s="41" t="n"/>
-      <c r="BY60" s="42" t="n"/>
+      <c r="BW60" s="38" t="n"/>
+      <c r="BX60" s="38" t="n"/>
+      <c r="BY60" s="37" t="n"/>
       <c r="BZ60" s="31" t="n"/>
-      <c r="CA60" s="41" t="n"/>
-      <c r="CB60" s="41" t="n"/>
-      <c r="CC60" s="42" t="n"/>
+      <c r="CA60" s="38" t="n"/>
+      <c r="CB60" s="38" t="n"/>
+      <c r="CC60" s="37" t="n"/>
       <c r="CD60" s="31" t="n"/>
-      <c r="CE60" s="41" t="n"/>
-      <c r="CF60" s="41" t="n"/>
-      <c r="CG60" s="54" t="n"/>
+      <c r="CE60" s="38" t="n"/>
+      <c r="CF60" s="38" t="n"/>
+      <c r="CG60" s="48" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="29" t="inlineStr"/>
@@ -8053,85 +7397,85 @@
       <c r="D61" s="30" t="n"/>
       <c r="E61" s="30" t="n"/>
       <c r="F61" s="31" t="n"/>
-      <c r="G61" s="41" t="n"/>
-      <c r="H61" s="41" t="n"/>
-      <c r="I61" s="42" t="n"/>
+      <c r="G61" s="38" t="n"/>
+      <c r="H61" s="38" t="n"/>
+      <c r="I61" s="37" t="n"/>
       <c r="J61" s="31" t="n"/>
-      <c r="K61" s="41" t="n"/>
-      <c r="L61" s="41" t="n"/>
-      <c r="M61" s="42" t="n"/>
+      <c r="K61" s="38" t="n"/>
+      <c r="L61" s="38" t="n"/>
+      <c r="M61" s="37" t="n"/>
       <c r="N61" s="31" t="n"/>
-      <c r="O61" s="41" t="n"/>
-      <c r="P61" s="41" t="n"/>
-      <c r="Q61" s="42" t="n"/>
+      <c r="O61" s="38" t="n"/>
+      <c r="P61" s="38" t="n"/>
+      <c r="Q61" s="37" t="n"/>
       <c r="R61" s="31" t="n"/>
-      <c r="S61" s="41" t="n"/>
-      <c r="T61" s="41" t="n"/>
-      <c r="U61" s="42" t="n"/>
+      <c r="S61" s="38" t="n"/>
+      <c r="T61" s="38" t="n"/>
+      <c r="U61" s="37" t="n"/>
       <c r="V61" s="31" t="n"/>
-      <c r="W61" s="41" t="n"/>
-      <c r="X61" s="41" t="n"/>
-      <c r="Y61" s="42" t="n"/>
+      <c r="W61" s="38" t="n"/>
+      <c r="X61" s="38" t="n"/>
+      <c r="Y61" s="37" t="n"/>
       <c r="Z61" s="31" t="n"/>
-      <c r="AA61" s="41" t="n"/>
-      <c r="AB61" s="41" t="n"/>
-      <c r="AC61" s="42" t="n"/>
+      <c r="AA61" s="38" t="n"/>
+      <c r="AB61" s="38" t="n"/>
+      <c r="AC61" s="37" t="n"/>
       <c r="AD61" s="31" t="n"/>
-      <c r="AE61" s="41" t="n"/>
-      <c r="AF61" s="41" t="n"/>
-      <c r="AG61" s="42" t="n"/>
+      <c r="AE61" s="38" t="n"/>
+      <c r="AF61" s="38" t="n"/>
+      <c r="AG61" s="37" t="n"/>
       <c r="AH61" s="31" t="n"/>
-      <c r="AI61" s="41" t="n"/>
-      <c r="AJ61" s="41" t="n"/>
-      <c r="AK61" s="42" t="n"/>
+      <c r="AI61" s="38" t="n"/>
+      <c r="AJ61" s="38" t="n"/>
+      <c r="AK61" s="37" t="n"/>
       <c r="AL61" s="31" t="n"/>
-      <c r="AM61" s="41" t="n"/>
-      <c r="AN61" s="41" t="n"/>
-      <c r="AO61" s="42" t="n"/>
+      <c r="AM61" s="38" t="n"/>
+      <c r="AN61" s="38" t="n"/>
+      <c r="AO61" s="37" t="n"/>
       <c r="AP61" s="31" t="n"/>
-      <c r="AQ61" s="41" t="n"/>
-      <c r="AR61" s="41" t="n"/>
-      <c r="AS61" s="42" t="n"/>
+      <c r="AQ61" s="38" t="n"/>
+      <c r="AR61" s="38" t="n"/>
+      <c r="AS61" s="37" t="n"/>
       <c r="AT61" s="31" t="n"/>
-      <c r="AU61" s="41" t="n"/>
-      <c r="AV61" s="41" t="n"/>
-      <c r="AW61" s="42" t="n"/>
+      <c r="AU61" s="38" t="n"/>
+      <c r="AV61" s="38" t="n"/>
+      <c r="AW61" s="37" t="n"/>
       <c r="AX61" s="31" t="n"/>
-      <c r="AY61" s="41" t="n"/>
-      <c r="AZ61" s="41" t="n"/>
-      <c r="BA61" s="42" t="n"/>
+      <c r="AY61" s="38" t="n"/>
+      <c r="AZ61" s="38" t="n"/>
+      <c r="BA61" s="37" t="n"/>
       <c r="BB61" s="31" t="n"/>
-      <c r="BC61" s="41" t="n"/>
-      <c r="BD61" s="41" t="n"/>
-      <c r="BE61" s="42" t="n"/>
+      <c r="BC61" s="38" t="n"/>
+      <c r="BD61" s="38" t="n"/>
+      <c r="BE61" s="37" t="n"/>
       <c r="BF61" s="31" t="n"/>
-      <c r="BG61" s="41" t="n"/>
-      <c r="BH61" s="41" t="n"/>
-      <c r="BI61" s="42" t="n"/>
+      <c r="BG61" s="38" t="n"/>
+      <c r="BH61" s="38" t="n"/>
+      <c r="BI61" s="37" t="n"/>
       <c r="BJ61" s="31" t="n"/>
-      <c r="BK61" s="41" t="n"/>
-      <c r="BL61" s="41" t="n"/>
-      <c r="BM61" s="42" t="n"/>
+      <c r="BK61" s="38" t="n"/>
+      <c r="BL61" s="38" t="n"/>
+      <c r="BM61" s="37" t="n"/>
       <c r="BN61" s="31" t="n"/>
-      <c r="BO61" s="41" t="n"/>
-      <c r="BP61" s="41" t="n"/>
-      <c r="BQ61" s="42" t="n"/>
+      <c r="BO61" s="38" t="n"/>
+      <c r="BP61" s="38" t="n"/>
+      <c r="BQ61" s="37" t="n"/>
       <c r="BR61" s="31" t="n"/>
-      <c r="BS61" s="41" t="n"/>
-      <c r="BT61" s="41" t="n"/>
-      <c r="BU61" s="42" t="n"/>
+      <c r="BS61" s="38" t="n"/>
+      <c r="BT61" s="38" t="n"/>
+      <c r="BU61" s="37" t="n"/>
       <c r="BV61" s="31" t="n"/>
-      <c r="BW61" s="41" t="n"/>
-      <c r="BX61" s="41" t="n"/>
-      <c r="BY61" s="42" t="n"/>
+      <c r="BW61" s="38" t="n"/>
+      <c r="BX61" s="38" t="n"/>
+      <c r="BY61" s="37" t="n"/>
       <c r="BZ61" s="31" t="n"/>
-      <c r="CA61" s="41" t="n"/>
-      <c r="CB61" s="41" t="n"/>
-      <c r="CC61" s="42" t="n"/>
+      <c r="CA61" s="38" t="n"/>
+      <c r="CB61" s="38" t="n"/>
+      <c r="CC61" s="37" t="n"/>
       <c r="CD61" s="31" t="n"/>
-      <c r="CE61" s="41" t="n"/>
-      <c r="CF61" s="41" t="n"/>
-      <c r="CG61" s="54" t="n"/>
+      <c r="CE61" s="38" t="n"/>
+      <c r="CF61" s="38" t="n"/>
+      <c r="CG61" s="48" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="29" t="inlineStr"/>
@@ -8140,85 +7484,85 @@
       <c r="D62" s="30" t="n"/>
       <c r="E62" s="30" t="n"/>
       <c r="F62" s="31" t="n"/>
-      <c r="G62" s="41" t="n"/>
-      <c r="H62" s="41" t="n"/>
-      <c r="I62" s="42" t="n"/>
+      <c r="G62" s="38" t="n"/>
+      <c r="H62" s="38" t="n"/>
+      <c r="I62" s="37" t="n"/>
       <c r="J62" s="31" t="n"/>
-      <c r="K62" s="41" t="n"/>
-      <c r="L62" s="41" t="n"/>
-      <c r="M62" s="42" t="n"/>
+      <c r="K62" s="38" t="n"/>
+      <c r="L62" s="38" t="n"/>
+      <c r="M62" s="37" t="n"/>
       <c r="N62" s="31" t="n"/>
-      <c r="O62" s="41" t="n"/>
-      <c r="P62" s="41" t="n"/>
-      <c r="Q62" s="42" t="n"/>
+      <c r="O62" s="38" t="n"/>
+      <c r="P62" s="38" t="n"/>
+      <c r="Q62" s="37" t="n"/>
       <c r="R62" s="31" t="n"/>
-      <c r="S62" s="41" t="n"/>
-      <c r="T62" s="41" t="n"/>
-      <c r="U62" s="42" t="n"/>
+      <c r="S62" s="38" t="n"/>
+      <c r="T62" s="38" t="n"/>
+      <c r="U62" s="37" t="n"/>
       <c r="V62" s="31" t="n"/>
-      <c r="W62" s="41" t="n"/>
-      <c r="X62" s="41" t="n"/>
-      <c r="Y62" s="42" t="n"/>
+      <c r="W62" s="38" t="n"/>
+      <c r="X62" s="38" t="n"/>
+      <c r="Y62" s="37" t="n"/>
       <c r="Z62" s="31" t="n"/>
-      <c r="AA62" s="41" t="n"/>
-      <c r="AB62" s="41" t="n"/>
-      <c r="AC62" s="42" t="n"/>
+      <c r="AA62" s="38" t="n"/>
+      <c r="AB62" s="38" t="n"/>
+      <c r="AC62" s="37" t="n"/>
       <c r="AD62" s="31" t="n"/>
-      <c r="AE62" s="41" t="n"/>
-      <c r="AF62" s="41" t="n"/>
-      <c r="AG62" s="42" t="n"/>
+      <c r="AE62" s="38" t="n"/>
+      <c r="AF62" s="38" t="n"/>
+      <c r="AG62" s="37" t="n"/>
       <c r="AH62" s="31" t="n"/>
-      <c r="AI62" s="41" t="n"/>
-      <c r="AJ62" s="41" t="n"/>
-      <c r="AK62" s="42" t="n"/>
+      <c r="AI62" s="38" t="n"/>
+      <c r="AJ62" s="38" t="n"/>
+      <c r="AK62" s="37" t="n"/>
       <c r="AL62" s="31" t="n"/>
-      <c r="AM62" s="41" t="n"/>
-      <c r="AN62" s="41" t="n"/>
-      <c r="AO62" s="42" t="n"/>
+      <c r="AM62" s="38" t="n"/>
+      <c r="AN62" s="38" t="n"/>
+      <c r="AO62" s="37" t="n"/>
       <c r="AP62" s="31" t="n"/>
-      <c r="AQ62" s="41" t="n"/>
-      <c r="AR62" s="41" t="n"/>
-      <c r="AS62" s="42" t="n"/>
+      <c r="AQ62" s="38" t="n"/>
+      <c r="AR62" s="38" t="n"/>
+      <c r="AS62" s="37" t="n"/>
       <c r="AT62" s="31" t="n"/>
-      <c r="AU62" s="41" t="n"/>
-      <c r="AV62" s="41" t="n"/>
-      <c r="AW62" s="42" t="n"/>
+      <c r="AU62" s="38" t="n"/>
+      <c r="AV62" s="38" t="n"/>
+      <c r="AW62" s="37" t="n"/>
       <c r="AX62" s="31" t="n"/>
-      <c r="AY62" s="41" t="n"/>
-      <c r="AZ62" s="41" t="n"/>
-      <c r="BA62" s="42" t="n"/>
+      <c r="AY62" s="38" t="n"/>
+      <c r="AZ62" s="38" t="n"/>
+      <c r="BA62" s="37" t="n"/>
       <c r="BB62" s="31" t="n"/>
-      <c r="BC62" s="41" t="n"/>
-      <c r="BD62" s="41" t="n"/>
-      <c r="BE62" s="42" t="n"/>
+      <c r="BC62" s="38" t="n"/>
+      <c r="BD62" s="38" t="n"/>
+      <c r="BE62" s="37" t="n"/>
       <c r="BF62" s="31" t="n"/>
-      <c r="BG62" s="41" t="n"/>
-      <c r="BH62" s="41" t="n"/>
-      <c r="BI62" s="42" t="n"/>
+      <c r="BG62" s="38" t="n"/>
+      <c r="BH62" s="38" t="n"/>
+      <c r="BI62" s="37" t="n"/>
       <c r="BJ62" s="31" t="n"/>
-      <c r="BK62" s="41" t="n"/>
-      <c r="BL62" s="41" t="n"/>
-      <c r="BM62" s="42" t="n"/>
+      <c r="BK62" s="38" t="n"/>
+      <c r="BL62" s="38" t="n"/>
+      <c r="BM62" s="37" t="n"/>
       <c r="BN62" s="31" t="n"/>
-      <c r="BO62" s="41" t="n"/>
-      <c r="BP62" s="41" t="n"/>
-      <c r="BQ62" s="42" t="n"/>
+      <c r="BO62" s="38" t="n"/>
+      <c r="BP62" s="38" t="n"/>
+      <c r="BQ62" s="37" t="n"/>
       <c r="BR62" s="31" t="n"/>
-      <c r="BS62" s="41" t="n"/>
-      <c r="BT62" s="41" t="n"/>
-      <c r="BU62" s="42" t="n"/>
+      <c r="BS62" s="38" t="n"/>
+      <c r="BT62" s="38" t="n"/>
+      <c r="BU62" s="37" t="n"/>
       <c r="BV62" s="31" t="n"/>
-      <c r="BW62" s="41" t="n"/>
-      <c r="BX62" s="41" t="n"/>
-      <c r="BY62" s="42" t="n"/>
+      <c r="BW62" s="38" t="n"/>
+      <c r="BX62" s="38" t="n"/>
+      <c r="BY62" s="37" t="n"/>
       <c r="BZ62" s="31" t="n"/>
-      <c r="CA62" s="41" t="n"/>
-      <c r="CB62" s="41" t="n"/>
-      <c r="CC62" s="42" t="n"/>
+      <c r="CA62" s="38" t="n"/>
+      <c r="CB62" s="38" t="n"/>
+      <c r="CC62" s="37" t="n"/>
       <c r="CD62" s="31" t="n"/>
-      <c r="CE62" s="41" t="n"/>
-      <c r="CF62" s="41" t="n"/>
-      <c r="CG62" s="54" t="n"/>
+      <c r="CE62" s="38" t="n"/>
+      <c r="CF62" s="38" t="n"/>
+      <c r="CG62" s="48" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="29" t="inlineStr"/>
@@ -8227,238 +7571,220 @@
       <c r="D63" s="30" t="n"/>
       <c r="E63" s="30" t="n"/>
       <c r="F63" s="31" t="n"/>
-      <c r="G63" s="41" t="n"/>
-      <c r="H63" s="41" t="n"/>
-      <c r="I63" s="42" t="n"/>
+      <c r="G63" s="38" t="n"/>
+      <c r="H63" s="38" t="n"/>
+      <c r="I63" s="37" t="n"/>
       <c r="J63" s="31" t="n"/>
-      <c r="K63" s="41" t="n"/>
-      <c r="L63" s="41" t="n"/>
-      <c r="M63" s="42" t="n"/>
+      <c r="K63" s="38" t="n"/>
+      <c r="L63" s="38" t="n"/>
+      <c r="M63" s="37" t="n"/>
       <c r="N63" s="31" t="n"/>
-      <c r="O63" s="41" t="n"/>
-      <c r="P63" s="41" t="n"/>
-      <c r="Q63" s="42" t="n"/>
+      <c r="O63" s="38" t="n"/>
+      <c r="P63" s="38" t="n"/>
+      <c r="Q63" s="37" t="n"/>
       <c r="R63" s="31" t="n"/>
-      <c r="S63" s="41" t="n"/>
-      <c r="T63" s="41" t="n"/>
-      <c r="U63" s="42" t="n"/>
+      <c r="S63" s="38" t="n"/>
+      <c r="T63" s="38" t="n"/>
+      <c r="U63" s="37" t="n"/>
       <c r="V63" s="31" t="n"/>
-      <c r="W63" s="41" t="n"/>
-      <c r="X63" s="41" t="n"/>
-      <c r="Y63" s="42" t="n"/>
+      <c r="W63" s="38" t="n"/>
+      <c r="X63" s="38" t="n"/>
+      <c r="Y63" s="37" t="n"/>
       <c r="Z63" s="31" t="n"/>
-      <c r="AA63" s="41" t="n"/>
-      <c r="AB63" s="41" t="n"/>
-      <c r="AC63" s="42" t="n"/>
+      <c r="AA63" s="38" t="n"/>
+      <c r="AB63" s="38" t="n"/>
+      <c r="AC63" s="37" t="n"/>
       <c r="AD63" s="31" t="n"/>
-      <c r="AE63" s="41" t="n"/>
-      <c r="AF63" s="41" t="n"/>
-      <c r="AG63" s="42" t="n"/>
+      <c r="AE63" s="38" t="n"/>
+      <c r="AF63" s="38" t="n"/>
+      <c r="AG63" s="37" t="n"/>
       <c r="AH63" s="31" t="n"/>
-      <c r="AI63" s="41" t="n"/>
-      <c r="AJ63" s="41" t="n"/>
-      <c r="AK63" s="42" t="n"/>
+      <c r="AI63" s="38" t="n"/>
+      <c r="AJ63" s="38" t="n"/>
+      <c r="AK63" s="37" t="n"/>
       <c r="AL63" s="31" t="n"/>
-      <c r="AM63" s="41" t="n"/>
-      <c r="AN63" s="41" t="n"/>
-      <c r="AO63" s="42" t="n"/>
+      <c r="AM63" s="38" t="n"/>
+      <c r="AN63" s="38" t="n"/>
+      <c r="AO63" s="37" t="n"/>
       <c r="AP63" s="31" t="n"/>
-      <c r="AQ63" s="41" t="n"/>
-      <c r="AR63" s="41" t="n"/>
-      <c r="AS63" s="42" t="n"/>
+      <c r="AQ63" s="38" t="n"/>
+      <c r="AR63" s="38" t="n"/>
+      <c r="AS63" s="37" t="n"/>
       <c r="AT63" s="31" t="n"/>
-      <c r="AU63" s="41" t="n"/>
-      <c r="AV63" s="41" t="n"/>
-      <c r="AW63" s="42" t="n"/>
+      <c r="AU63" s="38" t="n"/>
+      <c r="AV63" s="38" t="n"/>
+      <c r="AW63" s="37" t="n"/>
       <c r="AX63" s="31" t="n"/>
-      <c r="AY63" s="41" t="n"/>
-      <c r="AZ63" s="41" t="n"/>
-      <c r="BA63" s="42" t="n"/>
+      <c r="AY63" s="38" t="n"/>
+      <c r="AZ63" s="38" t="n"/>
+      <c r="BA63" s="37" t="n"/>
       <c r="BB63" s="31" t="n"/>
-      <c r="BC63" s="41" t="n"/>
-      <c r="BD63" s="41" t="n"/>
-      <c r="BE63" s="42" t="n"/>
+      <c r="BC63" s="38" t="n"/>
+      <c r="BD63" s="38" t="n"/>
+      <c r="BE63" s="37" t="n"/>
       <c r="BF63" s="31" t="n"/>
-      <c r="BG63" s="41" t="n"/>
-      <c r="BH63" s="41" t="n"/>
-      <c r="BI63" s="42" t="n"/>
+      <c r="BG63" s="38" t="n"/>
+      <c r="BH63" s="38" t="n"/>
+      <c r="BI63" s="37" t="n"/>
       <c r="BJ63" s="31" t="n"/>
-      <c r="BK63" s="41" t="n"/>
-      <c r="BL63" s="41" t="n"/>
-      <c r="BM63" s="42" t="n"/>
+      <c r="BK63" s="38" t="n"/>
+      <c r="BL63" s="38" t="n"/>
+      <c r="BM63" s="37" t="n"/>
       <c r="BN63" s="31" t="n"/>
-      <c r="BO63" s="41" t="n"/>
-      <c r="BP63" s="41" t="n"/>
-      <c r="BQ63" s="42" t="n"/>
+      <c r="BO63" s="38" t="n"/>
+      <c r="BP63" s="38" t="n"/>
+      <c r="BQ63" s="37" t="n"/>
       <c r="BR63" s="31" t="n"/>
-      <c r="BS63" s="41" t="n"/>
-      <c r="BT63" s="41" t="n"/>
-      <c r="BU63" s="42" t="n"/>
+      <c r="BS63" s="38" t="n"/>
+      <c r="BT63" s="38" t="n"/>
+      <c r="BU63" s="37" t="n"/>
       <c r="BV63" s="31" t="n"/>
-      <c r="BW63" s="41" t="n"/>
-      <c r="BX63" s="41" t="n"/>
-      <c r="BY63" s="42" t="n"/>
+      <c r="BW63" s="38" t="n"/>
+      <c r="BX63" s="38" t="n"/>
+      <c r="BY63" s="37" t="n"/>
       <c r="BZ63" s="31" t="n"/>
-      <c r="CA63" s="41" t="n"/>
-      <c r="CB63" s="41" t="n"/>
-      <c r="CC63" s="42" t="n"/>
+      <c r="CA63" s="38" t="n"/>
+      <c r="CB63" s="38" t="n"/>
+      <c r="CC63" s="37" t="n"/>
       <c r="CD63" s="31" t="n"/>
-      <c r="CE63" s="41" t="n"/>
-      <c r="CF63" s="41" t="n"/>
-      <c r="CG63" s="54" t="n"/>
+      <c r="CE63" s="38" t="n"/>
+      <c r="CF63" s="38" t="n"/>
+      <c r="CG63" s="48" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="73" t="inlineStr"/>
-      <c r="B64" s="74" t="n"/>
-      <c r="C64" s="74" t="n"/>
-      <c r="D64" s="74" t="n"/>
-      <c r="E64" s="74" t="n"/>
-      <c r="F64" s="75" t="n"/>
-      <c r="G64" s="76" t="n"/>
-      <c r="H64" s="76" t="n"/>
-      <c r="I64" s="77" t="n"/>
-      <c r="J64" s="75" t="n"/>
-      <c r="K64" s="76" t="n"/>
-      <c r="L64" s="76" t="n"/>
-      <c r="M64" s="77" t="n"/>
-      <c r="N64" s="75" t="n"/>
-      <c r="O64" s="76" t="n"/>
-      <c r="P64" s="76" t="n"/>
-      <c r="Q64" s="77" t="n"/>
-      <c r="R64" s="75" t="n"/>
-      <c r="S64" s="76" t="n"/>
-      <c r="T64" s="76" t="n"/>
-      <c r="U64" s="77" t="n"/>
-      <c r="V64" s="75" t="n"/>
-      <c r="W64" s="76" t="n"/>
-      <c r="X64" s="76" t="n"/>
-      <c r="Y64" s="77" t="n"/>
-      <c r="Z64" s="75" t="n"/>
-      <c r="AA64" s="76" t="n"/>
-      <c r="AB64" s="76" t="n"/>
-      <c r="AC64" s="77" t="n"/>
-      <c r="AD64" s="75" t="n"/>
-      <c r="AE64" s="76" t="n"/>
-      <c r="AF64" s="76" t="n"/>
-      <c r="AG64" s="77" t="n"/>
-      <c r="AH64" s="75" t="n"/>
-      <c r="AI64" s="76" t="n"/>
-      <c r="AJ64" s="76" t="n"/>
-      <c r="AK64" s="77" t="n"/>
-      <c r="AL64" s="75" t="n"/>
-      <c r="AM64" s="76" t="n"/>
-      <c r="AN64" s="76" t="n"/>
-      <c r="AO64" s="77" t="n"/>
-      <c r="AP64" s="75" t="n"/>
-      <c r="AQ64" s="76" t="n"/>
-      <c r="AR64" s="76" t="n"/>
-      <c r="AS64" s="77" t="n"/>
-      <c r="AT64" s="75" t="n"/>
-      <c r="AU64" s="76" t="n"/>
-      <c r="AV64" s="76" t="n"/>
-      <c r="AW64" s="77" t="n"/>
-      <c r="AX64" s="75" t="n"/>
-      <c r="AY64" s="76" t="n"/>
-      <c r="AZ64" s="76" t="n"/>
-      <c r="BA64" s="77" t="n"/>
-      <c r="BB64" s="75" t="n"/>
-      <c r="BC64" s="76" t="n"/>
-      <c r="BD64" s="76" t="n"/>
-      <c r="BE64" s="77" t="n"/>
-      <c r="BF64" s="75" t="n"/>
-      <c r="BG64" s="76" t="n"/>
-      <c r="BH64" s="76" t="n"/>
-      <c r="BI64" s="77" t="n"/>
-      <c r="BJ64" s="75" t="n"/>
-      <c r="BK64" s="76" t="n"/>
-      <c r="BL64" s="76" t="n"/>
-      <c r="BM64" s="77" t="n"/>
-      <c r="BN64" s="75" t="n"/>
-      <c r="BO64" s="76" t="n"/>
-      <c r="BP64" s="76" t="n"/>
-      <c r="BQ64" s="77" t="n"/>
-      <c r="BR64" s="75" t="n"/>
-      <c r="BS64" s="76" t="n"/>
-      <c r="BT64" s="76" t="n"/>
-      <c r="BU64" s="77" t="n"/>
-      <c r="BV64" s="75" t="n"/>
-      <c r="BW64" s="76" t="n"/>
-      <c r="BX64" s="76" t="n"/>
-      <c r="BY64" s="77" t="n"/>
-      <c r="BZ64" s="75" t="n"/>
-      <c r="CA64" s="76" t="n"/>
-      <c r="CB64" s="76" t="n"/>
-      <c r="CC64" s="77" t="n"/>
-      <c r="CD64" s="75" t="n"/>
-      <c r="CE64" s="76" t="n"/>
-      <c r="CF64" s="76" t="n"/>
-      <c r="CG64" s="78" t="n"/>
+      <c r="A64" s="50" t="inlineStr"/>
+      <c r="B64" s="51" t="n"/>
+      <c r="C64" s="51" t="n"/>
+      <c r="D64" s="51" t="n"/>
+      <c r="E64" s="51" t="n"/>
+      <c r="F64" s="52" t="n"/>
+      <c r="G64" s="53" t="n"/>
+      <c r="H64" s="53" t="n"/>
+      <c r="I64" s="54" t="n"/>
+      <c r="J64" s="52" t="n"/>
+      <c r="K64" s="53" t="n"/>
+      <c r="L64" s="53" t="n"/>
+      <c r="M64" s="54" t="n"/>
+      <c r="N64" s="52" t="n"/>
+      <c r="O64" s="53" t="n"/>
+      <c r="P64" s="53" t="n"/>
+      <c r="Q64" s="54" t="n"/>
+      <c r="R64" s="52" t="n"/>
+      <c r="S64" s="53" t="n"/>
+      <c r="T64" s="53" t="n"/>
+      <c r="U64" s="54" t="n"/>
+      <c r="V64" s="52" t="n"/>
+      <c r="W64" s="53" t="n"/>
+      <c r="X64" s="53" t="n"/>
+      <c r="Y64" s="54" t="n"/>
+      <c r="Z64" s="52" t="n"/>
+      <c r="AA64" s="53" t="n"/>
+      <c r="AB64" s="53" t="n"/>
+      <c r="AC64" s="54" t="n"/>
+      <c r="AD64" s="52" t="n"/>
+      <c r="AE64" s="53" t="n"/>
+      <c r="AF64" s="53" t="n"/>
+      <c r="AG64" s="54" t="n"/>
+      <c r="AH64" s="52" t="n"/>
+      <c r="AI64" s="53" t="n"/>
+      <c r="AJ64" s="53" t="n"/>
+      <c r="AK64" s="54" t="n"/>
+      <c r="AL64" s="52" t="n"/>
+      <c r="AM64" s="53" t="n"/>
+      <c r="AN64" s="53" t="n"/>
+      <c r="AO64" s="54" t="n"/>
+      <c r="AP64" s="52" t="n"/>
+      <c r="AQ64" s="53" t="n"/>
+      <c r="AR64" s="53" t="n"/>
+      <c r="AS64" s="54" t="n"/>
+      <c r="AT64" s="52" t="n"/>
+      <c r="AU64" s="53" t="n"/>
+      <c r="AV64" s="53" t="n"/>
+      <c r="AW64" s="54" t="n"/>
+      <c r="AX64" s="52" t="n"/>
+      <c r="AY64" s="53" t="n"/>
+      <c r="AZ64" s="53" t="n"/>
+      <c r="BA64" s="54" t="n"/>
+      <c r="BB64" s="52" t="n"/>
+      <c r="BC64" s="53" t="n"/>
+      <c r="BD64" s="53" t="n"/>
+      <c r="BE64" s="54" t="n"/>
+      <c r="BF64" s="52" t="n"/>
+      <c r="BG64" s="53" t="n"/>
+      <c r="BH64" s="53" t="n"/>
+      <c r="BI64" s="54" t="n"/>
+      <c r="BJ64" s="52" t="n"/>
+      <c r="BK64" s="53" t="n"/>
+      <c r="BL64" s="53" t="n"/>
+      <c r="BM64" s="54" t="n"/>
+      <c r="BN64" s="52" t="n"/>
+      <c r="BO64" s="53" t="n"/>
+      <c r="BP64" s="53" t="n"/>
+      <c r="BQ64" s="54" t="n"/>
+      <c r="BR64" s="52" t="n"/>
+      <c r="BS64" s="53" t="n"/>
+      <c r="BT64" s="53" t="n"/>
+      <c r="BU64" s="54" t="n"/>
+      <c r="BV64" s="52" t="n"/>
+      <c r="BW64" s="53" t="n"/>
+      <c r="BX64" s="53" t="n"/>
+      <c r="BY64" s="54" t="n"/>
+      <c r="BZ64" s="52" t="n"/>
+      <c r="CA64" s="53" t="n"/>
+      <c r="CB64" s="53" t="n"/>
+      <c r="CC64" s="54" t="n"/>
+      <c r="CD64" s="52" t="n"/>
+      <c r="CE64" s="53" t="n"/>
+      <c r="CF64" s="53" t="n"/>
+      <c r="CG64" s="55" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="487">
+  <mergeCells count="422">
     <mergeCell ref="BN41:BQ41"/>
-    <mergeCell ref="BZ12:CG12"/>
     <mergeCell ref="BF58:BI58"/>
-    <mergeCell ref="BP22:BQ22"/>
     <mergeCell ref="A4:E5"/>
     <mergeCell ref="Z9:AC9"/>
     <mergeCell ref="AT17:AW17"/>
     <mergeCell ref="CD2:CG3"/>
-    <mergeCell ref="BZ13:CG13"/>
     <mergeCell ref="AP53:AS53"/>
+    <mergeCell ref="Z11:AC11"/>
     <mergeCell ref="BB19:BE19"/>
     <mergeCell ref="BD23:BE23"/>
-    <mergeCell ref="AL37:AM37"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="BV10:BY10"/>
     <mergeCell ref="R13:U13"/>
     <mergeCell ref="BF18:BI18"/>
     <mergeCell ref="BR44:BU44"/>
     <mergeCell ref="J53:M53"/>
-    <mergeCell ref="CD45:CF45"/>
     <mergeCell ref="BB20:BE20"/>
+    <mergeCell ref="CD59:CG59"/>
     <mergeCell ref="AX52:BA52"/>
-    <mergeCell ref="AD31:AG31"/>
-    <mergeCell ref="V31:Y31"/>
     <mergeCell ref="Z52:AC52"/>
     <mergeCell ref="R55:U55"/>
     <mergeCell ref="J55:M55"/>
     <mergeCell ref="AX4:BA5"/>
     <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="AH32:AI32"/>
     <mergeCell ref="AP4:AS5"/>
     <mergeCell ref="BF42:BI42"/>
     <mergeCell ref="AX53:BA53"/>
     <mergeCell ref="AD32:AG32"/>
     <mergeCell ref="BF44:BI44"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="BT45:BU45"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="X8:Y8"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="AH54:AK54"/>
-    <mergeCell ref="BB18:BC18"/>
-    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AX38:BA38"/>
     <mergeCell ref="AP16:AS16"/>
-    <mergeCell ref="BD18:BE18"/>
     <mergeCell ref="BZ21:CC21"/>
     <mergeCell ref="R33:U33"/>
     <mergeCell ref="R8:U8"/>
     <mergeCell ref="J8:M8"/>
     <mergeCell ref="AH56:AK56"/>
     <mergeCell ref="N35:Q35"/>
-    <mergeCell ref="AB36:AC36"/>
     <mergeCell ref="R10:U10"/>
-    <mergeCell ref="AX57:AY57"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="BN57:BQ57"/>
     <mergeCell ref="BV41:BY41"/>
     <mergeCell ref="J2:M3"/>
     <mergeCell ref="BN58:BQ58"/>
-    <mergeCell ref="AX39:AY39"/>
-    <mergeCell ref="AZ39:BA39"/>
-    <mergeCell ref="BN59:BO59"/>
-    <mergeCell ref="BP59:BQ59"/>
+    <mergeCell ref="Z12:AC12"/>
     <mergeCell ref="BJ17:BM17"/>
     <mergeCell ref="BR52:BU52"/>
     <mergeCell ref="BF53:BI53"/>
@@ -8473,21 +7799,16 @@
     <mergeCell ref="BB59:BE59"/>
     <mergeCell ref="AX43:BA43"/>
     <mergeCell ref="R4:U5"/>
-    <mergeCell ref="CD59:CF59"/>
     <mergeCell ref="V4:Y5"/>
     <mergeCell ref="CD6:CG6"/>
-    <mergeCell ref="AL31:AO31"/>
     <mergeCell ref="Z55:AC55"/>
     <mergeCell ref="BR21:BU21"/>
     <mergeCell ref="BF4:BI5"/>
     <mergeCell ref="N54:Q54"/>
-    <mergeCell ref="AX17:AY17"/>
     <mergeCell ref="V13:Y13"/>
     <mergeCell ref="BZ23:CC23"/>
     <mergeCell ref="BR23:BU23"/>
-    <mergeCell ref="AB11:AC11"/>
     <mergeCell ref="BJ38:BM38"/>
-    <mergeCell ref="BV31:BY31"/>
     <mergeCell ref="R7:U7"/>
     <mergeCell ref="R34:U34"/>
     <mergeCell ref="AP1:AS1"/>
@@ -8501,8 +7822,7 @@
     <mergeCell ref="Z8:AC8"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="V55:W55"/>
-    <mergeCell ref="BJ42:BK42"/>
+    <mergeCell ref="N9:Q9"/>
     <mergeCell ref="AT39:AW39"/>
     <mergeCell ref="AD53:AG53"/>
     <mergeCell ref="BB37:BC37"/>
@@ -8510,29 +7830,28 @@
     <mergeCell ref="AD55:AG55"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="AP37:AS37"/>
+    <mergeCell ref="BR45:BU45"/>
     <mergeCell ref="BJ45:BM45"/>
     <mergeCell ref="AP12:AS12"/>
     <mergeCell ref="AH12:AK12"/>
-    <mergeCell ref="CD23:CF23"/>
     <mergeCell ref="BJ20:BM20"/>
-    <mergeCell ref="BF31:BI31"/>
     <mergeCell ref="BZ52:CC52"/>
     <mergeCell ref="BF6:BI6"/>
     <mergeCell ref="AH52:AK52"/>
     <mergeCell ref="AP14:AS14"/>
-    <mergeCell ref="R31:U31"/>
+    <mergeCell ref="AH14:AK14"/>
     <mergeCell ref="BJ22:BM22"/>
     <mergeCell ref="AL4:AO5"/>
     <mergeCell ref="J6:M6"/>
-    <mergeCell ref="V32:W32"/>
     <mergeCell ref="AD4:AG5"/>
     <mergeCell ref="AJ16:AK16"/>
     <mergeCell ref="AT58:AW58"/>
     <mergeCell ref="AX16:BA16"/>
     <mergeCell ref="Z33:AC33"/>
-    <mergeCell ref="BL42:BM42"/>
+    <mergeCell ref="V54:Y54"/>
     <mergeCell ref="BZ45:CC45"/>
     <mergeCell ref="AX18:BA18"/>
+    <mergeCell ref="Z35:AC35"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="Z10:AC10"/>
     <mergeCell ref="BB1:BE1"/>
@@ -8544,25 +7863,19 @@
     <mergeCell ref="N11:Q11"/>
     <mergeCell ref="N12:Q12"/>
     <mergeCell ref="BB39:BE39"/>
+    <mergeCell ref="CD22:CG22"/>
     <mergeCell ref="BR59:BU59"/>
     <mergeCell ref="BJ59:BM59"/>
-    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AP38:AS38"/>
     <mergeCell ref="BN30:BQ30"/>
-    <mergeCell ref="AP38:AS38"/>
-    <mergeCell ref="AB13:AC13"/>
     <mergeCell ref="AD6:AG6"/>
     <mergeCell ref="BF45:BI45"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="F4:I5"/>
-    <mergeCell ref="BV12:BY12"/>
     <mergeCell ref="AP15:AS15"/>
     <mergeCell ref="R32:U32"/>
-    <mergeCell ref="BF41:BG41"/>
-    <mergeCell ref="AT31:AW31"/>
     <mergeCell ref="AH30:AK30"/>
-    <mergeCell ref="BV13:BY13"/>
     <mergeCell ref="BF21:BI21"/>
-    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="V56:Y56"/>
     <mergeCell ref="AX1:BA1"/>
     <mergeCell ref="BF16:BI16"/>
@@ -8577,26 +7890,22 @@
     <mergeCell ref="BN18:BQ18"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="AH35:AK35"/>
-    <mergeCell ref="BN22:BO22"/>
+    <mergeCell ref="BB58:BE58"/>
     <mergeCell ref="V9:Y9"/>
     <mergeCell ref="AL53:AO53"/>
     <mergeCell ref="BZ2:CC3"/>
     <mergeCell ref="AP30:AS30"/>
     <mergeCell ref="BN42:BQ42"/>
     <mergeCell ref="V11:Y11"/>
-    <mergeCell ref="CD22:CF22"/>
     <mergeCell ref="AX37:BA37"/>
     <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="BN31:BQ31"/>
-    <mergeCell ref="AH14:AI14"/>
+    <mergeCell ref="BN44:BQ44"/>
     <mergeCell ref="BN6:BQ6"/>
-    <mergeCell ref="AJ14:AK14"/>
     <mergeCell ref="AX20:BA20"/>
     <mergeCell ref="AT56:AU56"/>
     <mergeCell ref="BR6:BU6"/>
     <mergeCell ref="AX14:BA14"/>
     <mergeCell ref="BZ59:CC59"/>
-    <mergeCell ref="Z31:AC31"/>
     <mergeCell ref="AT4:AW5"/>
     <mergeCell ref="AP56:AS56"/>
     <mergeCell ref="BF40:BI40"/>
@@ -8604,14 +7913,13 @@
     <mergeCell ref="Z32:AC32"/>
     <mergeCell ref="BV30:BY30"/>
     <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="AL16:AO16"/>
     <mergeCell ref="R2:U3"/>
     <mergeCell ref="N33:Q33"/>
     <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="AZ17:BA17"/>
     <mergeCell ref="BJ7:CG8"/>
-    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="N10:Q10"/>
     <mergeCell ref="BR2:BU3"/>
-    <mergeCell ref="F31:I31"/>
     <mergeCell ref="BJ57:BM57"/>
     <mergeCell ref="AP36:AS36"/>
     <mergeCell ref="BR19:BU19"/>
@@ -8624,30 +7932,22 @@
     <mergeCell ref="V12:Y12"/>
     <mergeCell ref="BF17:BI17"/>
     <mergeCell ref="BN52:BQ52"/>
-    <mergeCell ref="BJ21:BK21"/>
     <mergeCell ref="AJ38:AK38"/>
     <mergeCell ref="BN39:BQ39"/>
     <mergeCell ref="AT6:AW6"/>
     <mergeCell ref="BN4:BQ5"/>
     <mergeCell ref="AL6:AO6"/>
-    <mergeCell ref="BZ10:CG10"/>
-    <mergeCell ref="Z56:AA56"/>
     <mergeCell ref="BV42:BY42"/>
-    <mergeCell ref="BP23:BQ23"/>
     <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="AB56:AC56"/>
+    <mergeCell ref="BF19:BI19"/>
     <mergeCell ref="AD13:AG13"/>
-    <mergeCell ref="AH15:AI15"/>
-    <mergeCell ref="AJ15:AK15"/>
-    <mergeCell ref="CD31:CG31"/>
+    <mergeCell ref="CD44:CG44"/>
     <mergeCell ref="Z7:AC7"/>
     <mergeCell ref="AD15:AG15"/>
     <mergeCell ref="BZ6:CC6"/>
-    <mergeCell ref="AH31:AK31"/>
     <mergeCell ref="J54:M54"/>
     <mergeCell ref="BZ1:CC1"/>
     <mergeCell ref="BF38:BI38"/>
-    <mergeCell ref="Z11:AA11"/>
     <mergeCell ref="N34:Q34"/>
     <mergeCell ref="AP17:AS17"/>
     <mergeCell ref="AL1:AO1"/>
@@ -8665,43 +7965,38 @@
     <mergeCell ref="BB42:BE42"/>
     <mergeCell ref="BN53:BQ53"/>
     <mergeCell ref="BV44:BY44"/>
+    <mergeCell ref="AL37:AO37"/>
     <mergeCell ref="BN45:BQ45"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="AL12:AO12"/>
-    <mergeCell ref="AX38:AY38"/>
+    <mergeCell ref="CD52:CG52"/>
     <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="CD52:CG52"/>
-    <mergeCell ref="AZ38:BA38"/>
-    <mergeCell ref="BB31:BE31"/>
     <mergeCell ref="BV52:BY52"/>
     <mergeCell ref="BB6:BE6"/>
     <mergeCell ref="BV4:BY5"/>
     <mergeCell ref="AD54:AG54"/>
     <mergeCell ref="AL14:AO14"/>
-    <mergeCell ref="N31:Q31"/>
-    <mergeCell ref="P10:Q10"/>
     <mergeCell ref="F52:I52"/>
     <mergeCell ref="AH4:AK5"/>
-    <mergeCell ref="BZ11:CG11"/>
     <mergeCell ref="BF1:BI1"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="AT16:AW16"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="CD21:CG21"/>
+    <mergeCell ref="V33:Y33"/>
     <mergeCell ref="AT52:AW52"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="BJ54:CG55"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="AB12:AC12"/>
     <mergeCell ref="AT18:AW18"/>
     <mergeCell ref="V35:Y35"/>
     <mergeCell ref="V10:Y10"/>
     <mergeCell ref="AP11:AQ11"/>
-    <mergeCell ref="BH19:BI19"/>
     <mergeCell ref="V34:Y34"/>
     <mergeCell ref="BN2:BQ3"/>
     <mergeCell ref="BF2:BI3"/>
     <mergeCell ref="N52:Q52"/>
+    <mergeCell ref="AX57:BA57"/>
     <mergeCell ref="AD36:AG36"/>
     <mergeCell ref="AD30:AG30"/>
     <mergeCell ref="V30:Y30"/>
@@ -8709,13 +8004,13 @@
     <mergeCell ref="N4:Q5"/>
     <mergeCell ref="BJ32:CG33"/>
     <mergeCell ref="BB44:BE44"/>
+    <mergeCell ref="AX39:BA39"/>
     <mergeCell ref="BB52:BE52"/>
     <mergeCell ref="BZ22:CC22"/>
     <mergeCell ref="BF59:BI59"/>
     <mergeCell ref="AL38:AO38"/>
     <mergeCell ref="BJ30:BM30"/>
     <mergeCell ref="BN21:BQ21"/>
-    <mergeCell ref="X7:Y7"/>
     <mergeCell ref="P56:Q56"/>
     <mergeCell ref="CD53:CG53"/>
     <mergeCell ref="R1:U1"/>
@@ -8723,21 +8018,20 @@
     <mergeCell ref="BV53:BY53"/>
     <mergeCell ref="AD56:AG56"/>
     <mergeCell ref="AH13:AK13"/>
+    <mergeCell ref="BN23:BQ23"/>
     <mergeCell ref="AL15:AO15"/>
     <mergeCell ref="N32:Q32"/>
     <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="AH7:AJ7"/>
     <mergeCell ref="BR41:BU41"/>
     <mergeCell ref="AT37:AW37"/>
-    <mergeCell ref="BZ14:CG14"/>
-    <mergeCell ref="N9:O9"/>
     <mergeCell ref="CD4:CG5"/>
+    <mergeCell ref="AX17:BA17"/>
     <mergeCell ref="AT53:AW53"/>
     <mergeCell ref="BJ16:BM16"/>
     <mergeCell ref="AT19:AW19"/>
     <mergeCell ref="AD11:AG11"/>
-    <mergeCell ref="AN37:AO37"/>
     <mergeCell ref="V36:Y36"/>
-    <mergeCell ref="BR45:BS45"/>
     <mergeCell ref="AL2:AO3"/>
     <mergeCell ref="BR17:BS17"/>
     <mergeCell ref="BJ18:BM18"/>
@@ -8746,32 +8040,28 @@
     <mergeCell ref="BF20:BI20"/>
     <mergeCell ref="R9:U9"/>
     <mergeCell ref="AD52:AG52"/>
+    <mergeCell ref="V55:Y55"/>
+    <mergeCell ref="N55:Q55"/>
     <mergeCell ref="BB4:BE5"/>
     <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="BF22:BI22"/>
     <mergeCell ref="AL30:AO30"/>
-    <mergeCell ref="BF22:BI22"/>
+    <mergeCell ref="BJ42:BM42"/>
     <mergeCell ref="R11:U11"/>
     <mergeCell ref="BB53:BE53"/>
     <mergeCell ref="BJ44:BM44"/>
-    <mergeCell ref="BR31:BU31"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="BJ31:BM31"/>
-    <mergeCell ref="V54:W54"/>
     <mergeCell ref="BJ6:BM6"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="AT14:AW14"/>
     <mergeCell ref="BV59:BY59"/>
     <mergeCell ref="BB38:BE38"/>
     <mergeCell ref="AT38:AW38"/>
-    <mergeCell ref="Z35:AA35"/>
-    <mergeCell ref="AH7:AI7"/>
     <mergeCell ref="AL56:AO56"/>
     <mergeCell ref="R35:U35"/>
     <mergeCell ref="BB40:BE40"/>
-    <mergeCell ref="AL24:BE26"/>
-    <mergeCell ref="AZ57:BA57"/>
     <mergeCell ref="AT15:AW15"/>
     <mergeCell ref="BN1:BQ1"/>
+    <mergeCell ref="V32:Y32"/>
     <mergeCell ref="AT40:AW40"/>
     <mergeCell ref="N2:Q3"/>
     <mergeCell ref="J33:M33"/>
@@ -8792,95 +8082,84 @@
     <mergeCell ref="R30:U30"/>
     <mergeCell ref="J30:M30"/>
     <mergeCell ref="Z37:AC37"/>
-    <mergeCell ref="BL21:BM21"/>
     <mergeCell ref="R12:U12"/>
-    <mergeCell ref="X54:Y54"/>
     <mergeCell ref="BJ52:BM52"/>
-    <mergeCell ref="AP31:AS31"/>
     <mergeCell ref="BJ39:BM39"/>
     <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="BJ4:BM5"/>
     <mergeCell ref="AH6:AK6"/>
     <mergeCell ref="R54:U54"/>
     <mergeCell ref="BR42:BU42"/>
-    <mergeCell ref="BN23:BO23"/>
+    <mergeCell ref="Z13:AC13"/>
+    <mergeCell ref="CD23:CG23"/>
     <mergeCell ref="BR53:BU53"/>
     <mergeCell ref="A2:E3"/>
     <mergeCell ref="BV23:BY23"/>
     <mergeCell ref="BZ44:CC44"/>
     <mergeCell ref="R56:U56"/>
     <mergeCell ref="AD7:AG7"/>
-    <mergeCell ref="BZ31:CC31"/>
-    <mergeCell ref="BH41:BI41"/>
+    <mergeCell ref="V7:Y7"/>
     <mergeCell ref="AX15:BA15"/>
     <mergeCell ref="Z15:AC15"/>
     <mergeCell ref="AT30:AW30"/>
     <mergeCell ref="AT1:AW1"/>
     <mergeCell ref="AP35:AQ35"/>
+    <mergeCell ref="BF41:BI41"/>
     <mergeCell ref="AV42:AW42"/>
     <mergeCell ref="AD8:AG8"/>
-    <mergeCell ref="BB58:BC58"/>
     <mergeCell ref="F6:I6"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="CD1:CG1"/>
     <mergeCell ref="BV1:BY1"/>
     <mergeCell ref="AH53:AK53"/>
     <mergeCell ref="AT2:AW3"/>
-    <mergeCell ref="BN44:BO44"/>
-    <mergeCell ref="BP44:BQ44"/>
     <mergeCell ref="BD45:BE45"/>
     <mergeCell ref="AH55:AK55"/>
-    <mergeCell ref="BV11:BY11"/>
-    <mergeCell ref="CD44:CF44"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="P55:Q55"/>
     <mergeCell ref="AL52:AO52"/>
-    <mergeCell ref="J31:M31"/>
     <mergeCell ref="AL39:AO39"/>
+    <mergeCell ref="BN22:BQ22"/>
     <mergeCell ref="V53:Y53"/>
     <mergeCell ref="AX30:BA30"/>
     <mergeCell ref="BB21:BE21"/>
     <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="X32:Y32"/>
     <mergeCell ref="AX42:BA42"/>
     <mergeCell ref="BJ53:BM53"/>
-    <mergeCell ref="BD58:BE58"/>
     <mergeCell ref="AH37:AK37"/>
-    <mergeCell ref="AL16:AM16"/>
-    <mergeCell ref="AN16:AO16"/>
     <mergeCell ref="BV6:BY6"/>
     <mergeCell ref="BB16:BE16"/>
     <mergeCell ref="BZ4:CC5"/>
     <mergeCell ref="AX6:BA6"/>
     <mergeCell ref="AD33:AG33"/>
     <mergeCell ref="Z54:AC54"/>
+    <mergeCell ref="V8:Y8"/>
     <mergeCell ref="BV45:BY45"/>
-    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="BB18:BE18"/>
     <mergeCell ref="AD35:AG35"/>
     <mergeCell ref="BF57:BI57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="BF23:BI23"/>
     <mergeCell ref="Z34:AC34"/>
     <mergeCell ref="BB17:BE17"/>
-    <mergeCell ref="BF19:BG19"/>
     <mergeCell ref="BF39:BI39"/>
     <mergeCell ref="G33:I33"/>
     <mergeCell ref="BV19:BY19"/>
     <mergeCell ref="BR30:BU30"/>
+    <mergeCell ref="BN59:BQ59"/>
     <mergeCell ref="BJ43:BM43"/>
     <mergeCell ref="J52:M52"/>
+    <mergeCell ref="Z36:AC36"/>
     <mergeCell ref="Z30:AC30"/>
     <mergeCell ref="J4:M5"/>
-    <mergeCell ref="BV14:BY14"/>
-    <mergeCell ref="AX31:BA31"/>
-    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="CD45:CG45"/>
+    <mergeCell ref="AH32:AJ32"/>
     <mergeCell ref="BR4:BU5"/>
     <mergeCell ref="BV22:BY22"/>
-    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="BJ21:BM21"/>
     <mergeCell ref="BZ53:CC53"/>
-    <mergeCell ref="CD21:CF21"/>
     <mergeCell ref="AL13:AO13"/>
+    <mergeCell ref="Z56:AC56"/>
     <mergeCell ref="BJ23:BM23"/>
+    <mergeCell ref="AH15:AK15"/>
     <mergeCell ref="J32:M32"/>
     <mergeCell ref="J7:M7"/>
   </mergeCells>
